--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1230"/>
+  <dimension ref="A1:H1248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31080,26 +31080,26 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>7800000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1095" t="n">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="E1095" t="n">
-        <v>404</v>
+        <v>627</v>
       </c>
       <c r="F1095" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1095" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1095" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1096">
@@ -31108,26 +31108,26 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>31900000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1096" t="n">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="E1096" t="n">
-        <v>350</v>
+        <v>696</v>
       </c>
       <c r="F1096" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1096" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1096" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1097">
@@ -31136,17 +31136,17 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Asri Nuansa Bali Lokasi Dekat Sekolah Prancis dan MRT dan Resto dan Cafe Cipete Raya Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>44000000000</v>
+        <v>39900000000</v>
       </c>
       <c r="D1097" t="n">
-        <v>1050</v>
+        <v>796</v>
       </c>
       <c r="E1097" t="n">
-        <v>627</v>
+        <v>864</v>
       </c>
       <c r="F1097" t="n">
         <v>5</v>
@@ -31155,7 +31155,7 @@
         <v>5</v>
       </c>
       <c r="H1097" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1098">
@@ -31164,26 +31164,26 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>13900000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1098" t="n">
-        <v>325</v>
+        <v>452</v>
       </c>
       <c r="E1098" t="n">
-        <v>696</v>
+        <v>1165</v>
       </c>
       <c r="F1098" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1098" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1098" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1099">
@@ -31192,26 +31192,26 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Asri Nuansa Bali Lokasi Dekat Sekolah Prancis dan MRT dan Resto dan Cafe Cipete Raya Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran dan Dekat Gatot Subroto dan Sudirman dan Dekat Menteng Area Mentri dan Kedutaan dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>39900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1099" t="n">
-        <v>796</v>
+        <v>1100</v>
       </c>
       <c r="E1099" t="n">
-        <v>864</v>
+        <v>540</v>
       </c>
       <c r="F1099" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1099" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1099" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1100">
@@ -31220,26 +31220,26 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Rumah Moh Kahfi 1 - 5 Menit ke Cilandak</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>22000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1100" t="n">
-        <v>650</v>
+        <v>65</v>
       </c>
       <c r="E1100" t="n">
-        <v>854</v>
+        <v>106</v>
       </c>
       <c r="F1100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1100" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1101">
@@ -31248,26 +31248,26 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Stategis, 5 Menit Ke Tb Simatupang ,butuh Minim Renovasi,</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>53500000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1101" t="n">
-        <v>452</v>
+        <v>250</v>
       </c>
       <c r="E1101" t="n">
-        <v>1165</v>
+        <v>144</v>
       </c>
       <c r="F1101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1101" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1102">
@@ -31276,26 +31276,26 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus 3 Lantai dan Kolam Renang Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>34900000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1102" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1102" t="n">
-        <v>538</v>
+        <v>143</v>
       </c>
       <c r="F1102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1102" t="n">
         <v>4</v>
       </c>
       <c r="H1102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1103">
@@ -31304,26 +31304,26 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran dan Dekat Gatot Subroto dan Sudirman dan Dekat Menteng Area Mentri dan Kedutaan dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Rumah Murah Harga di Bawah Pasar di Bintaro Sektor 1 Jakartasel</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>48000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1103" t="n">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="E1103" t="n">
-        <v>540</v>
+        <v>682</v>
       </c>
       <c r="F1103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1103" t="n">
         <v>4</v>
       </c>
       <c r="H1103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1104">
@@ -31332,17 +31332,17 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Luxurious Brand New Kebayoran Baru Dengan Balcony View Scbd</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>55000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1104" t="n">
-        <v>500</v>
+        <v>810</v>
       </c>
       <c r="E1104" t="n">
-        <v>500</v>
+        <v>338</v>
       </c>
       <c r="F1104" t="n">
         <v>4</v>
@@ -31351,7 +31351,7 @@
         <v>4</v>
       </c>
       <c r="H1104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1105">
@@ -31360,26 +31360,26 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Dijual Rumah Moh Kahfi 1 - 5 Menit ke Cilandak</t>
+          <t>For Sale Brand New American Classic Pondok Indah Parkir 15 Mobil</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>1500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1105" t="n">
-        <v>65</v>
+        <v>2000</v>
       </c>
       <c r="E1105" t="n">
-        <v>106</v>
+        <v>670</v>
       </c>
       <c r="F1105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1106">
@@ -31388,26 +31388,26 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Stategis, 5 Menit Ke Tb Simatupang ,butuh Minim Renovasi,</t>
+          <t>2025 Modern House Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>3600000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1106" t="n">
-        <v>250</v>
+        <v>871</v>
       </c>
       <c r="E1106" t="n">
-        <v>144</v>
+        <v>317</v>
       </c>
       <c r="F1106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1107">
@@ -31416,23 +31416,23 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Rumah Bagus 3 Lantai dan Kolam Renang Jagakarsa Jakarta Selatan</t>
+          <t>For Sale Rumah Hitung Tanah Tebet</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>3700000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1107" t="n">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="E1107" t="n">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="F1107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1107" t="n">
         <v>1</v>
@@ -31444,26 +31444,26 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Rumah Murah Harga di Bawah Pasar di Bintaro Sektor 1 Jakartasel</t>
+          <t>- Murah !! Dijual Cepat !! Rumah Siap Huni 10x25 dibawah NJOP di Niaga Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>7900000000</v>
+        <v>5700000000</v>
       </c>
       <c r="D1108" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="E1108" t="n">
-        <v>682</v>
+        <v>250</v>
       </c>
       <c r="F1108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1109">
@@ -31472,23 +31472,23 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Luxurious Brand New Kebayoran Baru Dengan Balcony View Scbd</t>
+          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>48000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1109" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="E1109" t="n">
-        <v>338</v>
+        <v>768</v>
       </c>
       <c r="F1109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1109" t="n">
         <v>2</v>
@@ -31500,26 +31500,26 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>For Sale Brand New American Classic Pondok Indah Parkir 15 Mobil</t>
+          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>62000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1110" t="n">
-        <v>2000</v>
+        <v>380</v>
       </c>
       <c r="E1110" t="n">
-        <v>670</v>
+        <v>300</v>
       </c>
       <c r="F1110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1111">
@@ -31528,26 +31528,26 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>2025 Modern House Kebayoran Baru For Sale</t>
+          <t>Khusus Investor | Cocok untuk Kost | Belakang Eka Hospital Tebet</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>46000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1111" t="n">
-        <v>871</v>
+        <v>150</v>
       </c>
       <c r="E1111" t="n">
-        <v>317</v>
+        <v>238</v>
       </c>
       <c r="F1111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1112">
@@ -31556,26 +31556,26 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>For Sale Rumah Hitung Tanah Tebet</t>
+          <t>Rumah Ex Cafe di Tebet | Lokasi Bisnis Ramai | Dekat Mall Kokas</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>1500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1112" t="n">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="E1112" t="n">
-        <v>81</v>
+        <v>675</v>
       </c>
       <c r="F1112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1112" t="n">
         <v>1</v>
       </c>
       <c r="H1112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1113">
@@ -31584,26 +31584,26 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>- Murah !! Dijual Cepat !! Rumah Siap Huni 10x25 dibawah NJOP di Niaga Hijau Pondok Indah</t>
+          <t>Rumah Mewah Gaya Perancis Full Furnished Dalam Komplek Elit Tebet</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>5700000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1113" t="n">
-        <v>180</v>
+        <v>725</v>
       </c>
       <c r="E1113" t="n">
-        <v>250</v>
+        <v>448</v>
       </c>
       <c r="F1113" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1114">
@@ -31612,26 +31612,26 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
+          <t>Turun Harga!! Dijual Rumah Lux Tropical di Cilandak, Siap Huni, Harga bisa Nego, SHM</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>32000000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1114" t="n">
-        <v>825</v>
+        <v>650</v>
       </c>
       <c r="E1114" t="n">
-        <v>768</v>
+        <v>982</v>
       </c>
       <c r="F1114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1114" t="n">
         <v>5</v>
       </c>
       <c r="H1114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1115">
@@ -31640,26 +31640,26 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
+          <t>Rumah Lokasi Langka Wijaya 2 Super Strategis Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>14000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1115" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="E1115" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="F1115" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1116">
@@ -31668,26 +31668,26 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Khusus Investor | Cocok untuk Kost | Belakang Eka Hospital Tebet</t>
+          <t>Rumah Classic Modern Siap Huni Fully Furnish Jual Cepat Jarang Ada Area Bebas Banjir</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>6500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1116" t="n">
-        <v>150</v>
+        <v>760</v>
       </c>
       <c r="E1116" t="n">
-        <v>238</v>
+        <v>517</v>
       </c>
       <c r="F1116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1117">
@@ -31696,26 +31696,26 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Rumah Ex Cafe di Tebet | Lokasi Bisnis Ramai | Dekat Mall Kokas</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>15500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1117" t="n">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="E1117" t="n">
-        <v>675</v>
+        <v>123</v>
       </c>
       <c r="F1117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1118">
@@ -31724,26 +31724,26 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gaya Perancis Full Furnished Dalam Komplek Elit Tebet</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>30000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1118" t="n">
-        <v>725</v>
+        <v>171</v>
       </c>
       <c r="E1118" t="n">
-        <v>448</v>
+        <v>181</v>
       </c>
       <c r="F1118" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1118" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1119">
@@ -31752,26 +31752,26 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Turun Harga!! Dijual Rumah Lux Tropical di Cilandak, Siap Huni, Harga bisa Nego, SHM</t>
+          <t>Rumah 2 Lantai 15 Menit ke One Belpark Mall Siap Huni Bebas Banjir J-25000</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>20500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1119" t="n">
-        <v>650</v>
+        <v>135</v>
       </c>
       <c r="E1119" t="n">
-        <v>982</v>
+        <v>82</v>
       </c>
       <c r="F1119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1120">
@@ -31780,26 +31780,26 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Langka Wijaya 2 Super Strategis Lihat Jamin Beli</t>
+          <t>Rumah Minimalis Terawat 17 Menit ke One Belpark Mall Dibantu KPR J34039</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>25000000000</v>
+        <v>1220000000</v>
       </c>
       <c r="D1120" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1120" t="n">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="F1120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1121">
@@ -31808,26 +31808,26 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Rumah Classic Modern Siap Huni Fully Furnish Jual Cepat Jarang Ada Area Bebas Banjir</t>
+          <t>Rumah LB 155 SHM Siap KPR 18 Menit ke AEON Mall Tanjung Barat J33899</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>38000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1121" t="n">
-        <v>760</v>
+        <v>155</v>
       </c>
       <c r="E1121" t="n">
-        <v>517</v>
+        <v>272</v>
       </c>
       <c r="F1121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1121" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1122">
@@ -31836,20 +31836,20 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Minimalis 8 Menit ke Gerbang Tol Brigif SHM Hadap Timur J26013</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>2550000000</v>
+        <v>2230000000</v>
       </c>
       <c r="D1122" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E1122" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F1122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1122" t="n">
         <v>2</v>
@@ -31864,23 +31864,23 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>Rumah 1 Lantai Tenang Di Pondok Indah - Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>2550000000</v>
+        <v>28900000000</v>
       </c>
       <c r="D1123" t="n">
-        <v>171</v>
+        <v>445</v>
       </c>
       <c r="E1123" t="n">
-        <v>181</v>
+        <v>756</v>
       </c>
       <c r="F1123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1123" t="n">
         <v>1</v>
@@ -31892,23 +31892,23 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15 Menit ke One Belpark Mall Siap Huni Bebas Banjir J-25000</t>
+          <t>Rumah Luas LT 180 Dekat Cilandak 10 Menit ke RS Bebas Banjir J30974</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>1900000000</v>
+        <v>1770000000</v>
       </c>
       <c r="D1124" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E1124" t="n">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="F1124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1124" t="n">
         <v>1</v>
@@ -31920,23 +31920,23 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Terawat 17 Menit ke One Belpark Mall Dibantu KPR J34039</t>
+          <t>Rumah 2 Lt SHM Siap Huni 15 Menit ke Stasiun MRT Lebak Bulus Grab J-35553</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>1220000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1125" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E1125" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F1125" t="n">
         <v>3</v>
       </c>
       <c r="G1125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1125" t="n">
         <v>1</v>
@@ -31948,20 +31948,20 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Rumah LB 155 SHM Siap KPR 18 Menit ke AEON Mall Tanjung Barat J33899</t>
+          <t>Dijual Rumah TERMURAAAH di Bintaro Utara,Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>5500000000</v>
+        <v>6600000000</v>
       </c>
       <c r="D1126" t="n">
-        <v>155</v>
+        <v>350</v>
       </c>
       <c r="E1126" t="n">
-        <v>272</v>
+        <v>378</v>
       </c>
       <c r="F1126" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1126" t="n">
         <v>3</v>
@@ -31976,23 +31976,23 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 8 Menit ke Gerbang Tol Brigif SHM Hadap Timur J26013</t>
+          <t>Cilandak Belakang Citos 2 Lt Tenang Private Asri Bebas Banjir</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>2230000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E1127" t="n">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="F1127" t="n">
         <v>3</v>
       </c>
       <c r="G1127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1127" t="n">
         <v>1</v>
@@ -32004,26 +32004,26 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Tenang Di Pondok Indah - Jakarta Selatan</t>
+          <t>Termurah Brawijaya Townhouse Kebayoran Baru, Dijual Rumah Hunian Property di Dalam Townhouse Perumahan Komplek Akses Jalan Lebar Akses Mudah di Lingkungan Elit dan Lokasi Strategis Sentral Dekat dengan MRT, Dharmawangsa, Senopati, di Jalan Brawijaya, Keba</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>28900000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E1128" t="n">
-        <v>756</v>
+        <v>196</v>
       </c>
       <c r="F1128" t="n">
         <v>4</v>
       </c>
       <c r="G1128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,26 +32032,26 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Rumah Luas LT 180 Dekat Cilandak 10 Menit ke RS Bebas Banjir J30974</t>
+          <t>Best Deal Luas Tanah Besar Siap Huni Kebayoran Baru! Rumah Modern Tropical Mewah Cantik Property Hunian Dijual Semi Furnished di Lokasi Strategis Akses dan Lingkungan Nyaman dan Asri di Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>1770000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E1129" t="n">
-        <v>180</v>
+        <v>307</v>
       </c>
       <c r="F1129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1130">
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Rumah 2 Lt SHM Siap Huni 15 Menit ke Stasiun MRT Lebak Bulus Grab J-35553</t>
+          <t>Best Deal Kebayoran Baru! Rumah Siap Huni Cantik Kebayoran Baru Jalan Lebar Dekat Hanya 200 Meter ke MRT Lingkungan Nyaman dan Aman di Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>2550000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>119</v>
+        <v>400</v>
       </c>
       <c r="E1130" t="n">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="F1130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,23 +32088,23 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Dijual Rumah TERMURAAAH di Bintaro Utara,Jakarta Selatan</t>
+          <t>Best Price Harga Bagus Pondok Indah untuk Bangun Rumah Impian, Rumah Hitung Tanah Dijual Luas Besar dengan Harga Murah Jalan Depan Lebar Lingkungan Nyaman Aman dan Asri di Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>6600000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="E1131" t="n">
-        <v>378</v>
+        <v>198</v>
       </c>
       <c r="F1131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1131" t="n">
         <v>1</v>
@@ -32116,17 +32116,17 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Cilandak Belakang Citos 2 Lt Tenang Private Asri Bebas Banjir</t>
+          <t>Best Price Pondok Indah Rumah Siap Huni! Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>6000000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1132" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F1132" t="n">
         <v>3</v>
@@ -32144,17 +32144,17 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Termurah Brawijaya Townhouse Kebayoran Baru, Dijual Rumah Hunian Property di Dalam Townhouse Perumahan Komplek Akses Jalan Lebar Akses Mudah di Lingkungan Elit dan Lokasi Strategis Sentral Dekat dengan MRT, Dharmawangsa, Senopati, di Jalan Brawijaya, Keba</t>
+          <t>Best Price Siap Huni Pondok Indah Rumah Cantik Terawat! Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>15200000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="E1133" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F1133" t="n">
         <v>4</v>
@@ -32163,7 +32163,7 @@
         <v>5</v>
       </c>
       <c r="H1133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,26 +32172,26 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Best Deal Luas Tanah Besar Siap Huni Kebayoran Baru! Rumah Modern Tropical Mewah Cantik Property Hunian Dijual Semi Furnished di Lokasi Strategis Akses dan Lingkungan Nyaman dan Asri di Kebayoran Baru, Jakarta Selatan</t>
+          <t>Rumah Siap Huni 2M-An di Tebet Dekat Kokas, Saharjo dan Tebet Raya!</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>15000000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>360</v>
+        <v>142</v>
       </c>
       <c r="E1134" t="n">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="F1134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1134" t="n">
         <v>4</v>
       </c>
       <c r="H1134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1135">
@@ -32200,17 +32200,17 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Best Deal Kebayoran Baru! Rumah Siap Huni Cantik Kebayoran Baru Jalan Lebar Dekat Hanya 200 Meter ke MRT Lingkungan Nyaman dan Aman di Kebayoran Baru, Jakarta Selatan</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>10100000000</v>
+        <v>41900000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>400</v>
+        <v>720</v>
       </c>
       <c r="E1135" t="n">
-        <v>200</v>
+        <v>634</v>
       </c>
       <c r="F1135" t="n">
         <v>4</v>
@@ -32219,7 +32219,7 @@
         <v>5</v>
       </c>
       <c r="H1135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,23 +32228,23 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Best Price Harga Bagus Pondok Indah untuk Bangun Rumah Impian, Rumah Hitung Tanah Dijual Luas Besar dengan Harga Murah Jalan Depan Lebar Lingkungan Nyaman Aman dan Asri di Pondok Indah, Jakarta Selatan</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>6500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="E1136" t="n">
-        <v>198</v>
+        <v>340</v>
       </c>
       <c r="F1136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1136" t="n">
         <v>1</v>
@@ -32256,26 +32256,26 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Rumah Siap Huni! Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah Strategis Di Tengah Kota</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>6760000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1137" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="F1137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1137" t="n">
         <v>4</v>
       </c>
       <c r="H1137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1138">
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Best Price Siap Huni Pondok Indah Rumah Cantik Terawat! Pondok Indah, Jakarta Selatan</t>
+          <t>Serenia Hills Cluster Signature Best Deal Jarang Ada</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>9500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>219</v>
+        <v>300</v>
       </c>
       <c r="E1138" t="n">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="F1138" t="n">
         <v>4</v>
       </c>
       <c r="G1138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni 2M-An di Tebet Dekat Kokas, Saharjo dan Tebet Raya!</t>
+          <t>House For Sale - [Lebak Bulus]Rumah Dalam Townhouse, Bangunan 4 Lantai Plus Rooftop.</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>2300000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>142</v>
+        <v>1005</v>
       </c>
       <c r="E1139" t="n">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="F1139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,26 +32340,26 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual Rumah Secondary dengan Modern Tropical Design Dalam Townhouse Berisi 13 Unit Rumah yang Aman dan Nyaman di Area R.c Veteran - Rempoa, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>41900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1140" t="n">
-        <v>720</v>
+        <v>257</v>
       </c>
       <c r="E1140" t="n">
-        <v>634</v>
+        <v>306</v>
       </c>
       <c r="F1140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1141">
@@ -32368,26 +32368,26 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Rumah Mewah Terawat dan Siap Huni, Tanah dan Bangunan Luas di Cilandak</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>4900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>325</v>
+        <v>650</v>
       </c>
       <c r="E1141" t="n">
-        <v>340</v>
+        <v>982</v>
       </c>
       <c r="F1141" t="n">
         <v>5</v>
       </c>
       <c r="G1141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1142">
@@ -32396,26 +32396,26 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Rumah Strategis Di Tengah Kota</t>
+          <t>Rumah di Bawah Harga Pasar Buat Kost dan Investasi Dekat Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>7800000000</v>
+        <v>3750000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E1142" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="F1142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,26 +32424,26 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Serenia Hills Cluster Signature Best Deal Jarang Ada</t>
+          <t>Rumah Tropical Resort With S Pool In Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>8500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1143" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E1143" t="n">
-        <v>307</v>
+        <v>1925</v>
       </c>
       <c r="F1143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1143" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1144">
@@ -32452,26 +32452,26 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>House For Sale - [Lebak Bulus]Rumah Dalam Townhouse, Bangunan 4 Lantai Plus Rooftop.</t>
+          <t>Rumah Kantor Buat Usaha di Bawah Harga NJOP Tersewa di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>15000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>1005</v>
+        <v>700</v>
       </c>
       <c r="E1144" t="n">
-        <v>308</v>
+        <v>1343</v>
       </c>
       <c r="F1144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1144" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1145">
@@ -32480,26 +32480,26 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Dijual Rumah Secondary dengan Modern Tropical Design Dalam Townhouse Berisi 13 Unit Rumah yang Aman dan Nyaman di Area R.c Veteran - Rempoa, Jakarta Selatan</t>
+          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>9500000000</v>
+        <v>31500000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>257</v>
+        <v>400</v>
       </c>
       <c r="E1145" t="n">
-        <v>306</v>
+        <v>2620</v>
       </c>
       <c r="F1145" t="n">
         <v>3</v>
       </c>
       <c r="G1145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1145" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,26 +32508,26 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat dan Siap Huni, Tanah dan Bangunan Luas di Cilandak</t>
+          <t>Rumah 2 Lantai Harga NJOP Lokasi Prestisius Dekat ke Pusat Bisnis Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>25000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>650</v>
+        <v>385</v>
       </c>
       <c r="E1146" t="n">
-        <v>982</v>
+        <v>504</v>
       </c>
       <c r="F1146" t="n">
         <v>5</v>
       </c>
       <c r="G1146" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1147">
@@ -32536,26 +32536,26 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Rumah di Bawah Harga Pasar Buat Kost dan Investasi Dekat Kebayoran Baru Jakarta Selatan</t>
+          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>3750000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1147" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E1147" t="n">
-        <v>300</v>
+        <v>161</v>
       </c>
       <c r="F1147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1148">
@@ -32564,26 +32564,26 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Rumah Tropical Resort With S Pool In Cipete Jakarta Selatan</t>
+          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>42000000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="E1148" t="n">
-        <v>1925</v>
+        <v>162</v>
       </c>
       <c r="F1148" t="n">
         <v>5</v>
       </c>
       <c r="G1148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1149">
@@ -32592,26 +32592,26 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Rumah Kantor Buat Usaha di Bawah Harga NJOP Tersewa di Kemang Jakarta Selatan</t>
+          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>25000000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="E1149" t="n">
-        <v>1343</v>
+        <v>162</v>
       </c>
       <c r="F1149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1149" t="n">
         <v>3</v>
       </c>
       <c r="H1149" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,26 +32620,26 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
+          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>31500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1150" t="n">
-        <v>2620</v>
+        <v>446</v>
       </c>
       <c r="F1150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1151">
@@ -32648,26 +32648,26 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Harga NJOP Lokasi Prestisius Dekat ke Pusat Bisnis Mega Kuningan, Jakarta Selatan</t>
+          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>32000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>385</v>
+        <v>300</v>
       </c>
       <c r="E1151" t="n">
-        <v>504</v>
+        <v>361</v>
       </c>
       <c r="F1151" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1152">
@@ -32676,23 +32676,23 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>3950000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="E1152" t="n">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="F1152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1152" t="n">
         <v>2</v>
@@ -32704,26 +32704,26 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
+          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>3950000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>180</v>
+        <v>650</v>
       </c>
       <c r="E1153" t="n">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="F1153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1154">
@@ -32732,26 +32732,26 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
+          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>3950000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="E1154" t="n">
-        <v>162</v>
+        <v>448</v>
       </c>
       <c r="F1154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1155">
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>11500000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>500</v>
+        <v>1374</v>
       </c>
       <c r="E1155" t="n">
-        <v>446</v>
+        <v>1493</v>
       </c>
       <c r="F1155" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1155" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H1155" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,26 +32788,26 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
+          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>9500000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>300</v>
+        <v>467</v>
       </c>
       <c r="E1156" t="n">
-        <v>361</v>
+        <v>899</v>
       </c>
       <c r="F1156" t="n">
         <v>4</v>
       </c>
       <c r="G1156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1156" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1157">
@@ -32816,26 +32816,26 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah Mewah Baru di Jagakarsa</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>6900000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>375</v>
+        <v>520</v>
       </c>
       <c r="E1157" t="n">
-        <v>76</v>
+        <v>720</v>
       </c>
       <c r="F1157" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1157" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1158">
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>35000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>650</v>
+        <v>375</v>
       </c>
       <c r="E1158" t="n">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="F1158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1158" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>30000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>274</v>
+        <v>1200</v>
       </c>
       <c r="E1159" t="n">
-        <v>448</v>
+        <v>620</v>
       </c>
       <c r="F1159" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G1159" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H1159" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1160">
@@ -32900,26 +32900,26 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>26000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>1374</v>
+        <v>700</v>
       </c>
       <c r="E1160" t="n">
-        <v>1493</v>
+        <v>960</v>
       </c>
       <c r="F1160" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1160" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H1160" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1161">
@@ -32928,26 +32928,26 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
+          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>18000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>467</v>
+        <v>150</v>
       </c>
       <c r="E1161" t="n">
-        <v>899</v>
+        <v>300</v>
       </c>
       <c r="F1161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1161" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1162">
@@ -32956,26 +32956,26 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Rumah Mewah Baru di Jagakarsa</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>12500000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>520</v>
+        <v>350</v>
       </c>
       <c r="E1162" t="n">
-        <v>720</v>
+        <v>534</v>
       </c>
       <c r="F1162" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1162" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,23 +32984,23 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>6900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1163" t="n">
-        <v>76</v>
+        <v>550</v>
       </c>
       <c r="F1163" t="n">
         <v>4</v>
       </c>
       <c r="G1163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1163" t="n">
         <v>2</v>
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>42000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>1200</v>
+        <v>128</v>
       </c>
       <c r="E1164" t="n">
-        <v>620</v>
+        <v>252</v>
       </c>
       <c r="F1164" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G1164" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H1164" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>21000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="E1165" t="n">
-        <v>960</v>
+        <v>351</v>
       </c>
       <c r="F1165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1165" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,23 +33068,23 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>13000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>150</v>
+        <v>366</v>
       </c>
       <c r="E1166" t="n">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="F1166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1166" t="n">
         <v>1</v>
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Brand New Modern American Classic House Pondok Indah</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>40500000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>350</v>
+        <v>750</v>
       </c>
       <c r="E1167" t="n">
-        <v>534</v>
+        <v>406</v>
       </c>
       <c r="F1167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>12000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E1168" t="n">
-        <v>550</v>
+        <v>248</v>
       </c>
       <c r="F1168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,26 +33152,26 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
+          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>6000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="E1169" t="n">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="F1169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1169" t="n">
         <v>3</v>
       </c>
       <c r="H1169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1170">
@@ -33180,26 +33180,26 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
+          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>34500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>280</v>
+        <v>72</v>
       </c>
       <c r="E1170" t="n">
-        <v>351</v>
+        <v>45</v>
       </c>
       <c r="F1170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1171">
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>25000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>366</v>
+        <v>430</v>
       </c>
       <c r="E1171" t="n">
-        <v>366</v>
+        <v>250</v>
       </c>
       <c r="F1171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,26 +33236,26 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Brand New Modern American Classic House Pondok Indah</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>28500000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="E1172" t="n">
-        <v>406</v>
+        <v>318</v>
       </c>
       <c r="F1172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,23 +33264,23 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>22500000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1173" t="n">
-        <v>248</v>
+        <v>384</v>
       </c>
       <c r="F1173" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1173" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1173" t="n">
         <v>3</v>
@@ -33292,23 +33292,23 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>7000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>183</v>
+        <v>375</v>
       </c>
       <c r="E1174" t="n">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="F1174" t="n">
         <v>4</v>
       </c>
       <c r="G1174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1174" t="n">
         <v>2</v>
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
+          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>1300000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>72</v>
+        <v>700</v>
       </c>
       <c r="E1175" t="n">
-        <v>45</v>
+        <v>353</v>
       </c>
       <c r="F1175" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>8000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>430</v>
+        <v>800</v>
       </c>
       <c r="E1176" t="n">
-        <v>250</v>
+        <v>1050</v>
       </c>
       <c r="F1176" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1176" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>5500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="E1177" t="n">
-        <v>318</v>
+        <v>787</v>
       </c>
       <c r="F1177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1177" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>14000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>850</v>
+        <v>375</v>
       </c>
       <c r="E1178" t="n">
-        <v>384</v>
+        <v>76</v>
       </c>
       <c r="F1178" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1178" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,23 +33432,23 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>6900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>375</v>
+        <v>140</v>
       </c>
       <c r="E1179" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F1179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1179" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1179" t="n">
         <v>2</v>
@@ -33460,26 +33460,26 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>20000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1180" t="n">
-        <v>353</v>
+        <v>127</v>
       </c>
       <c r="F1180" t="n">
         <v>5</v>
       </c>
       <c r="G1180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1181">
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>23000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1181" t="n">
-        <v>1050</v>
+        <v>1070</v>
       </c>
       <c r="F1181" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1181" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1181" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>24000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1182" t="n">
-        <v>787</v>
+        <v>76</v>
       </c>
       <c r="F1182" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1182" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1182" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>6900000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1183" t="n">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="F1183" t="n">
         <v>4</v>
       </c>
       <c r="G1183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,23 +33572,23 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>2400000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="E1184" t="n">
-        <v>105</v>
+        <v>510</v>
       </c>
       <c r="F1184" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1184" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1184" t="n">
         <v>2</v>
@@ -33600,23 +33600,23 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>1750000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="E1185" t="n">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="F1185" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1185" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1185" t="n">
         <v>1</v>
@@ -33628,26 +33628,26 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>17000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>350</v>
+        <v>232</v>
       </c>
       <c r="E1186" t="n">
-        <v>1070</v>
+        <v>284</v>
       </c>
       <c r="F1186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1186" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1187">
@@ -33656,23 +33656,23 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>7090000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>375</v>
+        <v>260</v>
       </c>
       <c r="E1187" t="n">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="F1187" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1187" t="n">
         <v>1</v>
@@ -33684,23 +33684,23 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>7500000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="E1188" t="n">
-        <v>246</v>
+        <v>196</v>
       </c>
       <c r="F1188" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G1188" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H1188" t="n">
         <v>1</v>
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>7300000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>600</v>
+        <v>88</v>
       </c>
       <c r="E1189" t="n">
-        <v>510</v>
+        <v>55</v>
       </c>
       <c r="F1189" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1189" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>998000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>64</v>
+        <v>1000</v>
       </c>
       <c r="E1190" t="n">
-        <v>32</v>
+        <v>675</v>
       </c>
       <c r="F1190" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1190" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,17 +33768,17 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>22000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>232</v>
+        <v>375</v>
       </c>
       <c r="E1191" t="n">
-        <v>284</v>
+        <v>534</v>
       </c>
       <c r="F1191" t="n">
         <v>3</v>
@@ -33787,7 +33787,7 @@
         <v>2</v>
       </c>
       <c r="H1191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,23 +33796,23 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>6250000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>260</v>
+        <v>928</v>
       </c>
       <c r="E1192" t="n">
-        <v>172</v>
+        <v>378</v>
       </c>
       <c r="F1192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1192" t="n">
         <v>1</v>
@@ -33824,23 +33824,23 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>7200000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>380</v>
+        <v>112</v>
       </c>
       <c r="E1193" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="F1193" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G1193" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H1193" t="n">
         <v>1</v>
@@ -33852,23 +33852,23 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>2600000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>88</v>
+        <v>1350</v>
       </c>
       <c r="E1194" t="n">
-        <v>55</v>
+        <v>863</v>
       </c>
       <c r="F1194" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1194" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1194" t="n">
         <v>1</v>
@@ -33880,23 +33880,23 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>65000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>1000</v>
+        <v>355</v>
       </c>
       <c r="E1195" t="n">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="F1195" t="n">
         <v>4</v>
       </c>
       <c r="G1195" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1195" t="n">
         <v>2</v>
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>23000000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>375</v>
+        <v>280</v>
       </c>
       <c r="E1196" t="n">
-        <v>534</v>
+        <v>120</v>
       </c>
       <c r="F1196" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1196" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,23 +33936,23 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>15500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>928</v>
+        <v>130</v>
       </c>
       <c r="E1197" t="n">
-        <v>378</v>
+        <v>117</v>
       </c>
       <c r="F1197" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1197" t="n">
         <v>1</v>
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>2830000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>112</v>
+        <v>440</v>
       </c>
       <c r="E1198" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="F1198" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>38000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="E1199" t="n">
-        <v>863</v>
+        <v>1050</v>
       </c>
       <c r="F1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1199" t="n">
         <v>6</v>
-      </c>
-      <c r="G1199" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1199" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>10000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>355</v>
+        <v>500</v>
       </c>
       <c r="E1200" t="n">
-        <v>648</v>
+        <v>351</v>
       </c>
       <c r="F1200" t="n">
         <v>4</v>
       </c>
       <c r="G1200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,26 +34048,26 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>8800000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="E1201" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="F1201" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1201" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>2600000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="E1202" t="n">
-        <v>117</v>
+        <v>307</v>
       </c>
       <c r="F1202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1202" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,23 +34104,23 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>9000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>440</v>
+        <v>300</v>
       </c>
       <c r="E1203" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F1203" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1203" t="n">
         <v>2</v>
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>68000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E1204" t="n">
-        <v>1050</v>
+        <v>304</v>
       </c>
       <c r="F1204" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1204" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1204" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>34500000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1205" t="n">
-        <v>351</v>
+        <v>240</v>
       </c>
       <c r="F1205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1205" t="n">
         <v>3</v>
       </c>
       <c r="H1205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,26 +34188,26 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>22000000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E1206" t="n">
-        <v>290</v>
+        <v>73</v>
       </c>
       <c r="F1206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1206" t="n">
         <v>3</v>
       </c>
       <c r="H1206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>15000000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>360</v>
+        <v>130</v>
       </c>
       <c r="E1207" t="n">
-        <v>307</v>
+        <v>88</v>
       </c>
       <c r="F1207" t="n">
         <v>4</v>
       </c>
       <c r="G1207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,26 +34244,26 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>4800000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>300</v>
+        <v>475</v>
       </c>
       <c r="E1208" t="n">
-        <v>150</v>
+        <v>475</v>
       </c>
       <c r="F1208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>13500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>600</v>
+        <v>3475</v>
       </c>
       <c r="E1209" t="n">
-        <v>304</v>
+        <v>3475</v>
       </c>
       <c r="F1209" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1209" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>14500000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>300</v>
+        <v>4535</v>
       </c>
       <c r="E1210" t="n">
-        <v>240</v>
+        <v>4535</v>
       </c>
       <c r="F1210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1210" t="n">
         <v>3</v>
       </c>
       <c r="H1210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,17 +34328,17 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>1850000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>190</v>
+        <v>528</v>
       </c>
       <c r="E1211" t="n">
-        <v>73</v>
+        <v>528</v>
       </c>
       <c r="F1211" t="n">
         <v>4</v>
@@ -34347,7 +34347,7 @@
         <v>3</v>
       </c>
       <c r="H1211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>3300000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>130</v>
+        <v>819</v>
       </c>
       <c r="E1212" t="n">
-        <v>88</v>
+        <v>819</v>
       </c>
       <c r="F1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>3350000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="E1213" t="n">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="F1213" t="n">
         <v>4</v>
       </c>
       <c r="G1213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>45000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>3475</v>
+        <v>600</v>
       </c>
       <c r="E1214" t="n">
-        <v>3475</v>
+        <v>400</v>
       </c>
       <c r="F1214" t="n">
         <v>5</v>
       </c>
       <c r="G1214" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>42500000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>4535</v>
+        <v>450</v>
       </c>
       <c r="E1215" t="n">
-        <v>4535</v>
+        <v>196</v>
       </c>
       <c r="F1215" t="n">
         <v>4</v>
       </c>
       <c r="G1215" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,23 +34468,23 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>7900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>528</v>
+        <v>360</v>
       </c>
       <c r="E1216" t="n">
-        <v>528</v>
+        <v>307</v>
       </c>
       <c r="F1216" t="n">
         <v>4</v>
       </c>
       <c r="G1216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1216" t="n">
         <v>2</v>
@@ -34496,23 +34496,23 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>13100000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>819</v>
+        <v>400</v>
       </c>
       <c r="E1217" t="n">
-        <v>819</v>
+        <v>200</v>
       </c>
       <c r="F1217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1217" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1217" t="n">
         <v>2</v>
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>7000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>600</v>
+        <v>436</v>
       </c>
       <c r="E1218" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
       </c>
       <c r="G1218" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>28000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>600</v>
+        <v>340</v>
       </c>
       <c r="E1219" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="F1219" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>15200000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>450</v>
+        <v>262</v>
       </c>
       <c r="E1220" t="n">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="F1220" t="n">
         <v>4</v>
       </c>
       <c r="G1220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,23 +34608,23 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>15000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>360</v>
+        <v>700</v>
       </c>
       <c r="E1221" t="n">
-        <v>307</v>
+        <v>1150</v>
       </c>
       <c r="F1221" t="n">
         <v>4</v>
       </c>
       <c r="G1221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1221" t="n">
         <v>2</v>
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>10100000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="E1222" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F1222" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1222" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,23 +34664,23 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>9500000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E1223" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F1223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1223" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1223" t="n">
         <v>2</v>
@@ -34692,17 +34692,17 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>15500000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="E1224" t="n">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="F1224" t="n">
         <v>3</v>
@@ -34711,7 +34711,7 @@
         <v>4</v>
       </c>
       <c r="H1224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>8500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E1225" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F1225" t="n">
         <v>4</v>
       </c>
       <c r="G1225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>55000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="E1226" t="n">
-        <v>1150</v>
+        <v>60</v>
       </c>
       <c r="F1226" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>6500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>180</v>
+        <v>850</v>
       </c>
       <c r="E1227" t="n">
-        <v>198</v>
+        <v>1925</v>
       </c>
       <c r="F1227" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1227" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1227" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>12900000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="E1228" t="n">
-        <v>209</v>
+        <v>692</v>
       </c>
       <c r="F1228" t="n">
         <v>5</v>
       </c>
       <c r="G1228" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>6760000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1229" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="F1229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1229" t="n">
         <v>4</v>
       </c>
       <c r="H1229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,530 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>9500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>219</v>
+        <v>1600</v>
       </c>
       <c r="E1230" t="n">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="F1230" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1230" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1230" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="n">
+        <v>1230</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>24900000000</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>331</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>34900000000</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>538</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>71900000000</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>882</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>1845</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1238" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>10900000000</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>276</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1239" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>1239</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>1240</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>21000000000</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>630</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1241" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>1241</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>140</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1242" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>1242</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>49000000000</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>540</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1243" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1243" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>1243</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1244" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>22000000000</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>854</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1245" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>404</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1246" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>1246</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>31900000000</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>350</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1247" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1248" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1248"/>
+  <dimension ref="A1:H1258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31080,26 +31080,26 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>44000000000</v>
+        <v>13900000000</v>
       </c>
       <c r="D1095" t="n">
-        <v>1050</v>
+        <v>325</v>
       </c>
       <c r="E1095" t="n">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="F1095" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1095" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1095" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1096">
@@ -31108,26 +31108,26 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Asri Nuansa Bali Lokasi Dekat Sekolah Prancis dan MRT dan Resto dan Cafe Cipete Raya Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>13900000000</v>
+        <v>39900000000</v>
       </c>
       <c r="D1096" t="n">
-        <v>325</v>
+        <v>796</v>
       </c>
       <c r="E1096" t="n">
-        <v>696</v>
+        <v>864</v>
       </c>
       <c r="F1096" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1096" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1096" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1097">
@@ -31136,26 +31136,26 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Asri Nuansa Bali Lokasi Dekat Sekolah Prancis dan MRT dan Resto dan Cafe Cipete Raya Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran dan Dekat Gatot Subroto dan Sudirman dan Dekat Menteng Area Mentri dan Kedutaan dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>39900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1097" t="n">
-        <v>796</v>
+        <v>1100</v>
       </c>
       <c r="E1097" t="n">
-        <v>864</v>
+        <v>540</v>
       </c>
       <c r="F1097" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1097" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1097" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1098">
@@ -31164,26 +31164,26 @@
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Dijual Rumah Moh Kahfi 1 - 5 Menit ke Cilandak</t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>53500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1098" t="n">
-        <v>452</v>
+        <v>65</v>
       </c>
       <c r="E1098" t="n">
-        <v>1165</v>
+        <v>106</v>
       </c>
       <c r="F1098" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1098" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1098" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1099">
@@ -31192,26 +31192,26 @@
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran dan Dekat Gatot Subroto dan Sudirman dan Dekat Menteng Area Mentri dan Kedutaan dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Stategis, 5 Menit Ke Tb Simatupang ,butuh Minim Renovasi,</t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>48000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1099" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1099" t="n">
-        <v>540</v>
+        <v>144</v>
       </c>
       <c r="F1099" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1099" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1099" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1100">
@@ -31220,26 +31220,26 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>Dijual Rumah Moh Kahfi 1 - 5 Menit ke Cilandak</t>
+          <t>Rumah Bagus 3 Lantai dan Kolam Renang Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>1500000000</v>
+        <v>3700000000</v>
       </c>
       <c r="D1100" t="n">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="E1100" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="F1100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1101">
@@ -31248,26 +31248,26 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Stategis, 5 Menit Ke Tb Simatupang ,butuh Minim Renovasi,</t>
+          <t>Rumah Murah Harga di Bawah Pasar di Bintaro Sektor 1 Jakartasel</t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>3600000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1101" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1101" t="n">
-        <v>144</v>
+        <v>682</v>
       </c>
       <c r="F1101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1102">
@@ -31276,26 +31276,26 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Rumah Bagus 3 Lantai dan Kolam Renang Jagakarsa Jakarta Selatan</t>
+          <t>Luxurious Brand New Kebayoran Baru Dengan Balcony View Scbd</t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>3700000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1102" t="n">
-        <v>300</v>
+        <v>810</v>
       </c>
       <c r="E1102" t="n">
-        <v>143</v>
+        <v>338</v>
       </c>
       <c r="F1102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1102" t="n">
         <v>4</v>
       </c>
       <c r="H1102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1103">
@@ -31304,26 +31304,26 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Rumah Murah Harga di Bawah Pasar di Bintaro Sektor 1 Jakartasel</t>
+          <t>For Sale Brand New American Classic Pondok Indah Parkir 15 Mobil</t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>7900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1103" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="E1103" t="n">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="F1103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1104">
@@ -31332,17 +31332,17 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Luxurious Brand New Kebayoran Baru Dengan Balcony View Scbd</t>
+          <t>2025 Modern House Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>48000000000</v>
+        <v>46000000000</v>
       </c>
       <c r="D1104" t="n">
-        <v>810</v>
+        <v>871</v>
       </c>
       <c r="E1104" t="n">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="F1104" t="n">
         <v>4</v>
@@ -31360,26 +31360,26 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>For Sale Brand New American Classic Pondok Indah Parkir 15 Mobil</t>
+          <t>For Sale Rumah Hitung Tanah Tebet</t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>62000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1105" t="n">
-        <v>2000</v>
+        <v>75</v>
       </c>
       <c r="E1105" t="n">
-        <v>670</v>
+        <v>81</v>
       </c>
       <c r="F1105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1106">
@@ -31388,26 +31388,26 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>2025 Modern House Kebayoran Baru For Sale</t>
+          <t>- Murah !! Dijual Cepat !! Rumah Siap Huni 10x25 dibawah NJOP di Niaga Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>46000000000</v>
+        <v>5700000000</v>
       </c>
       <c r="D1106" t="n">
-        <v>871</v>
+        <v>180</v>
       </c>
       <c r="E1106" t="n">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="F1106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1107">
@@ -31416,26 +31416,26 @@
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>For Sale Rumah Hitung Tanah Tebet</t>
+          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>1500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1107" t="n">
-        <v>75</v>
+        <v>825</v>
       </c>
       <c r="E1107" t="n">
-        <v>81</v>
+        <v>768</v>
       </c>
       <c r="F1107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1108">
@@ -31444,26 +31444,26 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>- Murah !! Dijual Cepat !! Rumah Siap Huni 10x25 dibawah NJOP di Niaga Hijau Pondok Indah</t>
+          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>5700000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1108" t="n">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="E1108" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F1108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1108" t="n">
         <v>3</v>
       </c>
       <c r="H1108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1109">
@@ -31472,26 +31472,26 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Rumah Hook Luas 850m 6+2 Kamar Shm Pondok Indah Dekat Pim</t>
+          <t>Khusus Investor | Cocok untuk Kost | Belakang Eka Hospital Tebet</t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>32000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1109" t="n">
-        <v>825</v>
+        <v>150</v>
       </c>
       <c r="E1109" t="n">
-        <v>768</v>
+        <v>238</v>
       </c>
       <c r="F1109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1110">
@@ -31500,26 +31500,26 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Rumah Nyaman Lebak Bulus Private Pool SHM Luas 400M 6+1 Kamar</t>
+          <t>Rumah Ex Cafe di Tebet | Lokasi Bisnis Ramai | Dekat Mall Kokas</t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>14000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1110" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="E1110" t="n">
-        <v>300</v>
+        <v>675</v>
       </c>
       <c r="F1110" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1111">
@@ -31528,26 +31528,26 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Khusus Investor | Cocok untuk Kost | Belakang Eka Hospital Tebet</t>
+          <t>Rumah Mewah Gaya Perancis Full Furnished Dalam Komplek Elit Tebet</t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>6500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1111" t="n">
-        <v>150</v>
+        <v>725</v>
       </c>
       <c r="E1111" t="n">
-        <v>238</v>
+        <v>448</v>
       </c>
       <c r="F1111" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1111" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1112">
@@ -31556,23 +31556,23 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Rumah Ex Cafe di Tebet | Lokasi Bisnis Ramai | Dekat Mall Kokas</t>
+          <t>Turun Harga!! Dijual Rumah Lux Tropical di Cilandak, Siap Huni, Harga bisa Nego, SHM</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>15500000000</v>
+        <v>20500000000</v>
       </c>
       <c r="D1112" t="n">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="E1112" t="n">
-        <v>675</v>
+        <v>982</v>
       </c>
       <c r="F1112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1112" t="n">
         <v>4</v>
@@ -31584,26 +31584,26 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gaya Perancis Full Furnished Dalam Komplek Elit Tebet</t>
+          <t>Rumah Lokasi Langka Wijaya 2 Super Strategis Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>30000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1113" t="n">
-        <v>725</v>
+        <v>90</v>
       </c>
       <c r="E1113" t="n">
-        <v>448</v>
+        <v>270</v>
       </c>
       <c r="F1113" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G1113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1114">
@@ -31612,26 +31612,26 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Turun Harga!! Dijual Rumah Lux Tropical di Cilandak, Siap Huni, Harga bisa Nego, SHM</t>
+          <t>Rumah Classic Modern Siap Huni Fully Furnish Jual Cepat Jarang Ada Area Bebas Banjir</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>20500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1114" t="n">
-        <v>650</v>
+        <v>760</v>
       </c>
       <c r="E1114" t="n">
-        <v>982</v>
+        <v>517</v>
       </c>
       <c r="F1114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1115">
@@ -31640,26 +31640,26 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Langka Wijaya 2 Super Strategis Lihat Jamin Beli</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>25000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1115" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="E1115" t="n">
-        <v>270</v>
+        <v>123</v>
       </c>
       <c r="F1115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1116">
@@ -31668,26 +31668,26 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Rumah Classic Modern Siap Huni Fully Furnish Jual Cepat Jarang Ada Area Bebas Banjir</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>38000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1116" t="n">
-        <v>760</v>
+        <v>171</v>
       </c>
       <c r="E1116" t="n">
-        <v>517</v>
+        <v>181</v>
       </c>
       <c r="F1116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1117">
@@ -31696,23 +31696,23 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah 2 Lantai 15 Menit ke One Belpark Mall Siap Huni Bebas Banjir J-25000</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>2550000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1117" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E1117" t="n">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="F1117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1117" t="n">
         <v>1</v>
@@ -31724,17 +31724,17 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>Rumah Minimalis Terawat 17 Menit ke One Belpark Mall Dibantu KPR J34039</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>2550000000</v>
+        <v>1220000000</v>
       </c>
       <c r="D1118" t="n">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="E1118" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="F1118" t="n">
         <v>3</v>
@@ -31752,23 +31752,23 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15 Menit ke One Belpark Mall Siap Huni Bebas Banjir J-25000</t>
+          <t>Rumah LB 155 SHM Siap KPR 18 Menit ke AEON Mall Tanjung Barat J33899</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>1900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1119" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E1119" t="n">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="F1119" t="n">
         <v>4</v>
       </c>
       <c r="G1119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1119" t="n">
         <v>1</v>
@@ -31780,17 +31780,17 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Terawat 17 Menit ke One Belpark Mall Dibantu KPR J34039</t>
+          <t>Rumah Minimalis 8 Menit ke Gerbang Tol Brigif SHM Hadap Timur J26013</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>1220000000</v>
+        <v>2230000000</v>
       </c>
       <c r="D1120" t="n">
         <v>120</v>
       </c>
       <c r="E1120" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="F1120" t="n">
         <v>3</v>
@@ -31808,23 +31808,23 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Rumah LB 155 SHM Siap KPR 18 Menit ke AEON Mall Tanjung Barat J33899</t>
+          <t>Rumah 1 Lantai Tenang Di Pondok Indah - Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>5500000000</v>
+        <v>28900000000</v>
       </c>
       <c r="D1121" t="n">
-        <v>155</v>
+        <v>445</v>
       </c>
       <c r="E1121" t="n">
-        <v>272</v>
+        <v>756</v>
       </c>
       <c r="F1121" t="n">
         <v>4</v>
       </c>
       <c r="G1121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1121" t="n">
         <v>1</v>
@@ -31836,23 +31836,23 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 8 Menit ke Gerbang Tol Brigif SHM Hadap Timur J26013</t>
+          <t>Rumah Luas LT 180 Dekat Cilandak 10 Menit ke RS Bebas Banjir J30974</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>2230000000</v>
+        <v>1770000000</v>
       </c>
       <c r="D1122" t="n">
         <v>120</v>
       </c>
       <c r="E1122" t="n">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="F1122" t="n">
         <v>3</v>
       </c>
       <c r="G1122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1122" t="n">
         <v>1</v>
@@ -31864,20 +31864,20 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Tenang Di Pondok Indah - Jakarta Selatan</t>
+          <t>Rumah 2 Lt SHM Siap Huni 15 Menit ke Stasiun MRT Lebak Bulus Grab J-35553</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>28900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1123" t="n">
-        <v>445</v>
+        <v>119</v>
       </c>
       <c r="E1123" t="n">
-        <v>756</v>
+        <v>84</v>
       </c>
       <c r="F1123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1123" t="n">
         <v>4</v>
@@ -31892,20 +31892,20 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Rumah Luas LT 180 Dekat Cilandak 10 Menit ke RS Bebas Banjir J30974</t>
+          <t>Dijual Rumah TERMURAAAH di Bintaro Utara,Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>1770000000</v>
+        <v>6600000000</v>
       </c>
       <c r="D1124" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="E1124" t="n">
-        <v>180</v>
+        <v>378</v>
       </c>
       <c r="F1124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1124" t="n">
         <v>3</v>
@@ -31920,17 +31920,17 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>Rumah 2 Lt SHM Siap Huni 15 Menit ke Stasiun MRT Lebak Bulus Grab J-35553</t>
+          <t>Cilandak Belakang Citos 2 Lt Tenang Private Asri Bebas Banjir</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>2550000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1125" t="n">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="E1125" t="n">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="F1125" t="n">
         <v>3</v>
@@ -31948,26 +31948,26 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Dijual Rumah TERMURAAAH di Bintaro Utara,Jakarta Selatan</t>
+          <t>Termurah Brawijaya Townhouse Kebayoran Baru, Dijual Rumah Hunian Property di Dalam Townhouse Perumahan Komplek Akses Jalan Lebar Akses Mudah di Lingkungan Elit dan Lokasi Strategis Sentral Dekat dengan MRT, Dharmawangsa, Senopati, di Jalan Brawijaya, Keba</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>6600000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1126" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E1126" t="n">
-        <v>378</v>
+        <v>196</v>
       </c>
       <c r="F1126" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1127">
@@ -31976,26 +31976,26 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Cilandak Belakang Citos 2 Lt Tenang Private Asri Bebas Banjir</t>
+          <t>Best Deal Luas Tanah Besar Siap Huni Kebayoran Baru! Rumah Modern Tropical Mewah Cantik Property Hunian Dijual Semi Furnished di Lokasi Strategis Akses dan Lingkungan Nyaman dan Asri di Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>6000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1127" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E1127" t="n">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="F1127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1127" t="n">
         <v>4</v>
       </c>
       <c r="H1127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1128">
@@ -32004,17 +32004,17 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Termurah Brawijaya Townhouse Kebayoran Baru, Dijual Rumah Hunian Property di Dalam Townhouse Perumahan Komplek Akses Jalan Lebar Akses Mudah di Lingkungan Elit dan Lokasi Strategis Sentral Dekat dengan MRT, Dharmawangsa, Senopati, di Jalan Brawijaya, Keba</t>
+          <t>Best Deal Kebayoran Baru! Rumah Siap Huni Cantik Kebayoran Baru Jalan Lebar Dekat Hanya 200 Meter ke MRT Lingkungan Nyaman dan Aman di Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>15200000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1128" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1128" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F1128" t="n">
         <v>4</v>
@@ -32023,7 +32023,7 @@
         <v>5</v>
       </c>
       <c r="H1128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1129">
@@ -32032,26 +32032,26 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Best Deal Luas Tanah Besar Siap Huni Kebayoran Baru! Rumah Modern Tropical Mewah Cantik Property Hunian Dijual Semi Furnished di Lokasi Strategis Akses dan Lingkungan Nyaman dan Asri di Kebayoran Baru, Jakarta Selatan</t>
+          <t>Best Price Harga Bagus Pondok Indah untuk Bangun Rumah Impian, Rumah Hitung Tanah Dijual Luas Besar dengan Harga Murah Jalan Depan Lebar Lingkungan Nyaman Aman dan Asri di Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1129" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="E1129" t="n">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="F1129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1130">
@@ -32060,26 +32060,26 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Best Deal Kebayoran Baru! Rumah Siap Huni Cantik Kebayoran Baru Jalan Lebar Dekat Hanya 200 Meter ke MRT Lingkungan Nyaman dan Aman di Kebayoran Baru, Jakarta Selatan</t>
+          <t>Best Price Pondok Indah Rumah Siap Huni! Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>10100000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1130" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1130" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F1130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1131">
@@ -32088,23 +32088,23 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Best Price Harga Bagus Pondok Indah untuk Bangun Rumah Impian, Rumah Hitung Tanah Dijual Luas Besar dengan Harga Murah Jalan Depan Lebar Lingkungan Nyaman Aman dan Asri di Pondok Indah, Jakarta Selatan</t>
+          <t>Best Price Siap Huni Pondok Indah Rumah Cantik Terawat! Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>6500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1131" t="n">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="E1131" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F1131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1131" t="n">
         <v>1</v>
@@ -32116,20 +32116,20 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Rumah Siap Huni! Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah Siap Huni 2M-An di Tebet Dekat Kokas, Saharjo dan Tebet Raya!</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>6760000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1132" t="n">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="E1132" t="n">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="F1132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1132" t="n">
         <v>4</v>
@@ -32144,17 +32144,17 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Best Price Siap Huni Pondok Indah Rumah Cantik Terawat! Pondok Indah, Jakarta Selatan</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>9500000000</v>
+        <v>41900000000</v>
       </c>
       <c r="D1133" t="n">
-        <v>219</v>
+        <v>720</v>
       </c>
       <c r="E1133" t="n">
-        <v>200</v>
+        <v>634</v>
       </c>
       <c r="F1133" t="n">
         <v>4</v>
@@ -32163,7 +32163,7 @@
         <v>5</v>
       </c>
       <c r="H1133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1134">
@@ -32172,17 +32172,17 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni 2M-An di Tebet Dekat Kokas, Saharjo dan Tebet Raya!</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>2300000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1134" t="n">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="E1134" t="n">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="F1134" t="n">
         <v>5</v>
@@ -32200,26 +32200,26 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Strategis Di Tengah Kota</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>41900000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1135" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1135" t="n">
-        <v>634</v>
+        <v>240</v>
       </c>
       <c r="F1135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1136">
@@ -32228,26 +32228,26 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Serenia Hills Cluster Signature Best Deal Jarang Ada</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>4900000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1136" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="E1136" t="n">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="F1136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1137">
@@ -32256,23 +32256,23 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Rumah Strategis Di Tengah Kota</t>
+          <t>House For Sale - [Lebak Bulus]Rumah Dalam Townhouse, Bangunan 4 Lantai Plus Rooftop.</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>7800000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1137" t="n">
-        <v>350</v>
+        <v>1005</v>
       </c>
       <c r="E1137" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="F1137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1137" t="n">
         <v>2</v>
@@ -32284,26 +32284,26 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Serenia Hills Cluster Signature Best Deal Jarang Ada</t>
+          <t>Dijual Rumah Secondary dengan Modern Tropical Design Dalam Townhouse Berisi 13 Unit Rumah yang Aman dan Nyaman di Area R.c Veteran - Rempoa, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>8500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1138" t="n">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="E1138" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F1138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1138" t="n">
         <v>3</v>
       </c>
       <c r="H1138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1139">
@@ -32312,26 +32312,26 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>House For Sale - [Lebak Bulus]Rumah Dalam Townhouse, Bangunan 4 Lantai Plus Rooftop.</t>
+          <t>Rumah Mewah Terawat dan Siap Huni, Tanah dan Bangunan Luas di Cilandak</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>15000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1139" t="n">
-        <v>1005</v>
+        <v>650</v>
       </c>
       <c r="E1139" t="n">
-        <v>308</v>
+        <v>982</v>
       </c>
       <c r="F1139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1139" t="n">
         <v>5</v>
       </c>
       <c r="H1139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1140">
@@ -32340,26 +32340,26 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Dijual Rumah Secondary dengan Modern Tropical Design Dalam Townhouse Berisi 13 Unit Rumah yang Aman dan Nyaman di Area R.c Veteran - Rempoa, Jakarta Selatan</t>
+          <t>Rumah di Bawah Harga Pasar Buat Kost dan Investasi Dekat Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>9500000000</v>
+        <v>3750000000</v>
       </c>
       <c r="D1140" t="n">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="E1140" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F1140" t="n">
         <v>3</v>
       </c>
       <c r="G1140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1141">
@@ -32368,17 +32368,17 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Rumah Mewah Terawat dan Siap Huni, Tanah dan Bangunan Luas di Cilandak</t>
+          <t>Rumah Tropical Resort With S Pool In Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>25000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1141" t="n">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="E1141" t="n">
-        <v>982</v>
+        <v>1925</v>
       </c>
       <c r="F1141" t="n">
         <v>5</v>
@@ -32387,7 +32387,7 @@
         <v>5</v>
       </c>
       <c r="H1141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1142">
@@ -32396,26 +32396,26 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Rumah di Bawah Harga Pasar Buat Kost dan Investasi Dekat Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Kantor Buat Usaha di Bawah Harga NJOP Tersewa di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>3750000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1142" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E1142" t="n">
-        <v>300</v>
+        <v>1343</v>
       </c>
       <c r="F1142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1142" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1143">
@@ -32424,26 +32424,26 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Rumah Tropical Resort With S Pool In Cipete Jakarta Selatan</t>
+          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>42000000000</v>
+        <v>31500000000</v>
       </c>
       <c r="D1143" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="E1143" t="n">
-        <v>1925</v>
+        <v>2620</v>
       </c>
       <c r="F1143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1143" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1144">
@@ -32452,26 +32452,26 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Rumah Kantor Buat Usaha di Bawah Harga NJOP Tersewa di Kemang Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Harga NJOP Lokasi Prestisius Dekat ke Pusat Bisnis Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>25000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1144" t="n">
-        <v>700</v>
+        <v>385</v>
       </c>
       <c r="E1144" t="n">
-        <v>1343</v>
+        <v>504</v>
       </c>
       <c r="F1144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1144" t="n">
         <v>3</v>
       </c>
       <c r="H1144" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1145">
@@ -32480,26 +32480,26 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Rumah Paling Murah Lokasi Bagus di Area Kemang Jakarta Selatan</t>
+          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>31500000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1145" t="n">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="E1145" t="n">
-        <v>2620</v>
+        <v>161</v>
       </c>
       <c r="F1145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1146">
@@ -32508,17 +32508,17 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Harga NJOP Lokasi Prestisius Dekat ke Pusat Bisnis Mega Kuningan, Jakarta Selatan</t>
+          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>32000000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1146" t="n">
-        <v>385</v>
+        <v>180</v>
       </c>
       <c r="E1146" t="n">
-        <v>504</v>
+        <v>162</v>
       </c>
       <c r="F1146" t="n">
         <v>5</v>
@@ -32536,7 +32536,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Jual Rumah Pondok Pinang Area Pondok Indah</t>
+          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -32546,7 +32546,7 @@
         <v>180</v>
       </c>
       <c r="E1147" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F1147" t="n">
         <v>5</v>
@@ -32564,20 +32564,20 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>Jual Rumah ******** Area Cilandak Pondok Indah</t>
+          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>3950000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1148" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E1148" t="n">
-        <v>162</v>
+        <v>446</v>
       </c>
       <c r="F1148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1148" t="n">
         <v>3</v>
@@ -32592,26 +32592,26 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Jual Rumah Lebak Bulus Area Pondok Pinang Pondok Indah</t>
+          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>3950000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1149" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1149" t="n">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="F1149" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1150">
@@ -32620,23 +32620,23 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Rumah Super Mewah dan Luas Komplek Elite Lebak Bulus Jakarta Selatan Wajib Survey</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>11500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E1150" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="F1150" t="n">
         <v>4</v>
       </c>
       <c r="G1150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1150" t="n">
         <v>2</v>
@@ -32648,26 +32648,26 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Rumah Harga Siap Nego Sampai Deal Dekat Blok A dan Jalan Rs Fatmawati</t>
+          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>9500000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E1151" t="n">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="F1151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1152">
@@ -32676,17 +32676,17 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>6900000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="E1152" t="n">
-        <v>76</v>
+        <v>448</v>
       </c>
       <c r="F1152" t="n">
         <v>4</v>
@@ -32695,7 +32695,7 @@
         <v>4</v>
       </c>
       <c r="H1152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1153">
@@ -32704,26 +32704,26 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>35000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>650</v>
+        <v>1374</v>
       </c>
       <c r="E1153" t="n">
-        <v>406</v>
+        <v>1493</v>
       </c>
       <c r="F1153" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1153" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H1153" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1154">
@@ -32732,17 +32732,17 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
+          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>30000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>274</v>
+        <v>467</v>
       </c>
       <c r="E1154" t="n">
-        <v>448</v>
+        <v>899</v>
       </c>
       <c r="F1154" t="n">
         <v>4</v>
@@ -32751,7 +32751,7 @@
         <v>4</v>
       </c>
       <c r="H1154" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1155">
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
+          <t>Rumah Mewah Baru di Jagakarsa</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>26000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>1374</v>
+        <v>520</v>
       </c>
       <c r="E1155" t="n">
-        <v>1493</v>
+        <v>720</v>
       </c>
       <c r="F1155" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G1155" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H1155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,17 +32788,17 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>18000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>467</v>
+        <v>375</v>
       </c>
       <c r="E1156" t="n">
-        <v>899</v>
+        <v>76</v>
       </c>
       <c r="F1156" t="n">
         <v>4</v>
@@ -32807,7 +32807,7 @@
         <v>4</v>
       </c>
       <c r="H1156" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1157">
@@ -32816,26 +32816,26 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Rumah Mewah Baru di Jagakarsa</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>12500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>520</v>
+        <v>1200</v>
       </c>
       <c r="E1157" t="n">
-        <v>720</v>
+        <v>620</v>
       </c>
       <c r="F1157" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G1157" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H1157" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1158">
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>6900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="E1158" t="n">
-        <v>76</v>
+        <v>960</v>
       </c>
       <c r="F1158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1158" t="n">
         <v>4</v>
       </c>
       <c r="H1158" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>42000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="E1159" t="n">
-        <v>620</v>
+        <v>300</v>
       </c>
       <c r="F1159" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G1159" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H1159" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1160">
@@ -32900,26 +32900,26 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>21000000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="E1160" t="n">
-        <v>960</v>
+        <v>534</v>
       </c>
       <c r="F1160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1160" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1160" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1161">
@@ -32928,26 +32928,26 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>13000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="E1161" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="F1161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1161" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1162">
@@ -32956,17 +32956,17 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>40500000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>350</v>
+        <v>128</v>
       </c>
       <c r="E1162" t="n">
-        <v>534</v>
+        <v>252</v>
       </c>
       <c r="F1162" t="n">
         <v>3</v>
@@ -32975,7 +32975,7 @@
         <v>3</v>
       </c>
       <c r="H1162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,23 +32984,23 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>12000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="E1163" t="n">
-        <v>550</v>
+        <v>351</v>
       </c>
       <c r="F1163" t="n">
         <v>4</v>
       </c>
       <c r="G1163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1163" t="n">
         <v>2</v>
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>6000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>128</v>
+        <v>366</v>
       </c>
       <c r="E1164" t="n">
-        <v>252</v>
+        <v>366</v>
       </c>
       <c r="F1164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1164" t="n">
         <v>3</v>
       </c>
       <c r="H1164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
+          <t>Brand New Modern American Classic House Pondok Indah</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>34500000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>280</v>
+        <v>750</v>
       </c>
       <c r="E1165" t="n">
-        <v>351</v>
+        <v>406</v>
       </c>
       <c r="F1165" t="n">
         <v>4</v>
       </c>
       <c r="G1165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,26 +33068,26 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>25000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>366</v>
+        <v>500</v>
       </c>
       <c r="E1166" t="n">
-        <v>366</v>
+        <v>248</v>
       </c>
       <c r="F1166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1166" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1167">
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Brand New Modern American Classic House Pondok Indah</t>
+          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>28500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>750</v>
+        <v>183</v>
       </c>
       <c r="E1167" t="n">
-        <v>406</v>
+        <v>149</v>
       </c>
       <c r="F1167" t="n">
         <v>4</v>
       </c>
       <c r="G1167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
+          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>22500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>500</v>
+        <v>72</v>
       </c>
       <c r="E1168" t="n">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="F1168" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1168" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,26 +33152,26 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>7000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>183</v>
+        <v>430</v>
       </c>
       <c r="E1169" t="n">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="F1169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1169" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1170">
@@ -33180,26 +33180,26 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>1300000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="E1170" t="n">
-        <v>45</v>
+        <v>318</v>
       </c>
       <c r="F1170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1171">
@@ -33208,23 +33208,23 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>8000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>430</v>
+        <v>850</v>
       </c>
       <c r="E1171" t="n">
-        <v>250</v>
+        <v>384</v>
       </c>
       <c r="F1171" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1171" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1171" t="n">
         <v>3</v>
@@ -33236,23 +33236,23 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="E1172" t="n">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="F1172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1172" t="n">
         <v>2</v>
@@ -33264,23 +33264,23 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>14000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="E1173" t="n">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="F1173" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1173" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1173" t="n">
         <v>3</v>
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>6900000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>375</v>
+        <v>800</v>
       </c>
       <c r="E1174" t="n">
-        <v>76</v>
+        <v>1050</v>
       </c>
       <c r="F1174" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1174" t="n">
         <v>4</v>
       </c>
       <c r="H1174" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>20000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E1175" t="n">
-        <v>353</v>
+        <v>787</v>
       </c>
       <c r="F1175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1175" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>23000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>800</v>
+        <v>375</v>
       </c>
       <c r="E1176" t="n">
-        <v>1050</v>
+        <v>76</v>
       </c>
       <c r="F1176" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1176" t="n">
         <v>4</v>
       </c>
       <c r="H1176" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>24000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="E1177" t="n">
-        <v>787</v>
+        <v>105</v>
       </c>
       <c r="F1177" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1177" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1177" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>6900000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1178" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>2400000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="E1179" t="n">
-        <v>105</v>
+        <v>1070</v>
       </c>
       <c r="F1179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1179" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,23 +33460,23 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>1750000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="E1180" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="F1180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1180" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1180" t="n">
         <v>1</v>
@@ -33488,17 +33488,17 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>17000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1181" t="n">
-        <v>1070</v>
+        <v>246</v>
       </c>
       <c r="F1181" t="n">
         <v>4</v>
@@ -33507,7 +33507,7 @@
         <v>3</v>
       </c>
       <c r="H1181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>7090000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1182" t="n">
-        <v>76</v>
+        <v>510</v>
       </c>
       <c r="F1182" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1182" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,23 +33544,23 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>7500000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="E1183" t="n">
-        <v>246</v>
+        <v>32</v>
       </c>
       <c r="F1183" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1183" t="n">
         <v>1</v>
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>7300000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>600</v>
+        <v>232</v>
       </c>
       <c r="E1184" t="n">
-        <v>510</v>
+        <v>284</v>
       </c>
       <c r="F1184" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1184" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,23 +33600,23 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>998000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="E1185" t="n">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="F1185" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1185" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1185" t="n">
         <v>1</v>
@@ -33628,23 +33628,23 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>22000000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>232</v>
+        <v>380</v>
       </c>
       <c r="E1186" t="n">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="F1186" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1186" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H1186" t="n">
         <v>1</v>
@@ -33656,23 +33656,23 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>6250000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="E1187" t="n">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="F1187" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1187" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1187" t="n">
         <v>1</v>
@@ -33684,26 +33684,26 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>7200000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="E1188" t="n">
-        <v>196</v>
+        <v>675</v>
       </c>
       <c r="F1188" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G1188" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H1188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1189">
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>2600000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>88</v>
+        <v>375</v>
       </c>
       <c r="E1189" t="n">
-        <v>55</v>
+        <v>534</v>
       </c>
       <c r="F1189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,26 +33740,26 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>65000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="E1190" t="n">
-        <v>675</v>
+        <v>378</v>
       </c>
       <c r="F1190" t="n">
         <v>4</v>
       </c>
       <c r="G1190" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1191">
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>23000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="E1191" t="n">
-        <v>534</v>
+        <v>70</v>
       </c>
       <c r="F1191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,23 +33796,23 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>15500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>928</v>
+        <v>1350</v>
       </c>
       <c r="E1192" t="n">
-        <v>378</v>
+        <v>863</v>
       </c>
       <c r="F1192" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1192" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1192" t="n">
         <v>1</v>
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>2830000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>112</v>
+        <v>355</v>
       </c>
       <c r="E1193" t="n">
-        <v>70</v>
+        <v>648</v>
       </c>
       <c r="F1193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,20 +33852,20 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>38000000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>1350</v>
+        <v>280</v>
       </c>
       <c r="E1194" t="n">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="F1194" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1194" t="n">
         <v>6</v>
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>10000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="E1195" t="n">
-        <v>648</v>
+        <v>117</v>
       </c>
       <c r="F1195" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1195" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>8800000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="E1196" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F1196" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1196" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>2600000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>130</v>
+        <v>1600</v>
       </c>
       <c r="E1197" t="n">
-        <v>117</v>
+        <v>1050</v>
       </c>
       <c r="F1197" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1197" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1197" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>9000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="E1198" t="n">
-        <v>200</v>
+        <v>351</v>
       </c>
       <c r="F1198" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1198" t="n">
         <v>3</v>
       </c>
       <c r="H1198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>68000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>1600</v>
+        <v>182</v>
       </c>
       <c r="E1199" t="n">
-        <v>1050</v>
+        <v>290</v>
       </c>
       <c r="F1199" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1199" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1199" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>34500000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="E1200" t="n">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="F1200" t="n">
         <v>4</v>
       </c>
       <c r="G1200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,23 +34048,23 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>22000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="E1201" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="F1201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1201" t="n">
         <v>2</v>
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>15000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="E1202" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F1202" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>4800000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1203" t="n">
         <v>300</v>
       </c>
       <c r="E1203" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F1203" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1203" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>13500000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="E1204" t="n">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="F1204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>14500000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="E1205" t="n">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="F1205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1205" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1206">
@@ -34188,17 +34188,17 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>1850000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>190</v>
+        <v>475</v>
       </c>
       <c r="E1206" t="n">
-        <v>73</v>
+        <v>475</v>
       </c>
       <c r="F1206" t="n">
         <v>4</v>
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>3300000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>130</v>
+        <v>3475</v>
       </c>
       <c r="E1207" t="n">
-        <v>88</v>
+        <v>3475</v>
       </c>
       <c r="F1207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,17 +34244,17 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>3350000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="E1208" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
@@ -34263,7 +34263,7 @@
         <v>3</v>
       </c>
       <c r="H1208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,26 +34272,26 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>45000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="E1209" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="F1209" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1209" t="n">
         <v>3</v>
       </c>
       <c r="H1209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1210">
@@ -34300,20 +34300,20 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>42500000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="E1210" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="F1210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1210" t="n">
         <v>3</v>
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>7900000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="E1211" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="F1211" t="n">
         <v>4</v>
       </c>
       <c r="G1211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,23 +34356,23 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>13100000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="E1212" t="n">
-        <v>819</v>
+        <v>400</v>
       </c>
       <c r="F1212" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1212" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1212" t="n">
         <v>2</v>
@@ -34384,23 +34384,23 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>7000000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1213" t="n">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="F1213" t="n">
         <v>4</v>
       </c>
       <c r="G1213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1213" t="n">
         <v>3</v>
@@ -34412,23 +34412,23 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>28000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="E1214" t="n">
-        <v>400</v>
+        <v>307</v>
       </c>
       <c r="F1214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1214" t="n">
         <v>2</v>
@@ -34440,17 +34440,17 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>15200000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1215" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F1215" t="n">
         <v>4</v>
@@ -34459,7 +34459,7 @@
         <v>5</v>
       </c>
       <c r="H1215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,17 +34468,17 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>15000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="E1216" t="n">
-        <v>307</v>
+        <v>200</v>
       </c>
       <c r="F1216" t="n">
         <v>4</v>
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>10100000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="E1217" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F1217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,17 +34524,17 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>9500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>436</v>
+        <v>262</v>
       </c>
       <c r="E1218" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>15500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>340</v>
+        <v>700</v>
       </c>
       <c r="E1219" t="n">
-        <v>350</v>
+        <v>1150</v>
       </c>
       <c r="F1219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>8500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="E1220" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="F1220" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1220" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,23 +34608,23 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>55000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="E1221" t="n">
-        <v>1150</v>
+        <v>209</v>
       </c>
       <c r="F1221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1221" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1221" t="n">
         <v>2</v>
@@ -34636,23 +34636,23 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>6500000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E1222" t="n">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="F1222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1222" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1222" t="n">
         <v>1</v>
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>12900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="E1223" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>6760000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="E1224" t="n">
-        <v>160</v>
+        <v>1800</v>
       </c>
       <c r="F1224" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1224" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1224" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>9500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="E1225" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1225" t="n">
         <v>4</v>
       </c>
       <c r="G1225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1225" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>7090000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1226" t="n">
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="F1226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1226" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1226" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,23 +34776,23 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>42000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="E1227" t="n">
-        <v>1925</v>
+        <v>517</v>
       </c>
       <c r="F1227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1227" t="n">
         <v>12</v>
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>13800000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>407</v>
+        <v>225</v>
       </c>
       <c r="E1228" t="n">
-        <v>692</v>
+        <v>108</v>
       </c>
       <c r="F1228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1228" t="n">
         <v>3</v>
       </c>
       <c r="H1228" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>14700000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1229" t="n">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="F1229" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1229" t="n">
         <v>4</v>
       </c>
       <c r="H1229" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>55000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="E1230" t="n">
-        <v>1800</v>
+        <v>276</v>
       </c>
       <c r="F1230" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1230" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1230" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>55000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1231" t="n">
-        <v>500</v>
+        <v>630</v>
       </c>
       <c r="F1231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>2600000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1232" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F1232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>24900000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E1233" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="F1233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1233" t="n">
         <v>4</v>
       </c>
       <c r="H1233" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>38000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>760</v>
+        <v>1600</v>
       </c>
       <c r="E1234" t="n">
-        <v>517</v>
+        <v>1800</v>
       </c>
       <c r="F1234" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1234" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1234" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>4900000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="E1235" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="F1235" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>2600000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E1236" t="n">
-        <v>60</v>
+        <v>1026</v>
       </c>
       <c r="F1236" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G1236" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1236" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>34900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1237" t="n">
-        <v>538</v>
+        <v>1925</v>
       </c>
       <c r="F1237" t="n">
         <v>6</v>
       </c>
       <c r="G1237" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1237" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1238">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>10900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="E1239" t="n">
-        <v>276</v>
+        <v>540</v>
       </c>
       <c r="F1239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1239" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>2830000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>60</v>
+        <v>470</v>
       </c>
       <c r="E1240" t="n">
-        <v>60</v>
+        <v>412</v>
       </c>
       <c r="F1240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1240" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1240" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>21000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1241" t="n">
-        <v>630</v>
+        <v>1925</v>
       </c>
       <c r="F1241" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1241" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1241" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>6500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E1242" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F1242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,23 +35224,23 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>49000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1243" t="n">
-        <v>540</v>
+        <v>404</v>
       </c>
       <c r="F1243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1243" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1243" t="n">
         <v>5</v>
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>42000000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1244" t="n">
         <v>850</v>
       </c>
       <c r="E1244" t="n">
-        <v>1925</v>
+        <v>1060</v>
       </c>
       <c r="F1244" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1244" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1244" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,23 +35280,23 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>22000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>650</v>
+        <v>325</v>
       </c>
       <c r="E1245" t="n">
-        <v>854</v>
+        <v>696</v>
       </c>
       <c r="F1245" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1245" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1245" t="n">
         <v>5</v>
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>7800000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1246" t="n">
-        <v>404</v>
+        <v>60</v>
       </c>
       <c r="F1246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1246" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>31900000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1247" t="n">
-        <v>350</v>
+        <v>1084</v>
       </c>
       <c r="F1247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1247" t="n">
         <v>4</v>
       </c>
       <c r="H1247" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,306 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>55000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>1600</v>
+        <v>1050</v>
       </c>
       <c r="E1248" t="n">
-        <v>1800</v>
+        <v>627</v>
       </c>
       <c r="F1248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1248" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1248" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>1248</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>696</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1249" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>1249</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1250" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1251" t="n">
+        <v>4690000000</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>187</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1252" t="n">
+        <v>8990000000</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>1252</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1253" t="n">
+        <v>22000000000</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>854</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>1253</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>14700000000</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>1254</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>880</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>1255</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>13800000000</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>407</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>692</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+        </is>
+      </c>
+      <c r="C1257" t="n">
+        <v>53500000000</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>452</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1258" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>404</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1258"/>
+  <dimension ref="A1:H1270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34692,23 +34692,23 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
         <v>55000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="E1224" t="n">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="F1224" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1224" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1224" t="n">
         <v>6</v>
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>55000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E1225" t="n">
-        <v>500</v>
+        <v>108</v>
       </c>
       <c r="F1225" t="n">
         <v>4</v>
       </c>
       <c r="G1225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1225" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>24900000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E1226" t="n">
-        <v>331</v>
+        <v>538</v>
       </c>
       <c r="F1226" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1226" t="n">
         <v>4</v>
       </c>
       <c r="H1226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>38000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>760</v>
+        <v>300</v>
       </c>
       <c r="E1227" t="n">
-        <v>517</v>
+        <v>276</v>
       </c>
       <c r="F1227" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1227" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>4900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>225</v>
+        <v>600</v>
       </c>
       <c r="E1228" t="n">
-        <v>108</v>
+        <v>630</v>
       </c>
       <c r="F1228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1228" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>34900000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1229" t="n">
-        <v>538</v>
+        <v>140</v>
       </c>
       <c r="F1229" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1229" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>10900000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1230" t="n">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="F1230" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>21000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1231" t="n">
-        <v>630</v>
+        <v>1026</v>
       </c>
       <c r="F1231" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1231" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>6500000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>250</v>
+        <v>882</v>
       </c>
       <c r="E1232" t="n">
-        <v>140</v>
+        <v>1845</v>
       </c>
       <c r="F1232" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1232" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>31900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E1233" t="n">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="F1233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1233" t="n">
         <v>4</v>
       </c>
       <c r="H1233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>55000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>1600</v>
+        <v>470</v>
       </c>
       <c r="E1234" t="n">
-        <v>1800</v>
+        <v>412</v>
       </c>
       <c r="F1234" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1234" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1234" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>7090000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1235" t="n">
-        <v>60</v>
+        <v>404</v>
       </c>
       <c r="F1235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1235" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>90000000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1236" t="n">
-        <v>1026</v>
+        <v>1060</v>
       </c>
       <c r="F1236" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1236" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>42000000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="E1237" t="n">
-        <v>1925</v>
+        <v>1084</v>
       </c>
       <c r="F1237" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1237" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1237" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,23 +35084,23 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>71900000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>882</v>
+        <v>1050</v>
       </c>
       <c r="E1238" t="n">
-        <v>1845</v>
+        <v>627</v>
       </c>
       <c r="F1238" t="n">
         <v>5</v>
       </c>
       <c r="G1238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1238" t="n">
         <v>6</v>
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>49000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>1100</v>
+        <v>325</v>
       </c>
       <c r="E1239" t="n">
-        <v>540</v>
+        <v>696</v>
       </c>
       <c r="F1239" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1239" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1239" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>17000000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="E1240" t="n">
-        <v>412</v>
+        <v>187</v>
       </c>
       <c r="F1240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1240" t="n">
         <v>4</v>
       </c>
       <c r="H1240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>42000000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E1241" t="n">
-        <v>1925</v>
+        <v>208</v>
       </c>
       <c r="F1241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1241" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1241" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>2600000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="E1242" t="n">
-        <v>60</v>
+        <v>854</v>
       </c>
       <c r="F1242" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1242" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1242" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>7890000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1243" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="F1243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1243" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>29900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>850</v>
+        <v>880</v>
       </c>
       <c r="E1244" t="n">
-        <v>1060</v>
+        <v>1000</v>
       </c>
       <c r="F1244" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1244" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1244" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>12900000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="E1245" t="n">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F1245" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1245" t="n">
         <v>3</v>
       </c>
       <c r="H1245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>2830000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>60</v>
+        <v>452</v>
       </c>
       <c r="E1246" t="n">
-        <v>60</v>
+        <v>1165</v>
       </c>
       <c r="F1246" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1246" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1246" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>39800000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1247" t="n">
-        <v>1084</v>
+        <v>404</v>
       </c>
       <c r="F1247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1247" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1247" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>44000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>1050</v>
+        <v>60</v>
       </c>
       <c r="E1248" t="n">
-        <v>627</v>
+        <v>60</v>
       </c>
       <c r="F1248" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1248" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1248" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>12900000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="E1249" t="n">
-        <v>696</v>
+        <v>120</v>
       </c>
       <c r="F1249" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1249" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1249" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>2600000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1250" t="n">
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="F1250" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1250" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>4690000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1251" t="n">
-        <v>187</v>
+        <v>500</v>
       </c>
       <c r="F1251" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1251" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1251" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>8990000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1252" t="n">
-        <v>208</v>
+        <v>1000</v>
       </c>
       <c r="F1252" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1252" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1252" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>22000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="E1253" t="n">
-        <v>854</v>
+        <v>660</v>
       </c>
       <c r="F1253" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="G1253" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1253" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>14700000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="E1254" t="n">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="F1254" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1254" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1254" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>62000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>880</v>
+        <v>60</v>
       </c>
       <c r="E1255" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="F1255" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1255" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1255" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>13800000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>407</v>
+        <v>600</v>
       </c>
       <c r="E1256" t="n">
-        <v>692</v>
+        <v>630</v>
       </c>
       <c r="F1256" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1256" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1256" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>53500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>452</v>
+        <v>250</v>
       </c>
       <c r="E1257" t="n">
-        <v>1165</v>
+        <v>140</v>
       </c>
       <c r="F1257" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G1257" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1257" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,25 +35644,361 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>7800000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1258" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>1258</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1259" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1260" t="n">
+        <v>31900000000</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>350</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+        </is>
+      </c>
+      <c r="C1261" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>1262</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>34900000000</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>538</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>1263</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>71900000000</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>882</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>1845</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>49000000000</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>540</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>10900000000</v>
+      </c>
+      <c r="D1269" t="n">
         <v>300</v>
       </c>
-      <c r="E1258" t="n">
-        <v>404</v>
-      </c>
-      <c r="F1258" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1258" t="n">
-        <v>2</v>
-      </c>
-      <c r="H1258" t="n">
+      <c r="E1269" t="n">
+        <v>276</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1269" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>1269</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>696</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1270" t="n">
         <v>5</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1270"/>
+  <dimension ref="A1:H1309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>14000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>850</v>
+        <v>375</v>
       </c>
       <c r="E1171" t="n">
-        <v>384</v>
+        <v>76</v>
       </c>
       <c r="F1171" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1171" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,26 +33236,26 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>6900000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="E1172" t="n">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="F1172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1172" t="n">
         <v>4</v>
       </c>
       <c r="H1172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,26 +33264,26 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>20000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E1173" t="n">
-        <v>353</v>
+        <v>1050</v>
       </c>
       <c r="F1173" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1173" t="n">
         <v>4</v>
       </c>
       <c r="H1173" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>23000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1174" t="n">
-        <v>1050</v>
+        <v>787</v>
       </c>
       <c r="F1174" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1174" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1174" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,26 +33320,26 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>24000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1175" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1175" t="n">
-        <v>787</v>
+        <v>76</v>
       </c>
       <c r="F1175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1175" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,23 +33348,23 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>6900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>375</v>
+        <v>140</v>
       </c>
       <c r="E1176" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F1176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1176" t="n">
         <v>2</v>
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2400000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E1177" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="F1177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1177" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>1750000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1178" t="n">
-        <v>127</v>
+        <v>1070</v>
       </c>
       <c r="F1178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1178" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1178" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,26 +33432,26 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>17000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1179" t="n">
-        <v>1070</v>
+        <v>76</v>
       </c>
       <c r="F1179" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1179" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1180">
@@ -33460,23 +33460,23 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>7090000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1180" t="n">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="F1180" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1180" t="n">
         <v>1</v>
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>7500000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1181" t="n">
-        <v>246</v>
+        <v>510</v>
       </c>
       <c r="F1181" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1181" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,26 +33516,26 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>7300000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>600</v>
+        <v>64</v>
       </c>
       <c r="E1182" t="n">
-        <v>510</v>
+        <v>32</v>
       </c>
       <c r="F1182" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1182" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1183">
@@ -33544,20 +33544,20 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>998000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>64</v>
+        <v>232</v>
       </c>
       <c r="E1183" t="n">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="F1183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1183" t="n">
         <v>2</v>
@@ -33572,23 +33572,23 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>22000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="E1184" t="n">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="F1184" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1184" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1184" t="n">
         <v>1</v>
@@ -33600,23 +33600,23 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>6250000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="E1185" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F1185" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G1185" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H1185" t="n">
         <v>1</v>
@@ -33628,23 +33628,23 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>7200000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="E1186" t="n">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="F1186" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G1186" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H1186" t="n">
         <v>1</v>
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>2600000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>88</v>
+        <v>1000</v>
       </c>
       <c r="E1187" t="n">
-        <v>55</v>
+        <v>675</v>
       </c>
       <c r="F1187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,23 +33684,23 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>65000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E1188" t="n">
-        <v>675</v>
+        <v>534</v>
       </c>
       <c r="F1188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1188" t="n">
         <v>2</v>
@@ -33712,26 +33712,26 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>23000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>375</v>
+        <v>928</v>
       </c>
       <c r="E1189" t="n">
-        <v>534</v>
+        <v>378</v>
       </c>
       <c r="F1189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1189" t="n">
         <v>2</v>
       </c>
       <c r="H1189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1190">
@@ -33740,23 +33740,23 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>15500000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>928</v>
+        <v>112</v>
       </c>
       <c r="E1190" t="n">
-        <v>378</v>
+        <v>70</v>
       </c>
       <c r="F1190" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1190" t="n">
         <v>1</v>
@@ -33768,23 +33768,23 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>2830000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>112</v>
+        <v>1350</v>
       </c>
       <c r="E1191" t="n">
-        <v>70</v>
+        <v>863</v>
       </c>
       <c r="F1191" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1191" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1191" t="n">
         <v>1</v>
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>38000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>1350</v>
+        <v>355</v>
       </c>
       <c r="E1192" t="n">
-        <v>863</v>
+        <v>648</v>
       </c>
       <c r="F1192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,26 +33824,26 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>10000000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="E1193" t="n">
-        <v>648</v>
+        <v>120</v>
       </c>
       <c r="F1193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1193" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1194">
@@ -33852,23 +33852,23 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>8800000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="E1194" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F1194" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1194" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1194" t="n">
         <v>1</v>
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>2600000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="E1195" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="F1195" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>9000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>440</v>
+        <v>1600</v>
       </c>
       <c r="E1196" t="n">
-        <v>200</v>
+        <v>1050</v>
       </c>
       <c r="F1196" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1196" t="n">
         <v>7</v>
       </c>
-      <c r="G1196" t="n">
-        <v>3</v>
-      </c>
       <c r="H1196" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>68000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="E1197" t="n">
-        <v>1050</v>
+        <v>351</v>
       </c>
       <c r="F1197" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1197" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1197" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>34500000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>500</v>
+        <v>182</v>
       </c>
       <c r="E1198" t="n">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="F1198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1198" t="n">
         <v>3</v>
       </c>
       <c r="H1198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>22000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>182</v>
+        <v>360</v>
       </c>
       <c r="E1199" t="n">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="F1199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>15000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E1200" t="n">
-        <v>307</v>
+        <v>150</v>
       </c>
       <c r="F1200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,23 +34048,23 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>4800000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1201" t="n">
-        <v>150</v>
+        <v>304</v>
       </c>
       <c r="F1201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1201" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1201" t="n">
         <v>2</v>
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>13500000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E1202" t="n">
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="F1202" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1202" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,26 +34104,26 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>14500000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="E1203" t="n">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="F1203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1203" t="n">
         <v>3</v>
       </c>
       <c r="H1203" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,23 +34132,23 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>1850000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="E1204" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F1204" t="n">
         <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1204" t="n">
         <v>1</v>
@@ -34160,23 +34160,23 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>3300000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>130</v>
+        <v>475</v>
       </c>
       <c r="E1205" t="n">
-        <v>88</v>
+        <v>475</v>
       </c>
       <c r="F1205" t="n">
         <v>4</v>
       </c>
       <c r="G1205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1205" t="n">
         <v>1</v>
@@ -34188,26 +34188,26 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>3350000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>475</v>
+        <v>3475</v>
       </c>
       <c r="E1206" t="n">
-        <v>475</v>
+        <v>3475</v>
       </c>
       <c r="F1206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1206" t="n">
         <v>3</v>
       </c>
       <c r="H1206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1207">
@@ -34216,26 +34216,26 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>45000000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>3475</v>
+        <v>4535</v>
       </c>
       <c r="E1207" t="n">
-        <v>3475</v>
+        <v>4535</v>
       </c>
       <c r="F1207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1207" t="n">
         <v>3</v>
       </c>
       <c r="H1207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1208">
@@ -34244,17 +34244,17 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>42500000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>4535</v>
+        <v>528</v>
       </c>
       <c r="E1208" t="n">
-        <v>4535</v>
+        <v>528</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
@@ -34272,20 +34272,20 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>7900000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>528</v>
+        <v>819</v>
       </c>
       <c r="E1209" t="n">
-        <v>528</v>
+        <v>819</v>
       </c>
       <c r="F1209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1209" t="n">
         <v>3</v>
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>13100000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="E1210" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="F1210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,26 +34328,26 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>7000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1211" t="n">
         <v>600</v>
       </c>
       <c r="E1211" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F1211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1211" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1212">
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>28000000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1212" t="n">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="F1212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1212" t="n">
         <v>5</v>
       </c>
       <c r="H1212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>15200000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="E1213" t="n">
-        <v>196</v>
+        <v>307</v>
       </c>
       <c r="F1213" t="n">
         <v>4</v>
       </c>
       <c r="G1213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,23 +34412,23 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>15000000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="E1214" t="n">
-        <v>307</v>
+        <v>200</v>
       </c>
       <c r="F1214" t="n">
         <v>4</v>
       </c>
       <c r="G1214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1214" t="n">
         <v>2</v>
@@ -34440,14 +34440,14 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>10100000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="E1215" t="n">
         <v>200</v>
@@ -34456,7 +34456,7 @@
         <v>4</v>
       </c>
       <c r="G1215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1215" t="n">
         <v>2</v>
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>9500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>436</v>
+        <v>340</v>
       </c>
       <c r="E1216" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F1216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1216" t="n">
         <v>4</v>
       </c>
       <c r="H1216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>15500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="E1217" t="n">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="F1217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1217" t="n">
         <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,23 +34524,23 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>8500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>262</v>
+        <v>700</v>
       </c>
       <c r="E1218" t="n">
-        <v>161</v>
+        <v>1150</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
       </c>
       <c r="G1218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1218" t="n">
         <v>2</v>
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="E1219" t="n">
-        <v>1150</v>
+        <v>198</v>
       </c>
       <c r="F1219" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>6500000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="E1220" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F1220" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1220" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>12900000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="E1221" t="n">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="F1221" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,23 +34636,23 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>6760000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1222" t="n">
+        <v>219</v>
+      </c>
+      <c r="E1222" t="n">
         <v>200</v>
       </c>
-      <c r="E1222" t="n">
-        <v>160</v>
-      </c>
       <c r="F1222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1222" t="n">
         <v>1</v>
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>9500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="E1223" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1223" t="n">
         <v>4</v>
       </c>
       <c r="G1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1223" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>55000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E1224" t="n">
-        <v>500</v>
+        <v>108</v>
       </c>
       <c r="F1224" t="n">
         <v>4</v>
       </c>
       <c r="G1224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1224" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>4900000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>225</v>
+        <v>800</v>
       </c>
       <c r="E1225" t="n">
-        <v>108</v>
+        <v>538</v>
       </c>
       <c r="F1225" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1225" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>34900000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1226" t="n">
-        <v>538</v>
+        <v>276</v>
       </c>
       <c r="F1226" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1226" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>10900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1227" t="n">
-        <v>276</v>
+        <v>630</v>
       </c>
       <c r="F1227" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1227" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1227" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>21000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1228" t="n">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="F1228" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1228" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1228" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>6500000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1229" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="F1229" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1229" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>31900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1230" t="n">
-        <v>350</v>
+        <v>1026</v>
       </c>
       <c r="F1230" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1230" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1230" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>90000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>800</v>
+        <v>882</v>
       </c>
       <c r="E1231" t="n">
-        <v>1026</v>
+        <v>1845</v>
       </c>
       <c r="F1231" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1231" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1231" t="n">
         <v>6</v>
-      </c>
-      <c r="H1231" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>71900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>882</v>
+        <v>1100</v>
       </c>
       <c r="E1232" t="n">
-        <v>1845</v>
+        <v>540</v>
       </c>
       <c r="F1232" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1232" t="n">
         <v>4</v>
       </c>
       <c r="H1232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>49000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>1100</v>
+        <v>470</v>
       </c>
       <c r="E1233" t="n">
-        <v>540</v>
+        <v>412</v>
       </c>
       <c r="F1233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1233" t="n">
         <v>4</v>
       </c>
       <c r="H1233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>17000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="E1234" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F1234" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1234" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1234" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,23 +35000,23 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>7890000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="E1235" t="n">
-        <v>404</v>
+        <v>1060</v>
       </c>
       <c r="F1235" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1235" t="n">
         <v>5</v>
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>29900000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="E1236" t="n">
-        <v>1060</v>
+        <v>1084</v>
       </c>
       <c r="F1236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1236" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>39800000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>500</v>
+        <v>1050</v>
       </c>
       <c r="E1237" t="n">
-        <v>1084</v>
+        <v>627</v>
       </c>
       <c r="F1237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1237" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>44000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>1050</v>
+        <v>325</v>
       </c>
       <c r="E1238" t="n">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="F1238" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1238" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1238" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>12900000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1239" t="n">
-        <v>696</v>
+        <v>187</v>
       </c>
       <c r="F1239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1239" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1239" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>4690000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1240" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F1240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1240" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>8990000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E1241" t="n">
-        <v>208</v>
+        <v>854</v>
       </c>
       <c r="F1241" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1241" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1241" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>22000000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="E1242" t="n">
-        <v>854</v>
+        <v>500</v>
       </c>
       <c r="F1242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1242" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>14700000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="E1243" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F1243" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1243" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1243" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>62000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="E1244" t="n">
-        <v>1000</v>
+        <v>692</v>
       </c>
       <c r="F1244" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1244" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1244" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>13800000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="E1245" t="n">
-        <v>692</v>
+        <v>1165</v>
       </c>
       <c r="F1245" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1245" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1245" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>53500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="E1246" t="n">
-        <v>1165</v>
+        <v>404</v>
       </c>
       <c r="F1246" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1246" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1246" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>7800000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1247" t="n">
-        <v>404</v>
+        <v>120</v>
       </c>
       <c r="F1247" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1247" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1247" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>7090000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1248" t="n">
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="F1248" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1248" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>7200000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1249" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="F1249" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1249" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1249" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>24900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1250" t="n">
-        <v>331</v>
+        <v>1000</v>
       </c>
       <c r="F1250" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1250" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1250" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>55000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1251" t="n">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="F1251" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1251" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H1251" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>15000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="E1252" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="F1252" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1252" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H1252" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>38000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1253" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="F1253" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1253" t="n">
         <v>52</v>
       </c>
-      <c r="G1253" t="n">
-        <v>51</v>
-      </c>
       <c r="H1253" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>1600</v>
+        <v>250</v>
       </c>
       <c r="E1254" t="n">
-        <v>1800</v>
+        <v>140</v>
       </c>
       <c r="F1254" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1254" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H1254" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>2600000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>60</v>
+        <v>760</v>
       </c>
       <c r="E1255" t="n">
-        <v>60</v>
+        <v>517</v>
       </c>
       <c r="F1255" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1255" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1255" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>21500000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1256" t="n">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="F1256" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1256" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1256" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>6500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>250</v>
+        <v>1600</v>
       </c>
       <c r="E1257" t="n">
-        <v>140</v>
+        <v>1800</v>
       </c>
       <c r="F1257" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G1257" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H1257" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>38000000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="E1258" t="n">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="F1258" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="G1258" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1258" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>2830000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>60</v>
+        <v>882</v>
       </c>
       <c r="E1259" t="n">
-        <v>60</v>
+        <v>1845</v>
       </c>
       <c r="F1259" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1259" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H1259" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>31900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1260" t="n">
-        <v>350</v>
+        <v>1925</v>
       </c>
       <c r="F1260" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="G1260" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1260" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>55000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="E1261" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="F1261" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1261" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1261" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>2600000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>60</v>
+        <v>1100</v>
       </c>
       <c r="E1262" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="F1262" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G1262" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1262" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>34900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1263" t="n">
-        <v>538</v>
+        <v>1925</v>
       </c>
       <c r="F1263" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="G1263" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1263" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>71900000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>882</v>
+        <v>300</v>
       </c>
       <c r="E1264" t="n">
-        <v>1845</v>
+        <v>276</v>
       </c>
       <c r="F1264" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G1264" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H1264" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>42000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>850</v>
+        <v>325</v>
       </c>
       <c r="E1265" t="n">
-        <v>1925</v>
+        <v>696</v>
       </c>
       <c r="F1265" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1265" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1265" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,26 +35868,26 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>14000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="E1266" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="F1266" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1266" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1267">
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>49000000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>1100</v>
+        <v>149</v>
       </c>
       <c r="E1267" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="F1267" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1267" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1267" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,23 +35924,23 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>42000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>850</v>
+        <v>358</v>
       </c>
       <c r="E1268" t="n">
-        <v>1925</v>
+        <v>159</v>
       </c>
       <c r="F1268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1268" t="n">
         <v>12</v>
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>10900000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="E1269" t="n">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="F1269" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1269" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,1118 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
         </is>
       </c>
       <c r="C1270" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>77</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>1270</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>156</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>128</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1272" t="n">
+        <v>94</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1272" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1273" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>4650000000</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>118</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>7300000000</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>322</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>384</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1276" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>206</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1278" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>1440000000</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1280" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>2770000000</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>143</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>143</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>2550000000</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>258</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1285" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1286" t="n">
+        <v>549</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1286" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1287" t="n">
+        <v>201</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1287" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>23500000000</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1288" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>101</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1289" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1290" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>268</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>303</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1291" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>317</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1292" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>366</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1293" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>4700000000</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>152</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>182</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1294" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>189</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1295" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>403</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1296" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>4600000000</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>187</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>187</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1297" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>6100000000</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>155</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>68</v>
+      </c>
+      <c r="H1299" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>258</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1300" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>129</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1301" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1302" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>52500000000</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1303" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>404</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1304" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>582</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1305" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
         <v>12900000000</v>
       </c>
-      <c r="D1270" t="n">
-        <v>325</v>
-      </c>
-      <c r="E1270" t="n">
-        <v>696</v>
-      </c>
-      <c r="F1270" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1270" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1270" t="n">
-        <v>5</v>
+      <c r="D1306" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>209</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1306" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>110000000000</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>805</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1307" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>5400000000</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>201</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1308" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>4990000000</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>275</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>135</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1309" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1309"/>
+  <dimension ref="A1:H1344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32620,26 +32620,26 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>6900000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1150" t="n">
-        <v>375</v>
+        <v>650</v>
       </c>
       <c r="E1150" t="n">
-        <v>76</v>
+        <v>406</v>
       </c>
       <c r="F1150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1151">
@@ -32648,26 +32648,26 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Lingkungan Elit Dekat JIS Cilandak Barat</t>
+          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>35000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1151" t="n">
-        <v>650</v>
+        <v>274</v>
       </c>
       <c r="E1151" t="n">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="F1151" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1151" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1152">
@@ -32676,26 +32676,26 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Hunian Strategis di Area Bulungan Jakarta Selatan</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>30000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1152" t="n">
-        <v>274</v>
+        <v>1374</v>
       </c>
       <c r="E1152" t="n">
-        <v>448</v>
+        <v>1493</v>
       </c>
       <c r="F1152" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1152" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H1152" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1153">
@@ -32704,26 +32704,26 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara 16Kt Murah</t>
+          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>26000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1153" t="n">
-        <v>1374</v>
+        <v>467</v>
       </c>
       <c r="E1153" t="n">
-        <v>1493</v>
+        <v>899</v>
       </c>
       <c r="F1153" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G1153" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H1153" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1154">
@@ -32732,26 +32732,26 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Rumah Cipete 2 Lantai Dalam Private Compound (Total 3 Rumah) With One Gate System dan Kolam Renang</t>
+          <t>Rumah Mewah Baru di Jagakarsa</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>18000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1154" t="n">
-        <v>467</v>
+        <v>520</v>
       </c>
       <c r="E1154" t="n">
-        <v>899</v>
+        <v>720</v>
       </c>
       <c r="F1154" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1154" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1155">
@@ -32760,26 +32760,26 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Rumah Mewah Baru di Jagakarsa</t>
+          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>12500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1155" t="n">
-        <v>520</v>
+        <v>1200</v>
       </c>
       <c r="E1155" t="n">
-        <v>720</v>
+        <v>620</v>
       </c>
       <c r="F1155" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G1155" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H1155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1156">
@@ -32788,26 +32788,26 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>6900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1156" t="n">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="E1156" t="n">
-        <v>76</v>
+        <v>960</v>
       </c>
       <c r="F1156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1156" t="n">
         <v>4</v>
       </c>
       <c r="H1156" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1157">
@@ -32816,26 +32816,26 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>Dijual Murah Guest House Exclusive Khusus Expat di Kebayoran Baru. Good Invest. Dekat Senopati. Occupancy Bagus</t>
+          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>42000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1157" t="n">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="E1157" t="n">
-        <v>620</v>
+        <v>300</v>
       </c>
       <c r="F1157" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G1157" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H1157" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1158">
@@ -32844,26 +32844,26 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>21000000000</v>
+        <v>40500000000</v>
       </c>
       <c r="D1158" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="E1158" t="n">
-        <v>960</v>
+        <v>534</v>
       </c>
       <c r="F1158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1159">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Pondok Indah Luas 300m Hanya 13 M . Jalan Lebar Dan Tenang, Dalam Portal</t>
+          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>13000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1159" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="E1159" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="F1159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1160">
@@ -32900,17 +32900,17 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Terbaik Di Jl. Hang Tuah</t>
+          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>40500000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1160" t="n">
-        <v>350</v>
+        <v>128</v>
       </c>
       <c r="E1160" t="n">
-        <v>534</v>
+        <v>252</v>
       </c>
       <c r="F1160" t="n">
         <v>3</v>
@@ -32919,7 +32919,7 @@
         <v>3</v>
       </c>
       <c r="H1160" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1161">
@@ -32928,23 +32928,23 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Cilandak (Seberang Citos Area Jl. Intan) Luas 550M Rp.12 M</t>
+          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>12000000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1161" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="E1161" t="n">
-        <v>550</v>
+        <v>351</v>
       </c>
       <c r="F1161" t="n">
         <v>4</v>
       </c>
       <c r="G1161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1161" t="n">
         <v>2</v>
@@ -32956,26 +32956,26 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Private Pool Dalam Cluster di Dekat Stasiun MRT Lebak Bulus</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>6000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1162" t="n">
-        <v>128</v>
+        <v>366</v>
       </c>
       <c r="E1162" t="n">
-        <v>252</v>
+        <v>366</v>
       </c>
       <c r="F1162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1162" t="n">
         <v>3</v>
       </c>
       <c r="H1162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1163">
@@ -32984,26 +32984,26 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Nol Jalan Raya Suryo Senopati Jakarta Selatan, Cocok untuk Kantor/Resto</t>
+          <t>Brand New Modern American Classic House Pondok Indah</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>34500000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1163" t="n">
-        <v>280</v>
+        <v>750</v>
       </c>
       <c r="E1163" t="n">
-        <v>351</v>
+        <v>406</v>
       </c>
       <c r="F1163" t="n">
         <v>4</v>
       </c>
       <c r="G1163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1164">
@@ -33012,26 +33012,26 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>25000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1164" t="n">
-        <v>366</v>
+        <v>500</v>
       </c>
       <c r="E1164" t="n">
-        <v>366</v>
+        <v>248</v>
       </c>
       <c r="F1164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1164" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1165">
@@ -33040,26 +33040,26 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>Brand New Modern American Classic House Pondok Indah</t>
+          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>28500000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1165" t="n">
-        <v>750</v>
+        <v>183</v>
       </c>
       <c r="E1165" t="n">
-        <v>406</v>
+        <v>149</v>
       </c>
       <c r="F1165" t="n">
         <v>4</v>
       </c>
       <c r="G1165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1166">
@@ -33068,26 +33068,26 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Kebayoran Baru 3 Lt Private Lift di Jual Bu</t>
+          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>22500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D1166" t="n">
-        <v>500</v>
+        <v>72</v>
       </c>
       <c r="E1166" t="n">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="F1166" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1166" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1167">
@@ -33096,26 +33096,26 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Jakarta Selatan Tanah Luas Hargamurahshm</t>
+          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>7000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1167" t="n">
-        <v>183</v>
+        <v>430</v>
       </c>
       <c r="E1167" t="n">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="F1167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1167" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1168">
@@ -33124,26 +33124,26 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Rumah Huni 2 Lantai Lokasi Pasar Minggu</t>
+          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>1300000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1168" t="n">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="E1168" t="n">
-        <v>45</v>
+        <v>318</v>
       </c>
       <c r="F1168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1169">
@@ -33152,23 +33152,23 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Di Pondok Indah 3 Lantai Dekat Mall Tol Rumahsakit</t>
+          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>8000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1169" t="n">
-        <v>430</v>
+        <v>700</v>
       </c>
       <c r="E1169" t="n">
-        <v>250</v>
+        <v>353</v>
       </c>
       <c r="F1169" t="n">
         <v>5</v>
       </c>
       <c r="G1169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1169" t="n">
         <v>3</v>
@@ -33180,26 +33180,26 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Rumah Mewah Di Pondok Indah Jakartaselatan Di Jual Sangat Murah</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>5500000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1170" t="n">
-        <v>320</v>
+        <v>800</v>
       </c>
       <c r="E1170" t="n">
-        <v>318</v>
+        <v>1050</v>
       </c>
       <c r="F1170" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1170" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1171">
@@ -33208,26 +33208,26 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>6900000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1171" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1171" t="n">
-        <v>76</v>
+        <v>787</v>
       </c>
       <c r="F1171" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1171" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1171" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1172">
@@ -33236,26 +33236,26 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Alam Asri Rumah Luxury Cantik Dekat Mall Pondok Indah, Jakarta Selatan</t>
+          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>20000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1172" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="E1172" t="n">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="F1172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1173">
@@ -33264,26 +33264,26 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>23000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1173" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E1173" t="n">
-        <v>1050</v>
+        <v>127</v>
       </c>
       <c r="F1173" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1173" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1174">
@@ -33292,26 +33292,26 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Rumah di Bungur Kemang Utara Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>24000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1174" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="E1174" t="n">
-        <v>787</v>
+        <v>1070</v>
       </c>
       <c r="F1174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1174" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1175">
@@ -33320,11 +33320,11 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>6900000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1175" t="n">
         <v>375</v>
@@ -33333,13 +33333,13 @@
         <v>76</v>
       </c>
       <c r="F1175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1176">
@@ -33348,26 +33348,26 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>Pomentia Residence Full Furnished Murah Jagakarsa</t>
+          <t>Pondok Indah Harga di Bawah NJOP</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>2400000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1176" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E1176" t="n">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="F1176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1177">
@@ -33376,26 +33376,26 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Rumah Nempel Lebak Bulus Dalam Cluster Hanya 15.Menit ke MRT Rumah</t>
+          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>1750000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1177" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E1177" t="n">
-        <v>127</v>
+        <v>510</v>
       </c>
       <c r="F1177" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1177" t="n">
         <v>5</v>
       </c>
       <c r="H1177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1178">
@@ -33404,26 +33404,26 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>17000000000</v>
+        <v>998000000</v>
       </c>
       <c r="D1178" t="n">
-        <v>350</v>
+        <v>64</v>
       </c>
       <c r="E1178" t="n">
-        <v>1070</v>
+        <v>32</v>
       </c>
       <c r="F1178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1178" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179">
@@ -33432,23 +33432,23 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>7090000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1179" t="n">
-        <v>375</v>
+        <v>232</v>
       </c>
       <c r="E1179" t="n">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="F1179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1179" t="n">
         <v>1</v>
@@ -33460,23 +33460,23 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>Pondok Indah Harga di Bawah NJOP</t>
+          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>7500000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1180" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E1180" t="n">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="F1180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1180" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1180" t="n">
         <v>1</v>
@@ -33488,26 +33488,26 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Murah Cilandak</t>
+          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>7300000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1181" t="n">
-        <v>600</v>
+        <v>380</v>
       </c>
       <c r="E1181" t="n">
-        <v>510</v>
+        <v>196</v>
       </c>
       <c r="F1181" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G1181" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H1181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1182">
@@ -33516,23 +33516,23 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>Harga dibawah 1 M - Rumah BRANDNEW di Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>998000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1182" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E1182" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F1182" t="n">
         <v>2</v>
       </c>
       <c r="G1182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1182" t="n">
         <v>1</v>
@@ -33544,26 +33544,26 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati Dekat Sekali ke Scbd, Gunawarman, Pacific Place</t>
+          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>22000000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1183" t="n">
-        <v>232</v>
+        <v>1000</v>
       </c>
       <c r="E1183" t="n">
-        <v>284</v>
+        <v>675</v>
       </c>
       <c r="F1183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1183" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1184">
@@ -33572,26 +33572,26 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>Rumah Tebet Strategis SHM Hadap Barat</t>
+          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>6250000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1184" t="n">
-        <v>260</v>
+        <v>375</v>
       </c>
       <c r="E1184" t="n">
-        <v>172</v>
+        <v>534</v>
       </c>
       <c r="F1184" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1184" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1185">
@@ -33600,23 +33600,23 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>Dijual Kost Exlusive Tebet Cocok untuk Investasi Negotiable</t>
+          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>7200000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1185" t="n">
-        <v>380</v>
+        <v>928</v>
       </c>
       <c r="E1185" t="n">
-        <v>196</v>
+        <v>378</v>
       </c>
       <c r="F1185" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G1185" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H1185" t="n">
         <v>1</v>
@@ -33628,17 +33628,17 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>2600000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1186" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E1186" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F1186" t="n">
         <v>2</v>
@@ -33656,26 +33656,26 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Rumah Modern di Kebayoran Baru Row Jalan Lebar Dekat ke Senayan</t>
+          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>65000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1187" t="n">
-        <v>1000</v>
+        <v>1350</v>
       </c>
       <c r="E1187" t="n">
-        <v>675</v>
+        <v>863</v>
       </c>
       <c r="F1187" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1188">
@@ -33684,23 +33684,23 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Bagus 534M2 di Bukit Hijau Pondok Indah</t>
+          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>23000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1188" t="n">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="E1188" t="n">
-        <v>534</v>
+        <v>648</v>
       </c>
       <c r="F1188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1188" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1188" t="n">
         <v>2</v>
@@ -33712,23 +33712,23 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>Murah! Townhouse Cantik Suralaya Residences A4 di Daerah Elit Kemang</t>
+          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>15500000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1189" t="n">
-        <v>928</v>
+        <v>280</v>
       </c>
       <c r="E1189" t="n">
-        <v>378</v>
+        <v>120</v>
       </c>
       <c r="F1189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1189" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1189" t="n">
         <v>1</v>
@@ -33740,17 +33740,17 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>2830000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1190" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E1190" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="F1190" t="n">
         <v>2</v>
@@ -33768,26 +33768,26 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni Di Kebayoran</t>
+          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>38000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1191" t="n">
-        <v>1350</v>
+        <v>440</v>
       </c>
       <c r="E1191" t="n">
-        <v>863</v>
+        <v>200</v>
       </c>
       <c r="F1191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1191" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1192">
@@ -33796,26 +33796,26 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>Jarang Ada Rumah Bagus Kemang Bangka Tanah 648</t>
+          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>10000000000</v>
+        <v>68000000000</v>
       </c>
       <c r="D1192" t="n">
-        <v>355</v>
+        <v>1600</v>
       </c>
       <c r="E1192" t="n">
-        <v>648</v>
+        <v>1050</v>
       </c>
       <c r="F1192" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1192" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1192" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1193">
@@ -33824,23 +33824,23 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>Brand New House 120m2 Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>8800000000</v>
+        <v>34500000000</v>
       </c>
       <c r="D1193" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="E1193" t="n">
-        <v>120</v>
+        <v>351</v>
       </c>
       <c r="F1193" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1193" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1193" t="n">
         <v>1</v>
@@ -33852,26 +33852,26 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>2600000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1194" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="E1194" t="n">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="F1194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1195">
@@ -33880,26 +33880,26 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Langkah! Rumah Semi Furnish European Style Taman Palem Jakarta Barat</t>
+          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>9000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1195" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="E1195" t="n">
-        <v>200</v>
+        <v>307</v>
       </c>
       <c r="F1195" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1196">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1.050 M2 Pondok Indah Jakarta Selatan</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>68000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1196" t="n">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="E1196" t="n">
-        <v>1050</v>
+        <v>150</v>
       </c>
       <c r="F1196" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1196" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1196" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nol Jalan Raya Suryo Senopati Jakarta Selatan.cocok Untuk Tempat Usaha</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>34500000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1197" t="n">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="F1197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1197" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,17 +33964,17 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Dinual Rumah Pinggir Jalan Raya Petogogan Jaksel</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>22000000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="E1198" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="F1198" t="n">
         <v>3</v>
@@ -33983,7 +33983,7 @@
         <v>3</v>
       </c>
       <c r="H1198" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,26 +33992,26 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Mewah Brand New Modern Design Dalam Perumahan di Radio Dalam</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>15000000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>360</v>
+        <v>190</v>
       </c>
       <c r="E1199" t="n">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="F1199" t="n">
         <v>4</v>
       </c>
       <c r="G1199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1200">
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>4800000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="E1200" t="n">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="F1200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1200" t="n">
         <v>2</v>
       </c>
       <c r="H1200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,26 +34048,26 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>13500000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>600</v>
+        <v>475</v>
       </c>
       <c r="E1201" t="n">
-        <v>304</v>
+        <v>475</v>
       </c>
       <c r="F1201" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1201" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>14500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>300</v>
+        <v>3475</v>
       </c>
       <c r="E1202" t="n">
-        <v>240</v>
+        <v>3475</v>
       </c>
       <c r="F1202" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1202" t="n">
         <v>3</v>
       </c>
       <c r="H1202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,17 +34104,17 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>1850000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>190</v>
+        <v>4535</v>
       </c>
       <c r="E1203" t="n">
-        <v>73</v>
+        <v>4535</v>
       </c>
       <c r="F1203" t="n">
         <v>4</v>
@@ -34123,7 +34123,7 @@
         <v>3</v>
       </c>
       <c r="H1203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1204">
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>3300000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>130</v>
+        <v>528</v>
       </c>
       <c r="E1204" t="n">
-        <v>88</v>
+        <v>528</v>
       </c>
       <c r="F1204" t="n">
         <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,26 +34160,26 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>3350000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>475</v>
+        <v>819</v>
       </c>
       <c r="E1205" t="n">
-        <v>475</v>
+        <v>819</v>
       </c>
       <c r="F1205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1205" t="n">
         <v>3</v>
       </c>
       <c r="H1205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1206">
@@ -34192,19 +34192,19 @@
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>45000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>3475</v>
+        <v>600</v>
       </c>
       <c r="E1206" t="n">
-        <v>3475</v>
+        <v>600</v>
       </c>
       <c r="F1206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1206" t="n">
         <v>3</v>
@@ -34216,23 +34216,23 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>42500000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>4535</v>
+        <v>600</v>
       </c>
       <c r="E1207" t="n">
-        <v>4535</v>
+        <v>400</v>
       </c>
       <c r="F1207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1207" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1207" t="n">
         <v>2</v>
@@ -34244,26 +34244,26 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>7900000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>528</v>
+        <v>450</v>
       </c>
       <c r="E1208" t="n">
-        <v>528</v>
+        <v>196</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
       </c>
       <c r="G1208" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,23 +34272,23 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>13100000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>819</v>
+        <v>360</v>
       </c>
       <c r="E1209" t="n">
-        <v>819</v>
+        <v>307</v>
       </c>
       <c r="F1209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1209" t="n">
         <v>2</v>
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>7000000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1210" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F1210" t="n">
         <v>4</v>
       </c>
       <c r="G1210" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,23 +34328,23 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>28000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>600</v>
+        <v>436</v>
       </c>
       <c r="E1211" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F1211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1211" t="n">
         <v>2</v>
@@ -34356,23 +34356,23 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>15200000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="E1212" t="n">
-        <v>196</v>
+        <v>350</v>
       </c>
       <c r="F1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1212" t="n">
         <v>3</v>
@@ -34384,17 +34384,17 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>15000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>360</v>
+        <v>262</v>
       </c>
       <c r="E1213" t="n">
-        <v>307</v>
+        <v>161</v>
       </c>
       <c r="F1213" t="n">
         <v>4</v>
@@ -34412,23 +34412,23 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>10100000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E1214" t="n">
-        <v>200</v>
+        <v>1150</v>
       </c>
       <c r="F1214" t="n">
         <v>4</v>
       </c>
       <c r="G1214" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1214" t="n">
         <v>2</v>
@@ -34440,26 +34440,26 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>9500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>436</v>
+        <v>180</v>
       </c>
       <c r="E1215" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F1215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1216">
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>15500000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>340</v>
+        <v>450</v>
       </c>
       <c r="E1216" t="n">
-        <v>350</v>
+        <v>209</v>
       </c>
       <c r="F1216" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1216" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>8500000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="E1217" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F1217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1217" t="n">
         <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>55000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>700</v>
+        <v>219</v>
       </c>
       <c r="E1218" t="n">
-        <v>1150</v>
+        <v>200</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
       </c>
       <c r="G1218" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>6500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E1219" t="n">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="F1219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1219" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,23 +34580,23 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>12900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="E1220" t="n">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="F1220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1220" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1220" t="n">
         <v>2</v>
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>6760000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1221" t="n">
-        <v>160</v>
+        <v>538</v>
       </c>
       <c r="F1221" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1221" t="n">
         <v>4</v>
       </c>
       <c r="H1221" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>9500000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>219</v>
+        <v>300</v>
       </c>
       <c r="E1222" t="n">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="F1222" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1222" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>55000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1223" t="n">
-        <v>500</v>
+        <v>630</v>
       </c>
       <c r="F1223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,20 +34692,20 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>4900000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="E1224" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="F1224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1224" t="n">
         <v>3</v>
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>34900000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1225" t="n">
-        <v>538</v>
+        <v>350</v>
       </c>
       <c r="F1225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1225" t="n">
         <v>4</v>
       </c>
       <c r="H1225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>10900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1226" t="n">
-        <v>276</v>
+        <v>1026</v>
       </c>
       <c r="F1226" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1226" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1226" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>21000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>600</v>
+        <v>882</v>
       </c>
       <c r="E1227" t="n">
-        <v>630</v>
+        <v>1845</v>
       </c>
       <c r="F1227" t="n">
         <v>5</v>
       </c>
       <c r="G1227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1227" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,26 +34804,26 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>6500000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1228" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="F1228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1229">
@@ -34832,17 +34832,17 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>31900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="E1229" t="n">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="F1229" t="n">
         <v>5</v>
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>90000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1230" t="n">
-        <v>1026</v>
+        <v>404</v>
       </c>
       <c r="F1230" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1230" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1230" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>71900000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="E1231" t="n">
-        <v>1845</v>
+        <v>1060</v>
       </c>
       <c r="F1231" t="n">
         <v>5</v>
       </c>
       <c r="G1231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,17 +34916,17 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>49000000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="E1232" t="n">
-        <v>540</v>
+        <v>1084</v>
       </c>
       <c r="F1232" t="n">
         <v>4</v>
@@ -34935,7 +34935,7 @@
         <v>4</v>
       </c>
       <c r="H1232" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>17000000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>470</v>
+        <v>1050</v>
       </c>
       <c r="E1233" t="n">
-        <v>412</v>
+        <v>627</v>
       </c>
       <c r="F1233" t="n">
         <v>5</v>
       </c>
       <c r="G1233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1233" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>7890000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1234" t="n">
-        <v>404</v>
+        <v>696</v>
       </c>
       <c r="F1234" t="n">
         <v>3</v>
       </c>
       <c r="G1234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1234" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>29900000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>850</v>
+        <v>250</v>
       </c>
       <c r="E1235" t="n">
-        <v>1060</v>
+        <v>187</v>
       </c>
       <c r="F1235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1235" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>39800000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1236" t="n">
-        <v>1084</v>
+        <v>208</v>
       </c>
       <c r="F1236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1236" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>44000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="E1237" t="n">
-        <v>627</v>
+        <v>854</v>
       </c>
       <c r="F1237" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1237" t="n">
         <v>5</v>
       </c>
       <c r="H1237" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>12900000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="E1238" t="n">
-        <v>696</v>
+        <v>500</v>
       </c>
       <c r="F1238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1238" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>4690000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>250</v>
+        <v>880</v>
       </c>
       <c r="E1239" t="n">
-        <v>187</v>
+        <v>1000</v>
       </c>
       <c r="F1239" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1239" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1239" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,17 +35140,17 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>8990000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>300</v>
+        <v>407</v>
       </c>
       <c r="E1240" t="n">
-        <v>208</v>
+        <v>692</v>
       </c>
       <c r="F1240" t="n">
         <v>5</v>
@@ -35159,7 +35159,7 @@
         <v>3</v>
       </c>
       <c r="H1240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,17 +35168,17 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>22000000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>650</v>
+        <v>452</v>
       </c>
       <c r="E1241" t="n">
-        <v>854</v>
+        <v>1165</v>
       </c>
       <c r="F1241" t="n">
         <v>6</v>
@@ -35187,7 +35187,7 @@
         <v>5</v>
       </c>
       <c r="H1241" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>14700000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1242" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="F1242" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1242" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1242" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>62000000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>880</v>
+        <v>200</v>
       </c>
       <c r="E1243" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="F1243" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1243" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1243" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>13800000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>407</v>
+        <v>500</v>
       </c>
       <c r="E1244" t="n">
-        <v>692</v>
+        <v>331</v>
       </c>
       <c r="F1244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1244" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>53500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="E1245" t="n">
-        <v>1165</v>
+        <v>500</v>
       </c>
       <c r="F1245" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1245" t="n">
         <v>6</v>
-      </c>
-      <c r="G1245" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1245" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>7800000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1246" t="n">
-        <v>404</v>
+        <v>1000</v>
       </c>
       <c r="F1246" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1246" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1246" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>7200000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>200</v>
+        <v>850</v>
       </c>
       <c r="E1247" t="n">
-        <v>120</v>
+        <v>660</v>
       </c>
       <c r="F1247" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1247" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1247" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,23 +35364,23 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>24900000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="E1248" t="n">
-        <v>331</v>
+        <v>1800</v>
       </c>
       <c r="F1248" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1248" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1248" t="n">
         <v>6</v>
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>55000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1249" t="n">
-        <v>500</v>
+        <v>630</v>
       </c>
       <c r="F1249" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1249" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H1249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1250" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="F1250" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1250" t="n">
         <v>31</v>
       </c>
       <c r="H1250" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
         <v>38000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="E1251" t="n">
-        <v>660</v>
+        <v>517</v>
       </c>
       <c r="F1251" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1251" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="H1251" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>55000000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="E1252" t="n">
-        <v>1800</v>
+        <v>350</v>
       </c>
       <c r="F1252" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G1252" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H1252" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>21500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="E1253" t="n">
-        <v>630</v>
+        <v>1800</v>
       </c>
       <c r="F1253" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G1253" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H1253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>6500000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1254" t="n">
-        <v>140</v>
+        <v>538</v>
       </c>
       <c r="F1254" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G1254" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1254" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>38000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>760</v>
+        <v>882</v>
       </c>
       <c r="E1255" t="n">
-        <v>517</v>
+        <v>1845</v>
       </c>
       <c r="F1255" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1255" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H1255" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>31900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1256" t="n">
-        <v>350</v>
+        <v>1925</v>
       </c>
       <c r="F1256" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="G1256" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1256" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>55000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="E1257" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="F1257" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1257" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1257" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,20 +35644,20 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>34900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E1258" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F1258" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G1258" t="n">
         <v>41</v>
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>71900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="E1259" t="n">
-        <v>1845</v>
+        <v>1925</v>
       </c>
       <c r="F1259" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1259" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H1259" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>42000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E1260" t="n">
-        <v>1925</v>
+        <v>276</v>
       </c>
       <c r="F1260" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G1260" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1260" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>14000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="E1261" t="n">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F1261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1261" t="n">
         <v>3</v>
       </c>
       <c r="H1261" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>49000000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>1100</v>
+        <v>149</v>
       </c>
       <c r="E1262" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="F1262" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1262" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1262" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,23 +35784,23 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>42000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>850</v>
+        <v>358</v>
       </c>
       <c r="E1263" t="n">
-        <v>1925</v>
+        <v>159</v>
       </c>
       <c r="F1263" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1263" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1263" t="n">
         <v>12</v>
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>10900000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="E1264" t="n">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="F1264" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1264" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>12900000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="E1265" t="n">
-        <v>696</v>
+        <v>72</v>
       </c>
       <c r="F1265" t="n">
         <v>3</v>
       </c>
       <c r="G1265" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1265" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,23 +35868,23 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>7090000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="E1266" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="F1266" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1266" t="n">
         <v>1</v>
@@ -35896,23 +35896,23 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>3800000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E1267" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F1267" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1267" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1267" t="n">
         <v>2</v>
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
+          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>4200000000</v>
+        <v>4650000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>358</v>
+        <v>110</v>
       </c>
       <c r="E1268" t="n">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="F1268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1268" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1268" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
+          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>1400000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>92</v>
+        <v>400</v>
       </c>
       <c r="E1269" t="n">
-        <v>86</v>
+        <v>322</v>
       </c>
       <c r="F1269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1269" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>2100000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>77</v>
+        <v>850</v>
       </c>
       <c r="E1270" t="n">
-        <v>72</v>
+        <v>384</v>
       </c>
       <c r="F1270" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1270" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1270" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>4200000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>156</v>
+        <v>400</v>
       </c>
       <c r="E1271" t="n">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="F1271" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1271" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1271" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,26 +36036,26 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>1800000000</v>
+        <v>1440000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E1272" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F1272" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1273">
@@ -36064,23 +36064,23 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
         </is>
       </c>
       <c r="C1273" t="n">
         <v>2600000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="E1273" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F1273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1273" t="n">
         <v>1</v>
@@ -36092,20 +36092,20 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
+          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>4650000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="E1274" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F1274" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1274" t="n">
         <v>2</v>
@@ -36120,23 +36120,23 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
+          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>7300000000</v>
+        <v>2770000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>400</v>
+        <v>143</v>
       </c>
       <c r="E1275" t="n">
-        <v>322</v>
+        <v>143</v>
       </c>
       <c r="F1275" t="n">
         <v>5</v>
       </c>
       <c r="G1275" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1275" t="n">
         <v>1</v>
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>14000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>850</v>
+        <v>60</v>
       </c>
       <c r="E1276" t="n">
-        <v>384</v>
+        <v>258</v>
       </c>
       <c r="F1276" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1276" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1276" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>2830000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>60</v>
+        <v>850</v>
       </c>
       <c r="E1277" t="n">
-        <v>60</v>
+        <v>1925</v>
       </c>
       <c r="F1277" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1277" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H1277" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,23 +36204,23 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>7100000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1278" t="n">
-        <v>206</v>
+        <v>549</v>
       </c>
       <c r="F1278" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G1278" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H1278" t="n">
         <v>22</v>
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>1440000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E1279" t="n">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="F1279" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1279" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1279" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
+          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>2600000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="E1280" t="n">
-        <v>80</v>
+        <v>525</v>
       </c>
       <c r="F1280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1280" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>2600000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E1281" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="F1281" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1281" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>2600000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E1282" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="F1282" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1282" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H1282" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
+          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>2770000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>143</v>
+        <v>268</v>
       </c>
       <c r="E1283" t="n">
-        <v>143</v>
+        <v>303</v>
       </c>
       <c r="F1283" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1283" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
+          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>2550000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1284" t="n">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="F1284" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1284" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>40000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>850</v>
+        <v>366</v>
       </c>
       <c r="E1285" t="n">
-        <v>1925</v>
+        <v>366</v>
       </c>
       <c r="F1285" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1285" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1285" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
+          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>11000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="E1286" t="n">
-        <v>549</v>
+        <v>182</v>
       </c>
       <c r="F1286" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G1286" t="n">
         <v>21</v>
       </c>
       <c r="H1286" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>3900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="E1287" t="n">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F1287" t="n">
         <v>41</v>
       </c>
       <c r="G1287" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1287" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,17 +36484,17 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>23500000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1288" t="n">
         <v>450</v>
       </c>
       <c r="E1288" t="n">
-        <v>525</v>
+        <v>403</v>
       </c>
       <c r="F1288" t="n">
         <v>4</v>
@@ -36503,7 +36503,7 @@
         <v>4</v>
       </c>
       <c r="H1288" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,23 +36512,23 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
+          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>2400000000</v>
+        <v>4600000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="E1289" t="n">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="F1289" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1289" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1289" t="n">
         <v>2</v>
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>7800000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>400</v>
+        <v>155</v>
       </c>
       <c r="E1290" t="n">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="F1290" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G1290" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H1290" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
+          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>8500000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="E1291" t="n">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="F1291" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G1291" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="H1291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>11500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E1292" t="n">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="F1292" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1292" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1292" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>22500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>366</v>
+        <v>129</v>
       </c>
       <c r="E1293" t="n">
-        <v>366</v>
+        <v>100</v>
       </c>
       <c r="F1293" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1293" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1293" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>4700000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>152</v>
+        <v>500</v>
       </c>
       <c r="E1294" t="n">
-        <v>182</v>
+        <v>1554</v>
       </c>
       <c r="F1294" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="G1294" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H1294" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
+          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>4800000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="E1295" t="n">
-        <v>189</v>
+        <v>404</v>
       </c>
       <c r="F1295" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G1295" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1295" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,23 +36708,23 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>14000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1296" t="n">
-        <v>403</v>
+        <v>582</v>
       </c>
       <c r="F1296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1296" t="n">
         <v>42</v>
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>4600000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>187</v>
+        <v>450</v>
       </c>
       <c r="E1297" t="n">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="F1297" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1297" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1297" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
+          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>6100000000</v>
+        <v>110000000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>155</v>
+        <v>1000</v>
       </c>
       <c r="E1298" t="n">
-        <v>155</v>
+        <v>805</v>
       </c>
       <c r="F1298" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G1298" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H1298" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,26 +36792,26 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
+          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>3000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="E1299" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F1299" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="G1299" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="H1299" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1300">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>4800000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="E1300" t="n">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="F1300" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G1300" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>1700000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="E1301" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F1301" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1301" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1302">
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Dijual Rumah Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>52500000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1303" t="n">
-        <v>1554</v>
+        <v>133</v>
       </c>
       <c r="F1303" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G1303" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H1303" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
+          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>17000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="E1304" t="n">
-        <v>404</v>
+        <v>1000</v>
       </c>
       <c r="F1304" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1304" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1304" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,26 +36960,26 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>32000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>400</v>
+        <v>201</v>
       </c>
       <c r="E1305" t="n">
-        <v>582</v>
+        <v>140</v>
       </c>
       <c r="F1305" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1305" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H1305" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,23 +36988,23 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>12900000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="E1306" t="n">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="F1306" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1306" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1306" t="n">
         <v>22</v>
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
+          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>110000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1307" t="n">
         <v>1000</v>
       </c>
       <c r="E1307" t="n">
-        <v>805</v>
+        <v>607</v>
       </c>
       <c r="F1307" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1307" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="H1307" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>5400000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="E1308" t="n">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="F1308" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1308" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1308" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,1006 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
+          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>4990000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="E1309" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="F1309" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1309" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1309" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>16000000000</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>632</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1310" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>141</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>119</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1311" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1313" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1314" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1315" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1317" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>1317</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>65000000000</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>850</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1318" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>1318</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>135000000000</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>56</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1319" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>1319</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>15500000000</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>340</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>350</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1320" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>9500000000</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>779</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>262</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>161</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1322" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>1322</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>248</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1323" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1324" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>18500000000</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>503</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>421</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1325" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>310</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>260</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>1326</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Rumah Dijual Kemang Jaksel</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>288</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>598</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>1328</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>1329</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>1330</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>979000000</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>1331</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>1333</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>1334</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>12900000000</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>390</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>307</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>1335</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>330</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1336" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>5750000000</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>208</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1337" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1338" t="n">
+        <v>108</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1338" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>80</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1339" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>1339</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>110</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1340" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>829000000</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1341" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>1420000000</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1343" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>1343</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>53000000000</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>457</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>494</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1344"/>
+  <dimension ref="A1:H1367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33908,26 +33908,26 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>4800000000</v>
+        <v>14500000000</v>
       </c>
       <c r="D1196" t="n">
         <v>300</v>
       </c>
       <c r="E1196" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="F1196" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1196" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1197">
@@ -33936,26 +33936,26 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Rumah Tebet 2M-An Siap Huni</t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>13500000000</v>
+        <v>1850000000</v>
       </c>
       <c r="D1197" t="n">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="E1197" t="n">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="F1197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
@@ -33964,26 +33964,26 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Konsep Villa  Dalam Kawasan Elit, Nempel Scbd, Nempel Akses Jl. Senopati</t>
+          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>14500000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1198" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="E1198" t="n">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="F1198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1199">
@@ -33992,17 +33992,17 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>Rumah Tebet 2M-An Siap Huni</t>
+          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>1850000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1199" t="n">
-        <v>190</v>
+        <v>475</v>
       </c>
       <c r="E1199" t="n">
-        <v>73</v>
+        <v>475</v>
       </c>
       <c r="F1199" t="n">
         <v>4</v>
@@ -34020,26 +34020,26 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Jalan 2 Mobil Dekat Kokas, Soepomo, Abdullah Syafei</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>3300000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1200" t="n">
-        <v>130</v>
+        <v>3475</v>
       </c>
       <c r="E1200" t="n">
-        <v>88</v>
+        <v>3475</v>
       </c>
       <c r="F1200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1201">
@@ -34048,17 +34048,17 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Murah Lt 475 M2 di Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>3350000000</v>
+        <v>42500000000</v>
       </c>
       <c r="D1201" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="E1201" t="n">
-        <v>475</v>
+        <v>4535</v>
       </c>
       <c r="F1201" t="n">
         <v>4</v>
@@ -34067,7 +34067,7 @@
         <v>3</v>
       </c>
       <c r="H1201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1202">
@@ -34076,26 +34076,26 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>45000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1202" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="E1202" t="n">
-        <v>3475</v>
+        <v>528</v>
       </c>
       <c r="F1202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1202" t="n">
         <v>3</v>
       </c>
       <c r="H1202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1203">
@@ -34104,20 +34104,20 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Dijual Lelang Rumah Mewah Lt 4535 M2 di Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>42500000000</v>
+        <v>13100000000</v>
       </c>
       <c r="D1203" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="E1203" t="n">
-        <v>4535</v>
+        <v>819</v>
       </c>
       <c r="F1203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1203" t="n">
         <v>3</v>
@@ -34132,26 +34132,26 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi Strategis Lt 528 M2 di Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>7900000000</v>
+        <v>7000000000</v>
       </c>
       <c r="D1204" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="E1204" t="n">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="F1204" t="n">
         <v>4</v>
       </c>
       <c r="G1204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1205">
@@ -34160,23 +34160,23 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Murah di Cilandak Jakarta Selatan</t>
+          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>13100000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1205" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="E1205" t="n">
-        <v>819</v>
+        <v>400</v>
       </c>
       <c r="F1205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1205" t="n">
         <v>2</v>
@@ -34188,23 +34188,23 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Cilandak Jakarta Selatan</t>
+          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>7000000000</v>
+        <v>15200000000</v>
       </c>
       <c r="D1206" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1206" t="n">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="F1206" t="n">
         <v>4</v>
       </c>
       <c r="G1206" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1206" t="n">
         <v>3</v>
@@ -34216,23 +34216,23 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>Top Luxurious Listing! Luxury American Classic Kebayoran Baru</t>
+          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>28000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1207" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="E1207" t="n">
-        <v>400</v>
+        <v>307</v>
       </c>
       <c r="F1207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1207" t="n">
         <v>2</v>
@@ -34244,17 +34244,17 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Brawijaya Townhouse 200 Meter ke Kemang Village dan MRT, Kebayoran Baru, Jakarta Selatan</t>
+          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>15200000000</v>
+        <v>10100000000</v>
       </c>
       <c r="D1208" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1208" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F1208" t="n">
         <v>4</v>
@@ -34263,7 +34263,7 @@
         <v>5</v>
       </c>
       <c r="H1208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1209">
@@ -34272,17 +34272,17 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>Best Deal Luxurious Tropical House, Kebayoran Baru, Jakarta Selatan</t>
+          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>15000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1209" t="n">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="E1209" t="n">
-        <v>307</v>
+        <v>200</v>
       </c>
       <c r="F1209" t="n">
         <v>4</v>
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Panglima Polim 10 M Nego Good Deal. Kebayoran Baru. Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>10100000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="E1210" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F1210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,17 +34328,17 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>10 M Budget Luxury Interior Villa Home Kemang Jakarta Selatan</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>9500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>436</v>
+        <v>262</v>
       </c>
       <c r="E1211" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="F1211" t="n">
         <v>4</v>
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>15500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>340</v>
+        <v>700</v>
       </c>
       <c r="E1212" t="n">
-        <v>350</v>
+        <v>1150</v>
       </c>
       <c r="F1212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>8500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>262</v>
+        <v>180</v>
       </c>
       <c r="E1213" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="F1213" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1213" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,23 +34412,23 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>55000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="E1214" t="n">
-        <v>1150</v>
+        <v>209</v>
       </c>
       <c r="F1214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1214" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1214" t="n">
         <v>2</v>
@@ -34440,23 +34440,23 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>6500000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1215" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E1215" t="n">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="F1215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1215" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1215" t="n">
         <v>1</v>
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>12900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="E1216" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F1216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>6760000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1217" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="F1217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1217" t="n">
         <v>4</v>
       </c>
       <c r="H1217" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>9500000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E1218" t="n">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="F1218" t="n">
         <v>4</v>
       </c>
       <c r="G1218" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>55000000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E1219" t="n">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="F1219" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1219" t="n">
         <v>4</v>
       </c>
       <c r="H1219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>4900000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E1220" t="n">
-        <v>108</v>
+        <v>276</v>
       </c>
       <c r="F1220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1220" t="n">
         <v>3</v>
       </c>
       <c r="H1220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,23 +34608,23 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>34900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1221" t="n">
-        <v>538</v>
+        <v>630</v>
       </c>
       <c r="F1221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1221" t="n">
         <v>5</v>
@@ -34636,17 +34636,17 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>10900000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E1222" t="n">
-        <v>276</v>
+        <v>140</v>
       </c>
       <c r="F1222" t="n">
         <v>3</v>
@@ -34655,7 +34655,7 @@
         <v>3</v>
       </c>
       <c r="H1222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>21000000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1223" t="n">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="F1223" t="n">
         <v>5</v>
       </c>
       <c r="G1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>6500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1224" t="n">
-        <v>140</v>
+        <v>1026</v>
       </c>
       <c r="F1224" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1224" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1224" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,17 +34720,17 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>31900000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>400</v>
+        <v>882</v>
       </c>
       <c r="E1225" t="n">
-        <v>350</v>
+        <v>1845</v>
       </c>
       <c r="F1225" t="n">
         <v>5</v>
@@ -34739,7 +34739,7 @@
         <v>4</v>
       </c>
       <c r="H1225" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>90000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="E1226" t="n">
-        <v>1026</v>
+        <v>540</v>
       </c>
       <c r="F1226" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1226" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1226" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,17 +34776,17 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>71900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>882</v>
+        <v>470</v>
       </c>
       <c r="E1227" t="n">
-        <v>1845</v>
+        <v>412</v>
       </c>
       <c r="F1227" t="n">
         <v>5</v>
@@ -34795,7 +34795,7 @@
         <v>4</v>
       </c>
       <c r="H1227" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,23 +34804,23 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>49000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>1100</v>
+        <v>250</v>
       </c>
       <c r="E1228" t="n">
-        <v>540</v>
+        <v>404</v>
       </c>
       <c r="F1228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1228" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1228" t="n">
         <v>5</v>
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>17000000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>470</v>
+        <v>850</v>
       </c>
       <c r="E1229" t="n">
-        <v>412</v>
+        <v>1060</v>
       </c>
       <c r="F1229" t="n">
         <v>5</v>
       </c>
       <c r="G1229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>7890000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1230" t="n">
-        <v>404</v>
+        <v>1084</v>
       </c>
       <c r="F1230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1230" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1230" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,17 +34888,17 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>29900000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>850</v>
+        <v>1050</v>
       </c>
       <c r="E1231" t="n">
-        <v>1060</v>
+        <v>627</v>
       </c>
       <c r="F1231" t="n">
         <v>5</v>
@@ -34907,7 +34907,7 @@
         <v>5</v>
       </c>
       <c r="H1231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>39800000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1232" t="n">
-        <v>1084</v>
+        <v>696</v>
       </c>
       <c r="F1232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1232" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>44000000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>1050</v>
+        <v>250</v>
       </c>
       <c r="E1233" t="n">
-        <v>627</v>
+        <v>187</v>
       </c>
       <c r="F1233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1233" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>12900000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="E1234" t="n">
-        <v>696</v>
+        <v>208</v>
       </c>
       <c r="F1234" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1234" t="n">
         <v>3</v>
       </c>
       <c r="H1234" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>4690000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="E1235" t="n">
-        <v>187</v>
+        <v>854</v>
       </c>
       <c r="F1235" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,23 +35028,23 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>8990000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1236" t="n">
-        <v>208</v>
+        <v>500</v>
       </c>
       <c r="F1236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1236" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1236" t="n">
         <v>3</v>
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>22000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>650</v>
+        <v>880</v>
       </c>
       <c r="E1237" t="n">
-        <v>854</v>
+        <v>1000</v>
       </c>
       <c r="F1237" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1237" t="n">
         <v>6</v>
       </c>
-      <c r="G1237" t="n">
-        <v>5</v>
-      </c>
       <c r="H1237" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>14700000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="E1238" t="n">
-        <v>500</v>
+        <v>692</v>
       </c>
       <c r="F1238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>62000000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>880</v>
+        <v>452</v>
       </c>
       <c r="E1239" t="n">
-        <v>1000</v>
+        <v>1165</v>
       </c>
       <c r="F1239" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1239" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1239" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>13800000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>407</v>
+        <v>300</v>
       </c>
       <c r="E1240" t="n">
-        <v>692</v>
+        <v>404</v>
       </c>
       <c r="F1240" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>53500000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>452</v>
+        <v>200</v>
       </c>
       <c r="E1241" t="n">
-        <v>1165</v>
+        <v>120</v>
       </c>
       <c r="F1241" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G1241" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1241" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,26 +35196,26 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>7800000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1242" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1242" t="n">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="F1242" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1242" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1242" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1243">
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>7200000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1243" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="F1243" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1243" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1243" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>24900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1244" t="n">
-        <v>331</v>
+        <v>1000</v>
       </c>
       <c r="F1244" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1244" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1244" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>55000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1245" t="n">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="F1245" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1245" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H1245" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>15000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="E1246" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="F1246" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1246" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H1246" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>38000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1247" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="F1247" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1247" t="n">
         <v>52</v>
       </c>
-      <c r="G1247" t="n">
-        <v>51</v>
-      </c>
       <c r="H1247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>1600</v>
+        <v>250</v>
       </c>
       <c r="E1248" t="n">
-        <v>1800</v>
+        <v>140</v>
       </c>
       <c r="F1248" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G1248" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H1248" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>21500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>600</v>
+        <v>760</v>
       </c>
       <c r="E1249" t="n">
-        <v>630</v>
+        <v>517</v>
       </c>
       <c r="F1249" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1249" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H1249" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>6500000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1250" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="F1250" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1250" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1250" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>38000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>760</v>
+        <v>1600</v>
       </c>
       <c r="E1251" t="n">
-        <v>517</v>
+        <v>1800</v>
       </c>
       <c r="F1251" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1251" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1251" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>31900000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1252" t="n">
-        <v>350</v>
+        <v>538</v>
       </c>
       <c r="F1252" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G1252" t="n">
         <v>41</v>
       </c>
       <c r="H1252" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,23 +35504,23 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>55000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>1600</v>
+        <v>882</v>
       </c>
       <c r="E1253" t="n">
-        <v>1800</v>
+        <v>1845</v>
       </c>
       <c r="F1253" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1253" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H1253" t="n">
         <v>6</v>
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>34900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1254" t="n">
-        <v>538</v>
+        <v>1925</v>
       </c>
       <c r="F1254" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="G1254" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1254" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>71900000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>882</v>
+        <v>400</v>
       </c>
       <c r="E1255" t="n">
-        <v>1845</v>
+        <v>700</v>
       </c>
       <c r="F1255" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1255" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>42000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="E1256" t="n">
-        <v>1925</v>
+        <v>540</v>
       </c>
       <c r="F1256" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1256" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1256" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>14000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1257" t="n">
-        <v>700</v>
+        <v>1925</v>
       </c>
       <c r="F1257" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1257" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1257" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>49000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1258" t="n">
-        <v>540</v>
+        <v>276</v>
       </c>
       <c r="F1258" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1258" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1258" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>42000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>850</v>
+        <v>325</v>
       </c>
       <c r="E1259" t="n">
-        <v>1925</v>
+        <v>696</v>
       </c>
       <c r="F1259" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1259" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1259" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,26 +35700,26 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>10900000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>300</v>
+        <v>149</v>
       </c>
       <c r="E1260" t="n">
-        <v>276</v>
+        <v>90</v>
       </c>
       <c r="F1260" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1260" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>12900000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="E1261" t="n">
-        <v>696</v>
+        <v>159</v>
       </c>
       <c r="F1261" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1261" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1261" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,23 +35756,23 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>3800000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="E1262" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F1262" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1262" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1262" t="n">
         <v>2</v>
@@ -35784,26 +35784,26 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
+          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>4200000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="E1263" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="F1263" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1263" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1263" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1264">
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
+          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>1400000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="E1264" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="F1264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>2100000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="E1265" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F1265" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,23 +35868,23 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
+          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>4200000000</v>
+        <v>4650000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E1266" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F1266" t="n">
         <v>4</v>
       </c>
       <c r="G1266" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1266" t="n">
         <v>1</v>
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>1800000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1267" t="n">
-        <v>94</v>
+        <v>322</v>
       </c>
       <c r="F1267" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>4650000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>110</v>
+        <v>850</v>
       </c>
       <c r="E1268" t="n">
-        <v>118</v>
+        <v>384</v>
       </c>
       <c r="F1268" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1268" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1268" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>7300000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1269" t="n">
         <v>400</v>
       </c>
       <c r="E1269" t="n">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="F1269" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1269" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,26 +35980,26 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>14000000000</v>
+        <v>1440000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>850</v>
+        <v>85</v>
       </c>
       <c r="E1270" t="n">
-        <v>384</v>
+        <v>95</v>
       </c>
       <c r="F1270" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1270" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1270" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1271">
@@ -36008,26 +36008,26 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>7100000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1271" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="E1271" t="n">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="F1271" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1271" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1271" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1272">
@@ -36036,20 +36036,20 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
+          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>1440000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E1272" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F1272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1272" t="n">
         <v>2</v>
@@ -36064,20 +36064,20 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
+          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>2600000000</v>
+        <v>2770000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E1273" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="F1273" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1273" t="n">
         <v>3</v>
@@ -36092,23 +36092,23 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
+          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>2600000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="E1274" t="n">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="F1274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1274" t="n">
         <v>1</v>
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
+          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>2770000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>143</v>
+        <v>850</v>
       </c>
       <c r="E1275" t="n">
-        <v>143</v>
+        <v>1925</v>
       </c>
       <c r="F1275" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1275" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1275" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
+          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>2550000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1276" t="n">
-        <v>258</v>
+        <v>549</v>
       </c>
       <c r="F1276" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1276" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H1276" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>40000000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="E1277" t="n">
-        <v>1925</v>
+        <v>525</v>
       </c>
       <c r="F1277" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1277" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1277" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
+          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>11000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E1278" t="n">
-        <v>549</v>
+        <v>101</v>
       </c>
       <c r="F1278" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G1278" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1278" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>3900000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E1279" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="F1279" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1279" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H1279" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>23500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="E1280" t="n">
-        <v>525</v>
+        <v>303</v>
       </c>
       <c r="F1280" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1280" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1280" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
+          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>2400000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E1281" t="n">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="F1281" t="n">
         <v>4</v>
       </c>
       <c r="G1281" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1281" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>7800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="E1282" t="n">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="F1282" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1282" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1282" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
+          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>8500000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="E1283" t="n">
-        <v>303</v>
+        <v>182</v>
       </c>
       <c r="F1283" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1283" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1283" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
+          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>11500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="E1284" t="n">
-        <v>317</v>
+        <v>189</v>
       </c>
       <c r="F1284" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1284" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1284" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>22500000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="E1285" t="n">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="F1285" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1285" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1285" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
+          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>4700000000</v>
+        <v>4600000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E1286" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F1286" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1286" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1286" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
+          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>4800000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="E1287" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="F1287" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1287" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
+          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>14000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="E1288" t="n">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="F1288" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="G1288" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="H1288" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,26 +36512,26 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>4600000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="E1289" t="n">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="F1289" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1289" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1289" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1290">
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>6100000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="E1290" t="n">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="F1290" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1290" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>3000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1291" t="n">
-        <v>200</v>
+        <v>1554</v>
       </c>
       <c r="F1291" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G1291" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H1291" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>4800000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>258</v>
+        <v>450</v>
       </c>
       <c r="E1292" t="n">
-        <v>108</v>
+        <v>404</v>
       </c>
       <c r="F1292" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="G1292" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1292" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>1700000000</v>
+        <v>110000000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>129</v>
+        <v>1000</v>
       </c>
       <c r="E1293" t="n">
-        <v>100</v>
+        <v>805</v>
       </c>
       <c r="F1293" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="G1293" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H1293" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,26 +36652,26 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>52500000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E1294" t="n">
-        <v>1554</v>
+        <v>201</v>
       </c>
       <c r="F1294" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G1294" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H1294" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1295">
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
+          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>17000000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>450</v>
+        <v>275</v>
       </c>
       <c r="E1295" t="n">
-        <v>404</v>
+        <v>135</v>
       </c>
       <c r="F1295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1295" t="n">
         <v>11</v>
-      </c>
-      <c r="G1295" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1295" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,26 +36708,26 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Dijual Rumah Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>32000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1296" t="n">
-        <v>582</v>
+        <v>133</v>
       </c>
       <c r="F1296" t="n">
         <v>5</v>
       </c>
       <c r="G1296" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1296" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1297">
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>12900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="E1297" t="n">
-        <v>209</v>
+        <v>1000</v>
       </c>
       <c r="F1297" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1297" t="n">
         <v>6</v>
       </c>
       <c r="H1297" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
+          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>110000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>1000</v>
+        <v>201</v>
       </c>
       <c r="E1298" t="n">
-        <v>805</v>
+        <v>140</v>
       </c>
       <c r="F1298" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="G1298" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H1298" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,26 +36792,26 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
+          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>5400000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>225</v>
+        <v>1000</v>
       </c>
       <c r="E1299" t="n">
-        <v>201</v>
+        <v>607</v>
       </c>
       <c r="F1299" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G1299" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="H1299" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1300">
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
+          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>4990000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="E1300" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="F1300" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1300" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1300" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>7090000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="E1301" t="n">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="F1301" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1301" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1302" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1302" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Dijual Rumah Akses 2 Mobil</t>
+          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>4200000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1303" t="n">
-        <v>133</v>
+        <v>1018</v>
       </c>
       <c r="F1303" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G1303" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="H1303" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
+          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>25000000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E1304" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="F1304" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1304" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1304" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,26 +36960,26 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>5200000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>201</v>
+        <v>800</v>
       </c>
       <c r="E1305" t="n">
-        <v>140</v>
+        <v>1980</v>
       </c>
       <c r="F1305" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="G1305" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H1305" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>6900000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E1306" t="n">
-        <v>76</v>
+        <v>779</v>
       </c>
       <c r="F1306" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1306" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1306" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>32000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>1000</v>
+        <v>262</v>
       </c>
       <c r="E1307" t="n">
-        <v>607</v>
+        <v>161</v>
       </c>
       <c r="F1307" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G1307" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="H1307" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>2600000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
       <c r="E1308" t="n">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="F1308" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G1308" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H1308" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,7 +37072,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1309" t="n">
@@ -37100,20 +37100,20 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>16000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>500</v>
+        <v>288</v>
       </c>
       <c r="E1310" t="n">
-        <v>632</v>
+        <v>598</v>
       </c>
       <c r="F1310" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G1310" t="n">
         <v>31</v>
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>4000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>141</v>
+        <v>600</v>
       </c>
       <c r="E1311" t="n">
-        <v>119</v>
+        <v>530</v>
       </c>
       <c r="F1311" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1311" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1311" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,26 +37156,26 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>2830000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="E1312" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="F1312" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1312" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="H1312" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1313">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1313" t="n">
@@ -37212,26 +37212,26 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>2000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="E1314" t="n">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="F1314" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1314" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1314" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,23 +37240,23 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>6900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1315" t="n">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="F1315" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1315" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1315" t="n">
         <v>22</v>
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>1900000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="E1316" t="n">
-        <v>60</v>
+        <v>394</v>
       </c>
       <c r="F1316" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G1316" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H1316" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,26 +37296,26 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>20000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E1317" t="n">
-        <v>1018</v>
+        <v>108</v>
       </c>
       <c r="F1317" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G1317" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="H1317" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1318">
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>65000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="E1318" t="n">
-        <v>850</v>
+        <v>40</v>
       </c>
       <c r="F1318" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1318" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>135000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="E1319" t="n">
-        <v>1980</v>
+        <v>110</v>
       </c>
       <c r="F1319" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G1319" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H1319" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,26 +37380,26 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>15500000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="E1320" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="F1320" t="n">
         <v>3</v>
       </c>
       <c r="G1320" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1321">
@@ -37408,23 +37408,23 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>9500000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="E1321" t="n">
-        <v>779</v>
+        <v>60</v>
       </c>
       <c r="F1321" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1321" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H1321" t="n">
         <v>1</v>
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>8500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>262</v>
+        <v>810</v>
       </c>
       <c r="E1322" t="n">
-        <v>161</v>
+        <v>370</v>
       </c>
       <c r="F1322" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1322" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1322" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>22500000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>560</v>
+        <v>457</v>
       </c>
       <c r="E1323" t="n">
-        <v>248</v>
+        <v>494</v>
       </c>
       <c r="F1323" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G1323" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1323" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>6900000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>375</v>
+        <v>60</v>
       </c>
       <c r="E1324" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F1324" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1324" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1324" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>18500000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>503</v>
+        <v>850</v>
       </c>
       <c r="E1325" t="n">
-        <v>421</v>
+        <v>1925</v>
       </c>
       <c r="F1325" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="G1325" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1325" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>11000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>310</v>
+        <v>1374</v>
       </c>
       <c r="E1326" t="n">
-        <v>260</v>
+        <v>1493</v>
       </c>
       <c r="F1326" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G1326" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="H1326" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>17000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="E1327" t="n">
-        <v>598</v>
+        <v>60</v>
       </c>
       <c r="F1327" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1327" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1327" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,26 +37604,26 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>8000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1328" t="n">
-        <v>165</v>
+        <v>632</v>
       </c>
       <c r="F1328" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1328" t="n">
         <v>31</v>
       </c>
       <c r="H1328" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1329">
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>15000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1329" t="n">
-        <v>530</v>
+        <v>76</v>
       </c>
       <c r="F1329" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1329" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,26 +37660,26 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>2000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E1330" t="n">
-        <v>60</v>
+        <v>582</v>
       </c>
       <c r="F1330" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1330" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1331">
@@ -37688,26 +37688,26 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>979000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="E1331" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="F1331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1331" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1332">
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>2000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="E1332" t="n">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="F1332" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1332" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1332" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>4900000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>360</v>
+        <v>503</v>
       </c>
       <c r="E1333" t="n">
-        <v>127</v>
+        <v>421</v>
       </c>
       <c r="F1333" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1333" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="H1333" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>6900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="E1334" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1334" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1334" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1334" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>12900000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="E1335" t="n">
-        <v>307</v>
+        <v>60</v>
       </c>
       <c r="F1335" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1335" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H1335" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>10000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1336" t="n">
         <v>250</v>
       </c>
       <c r="E1336" t="n">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="F1336" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1336" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1336" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,23 +37856,23 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>5750000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>208</v>
+        <v>600</v>
       </c>
       <c r="E1337" t="n">
-        <v>394</v>
+        <v>793</v>
       </c>
       <c r="F1337" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1337" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="H1337" t="n">
         <v>22</v>
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>3000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="E1338" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="F1338" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1338" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1338" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>850000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E1339" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F1339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>1900000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="E1340" t="n">
-        <v>110</v>
+        <v>696</v>
       </c>
       <c r="F1340" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1340" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1340" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>829000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="E1341" t="n">
-        <v>40</v>
+        <v>304</v>
       </c>
       <c r="F1341" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1341" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>1420000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="E1342" t="n">
-        <v>60</v>
+        <v>417</v>
       </c>
       <c r="F1342" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1342" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1342" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Jl. Kemang Dalam</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>48000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>810</v>
+        <v>450</v>
       </c>
       <c r="E1343" t="n">
-        <v>370</v>
+        <v>898</v>
       </c>
       <c r="F1343" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1343" t="n">
         <v>4</v>
       </c>
       <c r="H1343" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,670 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>53000000000</v>
+        <v>2250000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>457</v>
+        <v>125</v>
       </c>
       <c r="E1344" t="n">
-        <v>494</v>
+        <v>130</v>
       </c>
       <c r="F1344" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1344" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>1344</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>979000000</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>98</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>1345</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>144</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>232</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>1346</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>180</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>1347</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>1348</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>36</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>72</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>1349</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>90000000000</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>1038</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>1352</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>201</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>1353</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>6300000000</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>230</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1354" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>1354</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>15500000000</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>340</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>350</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1355" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>1355</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>135</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>1356</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>135000000000</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>53</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1357" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>1357</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1358" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>1358</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>4700000000</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>188</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1359" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>1359</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1360" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>1360</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1361" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>1361</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>57000000000</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>945</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1362" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>50000000000</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>865</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1363" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>1363</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>9100000000</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>438</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1364" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>1364</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1365" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>1365</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1366" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>1366</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1367"/>
+  <dimension ref="A1:H1392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37044,23 +37044,23 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>22500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>560</v>
+        <v>375</v>
       </c>
       <c r="E1308" t="n">
-        <v>248</v>
+        <v>76</v>
       </c>
       <c r="F1308" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G1308" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1308" t="n">
         <v>22</v>
@@ -37072,23 +37072,23 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>6900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>375</v>
+        <v>288</v>
       </c>
       <c r="E1309" t="n">
-        <v>76</v>
+        <v>598</v>
       </c>
       <c r="F1309" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1309" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1309" t="n">
         <v>22</v>
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>17000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>288</v>
+        <v>600</v>
       </c>
       <c r="E1310" t="n">
-        <v>598</v>
+        <v>530</v>
       </c>
       <c r="F1310" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1310" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1310" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>15000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="E1311" t="n">
-        <v>530</v>
+        <v>127</v>
       </c>
       <c r="F1311" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1311" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="H1311" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,26 +37156,26 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>4900000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="E1312" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="F1312" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1312" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1313">
@@ -37184,26 +37184,26 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>6900000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="E1313" t="n">
-        <v>76</v>
+        <v>307</v>
       </c>
       <c r="F1313" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1313" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1313" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1314">
@@ -37212,17 +37212,17 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>12900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="E1314" t="n">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="F1314" t="n">
         <v>41</v>
@@ -37231,7 +37231,7 @@
         <v>41</v>
       </c>
       <c r="H1314" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,23 +37240,23 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>10000000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="E1315" t="n">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="F1315" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1315" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1315" t="n">
         <v>22</v>
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>5750000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E1316" t="n">
-        <v>394</v>
+        <v>108</v>
       </c>
       <c r="F1316" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1316" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="H1316" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,23 +37296,23 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>3000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="E1317" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="F1317" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1317" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1317" t="n">
         <v>2</v>
@@ -37324,23 +37324,23 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>850000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="E1318" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F1318" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1318" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1318" t="n">
         <v>2</v>
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>1900000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="E1319" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F1319" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1319" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1319" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,17 +37380,17 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>829000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1320" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F1320" t="n">
         <v>3</v>
@@ -37408,26 +37408,26 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>1420000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>120</v>
+        <v>810</v>
       </c>
       <c r="E1321" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="F1321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1321" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1321" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1322">
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>48000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="E1322" t="n">
-        <v>370</v>
+        <v>1925</v>
       </c>
       <c r="F1322" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="G1322" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1322" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>53000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>457</v>
+        <v>1374</v>
       </c>
       <c r="E1323" t="n">
-        <v>494</v>
+        <v>1493</v>
       </c>
       <c r="F1323" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G1323" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H1323" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,26 +37492,26 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>7090000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1324" t="n">
-        <v>60</v>
+        <v>632</v>
       </c>
       <c r="F1324" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G1324" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1324" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1325">
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>42000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>850</v>
+        <v>375</v>
       </c>
       <c r="E1325" t="n">
-        <v>1925</v>
+        <v>76</v>
       </c>
       <c r="F1325" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="G1325" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1325" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>26000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>1374</v>
+        <v>400</v>
       </c>
       <c r="E1326" t="n">
-        <v>1493</v>
+        <v>582</v>
       </c>
       <c r="F1326" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1326" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H1326" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>2000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="E1327" t="n">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="F1327" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1327" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1327" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,23 +37604,23 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>16000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E1328" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="F1328" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G1328" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1328" t="n">
         <v>22</v>
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>6900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="E1329" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1329" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1329" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1329" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,26 +37660,26 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>32000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E1330" t="n">
-        <v>582</v>
+        <v>793</v>
       </c>
       <c r="F1330" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1330" t="n">
         <v>5</v>
       </c>
       <c r="H1330" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1331">
@@ -37688,26 +37688,26 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>2600000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="E1331" t="n">
-        <v>60</v>
+        <v>304</v>
       </c>
       <c r="F1331" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1331" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1332">
@@ -37716,23 +37716,23 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>12900000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E1332" t="n">
-        <v>209</v>
+        <v>417</v>
       </c>
       <c r="F1332" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G1332" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1332" t="n">
         <v>22</v>
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Jl. Kemang Dalam</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>18500000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>503</v>
+        <v>450</v>
       </c>
       <c r="E1333" t="n">
-        <v>421</v>
+        <v>898</v>
       </c>
       <c r="F1333" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1333" t="n">
         <v>4</v>
       </c>
       <c r="H1333" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,23 +37772,23 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>11000000000</v>
+        <v>2250000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>310</v>
+        <v>125</v>
       </c>
       <c r="E1334" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="F1334" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G1334" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="H1334" t="n">
         <v>1</v>
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>2830000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="E1335" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F1335" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1335" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,17 +37828,17 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>16500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="E1336" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
       <c r="F1336" t="n">
         <v>3</v>
@@ -37847,7 +37847,7 @@
         <v>3</v>
       </c>
       <c r="H1336" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>45000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="E1337" t="n">
-        <v>793</v>
+        <v>180</v>
       </c>
       <c r="F1337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1337" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>2000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>85</v>
+        <v>300</v>
       </c>
       <c r="E1338" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F1338" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1338" t="n">
         <v>2</v>
       </c>
       <c r="H1338" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>1900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E1339" t="n">
-        <v>60</v>
+        <v>1335</v>
       </c>
       <c r="F1339" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1339" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1339" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>11800000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="E1340" t="n">
-        <v>696</v>
+        <v>76</v>
       </c>
       <c r="F1340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1340" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>11500000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1341" t="n">
-        <v>304</v>
+        <v>201</v>
       </c>
       <c r="F1341" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1341" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1341" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>9000000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>350</v>
+        <v>230</v>
       </c>
       <c r="E1342" t="n">
-        <v>417</v>
+        <v>200</v>
       </c>
       <c r="F1342" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1342" t="n">
         <v>41</v>
       </c>
       <c r="H1342" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Jl. Kemang Dalam</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>26000000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="E1343" t="n">
-        <v>898</v>
+        <v>1980</v>
       </c>
       <c r="F1343" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G1343" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H1343" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,17 +38052,17 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>2250000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="E1344" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="F1344" t="n">
         <v>3</v>
@@ -38071,7 +38071,7 @@
         <v>2</v>
       </c>
       <c r="H1344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>979000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E1345" t="n">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F1345" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1345" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1345" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>1900000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>144</v>
+        <v>400</v>
       </c>
       <c r="E1346" t="n">
-        <v>232</v>
+        <v>945</v>
       </c>
       <c r="F1346" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1346" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1346" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>1200000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>110</v>
+        <v>438</v>
       </c>
       <c r="E1347" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F1347" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1347" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="H1347" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>4800000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1348" t="n">
-        <v>150</v>
+        <v>515</v>
       </c>
       <c r="F1348" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1348" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1348" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,17 +38192,17 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>750000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E1349" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F1349" t="n">
         <v>2</v>
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>27000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>800</v>
+        <v>225</v>
       </c>
       <c r="E1350" t="n">
-        <v>1335</v>
+        <v>312</v>
       </c>
       <c r="F1350" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1350" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H1350" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,23 +38248,23 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>6900000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>375</v>
+        <v>560</v>
       </c>
       <c r="E1351" t="n">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="F1351" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G1351" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1351" t="n">
         <v>22</v>
@@ -38276,26 +38276,26 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>90000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>1000</v>
+        <v>262</v>
       </c>
       <c r="E1352" t="n">
-        <v>1038</v>
+        <v>161</v>
       </c>
       <c r="F1352" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G1352" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H1352" t="n">
-        <v>412</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1353">
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>3900000000</v>
+        <v>599000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E1353" t="n">
-        <v>201</v>
+        <v>100</v>
       </c>
       <c r="F1353" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G1353" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1353" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>6300000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="E1354" t="n">
-        <v>200</v>
+        <v>448</v>
       </c>
       <c r="F1354" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G1354" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1354" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>15500000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>340</v>
+        <v>36</v>
       </c>
       <c r="E1355" t="n">
-        <v>350</v>
+        <v>72</v>
       </c>
       <c r="F1355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1355" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H1355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,23 +38388,23 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>2500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E1356" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F1356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1356" t="n">
         <v>1</v>
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>135000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="E1357" t="n">
-        <v>1980</v>
+        <v>60</v>
       </c>
       <c r="F1357" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="G1357" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H1357" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>8000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1358" t="n">
-        <v>200</v>
+        <v>865</v>
       </c>
       <c r="F1358" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1358" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1358" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>4700000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="E1359" t="n">
-        <v>200</v>
+        <v>284</v>
       </c>
       <c r="F1359" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1359" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1359" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>8000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E1360" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="F1360" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1360" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1360" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,7 +38528,7 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1361" t="n">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>57000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1362" t="n">
-        <v>945</v>
+        <v>1038</v>
       </c>
       <c r="F1362" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1362" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H1362" t="n">
-        <v>24</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,26 +38584,26 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>50000000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1363" t="n">
-        <v>865</v>
+        <v>696</v>
       </c>
       <c r="F1363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1363" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1364">
@@ -38612,26 +38612,26 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>9100000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>438</v>
+        <v>60</v>
       </c>
       <c r="E1364" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F1364" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1364" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H1364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1365">
@@ -38640,26 +38640,26 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>13500000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="E1365" t="n">
-        <v>515</v>
+        <v>350</v>
       </c>
       <c r="F1365" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1365" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1365" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1366">
@@ -38668,26 +38668,26 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>48000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>810</v>
+        <v>135</v>
       </c>
       <c r="E1366" t="n">
-        <v>370</v>
+        <v>30</v>
       </c>
       <c r="F1366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1366" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1366" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1367">
@@ -38696,26 +38696,726 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>9800000000</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>261</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1367" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>1367</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>466</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1368" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>1368</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>510</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>423</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1369" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>1369</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1370" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>1370</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1371" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>1371</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>27500000000</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1372" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
           <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
-      <c r="C1367" t="n">
+      <c r="C1373" t="n">
         <v>2000000000</v>
       </c>
-      <c r="D1367" t="n">
+      <c r="D1373" t="n">
         <v>85</v>
       </c>
-      <c r="E1367" t="n">
+      <c r="E1373" t="n">
         <v>60</v>
       </c>
-      <c r="F1367" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1367" t="n">
-        <v>2</v>
-      </c>
-      <c r="H1367" t="n">
+      <c r="F1373" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1373" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>550</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>450</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1374" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>9500000000</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>261</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1375" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>1375</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>53000000000</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>457</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>494</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1376" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>810</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1377" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Rumah.pdk.indah.siap.pakai</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>584</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>682</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1378" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>9200000000</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>241</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1379" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>858000000000</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>40</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1380" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>564</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>726</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1381" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>124</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>124</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1382" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>270</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1383" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>318</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>497</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1384" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>414</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1385" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1386" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1387" t="n">
+        <v>498</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>197</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>180</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>122</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>9800000000</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>1391</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>147</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>66</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1392"/>
+  <dimension ref="A1:H1415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34300,26 +34300,26 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>15500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1210" t="n">
-        <v>340</v>
+        <v>262</v>
       </c>
       <c r="E1210" t="n">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="F1210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1210" t="n">
         <v>4</v>
       </c>
       <c r="H1210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1211">
@@ -34328,23 +34328,23 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Hot On Sale! Bali Tropical Villahouse Kemang Jakarta Selatan</t>
+          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>8500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1211" t="n">
-        <v>262</v>
+        <v>700</v>
       </c>
       <c r="E1211" t="n">
-        <v>161</v>
+        <v>1150</v>
       </c>
       <c r="F1211" t="n">
         <v>4</v>
       </c>
       <c r="G1211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1211" t="n">
         <v>2</v>
@@ -34356,26 +34356,26 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Hot Sale! Luxury Mansion Estetik di Kemang-Ampera, Jakarta Selatan</t>
+          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1212" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="E1212" t="n">
-        <v>1150</v>
+        <v>198</v>
       </c>
       <c r="F1212" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1213">
@@ -34384,26 +34384,26 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Best Price Hitung Tanah Dekat NJOP, Pondok Indah, Jakarta Selatan</t>
+          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
         </is>
       </c>
       <c r="C1213" t="n">
-        <v>6500000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1213" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="E1213" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F1213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1213" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1214">
@@ -34412,26 +34412,26 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Last Unit! Tropical Estetik Villahouse Kemang Dalam</t>
+          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>12900000000</v>
+        <v>6760000000</v>
       </c>
       <c r="D1214" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="E1214" t="n">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="F1214" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1214" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1215">
@@ -34440,23 +34440,23 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Under 7 M Pondok Indah Best Price Siap Huni Jakarta Selatan</t>
+          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>6760000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1215" t="n">
+        <v>219</v>
+      </c>
+      <c r="E1215" t="n">
         <v>200</v>
       </c>
-      <c r="E1215" t="n">
-        <v>160</v>
-      </c>
       <c r="F1215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1215" t="n">
         <v>1</v>
@@ -34468,26 +34468,26 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Under 10 M Nego Dalam Komplek Pondok Indah. Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1216" t="n">
-        <v>9500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1216" t="n">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="E1216" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F1216" t="n">
         <v>4</v>
       </c>
       <c r="G1216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1216" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1217">
@@ -34496,26 +34496,26 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1217" t="n">
-        <v>55000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1217" t="n">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="E1217" t="n">
-        <v>500</v>
+        <v>108</v>
       </c>
       <c r="F1217" t="n">
         <v>4</v>
       </c>
       <c r="G1217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1217" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1218">
@@ -34524,26 +34524,26 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Harga Murah 4 M An Dekat Sekolah Internasional Dan Dekat Mampang Dan Kuningan Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1218" t="n">
-        <v>4900000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1218" t="n">
-        <v>225</v>
+        <v>800</v>
       </c>
       <c r="E1218" t="n">
-        <v>108</v>
+        <v>538</v>
       </c>
       <c r="F1218" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1218" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1219">
@@ -34552,26 +34552,26 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1219" t="n">
-        <v>34900000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1219" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1219" t="n">
-        <v>538</v>
+        <v>276</v>
       </c>
       <c r="F1219" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1219" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1219" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1220">
@@ -34580,26 +34580,26 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1220" t="n">
-        <v>10900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1220" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E1220" t="n">
-        <v>276</v>
+        <v>630</v>
       </c>
       <c r="F1220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1221">
@@ -34608,26 +34608,26 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri Dan Nyaman Tenang Dekat Sekolah Internasional Dan Dekat Kemang Raya Dan Dekat Kuningan Dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>21000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1221" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1221" t="n">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="F1221" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1221" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1221" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1222">
@@ -34636,26 +34636,26 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1222" t="n">
-        <v>6500000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1222" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1222" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="F1222" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1222" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1223">
@@ -34664,26 +34664,26 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>31900000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1223" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1223" t="n">
-        <v>350</v>
+        <v>1026</v>
       </c>
       <c r="F1223" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1223" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1223" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1224">
@@ -34692,26 +34692,26 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru, Jakarta Selatan, di Hook, bisa Parkir 14 Mobil</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>90000000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1224" t="n">
-        <v>800</v>
+        <v>882</v>
       </c>
       <c r="E1224" t="n">
-        <v>1026</v>
+        <v>1845</v>
       </c>
       <c r="F1224" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1224" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1224" t="n">
         <v>6</v>
-      </c>
-      <c r="H1224" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="1225">
@@ -34720,26 +34720,26 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>71900000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1225" t="n">
-        <v>882</v>
+        <v>1100</v>
       </c>
       <c r="E1225" t="n">
-        <v>1845</v>
+        <v>540</v>
       </c>
       <c r="F1225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1225" t="n">
         <v>4</v>
       </c>
       <c r="H1225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1226">
@@ -34748,26 +34748,26 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1226" t="n">
-        <v>49000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1226" t="n">
-        <v>1100</v>
+        <v>470</v>
       </c>
       <c r="E1226" t="n">
-        <v>540</v>
+        <v>412</v>
       </c>
       <c r="F1226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1226" t="n">
         <v>4</v>
       </c>
       <c r="H1226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1227">
@@ -34776,26 +34776,26 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Sekolah Internasional Dan Kuliner Dan Kemang Raya Harga Negosiable Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1227" t="n">
-        <v>17000000000</v>
+        <v>7890000000</v>
       </c>
       <c r="D1227" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="E1227" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F1227" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1228">
@@ -34804,23 +34804,23 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 7 M An Nego Harga NJOP Tanah Luas Dekat Sekolah Internasional dan Siap Huni Taman Luas Lokasi Strategis Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1228" t="n">
-        <v>7890000000</v>
+        <v>29900000000</v>
       </c>
       <c r="D1228" t="n">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="E1228" t="n">
-        <v>404</v>
+        <v>1060</v>
       </c>
       <c r="F1228" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1228" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1228" t="n">
         <v>5</v>
@@ -34832,26 +34832,26 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Harga Murah Tanah Luas Bisa Investasi Karna Saat Ini Ada Penyewa Dan Tinggal Lanjut Saja. Lokasi Strategis Dekat Sekolah New Zealand Dan Kuliner Dan Sekolah Internasional Harga Nego Sampai Deal Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>29900000000</v>
+        <v>39800000000</v>
       </c>
       <c r="D1229" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="E1229" t="n">
-        <v>1060</v>
+        <v>1084</v>
       </c>
       <c r="F1229" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1229" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1229" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1230">
@@ -34860,26 +34860,26 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Area Premium Zona Komersial Bisa Buat Kantor Atau Hotel Atau Kost Kostan Atau Klinik Atau Rumah Sakit Atau Bank Atau Ruko Atau Supermarket Atau Restoran Atau Cafe Atau Lainnya Lokasi Pinghir Jalan Raya Jl. Antasari Raya Dekat Kema</t>
+          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>39800000000</v>
+        <v>44000000000</v>
       </c>
       <c r="D1230" t="n">
-        <v>500</v>
+        <v>1050</v>
       </c>
       <c r="E1230" t="n">
-        <v>1084</v>
+        <v>627</v>
       </c>
       <c r="F1230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1230" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1231">
@@ -34888,26 +34888,26 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Mewah Dekat Sekolah Internasional Dan Dekat Mall Dan Bukit Golf Area Pondok Indah Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>44000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1231" t="n">
-        <v>1050</v>
+        <v>325</v>
       </c>
       <c r="E1231" t="n">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="F1231" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1231" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1232">
@@ -34916,26 +34916,26 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Tanah Luas Harga Murah 12 M An Nego bisa Buat Tempat Tinggal atau bisa Buat Usaha atau Lainnya Dekat Kebayoran Baru dan Kuningan Lokasi Strategis Area Bangka Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>12900000000</v>
+        <v>4690000000</v>
       </c>
       <c r="D1232" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="E1232" t="n">
-        <v>696</v>
+        <v>187</v>
       </c>
       <c r="F1232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1232" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1232" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1233">
@@ -34944,26 +34944,26 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Dijual Cepat Harga Murah Rumah Modern Cantik Asri Siap Huni Dalam Komplek Dekat MRT dan Fatmawati dan Cilandak Dekat MRT dan Tol Tb Simatupang dan Dekat Kuliner Rea Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>4690000000</v>
+        <v>8990000000</v>
       </c>
       <c r="D1233" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1233" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F1233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1234">
@@ -34972,26 +34972,26 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Bu Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Senayan dan Scbd dan Gunawarman Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>8990000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1234" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E1234" t="n">
-        <v>208</v>
+        <v>854</v>
       </c>
       <c r="F1234" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1234" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1234" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1235">
@@ -35000,26 +35000,26 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Murah Lokasi Strategis Area Kemang Dalam Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>22000000000</v>
+        <v>14700000000</v>
       </c>
       <c r="D1235" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="E1235" t="n">
-        <v>854</v>
+        <v>500</v>
       </c>
       <c r="F1235" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1235" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1236">
@@ -35028,26 +35028,26 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Dekat Sekolah Internasional dan MRT Cipete dan Kuliner Cipete Lokasi Dekat Kemang dan Kebayoran Baru Area Cipete Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>14700000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1236" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="E1236" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F1236" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1236" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1236" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1237">
@@ -35056,26 +35056,26 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Brand New Tropical Modern Kemang Lokasi Strategis Tanah Luas Parkiran Lebih Dari 10 Mobil Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat Kemang Raya Area Prime Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1237" t="n">
-        <v>62000000000</v>
+        <v>13800000000</v>
       </c>
       <c r="D1237" t="n">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="E1237" t="n">
-        <v>1000</v>
+        <v>692</v>
       </c>
       <c r="F1237" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1237" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1237" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1238">
@@ -35084,26 +35084,26 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Rumah Lama Tanah Luas Harga Murah Lokasi Strategis Dekat Sekolah Internasional Prancis dan Kuliner dan MRT Cipete dan Dekat Kebayoran Baru dan Dekat Pondok Indah dan Kemang Area Cipete Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>13800000000</v>
+        <v>53500000000</v>
       </c>
       <c r="D1238" t="n">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="E1238" t="n">
-        <v>692</v>
+        <v>1165</v>
       </c>
       <c r="F1238" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1238" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1238" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1239">
@@ -35112,26 +35112,26 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah atau Mini Building Bekas Kantor Lokasi Strategis Pinggir Jalan Raya bisa Bangun Sampai 8 Lantai bisa untuk Kantor atau Kost Kostan atau Ruang Usaha atau Klinik atau Restoran atau Cafe atau Ruang Usaha Komersil Dekat Darmawangsa Brawijay</t>
+          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>53500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1239" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="E1239" t="n">
-        <v>1165</v>
+        <v>404</v>
       </c>
       <c r="F1239" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1239" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1239" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1240">
@@ -35140,26 +35140,26 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga NJOP Bangunan 1 Lantai Harga 7 M An Dekat Sekolah Internasional dan Cocok untuk Investasi dan Tempat Tinggal Area Kemang Pejaten Barat Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>7800000000</v>
+        <v>7200000000</v>
       </c>
       <c r="D1240" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1240" t="n">
-        <v>404</v>
+        <v>120</v>
       </c>
       <c r="F1240" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1240" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1240" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1241">
@@ -35168,26 +35168,26 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah</t>
+          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>7200000000</v>
+        <v>24900000000</v>
       </c>
       <c r="D1241" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E1241" t="n">
-        <v>120</v>
+        <v>331</v>
       </c>
       <c r="F1241" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1241" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1241" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1242">
@@ -35196,23 +35196,23 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Lokasi Strategis Dekat Pakubuwono dan Senayan dan Senopati Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>24900000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1242" t="n">
         <v>500</v>
       </c>
       <c r="E1242" t="n">
-        <v>331</v>
+        <v>500</v>
       </c>
       <c r="F1242" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1242" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1242" t="n">
         <v>6</v>
@@ -35224,26 +35224,26 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Strategis Dekat Kemang Dan Mabes Dan Senopati Dan Sekolah Internasional Dan Dekat Area Darmawangsa Kebayoran Baru Jakarta Selatan</t>
+          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>55000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1243" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1243" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F1243" t="n">
         <v>41</v>
       </c>
       <c r="G1243" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H1243" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1244">
@@ -35252,26 +35252,26 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Regina Realty, Harga NJOP Dijual Rumah Pejaten Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>15000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1244" t="n">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="E1244" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="F1244" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1244" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="H1244" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1245">
@@ -35280,26 +35280,26 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Cantik Furnish Lokasi Strategis Dekat Senayan Dan Kuliner Dan Sekolah Internasional Dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>38000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1245" t="n">
-        <v>850</v>
+        <v>1600</v>
       </c>
       <c r="E1245" t="n">
-        <v>660</v>
+        <v>1800</v>
       </c>
       <c r="F1245" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1245" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="H1245" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1246">
@@ -35308,26 +35308,26 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP bisa Buat Gedung Kantor atau Hotel atau Kost atau Cafe atau Restoran atau Rumah atau Klinik atau Ruko atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Komersial Lokasi Hj Nawi Cipete Dekat Pondok Inda</t>
+          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>55000000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1246" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E1246" t="n">
-        <v>1800</v>
+        <v>630</v>
       </c>
       <c r="F1246" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1246" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H1246" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1247">
@@ -35336,26 +35336,26 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Siap Huni Lokasi Asri dan Nyaman Tenang Dekat Sekolah Internasional dan Dekat Kemang Raya dan Dekat Kuningan dan Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>21500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1247" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1247" t="n">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="F1247" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G1247" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1247" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1248">
@@ -35364,26 +35364,26 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cantik Modern Murah Dalam Townhouse Area Ampera Jeruk Purut Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>6500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1248" t="n">
-        <v>250</v>
+        <v>760</v>
       </c>
       <c r="E1248" t="n">
-        <v>140</v>
+        <v>517</v>
       </c>
       <c r="F1248" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1248" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1248" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1249">
@@ -35392,26 +35392,26 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Baru Semi Furnish Lokasi Strategis Dekat Sekolah Internasional dan Kuliner Area Kemang Dalam Kemang Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>38000000000</v>
+        <v>31900000000</v>
       </c>
       <c r="D1249" t="n">
-        <v>760</v>
+        <v>400</v>
       </c>
       <c r="E1249" t="n">
-        <v>517</v>
+        <v>350</v>
       </c>
       <c r="F1249" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G1249" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1249" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1250">
@@ -35420,26 +35420,26 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Modern Cantik Asri Siap Huni Lokasi Strategis Dekat Blok M dan Senopati dan Sudirman dan Kemang dan Wijaya Dekat Senopati Area dan Dekat Mabes Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
         </is>
       </c>
       <c r="C1250" t="n">
-        <v>31900000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1250" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="E1250" t="n">
-        <v>350</v>
+        <v>1800</v>
       </c>
       <c r="F1250" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1250" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H1250" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1251">
@@ -35448,26 +35448,26 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Harga Murah Dibawah NJOP Lokasi Pinggir Jalan Raya bisa untuk Gedung Kantor, Restoran, Cafe, Office, Clinic, Hotel atau Kost Kostan atau Dealer Mobil atau Motor atau Ruko atau Multifungsi Area Hj Nawi Cipete Dekat Pondok Indah Kebayoran</t>
+          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>55000000000</v>
+        <v>34900000000</v>
       </c>
       <c r="D1251" t="n">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E1251" t="n">
-        <v>1800</v>
+        <v>538</v>
       </c>
       <c r="F1251" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G1251" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H1251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1252">
@@ -35476,26 +35476,26 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Dekat Simprug dan Senayan dan Pakubuwono Lokasi Strategis Area Hanglekir Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>34900000000</v>
+        <v>71900000000</v>
       </c>
       <c r="D1252" t="n">
-        <v>800</v>
+        <v>882</v>
       </c>
       <c r="E1252" t="n">
-        <v>538</v>
+        <v>1845</v>
       </c>
       <c r="F1252" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G1252" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1252" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1253">
@@ -35504,26 +35504,26 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah Bangunan 1 Lantai Luas Tanah 1845 Meter Harga Murah Lokasi Prime Area Kuningan Dekat Menteng dan Sudirman dan Area Kedutaan dan Pejabat dan Pengusaha Dekat Mega Kuningan Area Kuningan Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>71900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1253" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="E1253" t="n">
-        <v>1845</v>
+        <v>1925</v>
       </c>
       <c r="F1253" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1253" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H1253" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1254">
@@ -35532,26 +35532,26 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat MRT dan Dekat Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>42000000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1254" t="n">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="E1254" t="n">
-        <v>1925</v>
+        <v>700</v>
       </c>
       <c r="F1254" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1254" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1254" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1255">
@@ -35560,26 +35560,26 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Harga Murah Tanah Luas Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>14000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1255" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E1255" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="F1255" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1255" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1255" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1256">
@@ -35588,26 +35588,26 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Siap Huni Private Lift Area Mentri Pejabat Ambbasy Dekat Perkantoran Dan Drkat Senayan Dan Dekat Gatot Subroto Dan Sudirman Dan Dekat Menteng Area Mentri Dan Pejabat Dan Perkantoran Dan Dekat Mall Dan Kedutaan Dan Area Mega Kuning</t>
+          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>49000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1256" t="n">
-        <v>1100</v>
+        <v>850</v>
       </c>
       <c r="E1256" t="n">
-        <v>540</v>
+        <v>1925</v>
       </c>
       <c r="F1256" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G1256" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1256" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1257">
@@ -35616,26 +35616,26 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Design Tropical Resort Parkir Banyak dan Tanah Luas Ada Paviliun Lokasi Strategis Dekat Sekolah Internasional dan Dekat Kuliner dan Dekat MRT dan Fatmawati dan Pondok Indah dan Kebayoran Baru Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>42000000000</v>
+        <v>10900000000</v>
       </c>
       <c r="D1257" t="n">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="E1257" t="n">
-        <v>1925</v>
+        <v>276</v>
       </c>
       <c r="F1257" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G1257" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H1257" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1258">
@@ -35644,26 +35644,26 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Dijual Rumah Murah Modern Mininalis Cantik Asri Siap Huni Lokasi Strategis Dekat Sekolah Internasional Dan Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>10900000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1258" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="E1258" t="n">
-        <v>276</v>
+        <v>696</v>
       </c>
       <c r="F1258" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1258" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1258" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1259">
@@ -35672,26 +35672,26 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Murah Harga 12 An Nego Antik Tanah Luas Lokasi Premium Dekat Kemang Raya dan Perbelanjaan dan Perkantoran dan Kuliner Area dan Dekat ke Kebayoran Baru Harga Murah Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>12900000000</v>
+        <v>3800000000</v>
       </c>
       <c r="D1259" t="n">
-        <v>325</v>
+        <v>149</v>
       </c>
       <c r="E1259" t="n">
-        <v>696</v>
+        <v>90</v>
       </c>
       <c r="F1259" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1259" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1259" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1260">
@@ -35700,17 +35700,17 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai Di Lebak Bulus Dekat Mrt Tol Clustermewah</t>
+          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>3800000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1260" t="n">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="E1260" t="n">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="F1260" t="n">
         <v>5</v>
@@ -35719,7 +35719,7 @@
         <v>5</v>
       </c>
       <c r="H1260" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1261">
@@ -35728,26 +35728,26 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Rumah Mewah 4lantaimurah Di Cilandak Pinggir Jalan Double Decker</t>
+          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>4200000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1261" t="n">
-        <v>358</v>
+        <v>92</v>
       </c>
       <c r="E1261" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="F1261" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1261" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1261" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1262">
@@ -35756,26 +35756,26 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah di Cinere Jaksel Dekat Tol Brigif Jaksel Murah</t>
+          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>1400000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1262" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E1262" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F1262" t="n">
         <v>3</v>
       </c>
       <c r="G1262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1263">
@@ -35784,23 +35784,23 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Rumah Strategis 8 Menit ke Aeon Mall Tanjung Barat Siap KPR J-39503</t>
+          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>2100000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1263" t="n">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="E1263" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="F1263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1263" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1263" t="n">
         <v>1</v>
@@ -35812,26 +35812,26 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Rumah LT 128 Terawat Dekat Cilandak Town Square Dibantu KPR J39849</t>
+          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>4200000000</v>
+        <v>1800000000</v>
       </c>
       <c r="D1264" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="E1264" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="F1264" t="n">
         <v>4</v>
       </c>
       <c r="G1264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1265">
@@ -35840,26 +35840,26 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnish di Jagakarsa Jakartaselatan Termurah</t>
+          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>1800000000</v>
+        <v>4650000000</v>
       </c>
       <c r="D1265" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E1265" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F1265" t="n">
         <v>4</v>
       </c>
       <c r="G1265" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1266">
@@ -35868,23 +35868,23 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>Rumah Minimalis 12 Menit ke Brawijaya Hospital Antasari Dibantu KPR J40053</t>
+          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>4650000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1266" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="E1266" t="n">
-        <v>118</v>
+        <v>322</v>
       </c>
       <c r="F1266" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1266" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1266" t="n">
         <v>1</v>
@@ -35896,26 +35896,26 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Rumah Luas Strategis 9 Menit ke Transmart Cilandak Dibantu KPR J41095</t>
+          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>7300000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1267" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="E1267" t="n">
-        <v>322</v>
+        <v>384</v>
       </c>
       <c r="F1267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1267" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1267" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1268">
@@ -35924,26 +35924,26 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Brand New House 3 Lantai Di Cipete Antasari Jakarta Selatan Murah</t>
+          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>14000000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1268" t="n">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="E1268" t="n">
-        <v>384</v>
+        <v>206</v>
       </c>
       <c r="F1268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1268" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H1268" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1269">
@@ -35952,26 +35952,26 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Ruma Mewah Murah di Cilandak Jakarta Selatan 3 Lantai Dkt Tol MRT</t>
+          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>7100000000</v>
+        <v>1440000000</v>
       </c>
       <c r="D1269" t="n">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="E1269" t="n">
-        <v>206</v>
+        <v>95</v>
       </c>
       <c r="F1269" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1269" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1269" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1270">
@@ -35980,23 +35980,23 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 7 Menit ke Stasiun MRT Haji Nawi SHM Dibantu KPR J-35907</t>
+          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>1440000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1270" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E1270" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F1270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1270" t="n">
         <v>1</v>
@@ -36008,7 +36008,7 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Menit ke Aeon Mall Tanjung Barat Dibantu KPR J-37805</t>
+          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
         </is>
       </c>
       <c r="C1271" t="n">
@@ -36024,7 +36024,7 @@
         <v>3</v>
       </c>
       <c r="G1271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1271" t="n">
         <v>1</v>
@@ -36036,23 +36036,23 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan 15 Mnt ke Aeon Mall Tanjung Barat Siap KPR J-39248</t>
+          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>2600000000</v>
+        <v>2770000000</v>
       </c>
       <c r="D1272" t="n">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E1272" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="F1272" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1272" t="n">
         <v>1</v>
@@ -36064,23 +36064,23 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Rumah 15 Mnt ke Aeon Mall Tanjung Barat SHM Luas Dibantu KPR J-32386</t>
+          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>2770000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1273" t="n">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="E1273" t="n">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="F1273" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1273" t="n">
         <v>1</v>
@@ -36092,26 +36092,26 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>Rumah Strategis Luas 16 Menit ke Gerbang Tol Cilandak Bebas Banjir J40229</t>
+          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>2550000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1274" t="n">
-        <v>60</v>
+        <v>850</v>
       </c>
       <c r="E1274" t="n">
-        <v>258</v>
+        <v>1925</v>
       </c>
       <c r="F1274" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1274" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H1274" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1275">
@@ -36120,26 +36120,26 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>Rumah Modern Dekat MRT Bergaya Resort di Cilandak Jakarta Selatan</t>
+          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>40000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1275" t="n">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="E1275" t="n">
-        <v>1925</v>
+        <v>549</v>
       </c>
       <c r="F1275" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G1275" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="H1275" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1276">
@@ -36148,26 +36148,26 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>Rumah Lama, Cocok untuk Usaha Kos Kosan karena Dekat Stasiun MRT Cipete</t>
+          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>11000000000</v>
+        <v>23500000000</v>
       </c>
       <c r="D1276" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="E1276" t="n">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="F1276" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1276" t="n">
         <v>21</v>
-      </c>
-      <c r="G1276" t="n">
-        <v>21</v>
-      </c>
-      <c r="H1276" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="1277">
@@ -36176,26 +36176,26 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Dharmawangsa, Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>23500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1277" t="n">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="E1277" t="n">
-        <v>525</v>
+        <v>101</v>
       </c>
       <c r="F1277" t="n">
         <v>4</v>
       </c>
       <c r="G1277" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1277" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1278">
@@ -36204,26 +36204,26 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Disaint Modern Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1278" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="E1278" t="n">
-        <v>101</v>
+        <v>300</v>
       </c>
       <c r="F1278" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1278" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H1278" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1279">
@@ -36232,26 +36232,26 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>7800000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1279" t="n">
-        <v>400</v>
+        <v>268</v>
       </c>
       <c r="E1279" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F1279" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1279" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H1279" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1280">
@@ -36260,26 +36260,26 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Cipete Dalam Kluster</t>
+          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>8500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1280" t="n">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="E1280" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F1280" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1280" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1280" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1281">
@@ -36288,26 +36288,26 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Very Good Deal. Hanya 1 Menit ke Mall Pim 2 [Jalan Lebar].</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>11500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1281" t="n">
-        <v>250</v>
+        <v>366</v>
       </c>
       <c r="E1281" t="n">
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="F1281" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1281" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1281" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1282">
@@ -36316,26 +36316,26 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>22500000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1282" t="n">
-        <v>366</v>
+        <v>152</v>
       </c>
       <c r="E1282" t="n">
-        <v>366</v>
+        <v>182</v>
       </c>
       <c r="F1282" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1282" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1282" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1283">
@@ -36344,26 +36344,26 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Rumah Kokoh 1,5 Lantai Terawat Bona Indah Lebak Bulus</t>
+          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>4700000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1283" t="n">
-        <v>152</v>
+        <v>320</v>
       </c>
       <c r="E1283" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F1283" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1283" t="n">
         <v>31</v>
       </c>
-      <c r="G1283" t="n">
-        <v>21</v>
-      </c>
       <c r="H1283" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1284">
@@ -36372,26 +36372,26 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dalam Townhouse Kemang</t>
+          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>4800000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1284" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="E1284" t="n">
-        <v>189</v>
+        <v>403</v>
       </c>
       <c r="F1284" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1284" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1284" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1285">
@@ -36400,26 +36400,26 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Harga Mendekati NJOP Pondok Indah</t>
+          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>14000000000</v>
+        <v>4600000000</v>
       </c>
       <c r="D1285" t="n">
-        <v>450</v>
+        <v>187</v>
       </c>
       <c r="E1285" t="n">
-        <v>403</v>
+        <v>187</v>
       </c>
       <c r="F1285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1285" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1286">
@@ -36428,26 +36428,26 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Good Price! Rumah Bagus Siap Huni Dalam Komplek Lebak Bulus</t>
+          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>4600000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1286" t="n">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="E1286" t="n">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="F1286" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1286" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1287">
@@ -36456,26 +36456,26 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Rumah Terawat Siap Huni SHM di Pondok Indah</t>
+          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>6100000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1287" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="E1287" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="F1287" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G1287" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="H1287" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1288">
@@ -36484,26 +36484,26 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Cluster Siaphuni di Cinere Private Pool Tanah Luas Harga Termurah</t>
+          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>3000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1288" t="n">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="E1288" t="n">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="F1288" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G1288" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="H1288" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1289">
@@ -36512,26 +36512,26 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Siap Huni 4 Lantai Private Lift 500 Meter Tol Andara Kawasa Artis</t>
+          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>4800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1289" t="n">
-        <v>258</v>
+        <v>129</v>
       </c>
       <c r="E1289" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F1289" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1289" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1289" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1290">
@@ -36540,26 +36540,26 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Rumah Modern di Lebak Bulus, Gratis Mobil Listrik &amp; Kitchen Set</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>1700000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1290" t="n">
-        <v>129</v>
+        <v>500</v>
       </c>
       <c r="E1290" t="n">
-        <v>100</v>
+        <v>1554</v>
       </c>
       <c r="F1290" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="G1290" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H1290" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1291">
@@ -36568,26 +36568,26 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>52500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1291" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E1291" t="n">
-        <v>1554</v>
+        <v>404</v>
       </c>
       <c r="F1291" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="G1291" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H1291" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1292">
@@ -36596,26 +36596,26 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Rumah Murah 11 Kmr di Setiabudi Timur I</t>
+          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>17000000000</v>
+        <v>110000000000</v>
       </c>
       <c r="D1292" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="E1292" t="n">
-        <v>404</v>
+        <v>805</v>
       </c>
       <c r="F1292" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G1292" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H1292" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1293">
@@ -36624,26 +36624,26 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Rumah Modern Brawijaya Lingkungan Prestige Aman Asri Siap Huni</t>
+          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>110000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1293" t="n">
-        <v>1000</v>
+        <v>225</v>
       </c>
       <c r="E1293" t="n">
-        <v>805</v>
+        <v>201</v>
       </c>
       <c r="F1293" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G1293" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H1293" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1294">
@@ -36652,20 +36652,20 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Dijual Rumah Nyaman di Daerah Tebet Jakarta Selatan</t>
+          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>5400000000</v>
+        <v>4990000000</v>
       </c>
       <c r="D1294" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="E1294" t="n">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="F1294" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1294" t="n">
         <v>3</v>
@@ -36680,26 +36680,26 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Siapa Cepat Dia Dapat 5.5m Turun Ke 4.99m</t>
+          <t>Dijual Rumah Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>4990000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1295" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="E1295" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F1295" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1295" t="n">
         <v>3</v>
       </c>
       <c r="H1295" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1296">
@@ -36708,26 +36708,26 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Dijual Rumah Akses 2 Mobil</t>
+          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>4200000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1296" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="E1296" t="n">
-        <v>133</v>
+        <v>1000</v>
       </c>
       <c r="F1296" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1296" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1296" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1297">
@@ -36736,26 +36736,26 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Dijual Rumah Furnished Akses Jl Lebar</t>
+          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>25000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1297" t="n">
-        <v>1200</v>
+        <v>201</v>
       </c>
       <c r="E1297" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="F1297" t="n">
         <v>12</v>
       </c>
       <c r="G1297" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H1297" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1298">
@@ -36764,26 +36764,26 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kost 12 Kmr Full 100%</t>
+          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>5200000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1298" t="n">
-        <v>201</v>
+        <v>1000</v>
       </c>
       <c r="E1298" t="n">
-        <v>140</v>
+        <v>607</v>
       </c>
       <c r="F1298" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G1298" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="H1298" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1299">
@@ -36792,23 +36792,23 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Harga Langka di Pondok Indah Rumah Mewah SHM</t>
+          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>32000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1299" t="n">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E1299" t="n">
-        <v>607</v>
+        <v>76</v>
       </c>
       <c r="F1299" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G1299" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H1299" t="n">
         <v>22</v>
@@ -36820,26 +36820,26 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru 4 Lantai di Jaksel Dekat SCBD</t>
+          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>6900000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1300" t="n">
-        <v>375</v>
+        <v>141</v>
       </c>
       <c r="E1300" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="F1300" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1300" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1300" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1301">
@@ -36848,26 +36848,26 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>Minimalis Modern Siap Huni Dekat Akses Tol Andara</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>4000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1301" t="n">
-        <v>141</v>
+        <v>375</v>
       </c>
       <c r="E1301" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="F1301" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1301" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1301" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1302">
@@ -36876,26 +36876,26 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di 10 menit ke SCBD Jaksel Jarang Ada</t>
+          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>6900000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1302" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="E1302" t="n">
-        <v>76</v>
+        <v>1018</v>
       </c>
       <c r="F1302" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="G1302" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="H1302" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1303">
@@ -36904,26 +36904,26 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Rumah Mewah dan Full Furnished, 5 Menit ke One Belpark Mall</t>
+          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>20000000000</v>
+        <v>65000000000</v>
       </c>
       <c r="D1303" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1303" t="n">
-        <v>1018</v>
+        <v>850</v>
       </c>
       <c r="F1303" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="G1303" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="H1303" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1304">
@@ -36932,26 +36932,26 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Rumah Hook di Karang Asem Kuningan, 300 Meter ke Jalan Prof Satrio</t>
+          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>65000000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1304" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1304" t="n">
-        <v>850</v>
+        <v>1980</v>
       </c>
       <c r="F1304" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="G1304" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H1304" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1305">
@@ -36960,26 +36960,26 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Rumah Hook Ada Lift dan Pool di Bukit Golf Pondok Indah</t>
+          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>135000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1305" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1305" t="n">
-        <v>1980</v>
+        <v>779</v>
       </c>
       <c r="F1305" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="G1305" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H1305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1306">
@@ -36988,26 +36988,26 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Dijual Cepat / Butuh Uang Cepat -Rumah Mewah (Di Hook) di Jakarta</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>9500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1306" t="n">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E1306" t="n">
-        <v>779</v>
+        <v>161</v>
       </c>
       <c r="F1306" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1306" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H1306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1307">
@@ -37016,26 +37016,26 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Tidak Banjir Jakarta Selatan</t>
+          <t>Rumah Dijual Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>8500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1307" t="n">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E1307" t="n">
-        <v>161</v>
+        <v>598</v>
       </c>
       <c r="F1307" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1307" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1307" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1308">
@@ -37044,26 +37044,26 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>6900000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1308" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1308" t="n">
-        <v>76</v>
+        <v>530</v>
       </c>
       <c r="F1308" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1308" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1308" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1309">
@@ -37072,26 +37072,26 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Rumah Dijual Kemang Jaksel</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>17000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1309" t="n">
-        <v>288</v>
+        <v>360</v>
       </c>
       <c r="E1309" t="n">
-        <v>598</v>
+        <v>127</v>
       </c>
       <c r="F1309" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1309" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="H1309" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1310">
@@ -37100,26 +37100,26 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Dijual Rumah Hitung Tanah di Tebet Timur, Selangkah Menuju Ecopark Tebet, Lokasi Strategis.</t>
+          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>15000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1310" t="n">
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="E1310" t="n">
-        <v>530</v>
+        <v>307</v>
       </c>
       <c r="F1310" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1310" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1310" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1311">
@@ -37128,26 +37128,26 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>4900000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1311" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="E1311" t="n">
-        <v>127</v>
+        <v>330</v>
       </c>
       <c r="F1311" t="n">
         <v>41</v>
       </c>
       <c r="G1311" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="H1311" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1312">
@@ -37156,23 +37156,23 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>6900000000</v>
+        <v>5750000000</v>
       </c>
       <c r="D1312" t="n">
-        <v>375</v>
+        <v>208</v>
       </c>
       <c r="E1312" t="n">
-        <v>76</v>
+        <v>394</v>
       </c>
       <c r="F1312" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1312" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1312" t="n">
         <v>22</v>
@@ -37184,26 +37184,26 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>For Sale Luxurious House Renovasi Modern Design . Dalam Komp Kebayoran Baru</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>12900000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1313" t="n">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="E1313" t="n">
-        <v>307</v>
+        <v>108</v>
       </c>
       <c r="F1313" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1313" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1313" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1314">
@@ -37212,26 +37212,26 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Komp Permata Hijau One Gate System Keb Lama Jakarta Selatan</t>
+          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>10000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1314" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E1314" t="n">
-        <v>330</v>
+        <v>40</v>
       </c>
       <c r="F1314" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1314" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1314" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1315">
@@ -37240,26 +37240,26 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Di Pejaten Barat Dalam Komplek</t>
+          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>5750000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1315" t="n">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E1315" t="n">
-        <v>394</v>
+        <v>110</v>
       </c>
       <c r="F1315" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G1315" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="H1315" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1316">
@@ -37268,26 +37268,26 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>3000000000</v>
+        <v>829000000</v>
       </c>
       <c r="D1316" t="n">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="E1316" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="F1316" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1316" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1317">
@@ -37296,26 +37296,26 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>800 Jtan Siaphuni 3 Lantai+ Roofto di Jalan Raya Utama Jagakarsa</t>
+          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>850000000</v>
+        <v>1420000000</v>
       </c>
       <c r="D1317" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E1317" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F1317" t="n">
         <v>3</v>
       </c>
       <c r="G1317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1318">
@@ -37324,26 +37324,26 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni Private Pool Dekat Tol Murah di Jagakarsa Jaksel</t>
+          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>1900000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1318" t="n">
-        <v>160</v>
+        <v>810</v>
       </c>
       <c r="E1318" t="n">
-        <v>110</v>
+        <v>370</v>
       </c>
       <c r="F1318" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1318" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1318" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1319">
@@ -37352,26 +37352,26 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Bata Merah di Jagakarsa Deket Tol Brigif</t>
+          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>829000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1319" t="n">
-        <v>90</v>
+        <v>850</v>
       </c>
       <c r="E1319" t="n">
-        <v>40</v>
+        <v>1925</v>
       </c>
       <c r="F1319" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G1319" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1319" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1320">
@@ -37380,26 +37380,26 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Wajib Survey!! Brand New KPR DP 0% Tanjung Barat</t>
+          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>1420000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1320" t="n">
-        <v>120</v>
+        <v>1374</v>
       </c>
       <c r="E1320" t="n">
-        <v>60</v>
+        <v>1493</v>
       </c>
       <c r="F1320" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G1320" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H1320" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1321">
@@ -37408,26 +37408,26 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Dijual rumah mewah dalam Gated community Kebayoran Baru Jakarta Selatan</t>
+          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>48000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1321" t="n">
-        <v>810</v>
+        <v>500</v>
       </c>
       <c r="E1321" t="n">
-        <v>370</v>
+        <v>632</v>
       </c>
       <c r="F1321" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1321" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1321" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1322">
@@ -37436,26 +37436,26 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Lokasi Cilandak Barat Jakarta Selatan</t>
+          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>42000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1322" t="n">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="E1322" t="n">
-        <v>1925</v>
+        <v>582</v>
       </c>
       <c r="F1322" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="G1322" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1322" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1323">
@@ -37464,26 +37464,26 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Dijual Via Lelang Rumah Mewah Raya Kemang Utara Jakarta</t>
+          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>26000000000</v>
+        <v>12900000000</v>
       </c>
       <c r="D1323" t="n">
-        <v>1374</v>
+        <v>450</v>
       </c>
       <c r="E1323" t="n">
-        <v>1493</v>
+        <v>209</v>
       </c>
       <c r="F1323" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1323" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H1323" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1324">
@@ -37492,23 +37492,23 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Harga Miring, Rumah Mewah, Bagus, Bersih, Terawat, 2 Lantai, Dalam Compound di Kemang, Cocok Utk Hunian Keluarga</t>
+          <t>Dijual Rumah Kencana Permai Semi Basement</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>16000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1324" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E1324" t="n">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="F1324" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G1324" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1324" t="n">
         <v>22</v>
@@ -37520,26 +37520,26 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>6900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1325" t="n">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="E1325" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1325" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G1325" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1325" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1326">
@@ -37548,26 +37548,26 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Pondok Indah Jakarta Selatan Swimming Pool</t>
+          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>32000000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1326" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E1326" t="n">
-        <v>582</v>
+        <v>793</v>
       </c>
       <c r="F1326" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1326" t="n">
         <v>5</v>
       </c>
       <c r="H1326" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1327">
@@ -37576,26 +37576,26 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Rumah Brand New Desain Industrial Modern 3 Lantai di Kemang Jaksel</t>
+          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>12900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1327" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="E1327" t="n">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="F1327" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1327" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1327" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1328">
@@ -37604,23 +37604,23 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kencana Permai Semi Basement</t>
+          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>18500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1328" t="n">
-        <v>503</v>
+        <v>350</v>
       </c>
       <c r="E1328" t="n">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F1328" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1328" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1328" t="n">
         <v>22</v>
@@ -37632,26 +37632,26 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Dijual Cepat Alam Segar Pondok Indah Harga Murah Semi Furnished Bagus, Rumah Pondok Indah</t>
+          <t>Jl. Kemang Dalam</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>11000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1329" t="n">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="E1329" t="n">
-        <v>260</v>
+        <v>898</v>
       </c>
       <c r="F1329" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1329" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1330">
@@ -37660,26 +37660,26 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>45000000000</v>
+        <v>2250000000</v>
       </c>
       <c r="D1330" t="n">
-        <v>600</v>
+        <v>125</v>
       </c>
       <c r="E1330" t="n">
-        <v>793</v>
+        <v>130</v>
       </c>
       <c r="F1330" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1330" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1330" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1331">
@@ -37688,26 +37688,26 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah - Townhouse Eksklusif Jl. Bangka, Jakarta Selatan</t>
+          <t>Super Murah!!! Selaras Resindence Pamulang</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>11500000000</v>
+        <v>979000000</v>
       </c>
       <c r="D1331" t="n">
-        <v>600</v>
+        <v>98</v>
       </c>
       <c r="E1331" t="n">
-        <v>304</v>
+        <v>98</v>
       </c>
       <c r="F1331" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1331" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1331" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1332">
@@ -37716,26 +37716,26 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah untuk Reatoran di Pejaten</t>
+          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>9000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1332" t="n">
-        <v>350</v>
+        <v>144</v>
       </c>
       <c r="E1332" t="n">
-        <v>417</v>
+        <v>232</v>
       </c>
       <c r="F1332" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1332" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1332" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1333">
@@ -37744,26 +37744,26 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Jl. Kemang Dalam</t>
+          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>26000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1333" t="n">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="E1333" t="n">
-        <v>898</v>
+        <v>180</v>
       </c>
       <c r="F1333" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1333" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1333" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1334">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Rumah di Pertanian Karang Tengah Lebak Bulus</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>2250000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="E1334" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F1334" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1334" t="n">
         <v>2</v>
       </c>
       <c r="H1334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Super Murah!!! Selaras Resindence Pamulang</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>979000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>98</v>
+        <v>800</v>
       </c>
       <c r="E1335" t="n">
-        <v>98</v>
+        <v>1335</v>
       </c>
       <c r="F1335" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1335" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1335" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,26 +37828,26 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Bu Sangat!! Rumah Hitung Tanah Karang Tengah Lebak Bulus</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>1900000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E1336" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="F1336" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1336" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1336" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Bu Cepat!! Rumah Dalam Komplek Dekat Uin</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>1200000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="E1337" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F1337" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1337" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1337" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>4800000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1338" t="n">
-        <v>150</v>
+        <v>1980</v>
       </c>
       <c r="F1338" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G1338" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H1338" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>27000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1339" t="n">
-        <v>1335</v>
+        <v>200</v>
       </c>
       <c r="F1339" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1339" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1339" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,17 +37940,17 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>6900000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>375</v>
+        <v>188</v>
       </c>
       <c r="E1340" t="n">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="F1340" t="n">
         <v>4</v>
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>3900000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E1341" t="n">
-        <v>201</v>
+        <v>945</v>
       </c>
       <c r="F1341" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1341" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1341" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,23 +37996,23 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>6300000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>230</v>
+        <v>438</v>
       </c>
       <c r="E1342" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1342" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1342" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1342" t="n">
         <v>2</v>
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>135000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1343" t="n">
-        <v>1980</v>
+        <v>515</v>
       </c>
       <c r="F1343" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G1343" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H1343" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>8000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E1344" t="n">
-        <v>200</v>
+        <v>312</v>
       </c>
       <c r="F1344" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1344" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H1344" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,23 +38080,23 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>4700000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>188</v>
+        <v>560</v>
       </c>
       <c r="E1345" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="F1345" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G1345" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H1345" t="n">
         <v>22</v>
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>57000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="E1346" t="n">
-        <v>945</v>
+        <v>161</v>
       </c>
       <c r="F1346" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1346" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1346" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>9100000000</v>
+        <v>599000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>438</v>
+        <v>140</v>
       </c>
       <c r="E1347" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F1347" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G1347" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>13500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="E1348" t="n">
-        <v>515</v>
+        <v>448</v>
       </c>
       <c r="F1348" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G1348" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1348" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,17 +38192,17 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>7090000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E1349" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F1349" t="n">
         <v>2</v>
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>16000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>225</v>
+        <v>500</v>
       </c>
       <c r="E1350" t="n">
-        <v>312</v>
+        <v>865</v>
       </c>
       <c r="F1350" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1350" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H1350" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>22500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="E1351" t="n">
-        <v>248</v>
+        <v>1038</v>
       </c>
       <c r="F1351" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G1351" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H1351" t="n">
-        <v>22</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,26 +38276,26 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>8500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="E1352" t="n">
-        <v>161</v>
+        <v>696</v>
       </c>
       <c r="F1352" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1352" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1352" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1353">
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>599000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="E1353" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F1353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1353" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>24000000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="E1354" t="n">
-        <v>448</v>
+        <v>261</v>
       </c>
       <c r="F1354" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1354" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1354" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>750000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>36</v>
+        <v>301</v>
       </c>
       <c r="E1355" t="n">
-        <v>72</v>
+        <v>466</v>
       </c>
       <c r="F1355" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1355" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1355" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>2600000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="E1356" t="n">
-        <v>60</v>
+        <v>423</v>
       </c>
       <c r="F1356" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1356" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1356" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>2000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="E1357" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="F1357" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1357" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1357" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>50000000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="E1358" t="n">
-        <v>865</v>
+        <v>1000</v>
       </c>
       <c r="F1358" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1358" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1358" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>16500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="E1359" t="n">
-        <v>284</v>
+        <v>450</v>
       </c>
       <c r="F1359" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1359" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>2830000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E1360" t="n">
-        <v>60</v>
+        <v>261</v>
       </c>
       <c r="F1360" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1360" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H1360" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,26 +38528,26 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>2000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>85</v>
+        <v>457</v>
       </c>
       <c r="E1361" t="n">
-        <v>60</v>
+        <v>494</v>
       </c>
       <c r="F1361" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1361" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1361" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1362">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>90000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>1000</v>
+        <v>810</v>
       </c>
       <c r="E1362" t="n">
-        <v>1038</v>
+        <v>370</v>
       </c>
       <c r="F1362" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1362" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H1362" t="n">
-        <v>412</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,26 +38584,26 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>11800000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>325</v>
+        <v>584</v>
       </c>
       <c r="E1363" t="n">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="F1363" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1363" t="n">
         <v>3</v>
       </c>
       <c r="H1363" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1364">
@@ -38612,26 +38612,26 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>1900000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E1364" t="n">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="F1364" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="G1364" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1364" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1365">
@@ -38640,26 +38640,26 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>15500000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="E1365" t="n">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="F1365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1365" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1366">
@@ -38668,26 +38668,26 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>2500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>135</v>
+        <v>564</v>
       </c>
       <c r="E1366" t="n">
-        <v>30</v>
+        <v>726</v>
       </c>
       <c r="F1366" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1366" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1366" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1367">
@@ -38696,26 +38696,26 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>9800000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1367" t="n">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="F1367" t="n">
         <v>4</v>
       </c>
       <c r="G1367" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1367" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1368">
@@ -38724,26 +38724,26 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>27000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>301</v>
+        <v>180</v>
       </c>
       <c r="E1368" t="n">
-        <v>466</v>
+        <v>122</v>
       </c>
       <c r="F1368" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G1368" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1368" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1369">
@@ -38752,26 +38752,26 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1369" t="n">
         <v>11500000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="E1369" t="n">
-        <v>423</v>
+        <v>570</v>
       </c>
       <c r="F1369" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1369" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1369" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1370">
@@ -38780,26 +38780,26 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>8000000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E1370" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="F1370" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1370" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1370" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1371">
@@ -38808,26 +38808,26 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>2000000000</v>
+        <v>7090000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E1371" t="n">
         <v>60</v>
       </c>
       <c r="F1371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1371" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1372">
@@ -38836,26 +38836,26 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>27500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>1200</v>
+        <v>560</v>
       </c>
       <c r="E1372" t="n">
-        <v>1000</v>
+        <v>248</v>
       </c>
       <c r="F1372" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1372" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1372" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1373">
@@ -38864,26 +38864,26 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>2000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>85</v>
+        <v>262</v>
       </c>
       <c r="E1373" t="n">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="F1373" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1373" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1373" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1374">
@@ -38892,26 +38892,26 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>25000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="E1374" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="F1374" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1374" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1375">
@@ -38920,26 +38920,26 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>9500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1375" t="n">
-        <v>261</v>
+        <v>1100</v>
       </c>
       <c r="F1375" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1375" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1375" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1376">
@@ -38948,26 +38948,26 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>53000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>457</v>
+        <v>800</v>
       </c>
       <c r="E1376" t="n">
-        <v>494</v>
+        <v>667</v>
       </c>
       <c r="F1376" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1376" t="n">
         <v>4</v>
       </c>
       <c r="H1376" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1377">
@@ -38976,26 +38976,26 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>48000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>810</v>
+        <v>301</v>
       </c>
       <c r="E1377" t="n">
-        <v>370</v>
+        <v>469</v>
       </c>
       <c r="F1377" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1377" t="n">
         <v>4</v>
       </c>
       <c r="H1377" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1378">
@@ -39004,26 +39004,26 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>28000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>584</v>
+        <v>60</v>
       </c>
       <c r="E1378" t="n">
-        <v>682</v>
+        <v>60</v>
       </c>
       <c r="F1378" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1378" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1379">
@@ -39032,26 +39032,26 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>9200000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>250</v>
+        <v>1050</v>
       </c>
       <c r="E1379" t="n">
-        <v>241</v>
+        <v>627</v>
       </c>
       <c r="F1379" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1379" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1379" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1380">
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>858000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="E1380" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F1380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,26 +39088,26 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>48000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>564</v>
+        <v>250</v>
       </c>
       <c r="E1381" t="n">
-        <v>726</v>
+        <v>284</v>
       </c>
       <c r="F1381" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1381" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1381" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1382">
@@ -39116,26 +39116,26 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>3500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="E1382" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="F1382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1383">
@@ -39144,26 +39144,26 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>5500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="E1383" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="F1383" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1383" t="n">
         <v>2</v>
       </c>
       <c r="H1383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1384">
@@ -39172,26 +39172,26 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>12500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>318</v>
+        <v>1104</v>
       </c>
       <c r="E1384" t="n">
-        <v>497</v>
+        <v>368</v>
       </c>
       <c r="F1384" t="n">
         <v>5</v>
       </c>
       <c r="G1384" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1384" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1385">
@@ -39200,17 +39200,17 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>9000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="E1385" t="n">
-        <v>414</v>
+        <v>76</v>
       </c>
       <c r="F1385" t="n">
         <v>4</v>
@@ -39219,7 +39219,7 @@
         <v>4</v>
       </c>
       <c r="H1385" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1386">
@@ -39228,26 +39228,26 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>25000000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="E1386" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="F1386" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1386" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1386" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1387">
@@ -39256,26 +39256,26 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>11000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="E1387" t="n">
-        <v>498</v>
+        <v>1038</v>
       </c>
       <c r="F1387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1387" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1387" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1388">
@@ -39284,26 +39284,26 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>6900000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="E1388" t="n">
-        <v>197</v>
+        <v>350</v>
       </c>
       <c r="F1388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1388" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1389">
@@ -39312,26 +39312,26 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>4800000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="E1389" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="F1389" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1389" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1390">
@@ -39340,26 +39340,26 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>11500000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="E1390" t="n">
-        <v>570</v>
+        <v>172</v>
       </c>
       <c r="F1390" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1390" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1390" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1391">
@@ -39368,26 +39368,26 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>9800000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>260</v>
+        <v>375</v>
       </c>
       <c r="E1391" t="n">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="F1391" t="n">
         <v>4</v>
       </c>
       <c r="G1391" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1391" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1392">
@@ -39396,25 +39396,669 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>46000000000</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>1392</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>175</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>1393</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>1396</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>4900000000</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>127</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>1398</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>37000000000</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>1399</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>18000000000</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1400" t="n">
+        <v>750</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>498</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>3500000000</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>124</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>124</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>270</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1404" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>12500000000</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>318</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>497</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>414</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1406" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1407" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
           <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
-      <c r="C1392" t="n">
+      <c r="C1408" t="n">
         <v>3500000000</v>
       </c>
-      <c r="D1392" t="n">
+      <c r="D1408" t="n">
         <v>147</v>
       </c>
-      <c r="E1392" t="n">
+      <c r="E1408" t="n">
         <v>66</v>
       </c>
-      <c r="F1392" t="n">
-        <v>3</v>
-      </c>
-      <c r="G1392" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1392" t="n">
+      <c r="F1408" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>6950000000</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>280</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>339</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1409" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>28700000000</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>479</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1410" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>16899999999</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>1412</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>17000000000</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>616</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>383</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1414" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>16500000000</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1415" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1415"/>
+  <dimension ref="A1:H1442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37772,26 +37772,26 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>4800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1334" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1334" t="n">
-        <v>150</v>
+        <v>1335</v>
       </c>
       <c r="F1334" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1334" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1334" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1335">
@@ -37800,26 +37800,26 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Flash Sale!! Rumah Vibes Villa Ubud di Ampera Full Furnished</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>27000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1335" t="n">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="E1335" t="n">
-        <v>1335</v>
+        <v>201</v>
       </c>
       <c r="F1335" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1335" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1335" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1336">
@@ -37828,17 +37828,17 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>3900000000</v>
+        <v>6300000000</v>
       </c>
       <c r="D1336" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="E1336" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F1336" t="n">
         <v>41</v>
@@ -37847,7 +37847,7 @@
         <v>41</v>
       </c>
       <c r="H1336" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1337">
@@ -37856,26 +37856,26 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Rumah Modern Industrialis Baru Dalam Komplek Segera Dibeli</t>
+          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>6300000000</v>
+        <v>135000000000</v>
       </c>
       <c r="D1337" t="n">
-        <v>230</v>
+        <v>800</v>
       </c>
       <c r="E1337" t="n">
-        <v>200</v>
+        <v>1980</v>
       </c>
       <c r="F1337" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G1337" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H1337" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1338">
@@ -37884,26 +37884,26 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Rare Hook Property | Private Lift &amp; Pool | Bukit Golf Pondok Indah | 1.980 M² | SHM</t>
+          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>135000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1338" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1338" t="n">
-        <v>1980</v>
+        <v>200</v>
       </c>
       <c r="F1338" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="G1338" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H1338" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1339">
@@ -37912,26 +37912,26 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Dijual.cepat Rumah Minimalis Siap Huni Cilandak Cipete Lokasi Strategis</t>
+          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>8000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1339" t="n">
-        <v>300</v>
+        <v>188</v>
       </c>
       <c r="E1339" t="n">
         <v>200</v>
       </c>
       <c r="F1339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1339" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1339" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1340">
@@ -37940,26 +37940,26 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Rumah Cluster di Lebak Bulus Siap Huni Nyaman Luas 200 Meter 1,5 Lantai Garasi 2 Mobil di Jakarta Selatan</t>
+          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>4700000000</v>
+        <v>57000000000</v>
       </c>
       <c r="D1340" t="n">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="E1340" t="n">
-        <v>200</v>
+        <v>945</v>
       </c>
       <c r="F1340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1340" t="n">
         <v>4</v>
       </c>
       <c r="H1340" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1341">
@@ -37968,26 +37968,26 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Komersil, Strategis Dekat MRT Dijual Harga NJOP</t>
+          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>57000000000</v>
+        <v>9100000000</v>
       </c>
       <c r="D1341" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="E1341" t="n">
-        <v>945</v>
+        <v>250</v>
       </c>
       <c r="F1341" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1341" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1341" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1342">
@@ -37996,26 +37996,26 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Gedung Hijau Pondok Indah, 150 m ke Jalan Raya Utama,</t>
+          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>9100000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1342" t="n">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="E1342" t="n">
-        <v>250</v>
+        <v>515</v>
       </c>
       <c r="F1342" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1342" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1342" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1343">
@@ -38024,26 +38024,26 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Sudah Lama Cari Rumah Tenang di Cilandak? Ini Dia - Brand New, 400M ke Fatmawati Raya, Taman, Pool-Ready, Dokumen On Hand</t>
+          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>13500000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1343" t="n">
-        <v>400</v>
+        <v>225</v>
       </c>
       <c r="E1343" t="n">
-        <v>515</v>
+        <v>312</v>
       </c>
       <c r="F1343" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1343" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1343" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1344">
@@ -38052,26 +38052,26 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>Prestigious Residence In Kebayoran Baru - South Jakarta</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>16000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1344" t="n">
-        <v>225</v>
+        <v>560</v>
       </c>
       <c r="E1344" t="n">
-        <v>312</v>
+        <v>248</v>
       </c>
       <c r="F1344" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G1344" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="H1344" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1345">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>22500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>560</v>
+        <v>262</v>
       </c>
       <c r="E1345" t="n">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="F1345" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G1345" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1345" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>8500000000</v>
+        <v>599000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="E1346" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="F1346" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G1346" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Termurah!! Rumah Furnished di Depok Cipayung Cuann</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>599000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>140</v>
+        <v>341</v>
       </c>
       <c r="E1347" t="n">
-        <v>100</v>
+        <v>448</v>
       </c>
       <c r="F1347" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1347" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1347" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>24000000000</v>
+        <v>750000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>341</v>
+        <v>36</v>
       </c>
       <c r="E1348" t="n">
-        <v>448</v>
+        <v>72</v>
       </c>
       <c r="F1348" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1348" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1348" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,26 +38192,26 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Murah!! Rumah Cluster Depok Beji bisa KPR</t>
+          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>750000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="E1349" t="n">
-        <v>72</v>
+        <v>865</v>
       </c>
       <c r="F1349" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1349" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1349" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1350">
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah Dibawah Harga NJOP di Mega Kuningan, Jakarta Selatan</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>50000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E1350" t="n">
-        <v>865</v>
+        <v>1038</v>
       </c>
       <c r="F1350" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1350" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H1350" t="n">
-        <v>43</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>90000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="E1351" t="n">
-        <v>1038</v>
+        <v>350</v>
       </c>
       <c r="F1351" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1351" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H1351" t="n">
-        <v>412</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,23 +38276,23 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>11800000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="E1352" t="n">
-        <v>696</v>
+        <v>261</v>
       </c>
       <c r="F1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1352" t="n">
         <v>24</v>
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>15500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="E1353" t="n">
-        <v>350</v>
+        <v>466</v>
       </c>
       <c r="F1353" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1353" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H1353" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,23 +38332,23 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical Villa Pejaten Barat, Jakarta Selatan</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>9800000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1354" t="n">
-        <v>261</v>
+        <v>165</v>
       </c>
       <c r="F1354" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1354" t="n">
         <v>24</v>
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>27000000000</v>
+        <v>27500000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>301</v>
+        <v>1200</v>
       </c>
       <c r="E1355" t="n">
-        <v>466</v>
+        <v>1000</v>
       </c>
       <c r="F1355" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1355" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1355" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>11500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="E1356" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="F1356" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1356" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>8000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1357" t="n">
-        <v>165</v>
+        <v>261</v>
       </c>
       <c r="F1357" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1357" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1357" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Mewah Terawat di Tebet 27,5 Milyar Nego</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>27500000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>1200</v>
+        <v>457</v>
       </c>
       <c r="E1358" t="n">
-        <v>1000</v>
+        <v>494</v>
       </c>
       <c r="F1358" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1358" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1358" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>25000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>550</v>
+        <v>810</v>
       </c>
       <c r="E1359" t="n">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="F1359" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1359" t="n">
         <v>4</v>
       </c>
       <c r="H1359" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>9500000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>300</v>
+        <v>584</v>
       </c>
       <c r="E1360" t="n">
-        <v>261</v>
+        <v>682</v>
       </c>
       <c r="F1360" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1360" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H1360" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,26 +38528,26 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>53000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>457</v>
+        <v>250</v>
       </c>
       <c r="E1361" t="n">
-        <v>494</v>
+        <v>241</v>
       </c>
       <c r="F1361" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1361" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1361" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1362">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>48000000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>810</v>
+        <v>40</v>
       </c>
       <c r="E1362" t="n">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="F1362" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1362" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1362" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,26 +38584,26 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>28000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="E1363" t="n">
-        <v>682</v>
+        <v>726</v>
       </c>
       <c r="F1363" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1363" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H1363" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1364">
@@ -38612,26 +38612,26 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>9200000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1364" t="n">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="F1364" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1364" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1364" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1365">
@@ -38640,26 +38640,26 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>858000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="E1365" t="n">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="F1365" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1365" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H1365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1366">
@@ -38668,26 +38668,26 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>48000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="E1366" t="n">
-        <v>726</v>
+        <v>570</v>
       </c>
       <c r="F1366" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G1366" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H1366" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1367">
@@ -38696,17 +38696,17 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>6900000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="E1367" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="F1367" t="n">
         <v>4</v>
@@ -38715,7 +38715,7 @@
         <v>3</v>
       </c>
       <c r="H1367" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1368">
@@ -38724,26 +38724,26 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>4800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>180</v>
+        <v>560</v>
       </c>
       <c r="E1368" t="n">
-        <v>122</v>
+        <v>248</v>
       </c>
       <c r="F1368" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1368" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1369">
@@ -38752,26 +38752,26 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>11500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="E1369" t="n">
-        <v>570</v>
+        <v>161</v>
       </c>
       <c r="F1369" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1369" t="n">
         <v>4</v>
       </c>
       <c r="H1369" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1370">
@@ -38780,26 +38780,26 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>9800000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="E1370" t="n">
-        <v>230</v>
+        <v>1100</v>
       </c>
       <c r="F1370" t="n">
         <v>4</v>
       </c>
       <c r="G1370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1370" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1371">
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>7090000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E1371" t="n">
-        <v>60</v>
+        <v>667</v>
       </c>
       <c r="F1371" t="n">
         <v>2</v>
       </c>
       <c r="G1371" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,17 +38836,17 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>22500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>560</v>
+        <v>301</v>
       </c>
       <c r="E1372" t="n">
-        <v>248</v>
+        <v>469</v>
       </c>
       <c r="F1372" t="n">
         <v>2</v>
@@ -38864,23 +38864,23 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>8500000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E1373" t="n">
-        <v>161</v>
+        <v>284</v>
       </c>
       <c r="F1373" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1373" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1373" t="n">
         <v>1</v>
@@ -38892,20 +38892,20 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>2000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>85</v>
+        <v>1104</v>
       </c>
       <c r="E1374" t="n">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="F1374" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1374" t="n">
         <v>2</v>
@@ -38920,23 +38920,23 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>17000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E1375" t="n">
-        <v>1100</v>
+        <v>1038</v>
       </c>
       <c r="F1375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1375" t="n">
         <v>1</v>
@@ -38948,20 +38948,20 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>48000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>800</v>
+        <v>340</v>
       </c>
       <c r="E1376" t="n">
-        <v>667</v>
+        <v>350</v>
       </c>
       <c r="F1376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1376" t="n">
         <v>4</v>
@@ -38976,23 +38976,23 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>27000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="E1377" t="n">
-        <v>469</v>
+        <v>30</v>
       </c>
       <c r="F1377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1377" t="n">
         <v>1</v>
@@ -39004,17 +39004,17 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>6400000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>60</v>
+        <v>395</v>
       </c>
       <c r="E1378" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F1378" t="n">
         <v>2</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>45000000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>1050</v>
+        <v>175</v>
       </c>
       <c r="E1379" t="n">
-        <v>627</v>
+        <v>175</v>
       </c>
       <c r="F1379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1379" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1380" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1380" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1380" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>16500000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>250</v>
+        <v>720</v>
       </c>
       <c r="E1381" t="n">
-        <v>284</v>
+        <v>634</v>
       </c>
       <c r="F1381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1381" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>2600000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="E1382" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="F1382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1382" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,17 +39144,17 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>2000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1383" t="n">
-        <v>60</v>
+        <v>498</v>
       </c>
       <c r="F1383" t="n">
         <v>3</v>
@@ -39172,20 +39172,20 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>11500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>1104</v>
+        <v>124</v>
       </c>
       <c r="E1384" t="n">
-        <v>368</v>
+        <v>124</v>
       </c>
       <c r="F1384" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1384" t="n">
         <v>2</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>6900000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>375</v>
+        <v>150</v>
       </c>
       <c r="E1385" t="n">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="F1385" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1385" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,23 +39228,23 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>2830000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>60</v>
+        <v>318</v>
       </c>
       <c r="E1386" t="n">
-        <v>60</v>
+        <v>497</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1386" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1386" t="n">
         <v>1</v>
@@ -39256,23 +39256,23 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>90000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="E1387" t="n">
-        <v>1038</v>
+        <v>414</v>
       </c>
       <c r="F1387" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1387" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1387" t="n">
         <v>1</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>15500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>340</v>
+        <v>1200</v>
       </c>
       <c r="E1388" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="F1388" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1388" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,17 +39312,17 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>2500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E1389" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F1389" t="n">
         <v>3</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>6700000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>395</v>
+        <v>280</v>
       </c>
       <c r="E1390" t="n">
-        <v>172</v>
+        <v>339</v>
       </c>
       <c r="F1390" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1390" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,20 +39368,20 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>6900000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
       <c r="E1391" t="n">
-        <v>76</v>
+        <v>479</v>
       </c>
       <c r="F1391" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1391" t="n">
         <v>4</v>
@@ -39396,20 +39396,20 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>46000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1392" t="n">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="E1392" t="n">
-        <v>600</v>
+        <v>425</v>
       </c>
       <c r="F1392" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1392" t="n">
         <v>4</v>
@@ -39424,23 +39424,23 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>2400000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="E1393" t="n">
-        <v>175</v>
+        <v>272</v>
       </c>
       <c r="F1393" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1393" t="n">
         <v>1</v>
@@ -39452,23 +39452,23 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>8000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="E1394" t="n">
-        <v>165</v>
+        <v>469</v>
       </c>
       <c r="F1394" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1394" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1394" t="n">
         <v>1</v>
@@ -39480,23 +39480,23 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>2000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>85</v>
+        <v>616</v>
       </c>
       <c r="E1395" t="n">
-        <v>60</v>
+        <v>383</v>
       </c>
       <c r="F1395" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1395" t="n">
         <v>1</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>2000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="E1396" t="n">
-        <v>60</v>
+        <v>525</v>
       </c>
       <c r="F1396" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>4900000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="E1397" t="n">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="F1397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1397" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,20 +39564,20 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah di Cilandak Jakarta Selatan Sisa.4 Rumah.saja</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>6900000000</v>
+        <v>3450000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>375</v>
+        <v>165</v>
       </c>
       <c r="E1398" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F1398" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1398" t="n">
         <v>4</v>
@@ -39592,23 +39592,23 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Mewah Kemang Utara, Lt 340 M2, Shm, Harga 12,5 Milyar</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>37000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="E1399" t="n">
-        <v>634</v>
+        <v>340</v>
       </c>
       <c r="F1399" t="n">
         <v>2</v>
       </c>
       <c r="G1399" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1399" t="n">
         <v>1</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>18000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="E1400" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="F1400" t="n">
         <v>3</v>
       </c>
       <c r="G1400" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>11000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1401" t="n">
-        <v>498</v>
+        <v>600</v>
       </c>
       <c r="F1401" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>1900000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>60</v>
+        <v>375</v>
       </c>
       <c r="E1402" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1402" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1402" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,23 +39704,23 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>3500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>124</v>
+        <v>1050</v>
       </c>
       <c r="E1403" t="n">
-        <v>124</v>
+        <v>627</v>
       </c>
       <c r="F1403" t="n">
         <v>3</v>
       </c>
       <c r="G1403" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1403" t="n">
         <v>1</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>5500000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1404" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E1404" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="F1404" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,23 +39760,23 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>12500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="E1405" t="n">
-        <v>497</v>
+        <v>150</v>
       </c>
       <c r="F1405" t="n">
         <v>5</v>
       </c>
       <c r="G1405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1405" t="n">
         <v>1</v>
@@ -39788,23 +39788,23 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>9000000000</v>
+        <v>32500000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>240</v>
+        <v>610</v>
       </c>
       <c r="E1406" t="n">
-        <v>414</v>
+        <v>822</v>
       </c>
       <c r="F1406" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1406" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1406" t="n">
         <v>1</v>
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>25000000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>1200</v>
+        <v>325</v>
       </c>
       <c r="E1407" t="n">
-        <v>1000</v>
+        <v>696</v>
       </c>
       <c r="F1407" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1407" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>3500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="E1408" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F1408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1408" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>6950000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="E1409" t="n">
-        <v>339</v>
+        <v>54</v>
       </c>
       <c r="F1409" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1409" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,20 +39900,20 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>28700000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1410" t="n">
-        <v>479</v>
+        <v>1050</v>
       </c>
       <c r="F1410" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1410" t="n">
         <v>4</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>16899999999</v>
+        <v>2000000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="E1411" t="n">
-        <v>425</v>
+        <v>60</v>
       </c>
       <c r="F1411" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1411" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>5500000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="E1412" t="n">
-        <v>272</v>
+        <v>60</v>
       </c>
       <c r="F1412" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1412" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>27000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="E1413" t="n">
-        <v>469</v>
+        <v>93</v>
       </c>
       <c r="F1413" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1413" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,20 +40012,20 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah 2.5 Lantai - Siap Huni - Dalam Cluster - Carport Luas - 20 Menit ke MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>17000000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>616</v>
+        <v>254</v>
       </c>
       <c r="E1414" t="n">
-        <v>383</v>
+        <v>139</v>
       </c>
       <c r="F1414" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -40040,25 +40040,781 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>16500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E1415" t="n">
-        <v>525</v>
+        <v>76</v>
       </c>
       <c r="F1415" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
       </c>
       <c r="H1415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>1415</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>220</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>98</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>466</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1418" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>510</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>423</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1419" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1420" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>147</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>9500000000</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>261</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>18700000000</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>410</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1425" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1427" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>160000000000</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1429" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>1429</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>11000000000</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>259</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1430" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>341</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>180</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1433" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>1433</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>27000000000</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>381</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1435" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>341</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>448</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1436" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>42000000000</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1437" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>235</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1438" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1439" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>823</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1440" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>7900000000</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>234</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1441" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>248</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1442" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1491"/>
+  <dimension ref="A1:H1517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>48000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>810</v>
+        <v>584</v>
       </c>
       <c r="E1354" t="n">
-        <v>370</v>
+        <v>682</v>
       </c>
       <c r="F1354" t="n">
         <v>4</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1354" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>28000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>584</v>
+        <v>250</v>
       </c>
       <c r="E1355" t="n">
-        <v>682</v>
+        <v>241</v>
       </c>
       <c r="F1355" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1355" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1355" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,26 +38388,26 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>9200000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="E1356" t="n">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="F1356" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1356" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1356" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1357">
@@ -38416,26 +38416,26 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>858000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>40</v>
+        <v>564</v>
       </c>
       <c r="E1357" t="n">
-        <v>21</v>
+        <v>726</v>
       </c>
       <c r="F1357" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G1357" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H1357" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1358">
@@ -38444,26 +38444,26 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>48000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="E1358" t="n">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="F1358" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1358" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1358" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1359">
@@ -38472,26 +38472,26 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>6900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E1359" t="n">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="F1359" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1359" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1359" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1360">
@@ -38500,26 +38500,26 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>4800000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1360" t="n">
-        <v>122</v>
+        <v>570</v>
       </c>
       <c r="F1360" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1360" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1360" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1361">
@@ -38528,26 +38528,26 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>11500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="E1361" t="n">
-        <v>570</v>
+        <v>230</v>
       </c>
       <c r="F1361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1361" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1362">
@@ -38556,26 +38556,26 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>9800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>260</v>
+        <v>560</v>
       </c>
       <c r="E1362" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F1362" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1362" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1362" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1363">
@@ -38584,20 +38584,20 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>22500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>560</v>
+        <v>262</v>
       </c>
       <c r="E1363" t="n">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="F1363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1363" t="n">
         <v>4</v>
@@ -38612,20 +38612,20 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>8500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="E1364" t="n">
-        <v>161</v>
+        <v>1100</v>
       </c>
       <c r="F1364" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1364" t="n">
         <v>4</v>
@@ -38640,20 +38640,20 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>17000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1365" t="n">
-        <v>1100</v>
+        <v>667</v>
       </c>
       <c r="F1365" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1365" t="n">
         <v>4</v>
@@ -38668,17 +38668,17 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>48000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>800</v>
+        <v>301</v>
       </c>
       <c r="E1366" t="n">
-        <v>667</v>
+        <v>469</v>
       </c>
       <c r="F1366" t="n">
         <v>2</v>
@@ -38696,23 +38696,23 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>27000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="E1367" t="n">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="F1367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1367" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1367" t="n">
         <v>1</v>
@@ -38724,23 +38724,23 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>16500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>250</v>
+        <v>1104</v>
       </c>
       <c r="E1368" t="n">
-        <v>284</v>
+        <v>368</v>
       </c>
       <c r="F1368" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1368" t="n">
         <v>1</v>
@@ -38752,23 +38752,23 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>11500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>1104</v>
+        <v>1000</v>
       </c>
       <c r="E1369" t="n">
-        <v>368</v>
+        <v>1038</v>
       </c>
       <c r="F1369" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1369" t="n">
         <v>1</v>
@@ -38780,23 +38780,23 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>90000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="E1370" t="n">
-        <v>1038</v>
+        <v>350</v>
       </c>
       <c r="F1370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1370" t="n">
         <v>1</v>
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>15500000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>340</v>
+        <v>135</v>
       </c>
       <c r="E1371" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="F1371" t="n">
         <v>3</v>
       </c>
       <c r="G1371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>2500000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>135</v>
+        <v>395</v>
       </c>
       <c r="E1372" t="n">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="F1372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1372" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,23 +38864,23 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>6700000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>395</v>
+        <v>175</v>
       </c>
       <c r="E1373" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F1373" t="n">
         <v>2</v>
       </c>
       <c r="G1373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1373" t="n">
         <v>1</v>
@@ -38892,23 +38892,23 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>2400000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>175</v>
+        <v>720</v>
       </c>
       <c r="E1374" t="n">
-        <v>175</v>
+        <v>634</v>
       </c>
       <c r="F1374" t="n">
         <v>2</v>
       </c>
       <c r="G1374" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -38920,23 +38920,23 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>37000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1375" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="E1375" t="n">
-        <v>634</v>
+        <v>750</v>
       </c>
       <c r="F1375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1375" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1375" t="n">
         <v>1</v>
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>18000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1376" t="n">
-        <v>750</v>
+        <v>498</v>
       </c>
       <c r="F1376" t="n">
         <v>3</v>
       </c>
       <c r="G1376" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,17 +38976,17 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>11000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>350</v>
+        <v>124</v>
       </c>
       <c r="E1377" t="n">
-        <v>498</v>
+        <v>124</v>
       </c>
       <c r="F1377" t="n">
         <v>3</v>
@@ -39004,20 +39004,20 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>3500000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="E1378" t="n">
-        <v>124</v>
+        <v>270</v>
       </c>
       <c r="F1378" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -39032,23 +39032,23 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>5500000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>150</v>
+        <v>318</v>
       </c>
       <c r="E1379" t="n">
-        <v>270</v>
+        <v>497</v>
       </c>
       <c r="F1379" t="n">
         <v>5</v>
       </c>
       <c r="G1379" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1379" t="n">
         <v>1</v>
@@ -39060,20 +39060,20 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>12500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>318</v>
+        <v>240</v>
       </c>
       <c r="E1380" t="n">
-        <v>497</v>
+        <v>414</v>
       </c>
       <c r="F1380" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1380" t="n">
         <v>4</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>9000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="E1381" t="n">
-        <v>414</v>
+        <v>1000</v>
       </c>
       <c r="F1381" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1381" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>25000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>1200</v>
+        <v>147</v>
       </c>
       <c r="E1382" t="n">
-        <v>1000</v>
+        <v>66</v>
       </c>
       <c r="F1382" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1382" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>3500000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="E1383" t="n">
-        <v>66</v>
+        <v>339</v>
       </c>
       <c r="F1383" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1383" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,23 +39172,23 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>6950000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="E1384" t="n">
-        <v>339</v>
+        <v>479</v>
       </c>
       <c r="F1384" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1384" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1384" t="n">
         <v>1</v>
@@ -39200,20 +39200,20 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>28700000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1385" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E1385" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="F1385" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1385" t="n">
         <v>4</v>
@@ -39228,20 +39228,20 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>16899999999</v>
+        <v>5500000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E1386" t="n">
-        <v>425</v>
+        <v>272</v>
       </c>
       <c r="F1386" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1386" t="n">
         <v>4</v>
@@ -39256,20 +39256,20 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>5500000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="E1387" t="n">
-        <v>272</v>
+        <v>469</v>
       </c>
       <c r="F1387" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1387" t="n">
         <v>4</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>27000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>301</v>
+        <v>616</v>
       </c>
       <c r="E1388" t="n">
-        <v>469</v>
+        <v>383</v>
       </c>
       <c r="F1388" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,23 +39312,23 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah di Cilandak Jakarta Selatan Sisa.4 Rumah.saja</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>17000000000</v>
+        <v>3450000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>616</v>
+        <v>165</v>
       </c>
       <c r="E1389" t="n">
-        <v>383</v>
+        <v>72</v>
       </c>
       <c r="F1389" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1389" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Jakarta Selatan Sisa.4 Rumah.saja</t>
+          <t>Rumah Mewah Kemang Utara, Lt 340 M2, Shm, Harga 12,5 Milyar</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>3450000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="E1390" t="n">
-        <v>72</v>
+        <v>340</v>
       </c>
       <c r="F1390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1390" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,23 +39368,23 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kemang Utara, Lt 340 M2, Shm, Harga 12,5 Milyar</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>12500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1391" t="n">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="F1391" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1391" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>48000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1392" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="F1392" t="n">
         <v>5</v>
       </c>
       <c r="G1392" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,23 +39424,23 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>4800000000</v>
+        <v>32500000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>300</v>
+        <v>610</v>
       </c>
       <c r="E1393" t="n">
-        <v>150</v>
+        <v>822</v>
       </c>
       <c r="F1393" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1393" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1393" t="n">
         <v>1</v>
@@ -39452,23 +39452,23 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>32500000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>610</v>
+        <v>56</v>
       </c>
       <c r="E1394" t="n">
-        <v>822</v>
+        <v>54</v>
       </c>
       <c r="F1394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1394" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1394" t="n">
         <v>1</v>
@@ -39480,20 +39480,20 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>11800000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="E1395" t="n">
-        <v>696</v>
+        <v>93</v>
       </c>
       <c r="F1395" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1395" t="n">
         <v>3</v>
@@ -39508,23 +39508,23 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
+          <t>Rumah 2.5 Lantai - Siap Huni - Dalam Cluster - Carport Luas - 20 Menit ke MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1396" t="n">
-        <v>830000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1396" t="n">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="E1396" t="n">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="F1396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>1950000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="E1397" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F1397" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1397" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,23 +39564,23 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Rumah 2.5 Lantai - Siap Huni - Dalam Cluster - Carport Luas - 20 Menit ke MRT Fatmawati</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>3350000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="E1398" t="n">
-        <v>139</v>
+        <v>466</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1398" t="n">
         <v>1</v>
@@ -39592,20 +39592,20 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>2900000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="E1399" t="n">
-        <v>98</v>
+        <v>423</v>
       </c>
       <c r="F1399" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1399" t="n">
         <v>6</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>27000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E1400" t="n">
-        <v>466</v>
+        <v>261</v>
       </c>
       <c r="F1400" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>11500000000</v>
+        <v>18700000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E1401" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="F1401" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>9500000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>300</v>
+        <v>1450</v>
       </c>
       <c r="E1402" t="n">
-        <v>261</v>
+        <v>1620</v>
       </c>
       <c r="F1402" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1402" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,23 +39704,23 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>18700000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>500</v>
+        <v>341</v>
       </c>
       <c r="E1403" t="n">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="F1403" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1403" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1403" t="n">
         <v>1</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>160000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1404" t="n">
-        <v>1450</v>
+        <v>180</v>
       </c>
       <c r="E1404" t="n">
-        <v>1620</v>
+        <v>230</v>
       </c>
       <c r="F1404" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1404" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,23 +39760,23 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>24000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>341</v>
+        <v>800</v>
       </c>
       <c r="E1405" t="n">
-        <v>448</v>
+        <v>1335</v>
       </c>
       <c r="F1405" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1405" t="n">
         <v>6</v>
-      </c>
-      <c r="G1405" t="n">
-        <v>1</v>
       </c>
       <c r="H1405" t="n">
         <v>1</v>
@@ -39788,20 +39788,20 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>2900000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>180</v>
+        <v>381</v>
       </c>
       <c r="E1406" t="n">
-        <v>230</v>
+        <v>448</v>
       </c>
       <c r="F1406" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1406" t="n">
         <v>3</v>
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>27000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>800</v>
+        <v>341</v>
       </c>
       <c r="E1407" t="n">
-        <v>1335</v>
+        <v>448</v>
       </c>
       <c r="F1407" t="n">
         <v>7</v>
       </c>
       <c r="G1407" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>24000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>381</v>
+        <v>850</v>
       </c>
       <c r="E1408" t="n">
-        <v>448</v>
+        <v>1925</v>
       </c>
       <c r="F1408" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,20 +39872,20 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>24000000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E1409" t="n">
-        <v>448</v>
+        <v>235</v>
       </c>
       <c r="F1409" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1409" t="n">
         <v>3</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>42000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E1410" t="n">
-        <v>1925</v>
+        <v>200</v>
       </c>
       <c r="F1410" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1410" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>7100000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1411" t="n">
-        <v>235</v>
+        <v>823</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1411" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>5200000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="E1412" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="F1412" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1412" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>12000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="E1413" t="n">
-        <v>823</v>
+        <v>60</v>
       </c>
       <c r="F1413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1413" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,20 +40012,20 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>7900000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="E1414" t="n">
-        <v>234</v>
+        <v>525</v>
       </c>
       <c r="F1414" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1414" t="n">
         <v>4</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Sutera Rasuna by Alam Sutera</t>
+          <t>Rumah Bagus di Komplek Bapem</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>1400000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E1415" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F1415" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
+          <t>Rumah Cocok untuk Usaha Lokasi Strategis Pinggir Jalan Raya @Bintaro</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>40000000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>796</v>
+        <v>228</v>
       </c>
       <c r="E1416" t="n">
-        <v>871</v>
+        <v>232</v>
       </c>
       <c r="F1416" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1416" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>16500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E1417" t="n">
-        <v>525</v>
+        <v>823</v>
       </c>
       <c r="F1417" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1417" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,23 +40124,23 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Komplek Bapem</t>
+          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>2100000000</v>
+        <v>900000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E1418" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="F1418" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1418" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1418" t="n">
         <v>1</v>
@@ -40152,23 +40152,23 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>2000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="E1419" t="n">
-        <v>60</v>
+        <v>899</v>
       </c>
       <c r="F1419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1419" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1419" t="n">
         <v>1</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Rumah Cocok untuk Usaha Lokasi Strategis Pinggir Jalan Raya @Bintaro</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>6750000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>228</v>
+        <v>500</v>
       </c>
       <c r="E1420" t="n">
-        <v>232</v>
+        <v>1554</v>
       </c>
       <c r="F1420" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1420" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>12000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1421" t="n">
-        <v>823</v>
+        <v>165</v>
       </c>
       <c r="F1421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1421" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E1422" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F1422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,23 +40264,23 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>2000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="E1423" t="n">
-        <v>60</v>
+        <v>344</v>
       </c>
       <c r="F1423" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1423" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1423" t="n">
         <v>1</v>
@@ -40292,20 +40292,20 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>16000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>467</v>
+        <v>325</v>
       </c>
       <c r="E1424" t="n">
-        <v>899</v>
+        <v>340</v>
       </c>
       <c r="F1424" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1424" t="n">
         <v>4</v>
@@ -40320,20 +40320,20 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>52500000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1425" t="n">
         <v>500</v>
       </c>
       <c r="E1425" t="n">
-        <v>1554</v>
+        <v>700</v>
       </c>
       <c r="F1425" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1425" t="n">
         <v>5</v>
@@ -40348,20 +40348,20 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>8500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1426" t="n">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="F1426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1426" t="n">
         <v>4</v>
@@ -40376,17 +40376,17 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>8000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E1427" t="n">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="F1427" t="n">
         <v>1</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>22500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>500</v>
+        <v>720</v>
       </c>
       <c r="E1428" t="n">
-        <v>366</v>
+        <v>634</v>
       </c>
       <c r="F1428" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1428" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>2000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E1429" t="n">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="F1429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,20 +40460,20 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>2000000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="E1430" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="F1430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1430" t="n">
         <v>2</v>
@@ -40488,23 +40488,23 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>8000000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="E1431" t="n">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="F1431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1431" t="n">
         <v>1</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>4800000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="E1432" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F1432" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1432" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,20 +40544,20 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>14800000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>500</v>
+        <v>417</v>
       </c>
       <c r="E1433" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="F1433" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1433" t="n">
         <v>5</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>11000000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E1434" t="n">
-        <v>259</v>
+        <v>65</v>
       </c>
       <c r="F1434" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1434" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,17 +40600,17 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>6250000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="E1435" t="n">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="F1435" t="n">
         <v>1</v>
@@ -40628,20 +40628,20 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>32000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>720</v>
+        <v>225</v>
       </c>
       <c r="E1436" t="n">
-        <v>634</v>
+        <v>108</v>
       </c>
       <c r="F1436" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1436" t="n">
         <v>5</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>1900000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>60</v>
+        <v>282</v>
       </c>
       <c r="E1437" t="n">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="F1437" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1437" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>5400000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="E1438" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1438" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,23 +40712,23 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>1170000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>56</v>
+        <v>375</v>
       </c>
       <c r="E1439" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F1439" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1439" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1439" t="n">
         <v>1</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>4390000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="E1440" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="F1440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>27000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E1441" t="n">
-        <v>335</v>
+        <v>65</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,20 +40796,20 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>7900000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>417</v>
+        <v>1050</v>
       </c>
       <c r="E1442" t="n">
-        <v>180</v>
+        <v>627</v>
       </c>
       <c r="F1442" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1442" t="n">
         <v>5</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>1650000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="E1443" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>2000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="E1444" t="n">
-        <v>80</v>
+        <v>1050</v>
       </c>
       <c r="F1444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1444" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>3000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>225</v>
+        <v>600</v>
       </c>
       <c r="E1445" t="n">
-        <v>108</v>
+        <v>335</v>
       </c>
       <c r="F1445" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1445" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1446" t="n">
         <v>5800000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="E1446" t="n">
-        <v>148</v>
+        <v>305</v>
       </c>
       <c r="F1446" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>4000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="E1447" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F1447" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1447" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>6900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="E1448" t="n">
-        <v>76</v>
+        <v>404</v>
       </c>
       <c r="F1448" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>850000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1449" t="n">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="E1449" t="n">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="F1449" t="n">
         <v>2</v>
       </c>
       <c r="G1449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>1400000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>120</v>
+        <v>375</v>
       </c>
       <c r="E1450" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F1450" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1450" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>45000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>1050</v>
+        <v>360</v>
       </c>
       <c r="E1451" t="n">
-        <v>627</v>
+        <v>127</v>
       </c>
       <c r="F1451" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1451" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>6900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E1452" t="n">
-        <v>76</v>
+        <v>696</v>
       </c>
       <c r="F1452" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1452" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,23 +41104,23 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>4500000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>300</v>
+        <v>850</v>
       </c>
       <c r="E1453" t="n">
-        <v>276</v>
+        <v>1925</v>
       </c>
       <c r="F1453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1453" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1453" t="n">
         <v>1</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>685000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="E1454" t="n">
-        <v>32</v>
+        <v>261</v>
       </c>
       <c r="F1454" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1454" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>7900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1455" t="n">
-        <v>60</v>
+        <v>703</v>
       </c>
       <c r="F1455" t="n">
         <v>2</v>
       </c>
       <c r="G1455" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,20 +41188,20 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>23000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E1456" t="n">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="F1456" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1456" t="n">
         <v>4</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>6900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>375</v>
+        <v>881</v>
       </c>
       <c r="E1457" t="n">
-        <v>76</v>
+        <v>1066</v>
       </c>
       <c r="F1457" t="n">
         <v>4</v>
       </c>
       <c r="G1457" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>22500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="E1458" t="n">
-        <v>335</v>
+        <v>921</v>
       </c>
       <c r="F1458" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>2600000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="E1459" t="n">
-        <v>60</v>
+        <v>634</v>
       </c>
       <c r="F1459" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1459" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>5800000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1460" t="n">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="F1460" t="n">
         <v>1</v>
       </c>
       <c r="G1460" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>2900000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="E1461" t="n">
-        <v>155</v>
+        <v>730</v>
       </c>
       <c r="F1461" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1461" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,23 +41356,23 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>10000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E1462" t="n">
-        <v>307</v>
+        <v>176</v>
       </c>
       <c r="F1462" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -41384,17 +41384,17 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>6900000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E1463" t="n">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="F1463" t="n">
         <v>4</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>21000000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="E1464" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="F1464" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1464" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>5500000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="E1465" t="n">
-        <v>147</v>
+        <v>248</v>
       </c>
       <c r="F1465" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1465" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>6400000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>60</v>
+        <v>321</v>
       </c>
       <c r="E1466" t="n">
-        <v>60</v>
+        <v>228</v>
       </c>
       <c r="F1466" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1466" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>4099999999</v>
+        <v>3320000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E1467" t="n">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="F1467" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1467" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>6900000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>375</v>
+        <v>600</v>
       </c>
       <c r="E1468" t="n">
-        <v>76</v>
+        <v>674</v>
       </c>
       <c r="F1468" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1468" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,23 +41552,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>4900000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="E1469" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F1469" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1469" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1469" t="n">
         <v>1</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>12000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>325</v>
+        <v>171</v>
       </c>
       <c r="E1470" t="n">
-        <v>696</v>
+        <v>181</v>
       </c>
       <c r="F1470" t="n">
         <v>3</v>
       </c>
       <c r="G1470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>41000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>850</v>
+        <v>1300</v>
       </c>
       <c r="E1471" t="n">
-        <v>1925</v>
+        <v>461</v>
       </c>
       <c r="F1471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1471" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>4500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="E1472" t="n">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="F1472" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1472" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,23 +41664,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>32000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="E1473" t="n">
-        <v>703</v>
+        <v>106</v>
       </c>
       <c r="F1473" t="n">
         <v>2</v>
       </c>
       <c r="G1473" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1473" t="n">
         <v>1</v>
@@ -41692,23 +41692,23 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>18500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="E1474" t="n">
-        <v>1035</v>
+        <v>60</v>
       </c>
       <c r="F1474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1474" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1474" t="n">
         <v>1</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>62000000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>881</v>
+        <v>150</v>
       </c>
       <c r="E1475" t="n">
-        <v>1066</v>
+        <v>274</v>
       </c>
       <c r="F1475" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1475" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>20000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>614</v>
+        <v>375</v>
       </c>
       <c r="E1476" t="n">
-        <v>921</v>
+        <v>76</v>
       </c>
       <c r="F1476" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1476" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>32000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>720</v>
+        <v>796</v>
       </c>
       <c r="E1477" t="n">
-        <v>634</v>
+        <v>871</v>
       </c>
       <c r="F1477" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1477" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>2830000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E1478" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="F1478" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>9700000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1479" t="n">
-        <v>257</v>
+        <v>1180</v>
       </c>
       <c r="F1479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>45000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>1100</v>
+        <v>60</v>
       </c>
       <c r="E1480" t="n">
-        <v>730</v>
+        <v>60</v>
       </c>
       <c r="F1480" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1480" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,23 +41888,23 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>4420000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E1481" t="n">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="F1481" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1481" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1481" t="n">
         <v>1</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>15300000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E1482" t="n">
-        <v>597</v>
+        <v>276</v>
       </c>
       <c r="F1482" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1482" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,23 +41944,23 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>6860000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>350</v>
+        <v>609</v>
       </c>
       <c r="E1483" t="n">
-        <v>500</v>
+        <v>822</v>
       </c>
       <c r="F1483" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1483" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1483" t="n">
         <v>1</v>
@@ -41972,23 +41972,23 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>7800000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1484" t="n">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="F1484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1484" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1484" t="n">
         <v>1</v>
@@ -42000,23 +42000,23 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>4150000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="E1485" t="n">
-        <v>228</v>
+        <v>60</v>
       </c>
       <c r="F1485" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1485" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1485" t="n">
         <v>1</v>
@@ -42028,17 +42028,17 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>3320000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="E1486" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F1486" t="n">
         <v>4</v>
@@ -42056,23 +42056,23 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>21500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>600</v>
+        <v>395</v>
       </c>
       <c r="E1487" t="n">
-        <v>674</v>
+        <v>172</v>
       </c>
       <c r="F1487" t="n">
         <v>2</v>
       </c>
       <c r="G1487" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1487" t="n">
         <v>1</v>
@@ -42084,23 +42084,23 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>2550000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="E1488" t="n">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="F1488" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1488" t="n">
         <v>1</v>
@@ -42112,23 +42112,23 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>2550000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>171</v>
+        <v>810</v>
       </c>
       <c r="E1489" t="n">
-        <v>181</v>
+        <v>370</v>
       </c>
       <c r="F1489" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1489" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1489" t="n">
         <v>1</v>
@@ -42140,23 +42140,23 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>15000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="E1490" t="n">
-        <v>461</v>
+        <v>76</v>
       </c>
       <c r="F1490" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1490" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1490" t="n">
         <v>1</v>
@@ -42168,25 +42168,753 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>6500000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1491" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>78</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1492" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>544</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="D1494" t="n">
         <v>250</v>
       </c>
-      <c r="E1491" t="n">
-        <v>179</v>
-      </c>
-      <c r="F1491" t="n">
-        <v>6</v>
-      </c>
-      <c r="G1491" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1491" t="n">
+      <c r="E1494" t="n">
+        <v>196</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1494" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>11800000000</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>325</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>696</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>942</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1496" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>17700000000</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>864</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1497" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>70000000000</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>275000000000</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>1585</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>52</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>27</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>366</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>154</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>11300000000</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>535</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>158</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>159</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>63</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1508" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>6900000000</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>375</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>76</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>307</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>7300000000</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>501</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>240</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>147</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>85</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>216</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1517" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1577"/>
+  <dimension ref="A1:H1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38080,26 +38080,26 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>25000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1345" t="n">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="E1345" t="n">
-        <v>450</v>
+        <v>261</v>
       </c>
       <c r="F1345" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1345" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1345" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1346">
@@ -38108,26 +38108,26 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>9500000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1346" t="n">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="E1346" t="n">
-        <v>261</v>
+        <v>494</v>
       </c>
       <c r="F1346" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1346" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1346" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1347">
@@ -38136,26 +38136,26 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah.pdk.indah.siap.pakai</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>53000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1347" t="n">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="E1347" t="n">
-        <v>494</v>
+        <v>682</v>
       </c>
       <c r="F1347" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1347" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1347" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1348">
@@ -38164,26 +38164,26 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Rumah.pdk.indah.siap.pakai</t>
+          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>28000000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1348" t="n">
-        <v>584</v>
+        <v>250</v>
       </c>
       <c r="E1348" t="n">
-        <v>682</v>
+        <v>241</v>
       </c>
       <c r="F1348" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1348" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1348" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1349">
@@ -38192,26 +38192,26 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Barat Jalan Besar, Jakarta Selatan</t>
+          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>9200000000</v>
+        <v>858000000000</v>
       </c>
       <c r="D1349" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="E1349" t="n">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="F1349" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1349" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1349" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1350">
@@ -38220,26 +38220,26 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Rumah Baru Dijual Murah di Setiabudi. Jakarta Selatan Strategis Bebas Banjir</t>
+          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>858000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1350" t="n">
-        <v>40</v>
+        <v>564</v>
       </c>
       <c r="E1350" t="n">
-        <v>21</v>
+        <v>726</v>
       </c>
       <c r="F1350" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G1350" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H1350" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1351">
@@ -38248,26 +38248,26 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Dharmawangsa Private Pool</t>
+          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>48000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1351" t="n">
-        <v>564</v>
+        <v>300</v>
       </c>
       <c r="E1351" t="n">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="F1351" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1351" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H1351" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1352">
@@ -38276,26 +38276,26 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Rumah di Kavling Polri Ampera Kemang Jakarta Selatan Siap Huni</t>
+          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
         </is>
       </c>
       <c r="C1352" t="n">
-        <v>6900000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1352" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E1352" t="n">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="F1352" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1352" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1352" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1353">
@@ -38304,26 +38304,26 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai American Style Di Pejaten Belakang Mall Siap Huni</t>
+          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
         </is>
       </c>
       <c r="C1353" t="n">
-        <v>4800000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1353" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E1353" t="n">
-        <v>122</v>
+        <v>570</v>
       </c>
       <c r="F1353" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1353" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1353" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1354">
@@ -38332,26 +38332,26 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai di Tanah Kusir Kebayoran Lama Hadap Timur SHM</t>
+          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
         </is>
       </c>
       <c r="C1354" t="n">
-        <v>11500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1354" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="E1354" t="n">
-        <v>570</v>
+        <v>230</v>
       </c>
       <c r="F1354" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1354" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1355">
@@ -38360,26 +38360,26 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>Rumah Cantik Di Kemang Private Pool Dan Rooftop Shm Siap Huni</t>
+          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1355" t="n">
-        <v>9800000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1355" t="n">
-        <v>260</v>
+        <v>560</v>
       </c>
       <c r="E1355" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F1355" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1355" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1355" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1356">
@@ -38388,20 +38388,20 @@
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Kebayoran Baru Brand New 4Lantai Ada Lift Lokasi Prime Dekat Pakubuwono Apt. Kebayoran Baru Jakarta Selatan</t>
+          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1356" t="n">
-        <v>22500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1356" t="n">
-        <v>560</v>
+        <v>262</v>
       </c>
       <c r="E1356" t="n">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="F1356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
@@ -38416,20 +38416,20 @@
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Kemang Rumah Brand New 2.5Lantai 100Meter ke Kemang Raya Jakarta Selatan</t>
+          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
         </is>
       </c>
       <c r="C1357" t="n">
-        <v>8500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1357" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="E1357" t="n">
-        <v>161</v>
+        <v>1100</v>
       </c>
       <c r="F1357" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1357" t="n">
         <v>4</v>
@@ -38444,20 +38444,20 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Siap Huni Area Kemang Harga Mendekati NJOP</t>
+          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1358" t="n">
-        <v>17000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1358" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1358" t="n">
-        <v>1100</v>
+        <v>667</v>
       </c>
       <c r="F1358" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1358" t="n">
         <v>4</v>
@@ -38472,17 +38472,17 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Rumah di Kebayoran Baru Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1359" t="n">
-        <v>48000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1359" t="n">
-        <v>800</v>
+        <v>301</v>
       </c>
       <c r="E1359" t="n">
-        <v>667</v>
+        <v>469</v>
       </c>
       <c r="F1359" t="n">
         <v>2</v>
@@ -38500,23 +38500,23 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman &amp; Balkon Luas Posisi Hook di Kebayoran Baru</t>
+          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1360" t="n">
-        <v>27000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1360" t="n">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="E1360" t="n">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="F1360" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1360" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1360" t="n">
         <v>1</v>
@@ -38528,23 +38528,23 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Rumah Hommy Adem Tampilan Vintage Lokasi Super Strategis Termurah Siap Huni Panglima Polim Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
         </is>
       </c>
       <c r="C1361" t="n">
-        <v>16500000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1361" t="n">
-        <v>250</v>
+        <v>1104</v>
       </c>
       <c r="E1361" t="n">
-        <v>284</v>
+        <v>368</v>
       </c>
       <c r="F1361" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1361" t="n">
         <v>1</v>
@@ -38556,23 +38556,23 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Rumah Kantor Bagus Rapi Siap Pakai di Cipete Selatan Cilandak</t>
+          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
         </is>
       </c>
       <c r="C1362" t="n">
-        <v>11500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1362" t="n">
-        <v>1104</v>
+        <v>1000</v>
       </c>
       <c r="E1362" t="n">
-        <v>368</v>
+        <v>1038</v>
       </c>
       <c r="F1362" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1362" t="n">
         <v>1</v>
@@ -38584,23 +38584,23 @@
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Runah Hoek Lokasi Super Strategis dan Langka Kebayoran Baru Jakarta Selatan Area Super Elite dan Adem</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1363" t="n">
-        <v>90000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1363" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="E1363" t="n">
-        <v>1038</v>
+        <v>350</v>
       </c>
       <c r="F1363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1363" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1363" t="n">
         <v>1</v>
@@ -38612,23 +38612,23 @@
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1364" t="n">
-        <v>15500000000</v>
+        <v>6700000000</v>
       </c>
       <c r="D1364" t="n">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="E1364" t="n">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="F1364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1364" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1364" t="n">
         <v>1</v>
@@ -38640,23 +38640,23 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Di Jual Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
         </is>
       </c>
       <c r="C1365" t="n">
-        <v>6700000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1365" t="n">
-        <v>395</v>
+        <v>175</v>
       </c>
       <c r="E1365" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F1365" t="n">
         <v>2</v>
       </c>
       <c r="G1365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1365" t="n">
         <v>1</v>
@@ -38668,23 +38668,23 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Rumah Murah Siap Huni Lokasi Grand Matoa Jagakarsa</t>
+          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1366" t="n">
-        <v>2400000000</v>
+        <v>37000000000</v>
       </c>
       <c r="D1366" t="n">
-        <v>175</v>
+        <v>720</v>
       </c>
       <c r="E1366" t="n">
-        <v>175</v>
+        <v>634</v>
       </c>
       <c r="F1366" t="n">
         <v>2</v>
       </c>
       <c r="G1366" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1366" t="n">
         <v>1</v>
@@ -38696,23 +38696,23 @@
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Murah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1367" t="n">
-        <v>37000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1367" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="E1367" t="n">
-        <v>634</v>
+        <v>750</v>
       </c>
       <c r="F1367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1367" t="n">
         <v>1</v>
@@ -38724,23 +38724,23 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Dijual - Rumah Ligamas Pancoran, Jakarta Selatan</t>
+          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
         </is>
       </c>
       <c r="C1368" t="n">
-        <v>18000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1368" t="n">
-        <v>400</v>
+        <v>124</v>
       </c>
       <c r="E1368" t="n">
-        <v>750</v>
+        <v>124</v>
       </c>
       <c r="F1368" t="n">
         <v>3</v>
       </c>
       <c r="G1368" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1368" t="n">
         <v>1</v>
@@ -38752,20 +38752,20 @@
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
         </is>
       </c>
       <c r="C1369" t="n">
-        <v>11000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1369" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E1369" t="n">
-        <v>498</v>
+        <v>270</v>
       </c>
       <c r="F1369" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1369" t="n">
         <v>2</v>
@@ -38780,23 +38780,23 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Rumah Tingkat bisa untuk Kantor 5 Menit ke Mall Kemvill</t>
+          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
         </is>
       </c>
       <c r="C1370" t="n">
-        <v>3500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1370" t="n">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="E1370" t="n">
-        <v>124</v>
+        <v>414</v>
       </c>
       <c r="F1370" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1370" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1370" t="n">
         <v>1</v>
@@ -38808,23 +38808,23 @@
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Mampang Duren Tiga Jakarta Selatan SHM</t>
+          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1371" t="n">
-        <v>5500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1371" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="E1371" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="F1371" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1371" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1371" t="n">
         <v>1</v>
@@ -38836,23 +38836,23 @@
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
         </is>
       </c>
       <c r="C1372" t="n">
-        <v>12500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1372" t="n">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="E1372" t="n">
-        <v>497</v>
+        <v>66</v>
       </c>
       <c r="F1372" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1372" t="n">
         <v>1</v>
@@ -38864,23 +38864,23 @@
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Rumah Cantik di Komplek Al Pasar Minggu Siap Huni Furnished SHM</t>
+          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
         </is>
       </c>
       <c r="C1373" t="n">
-        <v>9000000000</v>
+        <v>6950000000</v>
       </c>
       <c r="D1373" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="E1373" t="n">
-        <v>414</v>
+        <v>339</v>
       </c>
       <c r="F1373" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1373" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1373" t="n">
         <v>1</v>
@@ -38892,23 +38892,23 @@
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Rumah Heritage 2 Lantai di Asem Baris Raya Tebet Jakarta Selatan</t>
+          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
         </is>
       </c>
       <c r="C1374" t="n">
-        <v>25000000000</v>
+        <v>28700000000</v>
       </c>
       <c r="D1374" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="E1374" t="n">
-        <v>1000</v>
+        <v>479</v>
       </c>
       <c r="F1374" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1374" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1374" t="n">
         <v>1</v>
@@ -38920,23 +38920,23 @@
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Townhouse Minimalis 3 Lantai Di Kemang Harga Mulai 3 Miliaran</t>
+          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
         </is>
       </c>
       <c r="C1375" t="n">
-        <v>3500000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1375" t="n">
-        <v>147</v>
+        <v>450</v>
       </c>
       <c r="E1375" t="n">
-        <v>66</v>
+        <v>425</v>
       </c>
       <c r="F1375" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1375" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1375" t="n">
         <v>1</v>
@@ -38948,23 +38948,23 @@
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Fatmawati Dalam Kompleks Dekat ke Pondok Indah</t>
+          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
         </is>
       </c>
       <c r="C1376" t="n">
-        <v>6950000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1376" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E1376" t="n">
-        <v>339</v>
+        <v>272</v>
       </c>
       <c r="F1376" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1376" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1376" t="n">
         <v>1</v>
@@ -38976,20 +38976,20 @@
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai Hook di Sungai Sambas Kebayoran Baru Perlu Renov</t>
+          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
         </is>
       </c>
       <c r="C1377" t="n">
-        <v>28700000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1377" t="n">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="E1377" t="n">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F1377" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1377" t="n">
         <v>4</v>
@@ -39004,23 +39004,23 @@
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Rumah Tropical Siap Huni di Kemang Jakarta Selatan Aman 24 Jam</t>
+          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
         </is>
       </c>
       <c r="C1378" t="n">
-        <v>16899999999</v>
+        <v>17000000000</v>
       </c>
       <c r="D1378" t="n">
-        <v>450</v>
+        <v>616</v>
       </c>
       <c r="E1378" t="n">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="F1378" t="n">
         <v>4</v>
       </c>
       <c r="G1378" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1378" t="n">
         <v>1</v>
@@ -39032,20 +39032,20 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cilandak Dekat Citos Lokasi Strategis SHM</t>
+          <t>Rumah di Cilandak Jakarta Selatan Sisa.4 Rumah.saja</t>
         </is>
       </c>
       <c r="C1379" t="n">
-        <v>5500000000</v>
+        <v>3450000000</v>
       </c>
       <c r="D1379" t="n">
-        <v>350</v>
+        <v>165</v>
       </c>
       <c r="E1379" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="F1379" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1379" t="n">
         <v>4</v>
@@ -39060,23 +39060,23 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Rumah Hoek 2 Lantai di Kerinci Kebayoran Baru Dekat ke Senayan</t>
+          <t>Rumah Mewah Kemang Utara, Lt 340 M2, Shm, Harga 12,5 Milyar</t>
         </is>
       </c>
       <c r="C1380" t="n">
-        <v>27000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1380" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E1380" t="n">
-        <v>469</v>
+        <v>340</v>
       </c>
       <c r="F1380" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1380" t="n">
         <v>1</v>
@@ -39088,23 +39088,23 @@
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pinang Perak Pondok Indah SHM Lokasi Bagus Hook</t>
+          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
         </is>
       </c>
       <c r="C1381" t="n">
-        <v>17000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1381" t="n">
-        <v>616</v>
+        <v>800</v>
       </c>
       <c r="E1381" t="n">
-        <v>383</v>
+        <v>600</v>
       </c>
       <c r="F1381" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1381" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1381" t="n">
         <v>1</v>
@@ -39116,23 +39116,23 @@
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Rumah di Cilandak Jakarta Selatan Sisa.4 Rumah.saja</t>
+          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1382" t="n">
-        <v>3450000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1382" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="E1382" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="F1382" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1382" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1382" t="n">
         <v>1</v>
@@ -39144,23 +39144,23 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kemang Utara, Lt 340 M2, Shm, Harga 12,5 Milyar</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil</t>
         </is>
       </c>
       <c r="C1383" t="n">
-        <v>12500000000</v>
+        <v>32500000000</v>
       </c>
       <c r="D1383" t="n">
-        <v>300</v>
+        <v>610</v>
       </c>
       <c r="E1383" t="n">
-        <v>340</v>
+        <v>822</v>
       </c>
       <c r="F1383" t="n">
         <v>2</v>
       </c>
       <c r="G1383" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1383" t="n">
         <v>1</v>
@@ -39172,23 +39172,23 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Rumah Mewah Siap Huni di Kebayoran Baru For Sale</t>
+          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1384" t="n">
-        <v>48000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1384" t="n">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="E1384" t="n">
-        <v>600</v>
+        <v>93</v>
       </c>
       <c r="F1384" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1384" t="n">
         <v>1</v>
@@ -39200,23 +39200,23 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Jual Rumah Lama di Tebet Barat Jakarta Selatan Potensi Investasi Bangun Kost Akses Jalan Lebar</t>
+          <t>Rumah 2.5 Lantai - Siap Huni - Dalam Cluster - Carport Luas - 20 Menit ke MRT Fatmawati</t>
         </is>
       </c>
       <c r="C1385" t="n">
-        <v>4800000000</v>
+        <v>3350000000</v>
       </c>
       <c r="D1385" t="n">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="E1385" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F1385" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1385" t="n">
         <v>1</v>
@@ -39228,23 +39228,23 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil</t>
+          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1386" t="n">
-        <v>32500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1386" t="n">
-        <v>610</v>
+        <v>220</v>
       </c>
       <c r="E1386" t="n">
-        <v>822</v>
+        <v>98</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1386" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1386" t="n">
         <v>1</v>
@@ -39256,20 +39256,20 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
+          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
         </is>
       </c>
       <c r="C1387" t="n">
-        <v>830000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1387" t="n">
-        <v>56</v>
+        <v>301</v>
       </c>
       <c r="E1387" t="n">
-        <v>54</v>
+        <v>466</v>
       </c>
       <c r="F1387" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -39284,23 +39284,23 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Rumah Cluster M Kahfi 1 SHM 4 Kamar Luas 130M Jagakarsa Jaksel</t>
+          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1388" t="n">
-        <v>1950000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1388" t="n">
-        <v>130</v>
+        <v>510</v>
       </c>
       <c r="E1388" t="n">
-        <v>93</v>
+        <v>423</v>
       </c>
       <c r="F1388" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1388" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1388" t="n">
         <v>1</v>
@@ -39312,17 +39312,17 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Rumah 2.5 Lantai - Siap Huni - Dalam Cluster - Carport Luas - 20 Menit ke MRT Fatmawati</t>
+          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1389" t="n">
-        <v>3350000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1389" t="n">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="E1389" t="n">
-        <v>139</v>
+        <v>261</v>
       </c>
       <c r="F1389" t="n">
         <v>1</v>
@@ -39340,23 +39340,23 @@
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1390" t="n">
-        <v>2900000000</v>
+        <v>18700000000</v>
       </c>
       <c r="D1390" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="E1390" t="n">
-        <v>98</v>
+        <v>410</v>
       </c>
       <c r="F1390" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1390" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1390" t="n">
         <v>1</v>
@@ -39368,23 +39368,23 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Rumah Hoek Super Luas di Kebayoran Baru - Belakang Senayan City!</t>
+          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
         </is>
       </c>
       <c r="C1391" t="n">
-        <v>27000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1391" t="n">
-        <v>301</v>
+        <v>1450</v>
       </c>
       <c r="E1391" t="n">
-        <v>466</v>
+        <v>1620</v>
       </c>
       <c r="F1391" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1391" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H1391" t="n">
         <v>1</v>
@@ -39396,23 +39396,23 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Rumah Hoek Mewah dengan Basement dan Kolam Renang Kebayoran Lama Jakarta Selatan</t>
+          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1392" t="n">
-        <v>11500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1392" t="n">
-        <v>510</v>
+        <v>341</v>
       </c>
       <c r="E1392" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="F1392" t="n">
         <v>6</v>
       </c>
       <c r="G1392" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1392" t="n">
         <v>1</v>
@@ -39424,20 +39424,20 @@
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Rumah Klasik Bebas Banjir Lokasi Premium Wijaya Jakarta Selatan</t>
+          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
         </is>
       </c>
       <c r="C1393" t="n">
-        <v>9500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1393" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E1393" t="n">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="F1393" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1393" t="n">
         <v>3</v>
@@ -39452,23 +39452,23 @@
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Lokasi Elite Pondok Indah Jakarta Selatan</t>
+          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1394" t="n">
-        <v>18700000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1394" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E1394" t="n">
-        <v>410</v>
+        <v>1335</v>
       </c>
       <c r="F1394" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1394" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1394" t="n">
         <v>1</v>
@@ -39480,23 +39480,23 @@
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Rumah Spektakuler, di Pondok Indah, Bukit Golf</t>
+          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
         </is>
       </c>
       <c r="C1395" t="n">
-        <v>160000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1395" t="n">
-        <v>1450</v>
+        <v>381</v>
       </c>
       <c r="E1395" t="n">
-        <v>1620</v>
+        <v>448</v>
       </c>
       <c r="F1395" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1395" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H1395" t="n">
         <v>1</v>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Butuh Cepat!! Rumah di Menteng Domisili Pejabat</t>
+          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
         </is>
       </c>
       <c r="C1396" t="n">
@@ -39521,10 +39521,10 @@
         <v>448</v>
       </c>
       <c r="F1396" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1396" t="n">
         <v>1</v>
@@ -39536,23 +39536,23 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Butuh Uang!! Kios Jalan Raya Empang Tiga Kalibata</t>
+          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
         </is>
       </c>
       <c r="C1397" t="n">
-        <v>2900000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1397" t="n">
-        <v>180</v>
+        <v>850</v>
       </c>
       <c r="E1397" t="n">
-        <v>230</v>
+        <v>1925</v>
       </c>
       <c r="F1397" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1397" t="n">
         <v>1</v>
@@ -39564,23 +39564,23 @@
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Murah Luas!! Furnished Vibes Villa di Ampera Jaksel</t>
+          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1398" t="n">
-        <v>27000000000</v>
+        <v>7100000000</v>
       </c>
       <c r="D1398" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1398" t="n">
-        <v>1335</v>
+        <v>235</v>
       </c>
       <c r="F1398" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1398" t="n">
         <v>1</v>
@@ -39592,23 +39592,23 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Rumah di Menteng!! Harga Merakyat Domisili Pejabat</t>
+          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
         </is>
       </c>
       <c r="C1399" t="n">
-        <v>24000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1399" t="n">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="E1399" t="n">
-        <v>448</v>
+        <v>200</v>
       </c>
       <c r="F1399" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1399" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1399" t="n">
         <v>1</v>
@@ -39620,23 +39620,23 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Rumah Domisili Pejabat Harga Rakyat di Menteng</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1400" t="n">
-        <v>24000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1400" t="n">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="E1400" t="n">
-        <v>448</v>
+        <v>823</v>
       </c>
       <c r="F1400" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1400" t="n">
         <v>1</v>
@@ -39648,23 +39648,23 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Rumah Tropis Mewah di Cilandak Jakarta Lokasi Strategis dan Komersial Area</t>
+          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
         </is>
       </c>
       <c r="C1401" t="n">
-        <v>42000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1401" t="n">
-        <v>850</v>
+        <v>260</v>
       </c>
       <c r="E1401" t="n">
-        <v>1925</v>
+        <v>234</v>
       </c>
       <c r="F1401" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1401" t="n">
         <v>1</v>
@@ -39676,23 +39676,23 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Bagus 3Br. Ciepete. Dekat Fatmawati Lokasi Strategis</t>
+          <t>Sutera Rasuna by Alam Sutera</t>
         </is>
       </c>
       <c r="C1402" t="n">
-        <v>7100000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1402" t="n">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="E1402" t="n">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="F1402" t="n">
         <v>2</v>
       </c>
       <c r="G1402" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1402" t="n">
         <v>1</v>
@@ -39704,23 +39704,23 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Rumah American Clasic Private Pool Lokasi 10 Menit ke Pintu Tol</t>
+          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
         </is>
       </c>
       <c r="C1403" t="n">
-        <v>5200000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1403" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E1403" t="n">
-        <v>200</v>
+        <v>525</v>
       </c>
       <c r="F1403" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1403" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1403" t="n">
         <v>1</v>
@@ -39732,23 +39732,23 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Rumah Bagus di Komplek Bapem</t>
         </is>
       </c>
       <c r="C1404" t="n">
-        <v>12000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1404" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E1404" t="n">
-        <v>823</v>
+        <v>150</v>
       </c>
       <c r="F1404" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1404" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1404" t="n">
         <v>1</v>
@@ -39760,23 +39760,23 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Modern Minimalis By Andra Matin Veteran Bintaro</t>
+          <t>Rumah Cocok untuk Usaha Lokasi Strategis Pinggir Jalan Raya @Bintaro</t>
         </is>
       </c>
       <c r="C1405" t="n">
-        <v>7900000000</v>
+        <v>6750000000</v>
       </c>
       <c r="D1405" t="n">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="E1405" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F1405" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1405" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1405" t="n">
         <v>1</v>
@@ -39788,23 +39788,23 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Sutera Rasuna by Alam Sutera</t>
+          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
         </is>
       </c>
       <c r="C1406" t="n">
-        <v>1400000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1406" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="E1406" t="n">
-        <v>60</v>
+        <v>823</v>
       </c>
       <c r="F1406" t="n">
         <v>2</v>
       </c>
       <c r="G1406" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1406" t="n">
         <v>1</v>
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Rumah bagus Tropical Modern Di Cipete furnished pool siap huni</t>
+          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>16500000000</v>
+        <v>900000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>400</v>
+        <v>64</v>
       </c>
       <c r="E1407" t="n">
-        <v>525</v>
+        <v>48</v>
       </c>
       <c r="F1407" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1407" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Komplek Bapem</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>2100000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>100</v>
+        <v>467</v>
       </c>
       <c r="E1408" t="n">
-        <v>150</v>
+        <v>899</v>
       </c>
       <c r="F1408" t="n">
         <v>4</v>
       </c>
       <c r="G1408" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Rumah Cocok untuk Usaha Lokasi Strategis Pinggir Jalan Raya @Bintaro</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>6750000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>228</v>
+        <v>500</v>
       </c>
       <c r="E1409" t="n">
-        <v>232</v>
+        <v>1554</v>
       </c>
       <c r="F1409" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1409" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Jarang Ada !!! Rumah Harga NJOP di Bintaro Sektor 1</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>12000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1410" t="n">
-        <v>823</v>
+        <v>165</v>
       </c>
       <c r="F1410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1410" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>900000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E1411" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>16000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>467</v>
+        <v>580</v>
       </c>
       <c r="E1412" t="n">
-        <v>899</v>
+        <v>344</v>
       </c>
       <c r="F1412" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1412" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>52500000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="E1413" t="n">
-        <v>1554</v>
+        <v>340</v>
       </c>
       <c r="F1413" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1413" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,23 +40012,23 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>8000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E1414" t="n">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="F1414" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1414" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>2000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="E1415" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F1415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>8000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>580</v>
+        <v>720</v>
       </c>
       <c r="E1416" t="n">
-        <v>344</v>
+        <v>634</v>
       </c>
       <c r="F1416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1416" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>4800000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="E1417" t="n">
-        <v>340</v>
+        <v>184</v>
       </c>
       <c r="F1417" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1417" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,23 +40124,23 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>11000000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>500</v>
+        <v>56</v>
       </c>
       <c r="E1418" t="n">
-        <v>259</v>
+        <v>29</v>
       </c>
       <c r="F1418" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1418" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1418" t="n">
         <v>1</v>
@@ -40152,20 +40152,20 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>6250000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E1419" t="n">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="F1419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>32000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>720</v>
+        <v>200</v>
       </c>
       <c r="E1420" t="n">
-        <v>634</v>
+        <v>335</v>
       </c>
       <c r="F1420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1420" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>5400000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>125</v>
+        <v>417</v>
       </c>
       <c r="E1421" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F1421" t="n">
         <v>1</v>
       </c>
       <c r="G1421" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>1170000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="E1422" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F1422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,20 +40264,20 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>4390000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="E1423" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F1423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -40292,23 +40292,23 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>27000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="E1424" t="n">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F1424" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1424" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1424" t="n">
         <v>1</v>
@@ -40320,20 +40320,20 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>7900000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>417</v>
+        <v>282</v>
       </c>
       <c r="E1425" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="F1425" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1425" t="n">
         <v>5</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>1650000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="E1426" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="F1426" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1426" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,23 +40376,23 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>108</v>
+        <v>375</v>
       </c>
       <c r="E1427" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F1427" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1427" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1427" t="n">
         <v>1</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>3000000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>225</v>
+        <v>44</v>
       </c>
       <c r="E1428" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="F1428" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1428" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,20 +40432,20 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>5800000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>282</v>
+        <v>1050</v>
       </c>
       <c r="E1429" t="n">
-        <v>148</v>
+        <v>627</v>
       </c>
       <c r="F1429" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1429" t="n">
         <v>5</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>4000000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="E1430" t="n">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="F1430" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1430" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,20 +40488,20 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>6900000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>375</v>
+        <v>800</v>
       </c>
       <c r="E1431" t="n">
-        <v>76</v>
+        <v>1050</v>
       </c>
       <c r="F1431" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1431" t="n">
         <v>4</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>850000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="E1432" t="n">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="F1432" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>1400000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="E1433" t="n">
-        <v>65</v>
+        <v>305</v>
       </c>
       <c r="F1433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>45000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="E1434" t="n">
-        <v>627</v>
+        <v>155</v>
       </c>
       <c r="F1434" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1434" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>685000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>40</v>
+        <v>410</v>
       </c>
       <c r="E1435" t="n">
-        <v>32</v>
+        <v>404</v>
       </c>
       <c r="F1435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1435" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>23000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1436" t="n">
-        <v>800</v>
+        <v>180</v>
       </c>
       <c r="E1436" t="n">
-        <v>1050</v>
+        <v>244</v>
       </c>
       <c r="F1436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1436" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>22500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1437" t="n">
-        <v>335</v>
+        <v>76</v>
       </c>
       <c r="F1437" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1437" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>5800000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
       <c r="E1438" t="n">
-        <v>305</v>
+        <v>127</v>
       </c>
       <c r="F1438" t="n">
         <v>1</v>
       </c>
       <c r="G1438" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,23 +40712,23 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>2900000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>200</v>
+        <v>850</v>
       </c>
       <c r="E1439" t="n">
-        <v>155</v>
+        <v>1925</v>
       </c>
       <c r="F1439" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1439" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1439" t="n">
         <v>1</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>21000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="E1440" t="n">
-        <v>404</v>
+        <v>261</v>
       </c>
       <c r="F1440" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1440" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>4099999999</v>
+        <v>32000000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="E1441" t="n">
-        <v>244</v>
+        <v>703</v>
       </c>
       <c r="F1441" t="n">
         <v>2</v>
       </c>
       <c r="G1441" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,20 +40796,20 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>6900000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="E1442" t="n">
-        <v>76</v>
+        <v>1035</v>
       </c>
       <c r="F1442" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1442" t="n">
         <v>4</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>4900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>360</v>
+        <v>881</v>
       </c>
       <c r="E1443" t="n">
-        <v>127</v>
+        <v>1066</v>
       </c>
       <c r="F1443" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1443" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>41000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>850</v>
+        <v>614</v>
       </c>
       <c r="E1444" t="n">
-        <v>1925</v>
+        <v>921</v>
       </c>
       <c r="F1444" t="n">
         <v>1</v>
       </c>
       <c r="G1444" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="E1445" t="n">
-        <v>261</v>
+        <v>634</v>
       </c>
       <c r="F1445" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1445" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,20 +40908,20 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1446" t="n">
-        <v>703</v>
+        <v>257</v>
       </c>
       <c r="F1446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>18500000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E1447" t="n">
-        <v>1035</v>
+        <v>730</v>
       </c>
       <c r="F1447" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1447" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>62000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>881</v>
+        <v>300</v>
       </c>
       <c r="E1448" t="n">
-        <v>1066</v>
+        <v>176</v>
       </c>
       <c r="F1448" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>20000000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>614</v>
+        <v>200</v>
       </c>
       <c r="E1449" t="n">
-        <v>921</v>
+        <v>597</v>
       </c>
       <c r="F1449" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1449" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>32000000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1450" t="n">
-        <v>634</v>
+        <v>500</v>
       </c>
       <c r="F1450" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1450" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>9700000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1451" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F1451" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1451" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>45000000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>1100</v>
+        <v>321</v>
       </c>
       <c r="E1452" t="n">
-        <v>730</v>
+        <v>228</v>
       </c>
       <c r="F1452" t="n">
         <v>5</v>
       </c>
       <c r="G1452" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,20 +41104,20 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>4420000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="E1453" t="n">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="F1453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1453" t="n">
         <v>3</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>15300000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E1454" t="n">
-        <v>597</v>
+        <v>674</v>
       </c>
       <c r="F1454" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1454" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>6860000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="E1455" t="n">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="F1455" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>7800000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>300</v>
+        <v>171</v>
       </c>
       <c r="E1456" t="n">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="F1456" t="n">
         <v>3</v>
       </c>
       <c r="G1456" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1456" t="n">
         <v>1</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>4150000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>321</v>
+        <v>1300</v>
       </c>
       <c r="E1457" t="n">
-        <v>228</v>
+        <v>461</v>
       </c>
       <c r="F1457" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>3320000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="E1458" t="n">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="F1458" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1458" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>21500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="E1459" t="n">
-        <v>674</v>
+        <v>274</v>
       </c>
       <c r="F1459" t="n">
         <v>2</v>
       </c>
       <c r="G1459" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>2550000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>160</v>
+        <v>796</v>
       </c>
       <c r="E1460" t="n">
-        <v>123</v>
+        <v>871</v>
       </c>
       <c r="F1460" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1460" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>2550000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="E1461" t="n">
-        <v>181</v>
+        <v>535</v>
       </c>
       <c r="F1461" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,17 +41356,17 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>15000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="E1462" t="n">
-        <v>461</v>
+        <v>1180</v>
       </c>
       <c r="F1462" t="n">
         <v>2</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>6500000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="E1463" t="n">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="F1463" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1463" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
+          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>9800000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E1464" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F1464" t="n">
         <v>2</v>
       </c>
       <c r="G1464" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>40000000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>796</v>
+        <v>609</v>
       </c>
       <c r="E1465" t="n">
-        <v>871</v>
+        <v>822</v>
       </c>
       <c r="F1465" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1465" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>7500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E1466" t="n">
-        <v>535</v>
+        <v>60</v>
       </c>
       <c r="F1466" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>25000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="E1467" t="n">
-        <v>1180</v>
+        <v>60</v>
       </c>
       <c r="F1467" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>7900000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E1468" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F1468" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1468" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,17 +41552,17 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>4500000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="E1469" t="n">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="F1469" t="n">
         <v>2</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>29500000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>609</v>
+        <v>60</v>
       </c>
       <c r="E1470" t="n">
-        <v>822</v>
+        <v>60</v>
       </c>
       <c r="F1470" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1470" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>2600000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1471" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F1471" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1471" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>2000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E1472" t="n">
         <v>60</v>
       </c>
       <c r="F1472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,23 +41664,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>2300000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>90</v>
+        <v>650</v>
       </c>
       <c r="E1473" t="n">
-        <v>91</v>
+        <v>544</v>
       </c>
       <c r="F1473" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1473" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1473" t="n">
         <v>1</v>
@@ -41692,23 +41692,23 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>6400000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="E1474" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="F1474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1474" t="n">
         <v>1</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>2830000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>60</v>
+        <v>325</v>
       </c>
       <c r="E1475" t="n">
-        <v>60</v>
+        <v>696</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>2350000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="E1476" t="n">
-        <v>78</v>
+        <v>942</v>
       </c>
       <c r="F1476" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1476" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>6400000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="E1477" t="n">
-        <v>60</v>
+        <v>864</v>
       </c>
       <c r="F1477" t="n">
         <v>2</v>
       </c>
       <c r="G1477" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>28000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="E1478" t="n">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1478" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>4500000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1479" t="n">
-        <v>196</v>
+        <v>1300</v>
       </c>
       <c r="F1479" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>11800000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>325</v>
+        <v>1300</v>
       </c>
       <c r="E1480" t="n">
-        <v>696</v>
+        <v>1585</v>
       </c>
       <c r="F1480" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1480" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,23 +41888,23 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>25000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>450</v>
+        <v>52</v>
       </c>
       <c r="E1481" t="n">
-        <v>942</v>
+        <v>27</v>
       </c>
       <c r="F1481" t="n">
         <v>2</v>
       </c>
       <c r="G1481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1481" t="n">
         <v>1</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>17700000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>700</v>
+        <v>366</v>
       </c>
       <c r="E1482" t="n">
-        <v>864</v>
+        <v>366</v>
       </c>
       <c r="F1482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1482" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,17 +41944,17 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>8000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1483" t="n">
         <v>200</v>
       </c>
       <c r="E1483" t="n">
-        <v>600</v>
+        <v>154</v>
       </c>
       <c r="F1483" t="n">
         <v>1</v>
@@ -41972,23 +41972,23 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>70000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1484" t="n">
-        <v>1300</v>
+        <v>60</v>
       </c>
       <c r="F1484" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1484" t="n">
         <v>1</v>
@@ -42000,23 +42000,23 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>275000000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="E1485" t="n">
-        <v>1585</v>
+        <v>535</v>
       </c>
       <c r="F1485" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1485" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1485" t="n">
         <v>1</v>
@@ -42028,23 +42028,23 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>1100000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="E1486" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F1486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1486" t="n">
         <v>1</v>
@@ -42056,17 +42056,17 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>22500000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>366</v>
+        <v>159</v>
       </c>
       <c r="E1487" t="n">
-        <v>366</v>
+        <v>63</v>
       </c>
       <c r="F1487" t="n">
         <v>1</v>
@@ -42084,20 +42084,20 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>6800000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1488" t="n">
-        <v>154</v>
+        <v>300</v>
       </c>
       <c r="F1488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1488" t="n">
         <v>3</v>
@@ -42112,23 +42112,23 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>1700000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="E1489" t="n">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="F1489" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1489" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1489" t="n">
         <v>1</v>
@@ -42140,20 +42140,20 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>11300000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E1490" t="n">
-        <v>535</v>
+        <v>250</v>
       </c>
       <c r="F1490" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -42168,20 +42168,20 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>2100000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>158</v>
+        <v>501</v>
       </c>
       <c r="E1491" t="n">
-        <v>63</v>
+        <v>600</v>
       </c>
       <c r="F1491" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1491" t="n">
         <v>3</v>
@@ -42196,20 +42196,20 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>2400000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="E1492" t="n">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="F1492" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1492" t="n">
         <v>3</v>
@@ -42224,23 +42224,23 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>7800000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1493" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F1493" t="n">
         <v>2</v>
       </c>
       <c r="G1493" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1493" t="n">
         <v>1</v>
@@ -42252,23 +42252,23 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>10000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>360</v>
+        <v>85</v>
       </c>
       <c r="E1494" t="n">
-        <v>307</v>
+        <v>60</v>
       </c>
       <c r="F1494" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1494" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1494" t="n">
         <v>1</v>
@@ -42280,20 +42280,20 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>6000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1495" t="n">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="F1495" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1495" t="n">
         <v>3</v>
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>7300000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="E1496" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="F1496" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1496" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>5000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>240</v>
+        <v>481</v>
       </c>
       <c r="E1497" t="n">
-        <v>147</v>
+        <v>958</v>
       </c>
       <c r="F1497" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1497" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1497" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>8500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>250</v>
+        <v>810</v>
       </c>
       <c r="E1498" t="n">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="F1498" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1498" t="n">
         <v>4</v>
       </c>
       <c r="H1498" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,7 +42392,7 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1499" t="n">
@@ -42411,7 +42411,7 @@
         <v>2</v>
       </c>
       <c r="H1499" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>10000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1500" t="n">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="F1500" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1500" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1500" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>1750000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="E1501" t="n">
-        <v>120</v>
+        <v>696</v>
       </c>
       <c r="F1501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1501" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1501" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,26 +42476,26 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>12500000000</v>
+        <v>21300000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>481</v>
+        <v>600</v>
       </c>
       <c r="E1502" t="n">
-        <v>958</v>
+        <v>630</v>
       </c>
       <c r="F1502" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1502" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1502" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1503">
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>48000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="E1503" t="n">
-        <v>370</v>
+        <v>660</v>
       </c>
       <c r="F1503" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1503" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1503" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>2000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="E1504" t="n">
-        <v>60</v>
+        <v>584</v>
       </c>
       <c r="F1504" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1504" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1504" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>6900000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E1505" t="n">
-        <v>76</v>
+        <v>931</v>
       </c>
       <c r="F1505" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1505" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1505" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>12000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1506" t="n">
-        <v>696</v>
+        <v>550</v>
       </c>
       <c r="F1506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1506" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>21300000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1507" t="n">
-        <v>630</v>
+        <v>1925</v>
       </c>
       <c r="F1507" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1507" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1507" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>38000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1508" t="n">
         <v>850</v>
       </c>
       <c r="E1508" t="n">
-        <v>660</v>
+        <v>1925</v>
       </c>
       <c r="F1508" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1508" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1508" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>19000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1509" t="n">
-        <v>584</v>
+        <v>620</v>
       </c>
       <c r="F1509" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1509" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1509" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>40000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="E1510" t="n">
-        <v>627</v>
+        <v>1295</v>
       </c>
       <c r="F1510" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1510" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1510" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,23 +42728,23 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>55000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>1600</v>
+        <v>160</v>
       </c>
       <c r="E1511" t="n">
-        <v>1800</v>
+        <v>201</v>
       </c>
       <c r="F1511" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1511" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H1511" t="n">
         <v>11</v>
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>7500000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1512" t="n">
-        <v>404</v>
+        <v>263</v>
       </c>
       <c r="F1512" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1512" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1512" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>9000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1513" t="n">
-        <v>208</v>
+        <v>1180</v>
       </c>
       <c r="F1513" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1513" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1513" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,26 +42812,26 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>22000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="E1514" t="n">
-        <v>931</v>
+        <v>242</v>
       </c>
       <c r="F1514" t="n">
         <v>5</v>
       </c>
       <c r="G1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1515">
@@ -42840,17 +42840,17 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>32000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="E1515" t="n">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="F1515" t="n">
         <v>4</v>
@@ -42859,7 +42859,7 @@
         <v>4</v>
       </c>
       <c r="H1515" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>53500000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="E1516" t="n">
-        <v>1165</v>
+        <v>1554</v>
       </c>
       <c r="F1516" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="G1516" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H1516" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>42000000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>850</v>
+        <v>610</v>
       </c>
       <c r="E1517" t="n">
-        <v>1925</v>
+        <v>822</v>
       </c>
       <c r="F1517" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="G1517" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="H1517" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>42000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>850</v>
+        <v>375</v>
       </c>
       <c r="E1518" t="n">
-        <v>1925</v>
+        <v>76</v>
       </c>
       <c r="F1518" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1518" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1518" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1519" t="n">
         <v>17000000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>450</v>
+        <v>245</v>
       </c>
       <c r="E1519" t="n">
-        <v>620</v>
+        <v>260</v>
       </c>
       <c r="F1519" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1519" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1519" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1520">
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>32000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>650</v>
+        <v>1220</v>
       </c>
       <c r="E1520" t="n">
-        <v>1230</v>
+        <v>1430</v>
       </c>
       <c r="F1520" t="n">
         <v>5</v>
       </c>
       <c r="G1520" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1520" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
+          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>35000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E1521" t="n">
-        <v>1295</v>
+        <v>575</v>
       </c>
       <c r="F1521" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1521" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1521" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>3600000000</v>
+        <v>12700000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="E1522" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F1522" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1522" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1522" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>5500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E1523" t="n">
-        <v>263</v>
+        <v>612</v>
       </c>
       <c r="F1523" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1523" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1523" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>25000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="E1524" t="n">
-        <v>1180</v>
+        <v>1925</v>
       </c>
       <c r="F1524" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="G1524" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="H1524" t="n">
-        <v>4</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,26 +43120,26 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>5500000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="E1525" t="n">
-        <v>242</v>
+        <v>2500</v>
       </c>
       <c r="F1525" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G1525" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1525" t="n">
-        <v>11</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1526">
@@ -43148,23 +43148,23 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Rumah Terawat dan Asri di Pondok Indah</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>6900000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1526" t="n">
-        <v>375</v>
+        <v>630</v>
       </c>
       <c r="E1526" t="n">
-        <v>76</v>
+        <v>750</v>
       </c>
       <c r="F1526" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G1526" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H1526" t="n">
         <v>22</v>
@@ -43176,26 +43176,26 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Rumah Asri Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>52500000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1527" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1527" t="n">
-        <v>1554</v>
+        <v>430</v>
       </c>
       <c r="F1527" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G1527" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1527" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1528">
@@ -43204,26 +43204,26 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>28500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>610</v>
+        <v>400</v>
       </c>
       <c r="E1528" t="n">
-        <v>822</v>
+        <v>347</v>
       </c>
       <c r="F1528" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1528" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H1528" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1529">
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>32000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>720</v>
+        <v>250</v>
       </c>
       <c r="E1529" t="n">
-        <v>634</v>
+        <v>305</v>
       </c>
       <c r="F1529" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1529" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1529" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,26 +43260,26 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>6900000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="E1530" t="n">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="F1530" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1530" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1530" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>17000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E1531" t="n">
-        <v>260</v>
+        <v>179</v>
       </c>
       <c r="F1531" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="G1531" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1531" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>100000000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>1220</v>
+        <v>600</v>
       </c>
       <c r="E1532" t="n">
-        <v>1430</v>
+        <v>324</v>
       </c>
       <c r="F1532" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1532" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1532" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>15800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>600</v>
+        <v>92</v>
       </c>
       <c r="E1533" t="n">
-        <v>575</v>
+        <v>90</v>
       </c>
       <c r="F1533" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1533" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1533" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>12700000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>450</v>
+        <v>65</v>
       </c>
       <c r="E1534" t="n">
-        <v>209</v>
+        <v>106</v>
       </c>
       <c r="F1534" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1534" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="H1534" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>20000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="E1535" t="n">
-        <v>612</v>
+        <v>425</v>
       </c>
       <c r="F1535" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G1535" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1535" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>49000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1536" t="n">
         <v>850</v>
       </c>
       <c r="E1536" t="n">
-        <v>1925</v>
+        <v>1800</v>
       </c>
       <c r="F1536" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="G1536" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="H1536" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>35000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>1000</v>
+        <v>609</v>
       </c>
       <c r="E1537" t="n">
-        <v>2500</v>
+        <v>822</v>
       </c>
       <c r="F1537" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1537" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H1537" t="n">
-        <v>412</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Rumah Terawat dan Asri di Pondok Indah</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>25000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>630</v>
+        <v>400</v>
       </c>
       <c r="E1538" t="n">
-        <v>750</v>
+        <v>580</v>
       </c>
       <c r="F1538" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G1538" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H1538" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>7900000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1539" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E1539" t="n">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="F1539" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G1539" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1539" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni di Pondok Indah</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>17500000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E1540" t="n">
-        <v>430</v>
+        <v>388</v>
       </c>
       <c r="F1540" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1540" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1540" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,26 +43568,26 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>6800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1541" t="n">
-        <v>347</v>
+        <v>237</v>
       </c>
       <c r="F1541" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1541" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1542">
@@ -43596,26 +43596,26 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>5800000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="E1542" t="n">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="F1542" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1542" t="n">
         <v>31</v>
       </c>
       <c r="H1542" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1543">
@@ -43624,26 +43624,26 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>6400000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>308</v>
+        <v>150</v>
       </c>
       <c r="E1543" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="F1543" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1543" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1544">
@@ -43652,23 +43652,23 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>6500000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="E1544" t="n">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="F1544" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1544" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1544" t="n">
         <v>2</v>
@@ -43680,26 +43680,26 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>13000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>600</v>
+        <v>275</v>
       </c>
       <c r="E1545" t="n">
-        <v>324</v>
+        <v>130</v>
       </c>
       <c r="F1545" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1545" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1545" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,26 +43708,26 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>80000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E1546" t="n">
         <v>1050</v>
       </c>
       <c r="F1546" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1546" t="n">
         <v>41</v>
       </c>
-      <c r="G1546" t="n">
-        <v>32</v>
-      </c>
       <c r="H1546" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1547">
@@ -43736,26 +43736,26 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>1700000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="E1547" t="n">
-        <v>90</v>
+        <v>667</v>
       </c>
       <c r="F1547" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1547" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1547" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1548">
@@ -43764,26 +43764,26 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>15500000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="E1548" t="n">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="F1548" t="n">
         <v>3</v>
       </c>
       <c r="G1548" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1548" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1549">
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>1200000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="E1549" t="n">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="F1549" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G1549" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1549" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,26 +43820,26 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>2500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="E1550" t="n">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="F1550" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1550" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1550" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1551">
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>13500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>374</v>
+        <v>500</v>
       </c>
       <c r="E1551" t="n">
-        <v>181</v>
+        <v>703</v>
       </c>
       <c r="F1551" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G1551" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1551" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>25000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E1552" t="n">
-        <v>425</v>
+        <v>196</v>
       </c>
       <c r="F1552" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G1552" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1552" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>40000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1553" t="n">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="E1553" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F1553" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1553" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1553" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>30000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>609</v>
+        <v>200</v>
       </c>
       <c r="E1554" t="n">
-        <v>822</v>
+        <v>135</v>
       </c>
       <c r="F1554" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1554" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1554" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,26 +43960,26 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>12500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="E1555" t="n">
-        <v>580</v>
+        <v>91</v>
       </c>
       <c r="F1555" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G1555" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H1555" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1556">
@@ -43988,26 +43988,26 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>9600000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1556" t="n">
-        <v>257</v>
+        <v>700</v>
       </c>
       <c r="F1556" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="G1556" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1556" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1557">
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>3500000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E1557" t="n">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="F1557" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1557" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1557" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,20 +44044,20 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>1700000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="E1558" t="n">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="F1558" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1558" t="n">
         <v>3</v>
@@ -44072,26 +44072,26 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>2550000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E1559" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F1559" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1559" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1559" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1560">
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>2000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>150</v>
+        <v>720</v>
       </c>
       <c r="E1560" t="n">
-        <v>200</v>
+        <v>634</v>
       </c>
       <c r="F1560" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G1560" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1560" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>2100000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="E1561" t="n">
-        <v>93</v>
+        <v>625</v>
       </c>
       <c r="F1561" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1561" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1561" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,26 +44156,26 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>4700000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="E1562" t="n">
-        <v>130</v>
+        <v>528</v>
       </c>
       <c r="F1562" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1562" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H1562" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,26 +44184,26 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>2600000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>88</v>
+        <v>550</v>
       </c>
       <c r="E1563" t="n">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="F1563" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1563" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1563" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1564">
@@ -44212,26 +44212,26 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>23000000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>800</v>
+        <v>520</v>
       </c>
       <c r="E1564" t="n">
-        <v>1050</v>
+        <v>714</v>
       </c>
       <c r="F1564" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="G1564" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1564" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1565">
@@ -44240,23 +44240,23 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>890000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>56</v>
+        <v>375</v>
       </c>
       <c r="E1565" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F1565" t="n">
         <v>2</v>
       </c>
       <c r="G1565" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1565" t="n">
         <v>1</v>
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>48000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E1566" t="n">
-        <v>667</v>
+        <v>526</v>
       </c>
       <c r="F1566" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1566" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1566" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>2830000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>112</v>
+        <v>800</v>
       </c>
       <c r="E1567" t="n">
-        <v>70</v>
+        <v>650</v>
       </c>
       <c r="F1567" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1567" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="H1567" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,17 +44324,17 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>22500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1568" t="n">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="F1568" t="n">
         <v>3</v>
@@ -44343,7 +44343,7 @@
         <v>3</v>
       </c>
       <c r="H1568" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Luxe Court Permata Hijau Signature</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>8500000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="E1569" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="F1569" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="G1569" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1569" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,17 +44380,17 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>8000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E1570" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="F1570" t="n">
         <v>41</v>
@@ -44399,7 +44399,7 @@
         <v>31</v>
       </c>
       <c r="H1570" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>32000000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1571" t="n">
-        <v>703</v>
+        <v>1722</v>
       </c>
       <c r="F1571" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G1571" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1571" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>4500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="E1572" t="n">
-        <v>196</v>
+        <v>570</v>
       </c>
       <c r="F1572" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G1572" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1572" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>6800000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="E1573" t="n">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="F1573" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1573" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1573" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>3500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E1574" t="n">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="F1574" t="n">
         <v>41</v>
       </c>
       <c r="G1574" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H1574" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,26 +44520,26 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>2900000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="E1575" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F1575" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1575" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1575" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1576">
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>14800000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1576" t="n">
-        <v>700</v>
+        <v>498</v>
       </c>
       <c r="F1576" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1576" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1576" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,26 +44576,698 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>15700000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1577" t="n">
+        <v>318</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>497</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1577" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>9200000000</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>440</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>317</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>16500000000</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1580" t="n">
         <v>300</v>
       </c>
-      <c r="E1577" t="n">
+      <c r="F1580" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1581" t="n">
         <v>400</v>
       </c>
-      <c r="F1577" t="n">
-        <v>8</v>
-      </c>
-      <c r="G1577" t="n">
-        <v>4</v>
-      </c>
-      <c r="H1577" t="n">
+      <c r="E1581" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>120000000000</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>775</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>925</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>9500000000</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>664</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>301</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>890000000</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>56</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1585" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>80000000000</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1586" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>1587</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>15500000000</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>340</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>350</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1588" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>135</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>30</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1590" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1590" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1591" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>346</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1592" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>457</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>500</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1593" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>452</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1594" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>1594</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>880</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1595" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>17500000000</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>470</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>412</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1596" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>627</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1597" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>7500000000</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>404</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1598" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1598" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>1598</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1599" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1599" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>49000000000</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>540</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1600" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1601" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1601" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1601" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1601"/>
+  <dimension ref="A1:H1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>16000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="E1408" t="n">
-        <v>899</v>
+        <v>1554</v>
       </c>
       <c r="F1408" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1408" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>52500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1409" t="n">
-        <v>1554</v>
+        <v>165</v>
       </c>
       <c r="F1409" t="n">
         <v>1</v>
       </c>
       <c r="G1409" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>8000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1410" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="F1410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>2000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="E1411" t="n">
-        <v>60</v>
+        <v>344</v>
       </c>
       <c r="F1411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,23 +39956,23 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>8000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>580</v>
+        <v>325</v>
       </c>
       <c r="E1412" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F1412" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1412" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1412" t="n">
         <v>1</v>
@@ -39984,20 +39984,20 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>4800000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="E1413" t="n">
-        <v>340</v>
+        <v>259</v>
       </c>
       <c r="F1413" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1413" t="n">
         <v>4</v>
@@ -40012,23 +40012,23 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>11000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1414" t="n">
-        <v>259</v>
+        <v>122</v>
       </c>
       <c r="F1414" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>6250000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="E1415" t="n">
-        <v>122</v>
+        <v>634</v>
       </c>
       <c r="F1415" t="n">
         <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>32000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>720</v>
+        <v>125</v>
       </c>
       <c r="E1416" t="n">
-        <v>634</v>
+        <v>184</v>
       </c>
       <c r="F1416" t="n">
         <v>1</v>
       </c>
       <c r="G1416" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>5400000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="E1417" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="F1417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,23 +40124,23 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>1170000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="E1418" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F1418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1418" t="n">
         <v>1</v>
@@ -40152,20 +40152,20 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>4390000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E1419" t="n">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="F1419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1419" t="n">
         <v>3</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>27000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="E1420" t="n">
-        <v>335</v>
+        <v>180</v>
       </c>
       <c r="F1420" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1420" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,23 +40208,23 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>7900000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>417</v>
+        <v>150</v>
       </c>
       <c r="E1421" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="F1421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1421" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1421" t="n">
         <v>1</v>
@@ -40236,20 +40236,20 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>1650000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1422" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E1422" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F1422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1422" t="n">
         <v>3</v>
@@ -40264,23 +40264,23 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>2000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1423" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1423" t="n">
         <v>108</v>
       </c>
-      <c r="E1423" t="n">
-        <v>80</v>
-      </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1423" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1423" t="n">
         <v>1</v>
@@ -40292,17 +40292,17 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>3000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="E1424" t="n">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="F1424" t="n">
         <v>5</v>
@@ -40320,17 +40320,17 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>5800000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="E1425" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F1425" t="n">
         <v>5</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>4000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="E1426" t="n">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="F1426" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1426" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,23 +40376,23 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
+          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>6900000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="E1427" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="F1427" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1427" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1427" t="n">
         <v>1</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>850000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>44</v>
+        <v>1050</v>
       </c>
       <c r="E1428" t="n">
-        <v>24</v>
+        <v>627</v>
       </c>
       <c r="F1428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1428" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>45000000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>1050</v>
+        <v>40</v>
       </c>
       <c r="E1429" t="n">
-        <v>627</v>
+        <v>32</v>
       </c>
       <c r="F1429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1429" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>685000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="E1430" t="n">
-        <v>32</v>
+        <v>1050</v>
       </c>
       <c r="F1430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1430" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,23 +40488,23 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>23000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1431" t="n">
-        <v>1050</v>
+        <v>335</v>
       </c>
       <c r="F1431" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1431" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1431" t="n">
         <v>1</v>
@@ -40516,20 +40516,20 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>22500000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1432" t="n">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="F1432" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1432" t="n">
         <v>3</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>5800000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E1433" t="n">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="F1433" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1433" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>2900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="E1434" t="n">
-        <v>155</v>
+        <v>404</v>
       </c>
       <c r="F1434" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>21000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1435" t="n">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="E1435" t="n">
-        <v>404</v>
+        <v>244</v>
       </c>
       <c r="F1435" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1435" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>4099999999</v>
+        <v>6900000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="E1436" t="n">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="F1436" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1436" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1437" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1437" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1437" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>4900000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>360</v>
+        <v>850</v>
       </c>
       <c r="E1438" t="n">
-        <v>127</v>
+        <v>1925</v>
       </c>
       <c r="F1438" t="n">
         <v>1</v>
       </c>
       <c r="G1438" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,23 +40712,23 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>41000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>850</v>
+        <v>360</v>
       </c>
       <c r="E1439" t="n">
-        <v>1925</v>
+        <v>261</v>
       </c>
       <c r="F1439" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1439" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1439" t="n">
         <v>1</v>
@@ -40740,20 +40740,20 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="E1440" t="n">
-        <v>261</v>
+        <v>703</v>
       </c>
       <c r="F1440" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1440" t="n">
         <v>4</v>
@@ -40768,17 +40768,17 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E1441" t="n">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F1441" t="n">
         <v>2</v>
@@ -40796,23 +40796,23 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>18500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1442" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F1442" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1442" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1442" t="n">
         <v>1</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>62000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>881</v>
+        <v>614</v>
       </c>
       <c r="E1443" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="F1443" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1443" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>614</v>
+        <v>720</v>
       </c>
       <c r="E1444" t="n">
-        <v>921</v>
+        <v>634</v>
       </c>
       <c r="F1444" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1444" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1445" t="n">
-        <v>634</v>
+        <v>257</v>
       </c>
       <c r="F1445" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1445" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>9700000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1446" t="n">
-        <v>257</v>
+        <v>730</v>
       </c>
       <c r="F1446" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1446" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>45000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1447" t="n">
-        <v>730</v>
+        <v>176</v>
       </c>
       <c r="F1447" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1447" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>4420000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1448" t="n">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="F1448" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>15300000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1449" t="n">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F1449" t="n">
         <v>4</v>
       </c>
       <c r="G1449" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>6860000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1450" t="n">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="F1450" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1450" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>7800000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E1451" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F1451" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1451" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>4150000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="E1452" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F1452" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1452" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,23 +41104,23 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>3320000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>198</v>
+        <v>600</v>
       </c>
       <c r="E1453" t="n">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="F1453" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1453" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1453" t="n">
         <v>1</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>21500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1454" t="n">
-        <v>674</v>
+        <v>123</v>
       </c>
       <c r="F1454" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1454" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,20 +41160,20 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1455" t="n">
         <v>2550000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E1455" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F1455" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1455" t="n">
         <v>2</v>
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>2550000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="E1456" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="F1456" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1456" t="n">
         <v>1</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="E1457" t="n">
-        <v>461</v>
+        <v>179</v>
       </c>
       <c r="F1457" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1457" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>6500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1458" t="n">
-        <v>179</v>
+        <v>274</v>
       </c>
       <c r="F1458" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1458" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
+          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>9800000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>150</v>
+        <v>796</v>
       </c>
       <c r="E1459" t="n">
-        <v>274</v>
+        <v>871</v>
       </c>
       <c r="F1459" t="n">
         <v>2</v>
       </c>
       <c r="G1459" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
+          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>40000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>796</v>
+        <v>300</v>
       </c>
       <c r="E1460" t="n">
-        <v>871</v>
+        <v>535</v>
       </c>
       <c r="F1460" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1460" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,23 +41328,23 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>7500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1461" t="n">
-        <v>535</v>
+        <v>1180</v>
       </c>
       <c r="F1461" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1461" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1461" t="n">
         <v>1</v>
@@ -41356,17 +41356,17 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>25000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1462" t="n">
-        <v>1180</v>
+        <v>60</v>
       </c>
       <c r="F1462" t="n">
         <v>2</v>
@@ -41384,17 +41384,17 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>7900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E1463" t="n">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="F1463" t="n">
         <v>2</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>4500000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="E1464" t="n">
-        <v>276</v>
+        <v>822</v>
       </c>
       <c r="F1464" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1464" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>29500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>609</v>
+        <v>60</v>
       </c>
       <c r="E1465" t="n">
-        <v>822</v>
+        <v>60</v>
       </c>
       <c r="F1465" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1465" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>2600000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E1466" t="n">
         <v>60</v>
       </c>
       <c r="F1466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>2000000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E1467" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F1467" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1467" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>2300000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="E1468" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="F1468" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,17 +41552,17 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>6400000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>395</v>
+        <v>60</v>
       </c>
       <c r="E1469" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="F1469" t="n">
         <v>2</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>2830000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1470" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F1470" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1470" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>2350000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1471" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F1471" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1471" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>6400000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="E1472" t="n">
-        <v>60</v>
+        <v>544</v>
       </c>
       <c r="F1472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1472" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,23 +41664,23 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>28000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="E1473" t="n">
-        <v>544</v>
+        <v>196</v>
       </c>
       <c r="F1473" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1473" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1473" t="n">
         <v>1</v>
@@ -41692,20 +41692,20 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>4500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1474" t="n">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="F1474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1474" t="n">
         <v>3</v>
@@ -41720,20 +41720,20 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>11800000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="E1475" t="n">
-        <v>696</v>
+        <v>942</v>
       </c>
       <c r="F1475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>25000000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E1476" t="n">
-        <v>942</v>
+        <v>864</v>
       </c>
       <c r="F1476" t="n">
         <v>2</v>
       </c>
       <c r="G1476" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>17700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1477" t="n">
-        <v>864</v>
+        <v>600</v>
       </c>
       <c r="F1477" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1477" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>8000000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1478" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F1478" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>70000000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E1479" t="n">
-        <v>1300</v>
+        <v>1585</v>
       </c>
       <c r="F1479" t="n">
         <v>4</v>
       </c>
       <c r="G1479" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>275000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>1300</v>
+        <v>52</v>
       </c>
       <c r="E1480" t="n">
-        <v>1585</v>
+        <v>27</v>
       </c>
       <c r="F1480" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1480" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,23 +41888,23 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>1100000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>52</v>
+        <v>366</v>
       </c>
       <c r="E1481" t="n">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="F1481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1481" t="n">
         <v>1</v>
@@ -41916,17 +41916,17 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>22500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="E1482" t="n">
-        <v>366</v>
+        <v>154</v>
       </c>
       <c r="F1482" t="n">
         <v>1</v>
@@ -41944,23 +41944,23 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>6800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1483" t="n">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="F1483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1483" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1483" t="n">
         <v>1</v>
@@ -41972,23 +41972,23 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>1700000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="E1484" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="F1484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1484" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1484" t="n">
         <v>1</v>
@@ -42000,17 +42000,17 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>11300000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>600</v>
+        <v>158</v>
       </c>
       <c r="E1485" t="n">
-        <v>535</v>
+        <v>63</v>
       </c>
       <c r="F1485" t="n">
         <v>1</v>
@@ -42028,14 +42028,14 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>2100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E1486" t="n">
         <v>63</v>
@@ -42056,20 +42056,20 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E1487" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F1487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1487" t="n">
         <v>3</v>
@@ -42084,23 +42084,23 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>7800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1488" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F1488" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1488" t="n">
         <v>1</v>
@@ -42112,23 +42112,23 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>10000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E1489" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="F1489" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1489" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1489" t="n">
         <v>1</v>
@@ -42140,17 +42140,17 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>6000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="E1490" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F1490" t="n">
         <v>5</v>
@@ -42168,20 +42168,20 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>7300000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>501</v>
+        <v>240</v>
       </c>
       <c r="E1491" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F1491" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1491" t="n">
         <v>3</v>
@@ -42196,23 +42196,23 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>5000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E1492" t="n">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="F1492" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1492" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1492" t="n">
         <v>1</v>
@@ -42224,23 +42224,23 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>8500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1493" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1493" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1493" t="n">
         <v>1</v>
@@ -42252,23 +42252,23 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>2000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1494" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F1494" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1494" t="n">
         <v>1</v>
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>10000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="E1495" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F1495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1495" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>1750000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="E1496" t="n">
-        <v>120</v>
+        <v>958</v>
       </c>
       <c r="F1496" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1496" t="n">
         <v>21</v>
       </c>
       <c r="H1496" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,23 +42336,23 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>12500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>481</v>
+        <v>810</v>
       </c>
       <c r="E1497" t="n">
-        <v>958</v>
+        <v>370</v>
       </c>
       <c r="F1497" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1497" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1497" t="n">
         <v>42</v>
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>48000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>810</v>
+        <v>85</v>
       </c>
       <c r="E1498" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1498" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1498" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1498" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1499" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1499" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1499" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1499" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>6900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E1500" t="n">
-        <v>76</v>
+        <v>696</v>
       </c>
       <c r="F1500" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1500" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1500" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,26 +42448,26 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>12000000000</v>
+        <v>21300000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1501" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="F1501" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1501" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1501" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1502">
@@ -42476,17 +42476,17 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>21300000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1502" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="F1502" t="n">
         <v>5</v>
@@ -42504,17 +42504,17 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>38000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1503" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
       <c r="F1503" t="n">
         <v>5</v>
@@ -42532,23 +42532,23 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>19000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>600</v>
+        <v>325</v>
       </c>
       <c r="E1504" t="n">
-        <v>584</v>
+        <v>931</v>
       </c>
       <c r="F1504" t="n">
         <v>5</v>
       </c>
       <c r="G1504" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1504" t="n">
         <v>4</v>
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>22000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1505" t="n">
-        <v>931</v>
+        <v>550</v>
       </c>
       <c r="F1505" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1505" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1505" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>32000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1506" t="n">
-        <v>550</v>
+        <v>1925</v>
       </c>
       <c r="F1506" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1506" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1506" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,7 +42616,7 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
+          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
         </is>
       </c>
       <c r="C1507" t="n">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>42000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="E1508" t="n">
-        <v>1925</v>
+        <v>620</v>
       </c>
       <c r="F1508" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1508" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1508" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>17000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="E1509" t="n">
-        <v>620</v>
+        <v>1295</v>
       </c>
       <c r="F1509" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1509" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1509" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>35000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="E1510" t="n">
-        <v>1295</v>
+        <v>201</v>
       </c>
       <c r="F1510" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G1510" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1510" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,23 +42728,23 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>3600000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="E1511" t="n">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="F1511" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1511" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1511" t="n">
         <v>11</v>
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>5500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1512" t="n">
-        <v>263</v>
+        <v>1180</v>
       </c>
       <c r="F1512" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1512" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H1512" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>25000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1513" t="n">
-        <v>1180</v>
+        <v>242</v>
       </c>
       <c r="F1513" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1513" t="n">
         <v>11</v>
-      </c>
-      <c r="G1513" t="n">
-        <v>10</v>
-      </c>
-      <c r="H1513" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,26 +42812,26 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1514" t="n">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="F1514" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1515">
@@ -42840,23 +42840,23 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>6900000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>375</v>
+        <v>610</v>
       </c>
       <c r="E1515" t="n">
-        <v>76</v>
+        <v>822</v>
       </c>
       <c r="F1515" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1515" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1515" t="n">
         <v>22</v>
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>52500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E1516" t="n">
-        <v>1554</v>
+        <v>76</v>
       </c>
       <c r="F1516" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G1516" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1516" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>28500000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>610</v>
+        <v>245</v>
       </c>
       <c r="E1517" t="n">
-        <v>822</v>
+        <v>260</v>
       </c>
       <c r="F1517" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1517" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1517" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>6900000000</v>
+        <v>100000000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>375</v>
+        <v>1220</v>
       </c>
       <c r="E1518" t="n">
-        <v>76</v>
+        <v>1430</v>
       </c>
       <c r="F1518" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1518" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1518" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,26 +42952,26 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>17000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>245</v>
+        <v>600</v>
       </c>
       <c r="E1519" t="n">
-        <v>260</v>
+        <v>575</v>
       </c>
       <c r="F1519" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1519" t="n">
         <v>4</v>
       </c>
       <c r="H1519" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1520">
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
+          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>100000000000</v>
+        <v>12700000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>1220</v>
+        <v>450</v>
       </c>
       <c r="E1520" t="n">
-        <v>1430</v>
+        <v>209</v>
       </c>
       <c r="F1520" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="G1520" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H1520" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,23 +43008,23 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>15800000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1521" t="n">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="F1521" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1521" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1521" t="n">
         <v>22</v>
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>12700000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1522" t="n">
-        <v>209</v>
+        <v>1925</v>
       </c>
       <c r="F1522" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G1522" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1522" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>20000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="E1523" t="n">
-        <v>612</v>
+        <v>2500</v>
       </c>
       <c r="F1523" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1523" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H1523" t="n">
-        <v>22</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Rumah Terawat dan Asri di Pondok Indah</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>49000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>850</v>
+        <v>630</v>
       </c>
       <c r="E1524" t="n">
-        <v>1925</v>
+        <v>750</v>
       </c>
       <c r="F1524" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G1524" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H1524" t="n">
-        <v>210</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,26 +43120,26 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>Rumah Asri Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>35000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E1525" t="n">
-        <v>2500</v>
+        <v>430</v>
       </c>
       <c r="F1525" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G1525" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="H1525" t="n">
-        <v>412</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1526">
@@ -43148,26 +43148,26 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Rumah Terawat dan Asri di Pondok Indah</t>
+          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>25000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1526" t="n">
-        <v>630</v>
+        <v>400</v>
       </c>
       <c r="E1526" t="n">
-        <v>750</v>
+        <v>347</v>
       </c>
       <c r="F1526" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G1526" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H1526" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1527">
@@ -43176,20 +43176,20 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni di Pondok Indah</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>17500000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1527" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E1527" t="n">
-        <v>430</v>
+        <v>305</v>
       </c>
       <c r="F1527" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1527" t="n">
         <v>31</v>
@@ -43204,23 +43204,23 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
+          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>6800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1528" t="n">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="F1528" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1528" t="n">
         <v>41</v>
-      </c>
-      <c r="G1528" t="n">
-        <v>31</v>
       </c>
       <c r="H1528" t="n">
         <v>2</v>
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>5800000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1529" t="n">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="F1529" t="n">
         <v>41</v>
       </c>
       <c r="G1529" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1529" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,17 +43260,17 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>6400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="E1530" t="n">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="F1530" t="n">
         <v>2</v>
@@ -43279,7 +43279,7 @@
         <v>1</v>
       </c>
       <c r="H1530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>6500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="E1531" t="n">
-        <v>179</v>
+        <v>1800</v>
       </c>
       <c r="F1531" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G1531" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H1531" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>13000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="E1532" t="n">
-        <v>324</v>
+        <v>822</v>
       </c>
       <c r="F1532" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1532" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H1532" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>1700000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>92</v>
+        <v>400</v>
       </c>
       <c r="E1533" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="F1533" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G1533" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1533" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>1200000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="E1534" t="n">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="F1534" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G1534" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H1534" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>25000000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E1535" t="n">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="F1535" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="G1535" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1535" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>40000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1536" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E1536" t="n">
-        <v>1800</v>
+        <v>237</v>
       </c>
       <c r="F1536" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1536" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1536" t="n">
-        <v>220</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>30000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>609</v>
+        <v>145</v>
       </c>
       <c r="E1537" t="n">
-        <v>822</v>
+        <v>75</v>
       </c>
       <c r="F1537" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G1537" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H1537" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>12500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E1538" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="F1538" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1538" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1538" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>9600000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1539" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="E1539" t="n">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="F1539" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G1539" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H1539" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>3500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="E1540" t="n">
-        <v>388</v>
+        <v>667</v>
       </c>
       <c r="F1540" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1540" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1540" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,26 +43568,26 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>1700000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1541" t="n">
-        <v>237</v>
+        <v>703</v>
       </c>
       <c r="F1541" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1541" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1541" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1542">
@@ -43596,17 +43596,17 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>2550000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="E1542" t="n">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="F1542" t="n">
         <v>31</v>
@@ -43615,7 +43615,7 @@
         <v>31</v>
       </c>
       <c r="H1542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1543">
@@ -43624,17 +43624,17 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>2000000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E1543" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F1543" t="n">
         <v>5</v>
@@ -43643,7 +43643,7 @@
         <v>3</v>
       </c>
       <c r="H1543" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1544">
@@ -43652,23 +43652,23 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>2100000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E1544" t="n">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F1544" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1544" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1544" t="n">
         <v>2</v>
@@ -43680,17 +43680,17 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>4700000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>275</v>
+        <v>90</v>
       </c>
       <c r="E1545" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F1545" t="n">
         <v>31</v>
@@ -43699,7 +43699,7 @@
         <v>21</v>
       </c>
       <c r="H1545" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,26 +43708,26 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>23000000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1546" t="n">
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="F1546" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="G1546" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1546" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1547">
@@ -43736,26 +43736,26 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>48000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1547" t="n">
-        <v>667</v>
+        <v>400</v>
       </c>
       <c r="F1547" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="G1547" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1547" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1548">
@@ -43764,17 +43764,17 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>22500000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="E1548" t="n">
-        <v>366</v>
+        <v>95</v>
       </c>
       <c r="F1548" t="n">
         <v>3</v>
@@ -43783,7 +43783,7 @@
         <v>3</v>
       </c>
       <c r="H1548" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1549">
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>8500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E1549" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1549" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1549" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1549" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,23 +43820,23 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>8000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1550" t="n">
-        <v>165</v>
+        <v>625</v>
       </c>
       <c r="F1550" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1550" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1550" t="n">
         <v>24</v>
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>32000000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E1551" t="n">
-        <v>703</v>
+        <v>528</v>
       </c>
       <c r="F1551" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G1551" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H1551" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>4500000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>250</v>
+        <v>520</v>
       </c>
       <c r="E1552" t="n">
-        <v>196</v>
+        <v>714</v>
       </c>
       <c r="F1552" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G1552" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H1552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>6800000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1553" t="n">
         <v>400</v>
       </c>
       <c r="E1553" t="n">
-        <v>240</v>
+        <v>526</v>
       </c>
       <c r="F1553" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1553" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1553" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>3500000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1554" t="n">
-        <v>135</v>
+        <v>650</v>
       </c>
       <c r="F1554" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1554" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H1554" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,23 +43960,23 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>2900000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="E1555" t="n">
-        <v>91</v>
+        <v>345</v>
       </c>
       <c r="F1555" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1555" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1555" t="n">
         <v>11</v>
@@ -43988,26 +43988,26 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>14800000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1556" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="F1556" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1556" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1556" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1557">
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>15700000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E1557" t="n">
-        <v>400</v>
+        <v>1722</v>
       </c>
       <c r="F1557" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1557" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1557" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,26 +44044,26 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>1200000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="E1558" t="n">
-        <v>95</v>
+        <v>570</v>
       </c>
       <c r="F1558" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1558" t="n">
         <v>3</v>
       </c>
       <c r="H1558" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1559">
@@ -44072,23 +44072,23 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>1400000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E1559" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F1559" t="n">
         <v>3</v>
       </c>
       <c r="G1559" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1559" t="n">
         <v>1</v>
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>32000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="E1560" t="n">
-        <v>634</v>
+        <v>260</v>
       </c>
       <c r="F1560" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1560" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H1560" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>18500000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>400</v>
+        <v>56</v>
       </c>
       <c r="E1561" t="n">
-        <v>625</v>
+        <v>54</v>
       </c>
       <c r="F1561" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1561" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1561" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,26 +44156,26 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>12800000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1562" t="n">
         <v>350</v>
       </c>
       <c r="E1562" t="n">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="F1562" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1562" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H1562" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,20 +44184,20 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>20000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>550</v>
+        <v>318</v>
       </c>
       <c r="E1563" t="n">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="F1563" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1563" t="n">
         <v>4</v>
@@ -44212,23 +44212,23 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>50000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>520</v>
+        <v>120</v>
       </c>
       <c r="E1564" t="n">
-        <v>714</v>
+        <v>65</v>
       </c>
       <c r="F1564" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1564" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1564" t="n">
         <v>2</v>
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>7900000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="E1565" t="n">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="F1565" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1565" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>18000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>400</v>
+        <v>185</v>
       </c>
       <c r="E1566" t="n">
-        <v>526</v>
+        <v>300</v>
       </c>
       <c r="F1566" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1566" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1566" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>97000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1567" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1567" t="n">
         <v>800</v>
       </c>
-      <c r="E1567" t="n">
-        <v>650</v>
-      </c>
       <c r="F1567" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="G1567" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="H1567" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>11000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>300</v>
+        <v>775</v>
       </c>
       <c r="E1568" t="n">
-        <v>345</v>
+        <v>925</v>
       </c>
       <c r="F1568" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1568" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1568" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>13500000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="E1569" t="n">
-        <v>181</v>
+        <v>664</v>
       </c>
       <c r="F1569" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1569" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1569" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>4200000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E1570" t="n">
-        <v>90</v>
+        <v>301</v>
       </c>
       <c r="F1570" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G1570" t="n">
         <v>31</v>
       </c>
       <c r="H1570" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>17200000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="E1571" t="n">
-        <v>1722</v>
+        <v>29</v>
       </c>
       <c r="F1571" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1571" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>30000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="E1572" t="n">
-        <v>570</v>
+        <v>208</v>
       </c>
       <c r="F1572" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1572" t="n">
         <v>3</v>
       </c>
       <c r="H1572" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>2500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="E1573" t="n">
-        <v>68</v>
+        <v>346</v>
       </c>
       <c r="F1573" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1573" t="n">
         <v>4</v>
       </c>
       <c r="H1573" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>6500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>400</v>
+        <v>457</v>
       </c>
       <c r="E1574" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="F1574" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1574" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H1574" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,26 +44520,26 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>830000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>56</v>
+        <v>452</v>
       </c>
       <c r="E1575" t="n">
-        <v>54</v>
+        <v>1165</v>
       </c>
       <c r="F1575" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1575" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1575" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1576">
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>11000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="E1576" t="n">
-        <v>498</v>
+        <v>1000</v>
       </c>
       <c r="F1576" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1576" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1576" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,17 +44576,17 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>12500000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1577" t="n">
-        <v>318</v>
+        <v>470</v>
       </c>
       <c r="E1577" t="n">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="F1577" t="n">
         <v>5</v>
@@ -44595,7 +44595,7 @@
         <v>4</v>
       </c>
       <c r="H1577" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1578">
@@ -44604,26 +44604,26 @@
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>1400000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1578" t="n">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="E1578" t="n">
-        <v>65</v>
+        <v>627</v>
       </c>
       <c r="F1578" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1578" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1578" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1579">
@@ -44632,26 +44632,26 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>9200000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1579" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="E1579" t="n">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="F1579" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1579" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1579" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1580">
@@ -44660,26 +44660,26 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>16500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1580" t="n">
-        <v>185</v>
+        <v>1600</v>
       </c>
       <c r="E1580" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="F1580" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G1580" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H1580" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1581">
@@ -44688,26 +44688,26 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Dijual Rumah Area Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>25000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1581" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E1581" t="n">
-        <v>800</v>
+        <v>540</v>
       </c>
       <c r="F1581" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1581" t="n">
         <v>5</v>
       </c>
       <c r="H1581" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1582">
@@ -44716,26 +44716,26 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>120000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1582" t="n">
-        <v>775</v>
+        <v>650</v>
       </c>
       <c r="E1582" t="n">
-        <v>925</v>
+        <v>1230</v>
       </c>
       <c r="F1582" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1582" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1582" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1583">
@@ -44744,26 +44744,26 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>9500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1583" t="n">
-        <v>320</v>
+        <v>750</v>
       </c>
       <c r="E1583" t="n">
-        <v>664</v>
+        <v>425</v>
       </c>
       <c r="F1583" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1583" t="n">
         <v>51</v>
       </c>
-      <c r="G1583" t="n">
-        <v>41</v>
-      </c>
       <c r="H1583" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1584">
@@ -44772,26 +44772,26 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>6000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1584" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1584" t="n">
-        <v>301</v>
+        <v>1050</v>
       </c>
       <c r="F1584" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G1584" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1584" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1585">
@@ -44800,26 +44800,26 @@
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>890000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1585" t="n">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="E1585" t="n">
-        <v>29</v>
+        <v>1554</v>
       </c>
       <c r="F1585" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="G1585" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="H1585" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1586">
@@ -44828,26 +44828,26 @@
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>80000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1586" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="E1586" t="n">
-        <v>1050</v>
+        <v>70</v>
       </c>
       <c r="F1586" t="n">
         <v>41</v>
       </c>
       <c r="G1586" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H1586" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1587">
@@ -44856,26 +44856,26 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>2600000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1587" t="n">
-        <v>88</v>
+        <v>550</v>
       </c>
       <c r="E1587" t="n">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="F1587" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1587" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1587" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1588">
@@ -44884,26 +44884,26 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>15500000000</v>
+        <v>7950000000</v>
       </c>
       <c r="D1588" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="E1588" t="n">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="F1588" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1588" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H1588" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1589">
@@ -44912,26 +44912,26 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>2500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1589" t="n">
-        <v>135</v>
+        <v>1500</v>
       </c>
       <c r="E1589" t="n">
-        <v>30</v>
+        <v>475</v>
       </c>
       <c r="F1589" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G1589" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1589" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1590">
@@ -44940,26 +44940,26 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>9000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1590" t="n">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E1590" t="n">
-        <v>208</v>
+        <v>76</v>
       </c>
       <c r="F1590" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1591">
@@ -44968,26 +44968,26 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>2830000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1591" t="n">
-        <v>112</v>
+        <v>366</v>
       </c>
       <c r="E1591" t="n">
-        <v>70</v>
+        <v>393</v>
       </c>
       <c r="F1591" t="n">
         <v>3</v>
       </c>
       <c r="G1591" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1591" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1592">
@@ -44996,26 +44996,26 @@
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>32000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1592" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1592" t="n">
-        <v>346</v>
+        <v>518</v>
       </c>
       <c r="F1592" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1592" t="n">
         <v>4</v>
       </c>
       <c r="H1592" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1593">
@@ -45024,26 +45024,26 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>55000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1593" t="n">
-        <v>457</v>
+        <v>69</v>
       </c>
       <c r="E1593" t="n">
-        <v>500</v>
+        <v>63</v>
       </c>
       <c r="F1593" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1593" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1593" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1594">
@@ -45052,26 +45052,26 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>55000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1594" t="n">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="E1594" t="n">
-        <v>1165</v>
+        <v>160</v>
       </c>
       <c r="F1594" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1594" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1594" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1595">
@@ -45080,26 +45080,26 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>62000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1595" t="n">
-        <v>880</v>
+        <v>600</v>
       </c>
       <c r="E1595" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="F1595" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1595" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1595" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1596">
@@ -45108,26 +45108,26 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>17500000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1596" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E1596" t="n">
-        <v>412</v>
+        <v>899</v>
       </c>
       <c r="F1596" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1596" t="n">
         <v>4</v>
       </c>
       <c r="H1596" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1597">
@@ -45136,26 +45136,26 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>40000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1597" t="n">
-        <v>1050</v>
+        <v>340</v>
       </c>
       <c r="E1597" t="n">
-        <v>627</v>
+        <v>350</v>
       </c>
       <c r="F1597" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1597" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H1597" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1598">
@@ -45164,26 +45164,26 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>7500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1598" t="n">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="E1598" t="n">
-        <v>404</v>
+        <v>90</v>
       </c>
       <c r="F1598" t="n">
         <v>3</v>
       </c>
       <c r="G1598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1598" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1599">
@@ -45192,26 +45192,26 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>55000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1599" t="n">
-        <v>1600</v>
+        <v>135</v>
       </c>
       <c r="E1599" t="n">
-        <v>1800</v>
+        <v>30</v>
       </c>
       <c r="F1599" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1599" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1599" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1600">
@@ -45220,26 +45220,26 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>49000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1600" t="n">
-        <v>1100</v>
+        <v>90</v>
       </c>
       <c r="E1600" t="n">
-        <v>540</v>
+        <v>80</v>
       </c>
       <c r="F1600" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1600" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H1600" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1601">
@@ -45248,26 +45248,782 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1601" t="n">
+        <v>90000000000</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>2382</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1601" t="n">
+        <v>81</v>
+      </c>
+      <c r="H1601" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1602" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1602" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1602" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+        </is>
+      </c>
+      <c r="C1603" t="n">
+        <v>8500000000</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1603" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1603" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1604" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1604" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1604" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+        </is>
+      </c>
+      <c r="C1605" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>165</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1605" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1605" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="D1606" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1606" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1606" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>95</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>95</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1607" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1607" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Dijual Rumah bisa Buatusaha</t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>610</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>310</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1608" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1608" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1609" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1609" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
         <v>32000000000</v>
       </c>
-      <c r="D1601" t="n">
-        <v>650</v>
-      </c>
-      <c r="E1601" t="n">
-        <v>1230</v>
-      </c>
-      <c r="F1601" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1601" t="n">
-        <v>4</v>
-      </c>
-      <c r="H1601" t="n">
-        <v>5</v>
+      <c r="D1610" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1610" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1610" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>16899999999</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1611" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>4099999999</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>160</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1612" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>21000000000</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1613" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1614" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>1614</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>281000000000</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>6250</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>104</v>
+      </c>
+      <c r="H1615" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Rumah Besar di Jl. Wijaya.</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>579</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1616" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="n">
+        <v>1616</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>750</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>607</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>74</v>
+      </c>
+      <c r="H1617" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="n">
+        <v>1617</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1618" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="n">
+        <v>1618</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
+        <v>11500000000</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>475</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1619" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>28500000000</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>637</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1620" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1620" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1621" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1621" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="n">
+        <v>1621</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>530</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1622" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1622" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>450</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>931</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1623" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1623" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>676</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1624" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1624" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>3900000000</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>264</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>141</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1625" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>950</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>704</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1626" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1626" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>60</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1627" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1627" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>93</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1628" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1628" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1628"/>
+  <dimension ref="A1:H1661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>2900000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1433" t="n">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="E1433" t="n">
-        <v>155</v>
+        <v>404</v>
       </c>
       <c r="F1433" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1433" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>21000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1434" t="n">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="E1434" t="n">
-        <v>404</v>
+        <v>244</v>
       </c>
       <c r="F1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>4099999999</v>
+        <v>6900000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="E1435" t="n">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="F1435" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1436" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1436" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1436" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>4900000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>360</v>
+        <v>850</v>
       </c>
       <c r="E1437" t="n">
-        <v>127</v>
+        <v>1925</v>
       </c>
       <c r="F1437" t="n">
         <v>1</v>
       </c>
       <c r="G1437" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,23 +40684,23 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>41000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>850</v>
+        <v>360</v>
       </c>
       <c r="E1438" t="n">
-        <v>1925</v>
+        <v>261</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1438" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1438" t="n">
         <v>1</v>
@@ -40712,20 +40712,20 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="E1439" t="n">
-        <v>261</v>
+        <v>703</v>
       </c>
       <c r="F1439" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1439" t="n">
         <v>4</v>
@@ -40740,17 +40740,17 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E1440" t="n">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F1440" t="n">
         <v>2</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>18500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1441" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1441" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,23 +40796,23 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>62000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>881</v>
+        <v>614</v>
       </c>
       <c r="E1442" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="F1442" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1442" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1442" t="n">
         <v>1</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>614</v>
+        <v>720</v>
       </c>
       <c r="E1443" t="n">
-        <v>921</v>
+        <v>634</v>
       </c>
       <c r="F1443" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1443" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1444" t="n">
-        <v>634</v>
+        <v>257</v>
       </c>
       <c r="F1444" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1444" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>9700000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1445" t="n">
-        <v>257</v>
+        <v>730</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1445" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>45000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1446" t="n">
-        <v>730</v>
+        <v>176</v>
       </c>
       <c r="F1446" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>4420000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1447" t="n">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="F1447" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>15300000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1448" t="n">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F1448" t="n">
         <v>4</v>
       </c>
       <c r="G1448" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>6860000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1449" t="n">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="F1449" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1449" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>7800000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E1450" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F1450" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1450" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>4150000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="E1451" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F1451" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1451" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>3320000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>198</v>
+        <v>600</v>
       </c>
       <c r="E1452" t="n">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="F1452" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1452" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,23 +41104,23 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1453" t="n">
-        <v>21500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1453" t="n">
-        <v>674</v>
+        <v>123</v>
       </c>
       <c r="F1453" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1453" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1453" t="n">
         <v>1</v>
@@ -41132,20 +41132,20 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1454" t="n">
         <v>2550000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E1454" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F1454" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1454" t="n">
         <v>2</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>2550000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="E1455" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="F1455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="E1456" t="n">
-        <v>461</v>
+        <v>179</v>
       </c>
       <c r="F1456" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1456" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1456" t="n">
         <v>1</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>6500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1457" t="n">
-        <v>179</v>
+        <v>274</v>
       </c>
       <c r="F1457" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
+          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>9800000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>150</v>
+        <v>796</v>
       </c>
       <c r="E1458" t="n">
-        <v>274</v>
+        <v>871</v>
       </c>
       <c r="F1458" t="n">
         <v>2</v>
       </c>
       <c r="G1458" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
+          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>40000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>796</v>
+        <v>300</v>
       </c>
       <c r="E1459" t="n">
-        <v>871</v>
+        <v>535</v>
       </c>
       <c r="F1459" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1459" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,23 +41300,23 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>7500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1460" t="n">
-        <v>535</v>
+        <v>1180</v>
       </c>
       <c r="F1460" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1460" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1460" t="n">
         <v>1</v>
@@ -41328,17 +41328,17 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>25000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1461" t="n">
-        <v>1180</v>
+        <v>60</v>
       </c>
       <c r="F1461" t="n">
         <v>2</v>
@@ -41356,17 +41356,17 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>7900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E1462" t="n">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="F1462" t="n">
         <v>2</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>4500000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="E1463" t="n">
-        <v>276</v>
+        <v>822</v>
       </c>
       <c r="F1463" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1463" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>29500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>609</v>
+        <v>60</v>
       </c>
       <c r="E1464" t="n">
-        <v>822</v>
+        <v>60</v>
       </c>
       <c r="F1464" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1464" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>2600000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E1465" t="n">
         <v>60</v>
       </c>
       <c r="F1465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>2000000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E1466" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F1466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,23 +41496,23 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>2300000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="E1467" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="F1467" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1467" t="n">
         <v>1</v>
@@ -41524,17 +41524,17 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>6400000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>395</v>
+        <v>60</v>
       </c>
       <c r="E1468" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="F1468" t="n">
         <v>2</v>
@@ -41552,23 +41552,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>2830000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1469" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F1469" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1469" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1469" t="n">
         <v>1</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>2350000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1470" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F1470" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1470" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>6400000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="E1471" t="n">
-        <v>60</v>
+        <v>544</v>
       </c>
       <c r="F1471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1471" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,23 +41636,23 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>28000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="E1472" t="n">
-        <v>544</v>
+        <v>196</v>
       </c>
       <c r="F1472" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1472" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1472" t="n">
         <v>1</v>
@@ -41664,20 +41664,20 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>4500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1473" t="n">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="F1473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1473" t="n">
         <v>3</v>
@@ -41692,20 +41692,20 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>11800000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="E1474" t="n">
-        <v>696</v>
+        <v>942</v>
       </c>
       <c r="F1474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1474" t="n">
         <v>3</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>25000000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E1475" t="n">
-        <v>942</v>
+        <v>864</v>
       </c>
       <c r="F1475" t="n">
         <v>2</v>
       </c>
       <c r="G1475" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>17700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1476" t="n">
-        <v>864</v>
+        <v>600</v>
       </c>
       <c r="F1476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>8000000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1477" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F1477" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>70000000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E1478" t="n">
-        <v>1300</v>
+        <v>1585</v>
       </c>
       <c r="F1478" t="n">
         <v>4</v>
       </c>
       <c r="G1478" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>275000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>1300</v>
+        <v>52</v>
       </c>
       <c r="E1479" t="n">
-        <v>1585</v>
+        <v>27</v>
       </c>
       <c r="F1479" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,23 +41860,23 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>1100000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>52</v>
+        <v>366</v>
       </c>
       <c r="E1480" t="n">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="F1480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1480" t="n">
         <v>1</v>
@@ -41888,17 +41888,17 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>22500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="E1481" t="n">
-        <v>366</v>
+        <v>154</v>
       </c>
       <c r="F1481" t="n">
         <v>1</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>6800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1482" t="n">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="F1482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1482" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,23 +41944,23 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>1700000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="E1483" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="F1483" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1483" t="n">
         <v>1</v>
@@ -41972,17 +41972,17 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>11300000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>600</v>
+        <v>158</v>
       </c>
       <c r="E1484" t="n">
-        <v>535</v>
+        <v>63</v>
       </c>
       <c r="F1484" t="n">
         <v>1</v>
@@ -42000,14 +42000,14 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>2100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E1485" t="n">
         <v>63</v>
@@ -42028,20 +42028,20 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E1486" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F1486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1486" t="n">
         <v>3</v>
@@ -42056,23 +42056,23 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>7800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1487" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F1487" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1487" t="n">
         <v>1</v>
@@ -42084,23 +42084,23 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>10000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E1488" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="F1488" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1488" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1488" t="n">
         <v>1</v>
@@ -42112,17 +42112,17 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>6000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="E1489" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F1489" t="n">
         <v>5</v>
@@ -42140,20 +42140,20 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>7300000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>501</v>
+        <v>240</v>
       </c>
       <c r="E1490" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F1490" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -42168,23 +42168,23 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>5000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E1491" t="n">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="F1491" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1491" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1491" t="n">
         <v>1</v>
@@ -42196,23 +42196,23 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>8500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1492" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1492" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1492" t="n">
         <v>1</v>
@@ -42224,23 +42224,23 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>2000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1493" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F1493" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1493" t="n">
         <v>1</v>
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>10000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="E1494" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F1494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1494" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,26 +42280,26 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>1750000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="E1495" t="n">
-        <v>120</v>
+        <v>958</v>
       </c>
       <c r="F1495" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1495" t="n">
         <v>21</v>
       </c>
       <c r="H1495" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1496">
@@ -42308,23 +42308,23 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>12500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>481</v>
+        <v>810</v>
       </c>
       <c r="E1496" t="n">
-        <v>958</v>
+        <v>370</v>
       </c>
       <c r="F1496" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1496" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1496" t="n">
         <v>42</v>
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>48000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>810</v>
+        <v>85</v>
       </c>
       <c r="E1497" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1497" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1497" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1497" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1498" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1498" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1498" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>6900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E1499" t="n">
-        <v>76</v>
+        <v>696</v>
       </c>
       <c r="F1499" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1499" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1499" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,26 +42420,26 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>12000000000</v>
+        <v>21300000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1500" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="F1500" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1500" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1500" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1501">
@@ -42448,17 +42448,17 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>21300000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1501" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="F1501" t="n">
         <v>5</v>
@@ -42476,17 +42476,17 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>38000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1502" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
       <c r="F1502" t="n">
         <v>5</v>
@@ -42504,23 +42504,23 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>19000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>600</v>
+        <v>325</v>
       </c>
       <c r="E1503" t="n">
-        <v>584</v>
+        <v>931</v>
       </c>
       <c r="F1503" t="n">
         <v>5</v>
       </c>
       <c r="G1503" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1503" t="n">
         <v>4</v>
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>22000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1504" t="n">
-        <v>931</v>
+        <v>550</v>
       </c>
       <c r="F1504" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1504" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1504" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,26 +42560,26 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>32000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1505" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1505" t="n">
-        <v>550</v>
+        <v>1925</v>
       </c>
       <c r="F1505" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1505" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1505" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1506">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
+          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>42000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="E1507" t="n">
-        <v>1925</v>
+        <v>620</v>
       </c>
       <c r="F1507" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1507" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1507" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>17000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="E1508" t="n">
-        <v>620</v>
+        <v>1295</v>
       </c>
       <c r="F1508" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1508" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1508" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,26 +42672,26 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>35000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="E1509" t="n">
-        <v>1295</v>
+        <v>201</v>
       </c>
       <c r="F1509" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G1509" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1509" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1510">
@@ -42700,23 +42700,23 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>3600000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="E1510" t="n">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="F1510" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1510" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1510" t="n">
         <v>11</v>
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>5500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1511" t="n">
-        <v>263</v>
+        <v>1180</v>
       </c>
       <c r="F1511" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1511" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H1511" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>25000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1512" t="n">
-        <v>1180</v>
+        <v>242</v>
       </c>
       <c r="F1512" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1512" t="n">
         <v>11</v>
-      </c>
-      <c r="G1512" t="n">
-        <v>10</v>
-      </c>
-      <c r="H1512" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,26 +42784,26 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1513" t="n">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="F1513" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1513" t="n">
         <v>4</v>
       </c>
       <c r="H1513" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1514">
@@ -42812,23 +42812,23 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>6900000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>375</v>
+        <v>610</v>
       </c>
       <c r="E1514" t="n">
-        <v>76</v>
+        <v>822</v>
       </c>
       <c r="F1514" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1514" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1514" t="n">
         <v>22</v>
@@ -42840,23 +42840,23 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>28500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>610</v>
+        <v>375</v>
       </c>
       <c r="E1515" t="n">
-        <v>822</v>
+        <v>76</v>
       </c>
       <c r="F1515" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1515" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1515" t="n">
         <v>22</v>
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>6900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>375</v>
+        <v>245</v>
       </c>
       <c r="E1516" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1516" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1516" t="n">
         <v>4</v>
       </c>
       <c r="H1516" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>17000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>245</v>
+        <v>1220</v>
       </c>
       <c r="E1517" t="n">
-        <v>260</v>
+        <v>1430</v>
       </c>
       <c r="F1517" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1517" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1517" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,26 +42924,26 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>100000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>1220</v>
+        <v>600</v>
       </c>
       <c r="E1518" t="n">
-        <v>1430</v>
+        <v>575</v>
       </c>
       <c r="F1518" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1518" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1518" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1519">
@@ -42952,23 +42952,23 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
+          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>15800000000</v>
+        <v>12700000000</v>
       </c>
       <c r="D1519" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1519" t="n">
-        <v>575</v>
+        <v>209</v>
       </c>
       <c r="F1519" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1519" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1519" t="n">
         <v>22</v>
@@ -42980,23 +42980,23 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>12700000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1520" t="n">
         <v>450</v>
       </c>
       <c r="E1520" t="n">
-        <v>209</v>
+        <v>612</v>
       </c>
       <c r="F1520" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1520" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H1520" t="n">
         <v>22</v>
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>20000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1521" t="n">
-        <v>612</v>
+        <v>1925</v>
       </c>
       <c r="F1521" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1521" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H1521" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>49000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="E1522" t="n">
-        <v>1925</v>
+        <v>2500</v>
       </c>
       <c r="F1522" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G1522" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1522" t="n">
-        <v>210</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>Rumah Terawat dan Asri di Pondok Indah</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>35000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="E1523" t="n">
-        <v>2500</v>
+        <v>750</v>
       </c>
       <c r="F1523" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G1523" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="H1523" t="n">
-        <v>412</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Terawat dan Asri di Pondok Indah</t>
+          <t>Rumah Asri Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>25000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>630</v>
+        <v>300</v>
       </c>
       <c r="E1524" t="n">
-        <v>750</v>
+        <v>430</v>
       </c>
       <c r="F1524" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G1524" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H1524" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,26 +43120,26 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni di Pondok Indah</t>
+          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>17500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1525" t="n">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="F1525" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1525" t="n">
         <v>31</v>
       </c>
       <c r="H1525" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1526">
@@ -43148,17 +43148,17 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>6800000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1526" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1526" t="n">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="F1526" t="n">
         <v>41</v>
@@ -43167,7 +43167,7 @@
         <v>31</v>
       </c>
       <c r="H1526" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1527">
@@ -43176,26 +43176,26 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>5800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1527" t="n">
         <v>250</v>
       </c>
       <c r="E1527" t="n">
-        <v>305</v>
+        <v>179</v>
       </c>
       <c r="F1527" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1527" t="n">
         <v>41</v>
       </c>
-      <c r="G1527" t="n">
-        <v>31</v>
-      </c>
       <c r="H1527" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1528">
@@ -43204,26 +43204,26 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
+          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>6500000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1528" t="n">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="F1528" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1528" t="n">
         <v>41</v>
       </c>
       <c r="H1528" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1529">
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>13000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="E1529" t="n">
-        <v>324</v>
+        <v>106</v>
       </c>
       <c r="F1529" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1529" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H1529" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,26 +43260,26 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>1200000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>65</v>
+        <v>850</v>
       </c>
       <c r="E1530" t="n">
-        <v>106</v>
+        <v>1800</v>
       </c>
       <c r="F1530" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1530" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1530" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>40000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>850</v>
+        <v>609</v>
       </c>
       <c r="E1531" t="n">
-        <v>1800</v>
+        <v>822</v>
       </c>
       <c r="F1531" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1531" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H1531" t="n">
-        <v>220</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>30000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>609</v>
+        <v>400</v>
       </c>
       <c r="E1532" t="n">
-        <v>822</v>
+        <v>580</v>
       </c>
       <c r="F1532" t="n">
         <v>51</v>
       </c>
       <c r="G1532" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H1532" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>12500000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1533" t="n">
-        <v>580</v>
+        <v>257</v>
       </c>
       <c r="F1533" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G1533" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1533" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>9600000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1534" t="n">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="F1534" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G1534" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1534" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>3500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1535" t="n">
-        <v>388</v>
+        <v>237</v>
       </c>
       <c r="F1535" t="n">
         <v>4</v>
       </c>
       <c r="G1535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1535" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>1700000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1536" t="n">
-        <v>350</v>
+        <v>145</v>
       </c>
       <c r="E1536" t="n">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="F1536" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1536" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>2550000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E1537" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F1537" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1537" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>2000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="E1538" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="F1538" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1538" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1538" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>4700000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1539" t="n">
-        <v>275</v>
+        <v>800</v>
       </c>
       <c r="E1539" t="n">
-        <v>130</v>
+        <v>667</v>
       </c>
       <c r="F1539" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1539" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H1539" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>48000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1540" t="n">
-        <v>667</v>
+        <v>703</v>
       </c>
       <c r="F1540" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G1540" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1540" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,26 +43568,26 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>32000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1541" t="n">
-        <v>703</v>
+        <v>196</v>
       </c>
       <c r="F1541" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G1541" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1541" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1542">
@@ -43596,26 +43596,26 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>4500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1542" t="n">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="F1542" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1542" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1542" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1543">
@@ -43624,26 +43624,26 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>6800000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1543" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="F1543" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1543" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1543" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1544">
@@ -43652,26 +43652,26 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>3500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E1544" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="F1544" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1544" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1544" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1545">
@@ -43680,26 +43680,26 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>2900000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E1545" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
       <c r="F1545" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1545" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1545" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,26 +43708,26 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>14800000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1546" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F1546" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1546" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1546" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1547">
@@ -43736,26 +43736,26 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>15700000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="E1547" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="F1547" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1547" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1547" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1548">
@@ -43764,17 +43764,17 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
+          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>1200000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E1548" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F1548" t="n">
         <v>3</v>
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
+          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>1400000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1549" t="n">
-        <v>60</v>
+        <v>625</v>
       </c>
       <c r="F1549" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1549" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1549" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,26 +43820,26 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
+          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>18500000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1550" t="n">
-        <v>625</v>
+        <v>528</v>
       </c>
       <c r="F1550" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1550" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H1550" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1551">
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
+          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>12800000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="E1551" t="n">
-        <v>528</v>
+        <v>714</v>
       </c>
       <c r="F1551" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1551" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H1551" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
+          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>50000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="E1552" t="n">
-        <v>714</v>
+        <v>526</v>
       </c>
       <c r="F1552" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1552" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
+          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>18000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1553" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1553" t="n">
-        <v>526</v>
+        <v>650</v>
       </c>
       <c r="F1553" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1553" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H1553" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
+          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>97000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1554" t="n">
-        <v>650</v>
+        <v>345</v>
       </c>
       <c r="F1554" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1554" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1554" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,26 +43960,26 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
+          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>11000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1555" t="n">
-        <v>345</v>
+        <v>90</v>
       </c>
       <c r="F1555" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1555" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1555" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1556">
@@ -43988,26 +43988,26 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
+          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>4200000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1556" t="n">
-        <v>90</v>
+        <v>1722</v>
       </c>
       <c r="F1556" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1556" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1556" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1557">
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>17200000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="E1557" t="n">
-        <v>1722</v>
+        <v>68</v>
       </c>
       <c r="F1557" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1557" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1557" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,26 +44044,26 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>30000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="E1558" t="n">
-        <v>570</v>
+        <v>260</v>
       </c>
       <c r="F1558" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1558" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H1558" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1559">
@@ -44072,23 +44072,23 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>2500000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="E1559" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F1559" t="n">
         <v>3</v>
       </c>
       <c r="G1559" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1559" t="n">
         <v>1</v>
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>6500000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1560" t="n">
-        <v>260</v>
+        <v>498</v>
       </c>
       <c r="F1560" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1560" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1560" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>830000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>56</v>
+        <v>318</v>
       </c>
       <c r="E1561" t="n">
-        <v>54</v>
+        <v>497</v>
       </c>
       <c r="F1561" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1561" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1561" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,17 +44156,17 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>11000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="E1562" t="n">
-        <v>498</v>
+        <v>65</v>
       </c>
       <c r="F1562" t="n">
         <v>3</v>
@@ -44175,7 +44175,7 @@
         <v>2</v>
       </c>
       <c r="H1562" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,26 +44184,26 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>12500000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>318</v>
+        <v>440</v>
       </c>
       <c r="E1563" t="n">
-        <v>497</v>
+        <v>317</v>
       </c>
       <c r="F1563" t="n">
         <v>5</v>
       </c>
       <c r="G1563" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1563" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1564">
@@ -44212,26 +44212,26 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>1400000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E1564" t="n">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="F1564" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1564" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1564" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1565">
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>9200000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="E1565" t="n">
-        <v>317</v>
+        <v>800</v>
       </c>
       <c r="F1565" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1565" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1565" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,23 +44268,23 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>16500000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>185</v>
+        <v>775</v>
       </c>
       <c r="E1566" t="n">
-        <v>300</v>
+        <v>925</v>
       </c>
       <c r="F1566" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G1566" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1566" t="n">
         <v>22</v>
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Dijual Rumah Area Jakarta Selatan</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>25000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="E1567" t="n">
-        <v>800</v>
+        <v>664</v>
       </c>
       <c r="F1567" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1567" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1567" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>120000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>775</v>
+        <v>300</v>
       </c>
       <c r="E1568" t="n">
-        <v>925</v>
+        <v>301</v>
       </c>
       <c r="F1568" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G1568" t="n">
         <v>31</v>
       </c>
       <c r="H1568" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>9500000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="E1569" t="n">
-        <v>664</v>
+        <v>29</v>
       </c>
       <c r="F1569" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1569" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1569" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>6000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1570" t="n">
         <v>300</v>
       </c>
       <c r="E1570" t="n">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="F1570" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G1570" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1570" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>890000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>56</v>
+        <v>400</v>
       </c>
       <c r="E1571" t="n">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="F1571" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1571" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1571" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>9000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="E1572" t="n">
-        <v>208</v>
+        <v>500</v>
       </c>
       <c r="F1572" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1572" t="n">
         <v>3</v>
       </c>
       <c r="H1572" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>32000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="E1573" t="n">
-        <v>346</v>
+        <v>1165</v>
       </c>
       <c r="F1573" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1573" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1573" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>55000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>457</v>
+        <v>880</v>
       </c>
       <c r="E1574" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F1574" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1574" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1574" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,26 +44520,26 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>55000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="E1575" t="n">
-        <v>1165</v>
+        <v>412</v>
       </c>
       <c r="F1575" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1575" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1575" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1576">
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>62000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>880</v>
+        <v>1050</v>
       </c>
       <c r="E1576" t="n">
-        <v>1000</v>
+        <v>627</v>
       </c>
       <c r="F1576" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1576" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1576" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,23 +44576,23 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>17500000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1577" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="E1577" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F1577" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1577" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1577" t="n">
         <v>4</v>
@@ -44604,26 +44604,26 @@
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>40000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1578" t="n">
-        <v>1050</v>
+        <v>1600</v>
       </c>
       <c r="E1578" t="n">
-        <v>627</v>
+        <v>1800</v>
       </c>
       <c r="F1578" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1578" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1578" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1579">
@@ -44632,23 +44632,23 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>7500000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1579" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1579" t="n">
-        <v>404</v>
+        <v>540</v>
       </c>
       <c r="F1579" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1579" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1579" t="n">
         <v>4</v>
@@ -44660,26 +44660,26 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>55000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1580" t="n">
-        <v>1600</v>
+        <v>650</v>
       </c>
       <c r="E1580" t="n">
-        <v>1800</v>
+        <v>1230</v>
       </c>
       <c r="F1580" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1580" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1580" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1581">
@@ -44688,26 +44688,26 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>49000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1581" t="n">
-        <v>1100</v>
+        <v>750</v>
       </c>
       <c r="E1581" t="n">
-        <v>540</v>
+        <v>425</v>
       </c>
       <c r="F1581" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G1581" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1581" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1582">
@@ -44716,26 +44716,26 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>32000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1582" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="E1582" t="n">
-        <v>1230</v>
+        <v>1050</v>
       </c>
       <c r="F1582" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="G1582" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1582" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1583">
@@ -44744,26 +44744,26 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>25000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1583" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E1583" t="n">
-        <v>425</v>
+        <v>1554</v>
       </c>
       <c r="F1583" t="n">
         <v>71</v>
       </c>
       <c r="G1583" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H1583" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1584">
@@ -44772,26 +44772,26 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>23000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1584" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="E1584" t="n">
-        <v>1050</v>
+        <v>70</v>
       </c>
       <c r="F1584" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G1584" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1584" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1585">
@@ -44800,26 +44800,26 @@
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>52500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1585" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E1585" t="n">
-        <v>1554</v>
+        <v>450</v>
       </c>
       <c r="F1585" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="G1585" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1585" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1586">
@@ -44828,26 +44828,26 @@
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
+          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>1700000000</v>
+        <v>7950000000</v>
       </c>
       <c r="D1586" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="E1586" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="F1586" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1586" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1586" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1587">
@@ -44856,26 +44856,26 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>20000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1587" t="n">
-        <v>550</v>
+        <v>1500</v>
       </c>
       <c r="E1587" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="F1587" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G1587" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1587" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1588">
@@ -44884,26 +44884,26 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
+          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>7950000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1588" t="n">
-        <v>260</v>
+        <v>366</v>
       </c>
       <c r="E1588" t="n">
-        <v>240</v>
+        <v>393</v>
       </c>
       <c r="F1588" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1588" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1588" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1589">
@@ -44912,26 +44912,26 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>30000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1589" t="n">
-        <v>1500</v>
+        <v>360</v>
       </c>
       <c r="E1589" t="n">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="F1589" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G1589" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1589" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1590">
@@ -44940,23 +44940,23 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>7900000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1590" t="n">
-        <v>375</v>
+        <v>69</v>
       </c>
       <c r="E1590" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F1590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1590" t="n">
         <v>1</v>
@@ -44968,26 +44968,26 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>20000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1591" t="n">
-        <v>366</v>
+        <v>600</v>
       </c>
       <c r="E1591" t="n">
-        <v>393</v>
+        <v>1050</v>
       </c>
       <c r="F1591" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1591" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H1591" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1592">
@@ -44996,17 +44996,17 @@
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>24000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1592" t="n">
-        <v>360</v>
+        <v>467</v>
       </c>
       <c r="E1592" t="n">
-        <v>518</v>
+        <v>899</v>
       </c>
       <c r="F1592" t="n">
         <v>4</v>
@@ -45015,7 +45015,7 @@
         <v>4</v>
       </c>
       <c r="H1592" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1593">
@@ -45024,26 +45024,26 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>1100000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1593" t="n">
-        <v>69</v>
+        <v>340</v>
       </c>
       <c r="E1593" t="n">
-        <v>63</v>
+        <v>350</v>
       </c>
       <c r="F1593" t="n">
         <v>3</v>
       </c>
       <c r="G1593" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1593" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1594">
@@ -45052,23 +45052,23 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>6400000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1594" t="n">
-        <v>308</v>
+        <v>135</v>
       </c>
       <c r="E1594" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="F1594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1594" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1594" t="n">
         <v>1</v>
@@ -45080,26 +45080,26 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>80000000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1595" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E1595" t="n">
-        <v>1050</v>
+        <v>80</v>
       </c>
       <c r="F1595" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1595" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H1595" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1596">
@@ -45108,26 +45108,26 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>16000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1596" t="n">
-        <v>467</v>
+        <v>2700</v>
       </c>
       <c r="E1596" t="n">
-        <v>899</v>
+        <v>2382</v>
       </c>
       <c r="F1596" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="G1596" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="H1596" t="n">
-        <v>28</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1597">
@@ -45136,26 +45136,26 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>15500000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1597" t="n">
-        <v>340</v>
+        <v>120</v>
       </c>
       <c r="E1597" t="n">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="F1597" t="n">
         <v>3</v>
       </c>
       <c r="G1597" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1597" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1598">
@@ -45164,17 +45164,17 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>1700000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1598" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E1598" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F1598" t="n">
         <v>3</v>
@@ -45192,26 +45192,26 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Dijual Rumah bisa Buatusaha</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>2500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1599" t="n">
-        <v>135</v>
+        <v>610</v>
       </c>
       <c r="E1599" t="n">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="F1599" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1599" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1599" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1600">
@@ -45220,26 +45220,26 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>1950000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1600" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
       <c r="E1600" t="n">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="F1600" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1600" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H1600" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1601">
@@ -45248,26 +45248,26 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1601" t="n">
-        <v>90000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1601" t="n">
-        <v>2700</v>
+        <v>600</v>
       </c>
       <c r="E1601" t="n">
-        <v>2382</v>
+        <v>570</v>
       </c>
       <c r="F1601" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="G1601" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="H1601" t="n">
-        <v>510</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1602">
@@ -45276,26 +45276,26 @@
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
         </is>
       </c>
       <c r="C1602" t="n">
-        <v>13500000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1602" t="n">
-        <v>374</v>
+        <v>160</v>
       </c>
       <c r="E1602" t="n">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="F1602" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1602" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1602" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1603">
@@ -45304,26 +45304,26 @@
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1603" t="n">
-        <v>8500000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1603" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1603" t="n">
-        <v>200</v>
+        <v>1020</v>
       </c>
       <c r="F1603" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G1603" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1603" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1604">
@@ -45332,26 +45332,26 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
         </is>
       </c>
       <c r="C1604" t="n">
-        <v>22500000000</v>
+        <v>281000000000</v>
       </c>
       <c r="D1604" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="E1604" t="n">
-        <v>366</v>
+        <v>6250</v>
       </c>
       <c r="F1604" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="G1604" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="H1604" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1605">
@@ -45360,26 +45360,26 @@
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Besar di Jl. Wijaya.</t>
         </is>
       </c>
       <c r="C1605" t="n">
-        <v>8000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1605" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1605" t="n">
-        <v>165</v>
+        <v>579</v>
       </c>
       <c r="F1605" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1605" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1605" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1606">
@@ -45388,26 +45388,26 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
+          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1606" t="n">
-        <v>1400000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1606" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="E1606" t="n">
-        <v>60</v>
+        <v>607</v>
       </c>
       <c r="F1606" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G1606" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="H1606" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1607">
@@ -45416,26 +45416,26 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
+          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>1200000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1607" t="n">
-        <v>95</v>
+        <v>800</v>
       </c>
       <c r="E1607" t="n">
-        <v>95</v>
+        <v>475</v>
       </c>
       <c r="F1607" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G1607" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1607" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1608">
@@ -45444,26 +45444,26 @@
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Dijual Rumah bisa Buatusaha</t>
+          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>30000000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1608" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E1608" t="n">
-        <v>310</v>
+        <v>637</v>
       </c>
       <c r="F1608" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="G1608" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H1608" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1609">
@@ -45472,26 +45472,26 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1609" t="n">
-        <v>10000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1609" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E1609" t="n">
-        <v>208</v>
+        <v>530</v>
       </c>
       <c r="F1609" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1609" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1609" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1610">
@@ -45500,26 +45500,26 @@
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
         </is>
       </c>
       <c r="C1610" t="n">
-        <v>32000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1610" t="n">
-        <v>720</v>
+        <v>450</v>
       </c>
       <c r="E1610" t="n">
-        <v>634</v>
+        <v>931</v>
       </c>
       <c r="F1610" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G1610" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1610" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1611">
@@ -45528,26 +45528,26 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>16899999999</v>
+        <v>25000000000</v>
       </c>
       <c r="D1611" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="E1611" t="n">
-        <v>570</v>
+        <v>676</v>
       </c>
       <c r="F1611" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1611" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1611" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1612">
@@ -45556,23 +45556,23 @@
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>4099999999</v>
+        <v>3900000000</v>
       </c>
       <c r="D1612" t="n">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="E1612" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F1612" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1612" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1612" t="n">
         <v>12</v>
@@ -45584,26 +45584,26 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
+          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>21000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1613" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="E1613" t="n">
-        <v>1020</v>
+        <v>704</v>
       </c>
       <c r="F1613" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1613" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1613" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1614">
@@ -45612,23 +45612,23 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>2600000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1614" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1614" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F1614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1614" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1614" t="n">
         <v>1</v>
@@ -45640,26 +45640,26 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>281000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1615" t="n">
-        <v>2000</v>
+        <v>140</v>
       </c>
       <c r="E1615" t="n">
-        <v>6250</v>
+        <v>93</v>
       </c>
       <c r="F1615" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="G1615" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="H1615" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1616">
@@ -45668,26 +45668,26 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Rumah Besar di Jl. Wijaya.</t>
+          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>40000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1616" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1616" t="n">
-        <v>579</v>
+        <v>235</v>
       </c>
       <c r="F1616" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="G1616" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1616" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1617">
@@ -45696,26 +45696,26 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>28000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1617" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="E1617" t="n">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="F1617" t="n">
         <v>52</v>
       </c>
       <c r="G1617" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H1617" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1618">
@@ -45724,26 +45724,26 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1618" t="n">
-        <v>2830000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1618" t="n">
-        <v>112</v>
+        <v>700</v>
       </c>
       <c r="E1618" t="n">
-        <v>70</v>
+        <v>660</v>
       </c>
       <c r="F1618" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1618" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H1618" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1619">
@@ -45752,23 +45752,23 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>11500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1619" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="E1619" t="n">
-        <v>475</v>
+        <v>71</v>
       </c>
       <c r="F1619" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="G1619" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H1619" t="n">
         <v>2</v>
@@ -45780,26 +45780,26 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1620" t="n">
-        <v>28500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1620" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E1620" t="n">
-        <v>637</v>
+        <v>2138</v>
       </c>
       <c r="F1620" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1620" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H1620" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1621">
@@ -45808,26 +45808,26 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Rumah Siap Huni Tebet Barat</t>
         </is>
       </c>
       <c r="C1621" t="n">
-        <v>62000000000</v>
+        <v>2800000000</v>
       </c>
       <c r="D1621" t="n">
-        <v>881</v>
+        <v>100</v>
       </c>
       <c r="E1621" t="n">
-        <v>1066</v>
+        <v>122</v>
       </c>
       <c r="F1621" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G1621" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H1621" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1622">
@@ -45836,26 +45836,26 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>30000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1622" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1622" t="n">
-        <v>530</v>
+        <v>200</v>
       </c>
       <c r="F1622" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G1622" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1622" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1623">
@@ -45864,26 +45864,26 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>12000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1623" t="n">
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="E1623" t="n">
-        <v>931</v>
+        <v>76</v>
       </c>
       <c r="F1623" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1623" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1623" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1624">
@@ -45892,26 +45892,26 @@
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1624" t="n">
-        <v>25000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1624" t="n">
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="E1624" t="n">
-        <v>676</v>
+        <v>366</v>
       </c>
       <c r="F1624" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1624" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1624" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1625">
@@ -45920,26 +45920,26 @@
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1625" t="n">
-        <v>3900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1625" t="n">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="E1625" t="n">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="F1625" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1625" t="n">
         <v>31</v>
       </c>
       <c r="H1625" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1626">
@@ -45948,26 +45948,26 @@
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
         </is>
       </c>
       <c r="C1626" t="n">
-        <v>15000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1626" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="E1626" t="n">
-        <v>704</v>
+        <v>74</v>
       </c>
       <c r="F1626" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1626" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1626" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1627">
@@ -45976,23 +45976,23 @@
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>1100000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1627" t="n">
-        <v>90</v>
+        <v>308</v>
       </c>
       <c r="E1627" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="F1627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1627" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1627" t="n">
         <v>1</v>
@@ -46004,17 +46004,17 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1628" t="n">
-        <v>2100000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1628" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="E1628" t="n">
-        <v>93</v>
+        <v>515</v>
       </c>
       <c r="F1628" t="n">
         <v>4</v>
@@ -46023,7 +46023,931 @@
         <v>4</v>
       </c>
       <c r="H1628" t="n">
-        <v>2</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1629" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1629" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>7900000000</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>262</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>161</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1630" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1630" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1631" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1631" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>114</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1632" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1632" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1633" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1633" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>17700000000</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1634" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1634" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1635" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1635" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>270</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1636" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1636" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>517</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1637" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1637" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>48000000000</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>2360</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>63</v>
+      </c>
+      <c r="G1638" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1638" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>23600000000</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1639" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1639" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>55000000000</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1640" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1640" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>26000000000</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>301</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>469</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1641" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1641" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>443</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>655</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1642" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1642" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>62000000000</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>881</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1643" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1643" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>76</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>26</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1644" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1644" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>72000000000</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>1267</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1645" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>256</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>256</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1646" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1646" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1647" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1647" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>160000000000</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>9635</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>9635</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1648" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1648" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1649" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1649" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1650" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1650" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1651" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1651" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>750</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>610</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1652" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1652" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>370</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1653" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1653" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>2700000000</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>105</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1654" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1654" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Rumah di Grinting Kebayoran Baru</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>198</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1655" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1655" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>38000000000</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>550</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1656" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1656" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>208</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1657" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1657" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>216</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1658" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1658" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>120</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1659" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1659" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>5200000000</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1660" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1660" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>175000000000</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>9635</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1661" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1661" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1661"/>
+  <dimension ref="A1:H1692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39816,23 +39816,23 @@
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1407" t="n">
-        <v>900000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1407" t="n">
-        <v>64</v>
+        <v>500</v>
       </c>
       <c r="E1407" t="n">
-        <v>48</v>
+        <v>1554</v>
       </c>
       <c r="F1407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1407" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1407" t="n">
         <v>1</v>
@@ -39844,23 +39844,23 @@
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1408" t="n">
-        <v>52500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1408" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1408" t="n">
-        <v>1554</v>
+        <v>165</v>
       </c>
       <c r="F1408" t="n">
         <v>1</v>
       </c>
       <c r="G1408" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1408" t="n">
         <v>1</v>
@@ -39872,23 +39872,23 @@
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
         </is>
       </c>
       <c r="C1409" t="n">
-        <v>8000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1409" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1409" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="F1409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1409" t="n">
         <v>1</v>
@@ -39900,23 +39900,23 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern 3 Kamar Tidur di Dalam Cluster Keamanan 24 Jam</t>
+          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
         </is>
       </c>
       <c r="C1410" t="n">
-        <v>2000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1410" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="E1410" t="n">
-        <v>60</v>
+        <v>344</v>
       </c>
       <c r="F1410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1410" t="n">
         <v>1</v>
@@ -39928,23 +39928,23 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Rumah Kost Dijual Jl Madrasah Dekat Akses MRT Haji Nawi</t>
+          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1411" t="n">
-        <v>8000000000</v>
+        <v>4800000000</v>
       </c>
       <c r="D1411" t="n">
-        <v>580</v>
+        <v>325</v>
       </c>
       <c r="E1411" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1411" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1411" t="n">
         <v>1</v>
@@ -39956,20 +39956,20 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Jual Rumah di Pejaten Barat Jakarta Selatan</t>
+          <t>Pondok Indah Jl. Gedung Hijau</t>
         </is>
       </c>
       <c r="C1412" t="n">
-        <v>4800000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1412" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="E1412" t="n">
-        <v>340</v>
+        <v>259</v>
       </c>
       <c r="F1412" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1412" t="n">
         <v>4</v>
@@ -39984,23 +39984,23 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Pondok Indah Jl. Gedung Hijau</t>
+          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1413" t="n">
-        <v>11000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="D1413" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E1413" t="n">
-        <v>259</v>
+        <v>122</v>
       </c>
       <c r="F1413" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1413" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1413" t="n">
         <v>1</v>
@@ -40012,23 +40012,23 @@
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni di Pondok Indah</t>
+          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1414" t="n">
-        <v>6250000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1414" t="n">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="E1414" t="n">
-        <v>122</v>
+        <v>634</v>
       </c>
       <c r="F1414" t="n">
         <v>1</v>
       </c>
       <c r="G1414" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1414" t="n">
         <v>1</v>
@@ -40040,23 +40040,23 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Termurah Jual Nego Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1415" t="n">
-        <v>32000000000</v>
+        <v>5400000000</v>
       </c>
       <c r="D1415" t="n">
-        <v>720</v>
+        <v>125</v>
       </c>
       <c r="E1415" t="n">
-        <v>634</v>
+        <v>184</v>
       </c>
       <c r="F1415" t="n">
         <v>1</v>
       </c>
       <c r="G1415" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1415" t="n">
         <v>1</v>
@@ -40068,23 +40068,23 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Dibawah NJOP! Rumah Hitung Tanah di Pondok Indah. Depan Taman Jalan Lebar SHM</t>
+          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
         </is>
       </c>
       <c r="C1416" t="n">
-        <v>5400000000</v>
+        <v>1170000000</v>
       </c>
       <c r="D1416" t="n">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="E1416" t="n">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="F1416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1416" t="n">
         <v>1</v>
@@ -40096,23 +40096,23 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Rumah Elegan, Harga Menggoda, Kesempatan Tak Terulang !</t>
+          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
         </is>
       </c>
       <c r="C1417" t="n">
-        <v>1170000000</v>
+        <v>4390000000</v>
       </c>
       <c r="D1417" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="E1417" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F1417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1417" t="n">
         <v>1</v>
@@ -40124,20 +40124,20 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Rumah baru design mewah dalam cluster area tenang di Kemang. Harga mulai 4M-an</t>
+          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
         </is>
       </c>
       <c r="C1418" t="n">
-        <v>4390000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1418" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E1418" t="n">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="F1418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1418" t="n">
         <v>3</v>
@@ -40152,23 +40152,23 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Dijual Rumah Sultan di Senopati, Dekat Scbd. Ada Swimming Pool &amp; Sauna, Parkir 5 Mobil</t>
+          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
         </is>
       </c>
       <c r="C1419" t="n">
-        <v>27000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1419" t="n">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="E1419" t="n">
-        <v>335</v>
+        <v>180</v>
       </c>
       <c r="F1419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1419" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1419" t="n">
         <v>1</v>
@@ -40180,23 +40180,23 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Dalam Cluster Aman dan Nyaman, Lebak Bulus</t>
+          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
         </is>
       </c>
       <c r="C1420" t="n">
-        <v>7900000000</v>
+        <v>1650000000</v>
       </c>
       <c r="D1420" t="n">
-        <v>417</v>
+        <v>150</v>
       </c>
       <c r="E1420" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="F1420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1420" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1420" t="n">
         <v>1</v>
@@ -40208,20 +40208,20 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Rumah Baru Siaphuni 3 Lantai Dalam Cluster Pinggir Jalan Raya Tol</t>
+          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1421" t="n">
-        <v>1650000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1421" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="E1421" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F1421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1421" t="n">
         <v>3</v>
@@ -40236,23 +40236,23 @@
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Rumah Mewah Paling Estetik 2 Lantai di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
         </is>
       </c>
       <c r="C1422" t="n">
-        <v>2000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1422" t="n">
+        <v>225</v>
+      </c>
+      <c r="E1422" t="n">
         <v>108</v>
       </c>
-      <c r="E1422" t="n">
-        <v>80</v>
-      </c>
       <c r="F1422" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1422" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1422" t="n">
         <v>1</v>
@@ -40264,17 +40264,17 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Jagakarsa Viewe Danau 4 Menit Tol Andara</t>
+          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1423" t="n">
-        <v>3000000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1423" t="n">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="E1423" t="n">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="F1423" t="n">
         <v>5</v>
@@ -40292,17 +40292,17 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Rumah Siaphuni 3 Lantai di Jagakarsajakartaselatan Dekat Tol KRL</t>
+          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
         </is>
       </c>
       <c r="C1424" t="n">
-        <v>5800000000</v>
+        <v>4000000000</v>
       </c>
       <c r="D1424" t="n">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="E1424" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="F1424" t="n">
         <v>5</v>
@@ -40320,23 +40320,23 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Rumah Baru 4 Lantai di Cilandak By Emporio Arsitek Dekat Tol KRL</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
         </is>
       </c>
       <c r="C1425" t="n">
-        <v>4000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1425" t="n">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="E1425" t="n">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="F1425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1425" t="n">
         <v>1</v>
@@ -40348,23 +40348,23 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Tengah Jaksel 4 Lantai Jarang Ada</t>
+          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1426" t="n">
-        <v>6900000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1426" t="n">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="E1426" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="F1426" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1426" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1426" t="n">
         <v>1</v>
@@ -40376,23 +40376,23 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1427" t="n">
-        <v>850000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1427" t="n">
-        <v>44</v>
+        <v>1050</v>
       </c>
       <c r="E1427" t="n">
-        <v>24</v>
+        <v>627</v>
       </c>
       <c r="F1427" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1427" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1427" t="n">
         <v>1</v>
@@ -40404,23 +40404,23 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Rumah di Jual di Pondok Indah Jakarta Selatan</t>
+          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
         </is>
       </c>
       <c r="C1428" t="n">
-        <v>45000000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1428" t="n">
-        <v>1050</v>
+        <v>40</v>
       </c>
       <c r="E1428" t="n">
-        <v>627</v>
+        <v>32</v>
       </c>
       <c r="F1428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1428" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1428" t="n">
         <v>1</v>
@@ -40432,23 +40432,23 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Rumah Baru &amp; Murah Joglo, Petukangan, Pesanggrahan, Larangan, Kreo</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1429" t="n">
-        <v>685000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1429" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="E1429" t="n">
-        <v>32</v>
+        <v>1050</v>
       </c>
       <c r="F1429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1429" t="n">
         <v>1</v>
@@ -40460,23 +40460,23 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1430" t="n">
-        <v>23000000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1430" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1430" t="n">
-        <v>1050</v>
+        <v>335</v>
       </c>
       <c r="F1430" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1430" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1430" t="n">
         <v>1</v>
@@ -40488,20 +40488,20 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Rumah Pondok Indah Bagus Hoek Jakarta Selatan</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1431" t="n">
-        <v>22500000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1431" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="E1431" t="n">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="F1431" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1431" t="n">
         <v>3</v>
@@ -40516,23 +40516,23 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
         </is>
       </c>
       <c r="C1432" t="n">
-        <v>5800000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1432" t="n">
-        <v>250</v>
+        <v>410</v>
       </c>
       <c r="E1432" t="n">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="F1432" t="n">
         <v>1</v>
       </c>
       <c r="G1432" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1432" t="n">
         <v>1</v>
@@ -40544,23 +40544,23 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Pondok Indah Jakarta</t>
+          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
         </is>
       </c>
       <c r="C1433" t="n">
-        <v>21000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1433" t="n">
-        <v>410</v>
+        <v>180</v>
       </c>
       <c r="E1433" t="n">
-        <v>404</v>
+        <v>244</v>
       </c>
       <c r="F1433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1433" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1433" t="n">
         <v>1</v>
@@ -40572,23 +40572,23 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>RUMAH TUA Jl PULO RAYA 2, HITUNG TANAH</t>
+          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
         </is>
       </c>
       <c r="C1434" t="n">
-        <v>4099999999</v>
+        <v>6900000000</v>
       </c>
       <c r="D1434" t="n">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="E1434" t="n">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="F1434" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1434" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1434" t="n">
         <v>1</v>
@@ -40600,23 +40600,23 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Kondisi Baru di Kebayoran Baru Jaksel Jarang Ada</t>
+          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
         </is>
       </c>
       <c r="C1435" t="n">
-        <v>6900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1435" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="E1435" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F1435" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1435" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1435" t="n">
         <v>1</v>
@@ -40628,23 +40628,23 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Rumah American Classic Luxury Home di Kawasan Elit Jagakarsa</t>
+          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1436" t="n">
-        <v>4900000000</v>
+        <v>41000000000</v>
       </c>
       <c r="D1436" t="n">
-        <v>360</v>
+        <v>850</v>
       </c>
       <c r="E1436" t="n">
-        <v>127</v>
+        <v>1925</v>
       </c>
       <c r="F1436" t="n">
         <v>1</v>
       </c>
       <c r="G1436" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1436" t="n">
         <v>1</v>
@@ -40656,23 +40656,23 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah SHM di Cilandak Barat Jakarta Selatan</t>
+          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1437" t="n">
-        <v>41000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1437" t="n">
-        <v>850</v>
+        <v>360</v>
       </c>
       <c r="E1437" t="n">
-        <v>1925</v>
+        <v>261</v>
       </c>
       <c r="F1437" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1437" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1437" t="n">
         <v>1</v>
@@ -40684,20 +40684,20 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Rumah Dalam Komplek di Kahfi 1 Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1438" t="n">
-        <v>4500000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1438" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="E1438" t="n">
-        <v>261</v>
+        <v>703</v>
       </c>
       <c r="F1438" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1438" t="n">
         <v>4</v>
@@ -40712,17 +40712,17 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1439" t="n">
-        <v>32000000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1439" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E1439" t="n">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F1439" t="n">
         <v>2</v>
@@ -40740,23 +40740,23 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>Turun Harga Rumah Mewah Harga Paling Murah Area Kemang Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1440" t="n">
-        <v>18500000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1440" t="n">
-        <v>700</v>
+        <v>881</v>
       </c>
       <c r="E1440" t="n">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="F1440" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1440" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1440" t="n">
         <v>1</v>
@@ -40768,23 +40768,23 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1441" t="n">
-        <v>62000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1441" t="n">
-        <v>881</v>
+        <v>614</v>
       </c>
       <c r="E1441" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="F1441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1441" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1441" t="n">
         <v>1</v>
@@ -40796,23 +40796,23 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Hunian Super Strategis di Kawasan Cipete, Jakarta Selatan</t>
+          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1442" t="n">
-        <v>20000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1442" t="n">
-        <v>614</v>
+        <v>720</v>
       </c>
       <c r="E1442" t="n">
-        <v>921</v>
+        <v>634</v>
       </c>
       <c r="F1442" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1442" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1442" t="n">
         <v>1</v>
@@ -40824,23 +40824,23 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Lux Murah, Jati Solid, Marmer Import, Lokasi Bagus</t>
+          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
         </is>
       </c>
       <c r="C1443" t="n">
-        <v>32000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1443" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="E1443" t="n">
-        <v>634</v>
+        <v>257</v>
       </c>
       <c r="F1443" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1443" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1443" t="n">
         <v>1</v>
@@ -40852,23 +40852,23 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Rumah Klasik Nyaman ~ Good Layout ~ di Pondok Indah</t>
+          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
         </is>
       </c>
       <c r="C1444" t="n">
-        <v>9700000000</v>
+        <v>45000000000</v>
       </c>
       <c r="D1444" t="n">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E1444" t="n">
-        <v>257</v>
+        <v>730</v>
       </c>
       <c r="F1444" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1444" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1444" t="n">
         <v>1</v>
@@ -40880,23 +40880,23 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Rumah Kemang American Classic Fully Furnished By Lifetime Design</t>
+          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
         </is>
       </c>
       <c r="C1445" t="n">
-        <v>45000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1445" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="E1445" t="n">
-        <v>730</v>
+        <v>176</v>
       </c>
       <c r="F1445" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1445" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1445" t="n">
         <v>1</v>
@@ -40908,23 +40908,23 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Rumah LT 176 Minimalis 10 Menit ke Stasiun Tanjung Barat bisa KPR J41466</t>
+          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
         </is>
       </c>
       <c r="C1446" t="n">
-        <v>4420000000</v>
+        <v>15300000000</v>
       </c>
       <c r="D1446" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1446" t="n">
-        <v>176</v>
+        <v>597</v>
       </c>
       <c r="F1446" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1446" t="n">
         <v>1</v>
@@ -40936,23 +40936,23 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Rumah Hadap Timur 6 Menit ke Gerbang Tol Ciputat Siap KPR J-44917</t>
+          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
         </is>
       </c>
       <c r="C1447" t="n">
-        <v>15300000000</v>
+        <v>6860000000</v>
       </c>
       <c r="D1447" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E1447" t="n">
-        <v>597</v>
+        <v>500</v>
       </c>
       <c r="F1447" t="n">
         <v>4</v>
       </c>
       <c r="G1447" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1447" t="n">
         <v>1</v>
@@ -40964,23 +40964,23 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Rumah LT 500 Hadap Timur 8 Menit ke Gerbang Tol Ampera J-43999</t>
+          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1448" t="n">
-        <v>6860000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1448" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E1448" t="n">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="F1448" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1448" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1448" t="n">
         <v>1</v>
@@ -40992,23 +40992,23 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Dijual Rumah dengan Harga Termurah di Area Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
         </is>
       </c>
       <c r="C1449" t="n">
-        <v>7800000000</v>
+        <v>4150000000</v>
       </c>
       <c r="D1449" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E1449" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F1449" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1449" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1449" t="n">
         <v>1</v>
@@ -41020,23 +41020,23 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Rumah Tanah Luas 8 Menit ke Gerbang Tol Cilandak Utama bisa KPR J41852</t>
+          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
         </is>
       </c>
       <c r="C1450" t="n">
-        <v>4150000000</v>
+        <v>3320000000</v>
       </c>
       <c r="D1450" t="n">
-        <v>321</v>
+        <v>198</v>
       </c>
       <c r="E1450" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="F1450" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1450" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1450" t="n">
         <v>1</v>
@@ -41048,23 +41048,23 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Rumah Strategis 16 Menit ke Cilandak Town Square Bebas Banjir J40038</t>
+          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1451" t="n">
-        <v>3320000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1451" t="n">
-        <v>198</v>
+        <v>600</v>
       </c>
       <c r="E1451" t="n">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="F1451" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1451" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1451" t="n">
         <v>1</v>
@@ -41076,23 +41076,23 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Tropical Kemang Jakarta Selatan</t>
+          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
         </is>
       </c>
       <c r="C1452" t="n">
-        <v>21500000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1452" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="E1452" t="n">
-        <v>674</v>
+        <v>123</v>
       </c>
       <c r="F1452" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1452" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1452" t="n">
         <v>1</v>
@@ -41104,20 +41104,20 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Rumah Strategis 7 Menit ke Pintu Tol Lenteng Agung 3 Bebas Banjir J38850</t>
+          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
         </is>
       </c>
       <c r="C1453" t="n">
         <v>2550000000</v>
       </c>
       <c r="D1453" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E1453" t="n">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="F1453" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -41132,23 +41132,23 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 Lantai 12 Menit ke Gerbang Tol Andara 4 Hadap Timur J38922</t>
+          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
         </is>
       </c>
       <c r="C1454" t="n">
-        <v>2550000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1454" t="n">
-        <v>171</v>
+        <v>1300</v>
       </c>
       <c r="E1454" t="n">
-        <v>181</v>
+        <v>461</v>
       </c>
       <c r="F1454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1454" t="n">
         <v>1</v>
@@ -41160,23 +41160,23 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>TERMEWAH DI PANCORAN - DALAM KOMPLEK ELIT, AKSES LEBAR</t>
+          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
         </is>
       </c>
       <c r="C1455" t="n">
-        <v>15000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1455" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="E1455" t="n">
-        <v>461</v>
+        <v>179</v>
       </c>
       <c r="F1455" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1455" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1455" t="n">
         <v>1</v>
@@ -41188,23 +41188,23 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Tebet Timur - Rumah Mewah Furnished (Akses 2 Mobil)</t>
+          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
         </is>
       </c>
       <c r="C1456" t="n">
-        <v>6500000000</v>
+        <v>9800000000</v>
       </c>
       <c r="D1456" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E1456" t="n">
-        <v>179</v>
+        <v>274</v>
       </c>
       <c r="F1456" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1456" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1456" t="n">
         <v>1</v>
@@ -41216,23 +41216,23 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Hitung Tanah di Area Kebayoran Baru Dekat ke Pakubuwono dan Senayan</t>
+          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
         </is>
       </c>
       <c r="C1457" t="n">
-        <v>9800000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1457" t="n">
-        <v>150</v>
+        <v>796</v>
       </c>
       <c r="E1457" t="n">
-        <v>274</v>
+        <v>871</v>
       </c>
       <c r="F1457" t="n">
         <v>2</v>
       </c>
       <c r="G1457" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1457" t="n">
         <v>1</v>
@@ -41244,23 +41244,23 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Dijual / For Sale Rumah Luxury Private Residence di Cilandak- Cipete</t>
+          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
         </is>
       </c>
       <c r="C1458" t="n">
-        <v>40000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1458" t="n">
-        <v>796</v>
+        <v>300</v>
       </c>
       <c r="E1458" t="n">
-        <v>871</v>
+        <v>535</v>
       </c>
       <c r="F1458" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1458" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1458" t="n">
         <v>1</v>
@@ -41272,23 +41272,23 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Dijual Cepat Murah Rumah 1 Lantai Di Kemang Timur 14 Jaksel</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1459" t="n">
-        <v>7500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1459" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E1459" t="n">
-        <v>535</v>
+        <v>1180</v>
       </c>
       <c r="F1459" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1459" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1459" t="n">
         <v>1</v>
@@ -41300,17 +41300,17 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1460" t="n">
-        <v>25000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1460" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="E1460" t="n">
-        <v>1180</v>
+        <v>60</v>
       </c>
       <c r="F1460" t="n">
         <v>2</v>
@@ -41328,17 +41328,17 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1461" t="n">
-        <v>7900000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1461" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="E1461" t="n">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="F1461" t="n">
         <v>2</v>
@@ -41356,23 +41356,23 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Murah! Rumah Cocok Kantor Radio Dalam Jaksel</t>
+          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
         </is>
       </c>
       <c r="C1462" t="n">
-        <v>4500000000</v>
+        <v>29500000000</v>
       </c>
       <c r="D1462" t="n">
-        <v>300</v>
+        <v>609</v>
       </c>
       <c r="E1462" t="n">
-        <v>276</v>
+        <v>822</v>
       </c>
       <c r="F1462" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1462" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1462" t="n">
         <v>1</v>
@@ -41384,23 +41384,23 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Rumah Hook Lokasi Bagus Row Jalan Lebar Dekat NJOP</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1463" t="n">
-        <v>29500000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1463" t="n">
-        <v>609</v>
+        <v>60</v>
       </c>
       <c r="E1463" t="n">
-        <v>822</v>
+        <v>60</v>
       </c>
       <c r="F1463" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1463" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1463" t="n">
         <v>1</v>
@@ -41412,23 +41412,23 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
         </is>
       </c>
       <c r="C1464" t="n">
-        <v>2600000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1464" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E1464" t="n">
         <v>60</v>
       </c>
       <c r="F1464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1464" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1464" t="n">
         <v>1</v>
@@ -41440,23 +41440,23 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai New Condition Jarang Ada Lokasi Strategis di Dalam Cluster</t>
+          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
         </is>
       </c>
       <c r="C1465" t="n">
-        <v>2000000000</v>
+        <v>2300000000</v>
       </c>
       <c r="D1465" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E1465" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="F1465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1465" t="n">
         <v>1</v>
@@ -41468,23 +41468,23 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Jual Rumah di Vasa Jagakarsa Dekat Akses Tol</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1466" t="n">
-        <v>2300000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1466" t="n">
-        <v>90</v>
+        <v>395</v>
       </c>
       <c r="E1466" t="n">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="F1466" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1466" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1466" t="n">
         <v>1</v>
@@ -41496,17 +41496,17 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1467" t="n">
-        <v>6400000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1467" t="n">
-        <v>395</v>
+        <v>60</v>
       </c>
       <c r="E1467" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="F1467" t="n">
         <v>2</v>
@@ -41524,23 +41524,23 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
         </is>
       </c>
       <c r="C1468" t="n">
-        <v>2830000000</v>
+        <v>2350000000</v>
       </c>
       <c r="D1468" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E1468" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F1468" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1468" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1468" t="n">
         <v>1</v>
@@ -41552,23 +41552,23 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Baru Minimalis 3 Lantai Ada Rooftop, Dekat Tol Andara,Rumah Baru Bangun Dalam Cluster Hanya 7 Unit</t>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
         </is>
       </c>
       <c r="C1469" t="n">
-        <v>2350000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1469" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1469" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F1469" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1469" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1469" t="n">
         <v>1</v>
@@ -41580,23 +41580,23 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
         </is>
       </c>
       <c r="C1470" t="n">
-        <v>6400000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1470" t="n">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="E1470" t="n">
-        <v>60</v>
+        <v>544</v>
       </c>
       <c r="F1470" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1470" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1470" t="n">
         <v>1</v>
@@ -41608,23 +41608,23 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Dijual Rumah 2 Lantai Bagus S Pool di Permata Hijau</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1471" t="n">
-        <v>28000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1471" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="E1471" t="n">
-        <v>544</v>
+        <v>196</v>
       </c>
       <c r="F1471" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1471" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1471" t="n">
         <v>1</v>
@@ -41636,20 +41636,20 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
         </is>
       </c>
       <c r="C1472" t="n">
-        <v>4500000000</v>
+        <v>11800000000</v>
       </c>
       <c r="D1472" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="E1472" t="n">
-        <v>196</v>
+        <v>696</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1472" t="n">
         <v>3</v>
@@ -41664,20 +41664,20 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Dijual Rumah Exclusive di Kawasan Elit Kemang Jaksel</t>
+          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
         </is>
       </c>
       <c r="C1473" t="n">
-        <v>11800000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1473" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="E1473" t="n">
-        <v>696</v>
+        <v>942</v>
       </c>
       <c r="F1473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1473" t="n">
         <v>3</v>
@@ -41692,23 +41692,23 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Kemang Dalam Area Strategis Bebas Banjir</t>
+          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
         </is>
       </c>
       <c r="C1474" t="n">
-        <v>25000000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1474" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E1474" t="n">
-        <v>942</v>
+        <v>864</v>
       </c>
       <c r="F1474" t="n">
         <v>2</v>
       </c>
       <c r="G1474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1474" t="n">
         <v>1</v>
@@ -41720,23 +41720,23 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Seharga NJOP Lokasi di Pinggir Jalan Raya Kemang</t>
+          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
         </is>
       </c>
       <c r="C1475" t="n">
-        <v>17700000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1475" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E1475" t="n">
-        <v>864</v>
+        <v>600</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1475" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1475" t="n">
         <v>1</v>
@@ -41748,23 +41748,23 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Jagakarsa, Tanah Luas Investasi Masa Depan</t>
+          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
         </is>
       </c>
       <c r="C1476" t="n">
-        <v>8000000000</v>
+        <v>70000000000</v>
       </c>
       <c r="D1476" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E1476" t="n">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F1476" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1476" t="n">
         <v>1</v>
@@ -41776,23 +41776,23 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Jual Rumah Kayu Lahan Luas Bukit Golf Pondok Indah</t>
+          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
         </is>
       </c>
       <c r="C1477" t="n">
-        <v>70000000000</v>
+        <v>275000000000</v>
       </c>
       <c r="D1477" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E1477" t="n">
-        <v>1300</v>
+        <v>1585</v>
       </c>
       <c r="F1477" t="n">
         <v>4</v>
       </c>
       <c r="G1477" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1477" t="n">
         <v>1</v>
@@ -41804,23 +41804,23 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Rumah Mewah Premium 2 Lantai di Pondok Indah, Sangat Bagus, Recommended, Siap Huni</t>
+          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
         </is>
       </c>
       <c r="C1478" t="n">
-        <v>275000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1478" t="n">
-        <v>1300</v>
+        <v>52</v>
       </c>
       <c r="E1478" t="n">
-        <v>1585</v>
+        <v>27</v>
       </c>
       <c r="F1478" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1478" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1478" t="n">
         <v>1</v>
@@ -41832,23 +41832,23 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah di Setiabudi Harga Terjangkau</t>
+          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
         </is>
       </c>
       <c r="C1479" t="n">
-        <v>1100000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1479" t="n">
-        <v>52</v>
+        <v>366</v>
       </c>
       <c r="E1479" t="n">
-        <v>27</v>
+        <v>366</v>
       </c>
       <c r="F1479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1479" t="n">
         <v>1</v>
@@ -41860,17 +41860,17 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Kebayoran Baru Dekat Scbd</t>
+          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
         </is>
       </c>
       <c r="C1480" t="n">
-        <v>22500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1480" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="E1480" t="n">
-        <v>366</v>
+        <v>154</v>
       </c>
       <c r="F1480" t="n">
         <v>1</v>
@@ -41888,23 +41888,23 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Pondok Indah Area Tenang Jalan Lebar</t>
+          <t>ZENITPARC HYTT</t>
         </is>
       </c>
       <c r="C1481" t="n">
-        <v>6800000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1481" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E1481" t="n">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="F1481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1481" t="n">
         <v>1</v>
@@ -41916,23 +41916,23 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
         </is>
       </c>
       <c r="C1482" t="n">
-        <v>1700000000</v>
+        <v>11300000000</v>
       </c>
       <c r="D1482" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="E1482" t="n">
-        <v>60</v>
+        <v>535</v>
       </c>
       <c r="F1482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1482" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1482" t="n">
         <v>1</v>
@@ -41944,17 +41944,17 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Rumah Tua Hitung Tanah Dalam Komplek Cilandak</t>
+          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
         </is>
       </c>
       <c r="C1483" t="n">
-        <v>11300000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1483" t="n">
-        <v>600</v>
+        <v>158</v>
       </c>
       <c r="E1483" t="n">
-        <v>535</v>
+        <v>63</v>
       </c>
       <c r="F1483" t="n">
         <v>1</v>
@@ -41972,14 +41972,14 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Rumah Baru 3 Lantai Smart Home Dekat Senayan</t>
+          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
         </is>
       </c>
       <c r="C1484" t="n">
-        <v>2100000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1484" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E1484" t="n">
         <v>63</v>
@@ -42000,20 +42000,20 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>Rumah Cantik Harga Menarik Dalam Komplek</t>
+          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
         </is>
       </c>
       <c r="C1485" t="n">
-        <v>2400000000</v>
+        <v>7800000000</v>
       </c>
       <c r="D1485" t="n">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E1485" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="F1485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1485" t="n">
         <v>3</v>
@@ -42028,23 +42028,23 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni Dlm Komplek Bona Lebak Bulus Harga Menarik</t>
+          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
         </is>
       </c>
       <c r="C1486" t="n">
-        <v>7800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1486" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="E1486" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F1486" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1486" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1486" t="n">
         <v>1</v>
@@ -42056,23 +42056,23 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Rumah Brandnew Siap Huni Dalam Komplek Radio Dalam Jaksel</t>
+          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1487" t="n">
-        <v>10000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1487" t="n">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E1487" t="n">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="F1487" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1487" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1487" t="n">
         <v>1</v>
@@ -42084,17 +42084,17 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Poltangan Raya Jakarta Selatan</t>
+          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
         </is>
       </c>
       <c r="C1488" t="n">
-        <v>6000000000</v>
+        <v>7300000000</v>
       </c>
       <c r="D1488" t="n">
-        <v>200</v>
+        <v>501</v>
       </c>
       <c r="E1488" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="F1488" t="n">
         <v>5</v>
@@ -42112,20 +42112,20 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Dijual Sangat Murah Via Lelang Rumah Mewah Komplek Bukit Pratama Lebak Bulus Jakarta Selatan Siap Huni Akses Kemana Saja Mudah Dekat Jalan Raya</t>
+          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
         </is>
       </c>
       <c r="C1489" t="n">
-        <v>7300000000</v>
+        <v>5000000000</v>
       </c>
       <c r="D1489" t="n">
-        <v>501</v>
+        <v>240</v>
       </c>
       <c r="E1489" t="n">
-        <v>600</v>
+        <v>147</v>
       </c>
       <c r="F1489" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1489" t="n">
         <v>3</v>
@@ -42140,23 +42140,23 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Rumah Dua Lantai di Lokasi Yg Sangat Strategis</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1490" t="n">
-        <v>5000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1490" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E1490" t="n">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="F1490" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1490" t="n">
         <v>1</v>
@@ -42168,23 +42168,23 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
         </is>
       </c>
       <c r="C1491" t="n">
-        <v>8500000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1491" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E1491" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F1491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1491" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1491" t="n">
         <v>1</v>
@@ -42196,23 +42196,23 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Dijual Rumah Baru di Cluster Jakarta Jarang Ada! 2 Lantai, 4 Kamar Tidur</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1492" t="n">
-        <v>2000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1492" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="E1492" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="F1492" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1492" t="n">
         <v>1</v>
@@ -42224,26 +42224,26 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
         </is>
       </c>
       <c r="C1493" t="n">
-        <v>10000000000</v>
+        <v>1750000000</v>
       </c>
       <c r="D1493" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="E1493" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F1493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1493" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1494">
@@ -42252,26 +42252,26 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Dalam Komplek Lokasi 5 Menit Pintu Ciledug Bebas Banjir Lokasi Petukangan Selatan</t>
+          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1494" t="n">
-        <v>1750000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1494" t="n">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="E1494" t="n">
-        <v>120</v>
+        <v>958</v>
       </c>
       <c r="F1494" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G1494" t="n">
         <v>21</v>
       </c>
       <c r="H1494" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1495">
@@ -42280,23 +42280,23 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Rumah Luas Ada Kolam Renang di Lebak Bulus Jakarta Selatan</t>
+          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1495" t="n">
-        <v>12500000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1495" t="n">
-        <v>481</v>
+        <v>810</v>
       </c>
       <c r="E1495" t="n">
-        <v>958</v>
+        <v>370</v>
       </c>
       <c r="F1495" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="G1495" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H1495" t="n">
         <v>42</v>
@@ -42308,26 +42308,26 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Dekat Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
         </is>
       </c>
       <c r="C1496" t="n">
-        <v>48000000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1496" t="n">
-        <v>810</v>
+        <v>85</v>
       </c>
       <c r="E1496" t="n">
-        <v>370</v>
+        <v>60</v>
       </c>
       <c r="F1496" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1496" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1496" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1497">
@@ -42336,26 +42336,26 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Dijual Segera Rumah 2 Lantai New Condition Area Strategis Dekat Sekolah dan Rumah Sakit</t>
+          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
         </is>
       </c>
       <c r="C1497" t="n">
-        <v>2000000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1497" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="E1497" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F1497" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1497" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1497" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1498">
@@ -42364,26 +42364,26 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kondisi Baru di Jakarta Selatan 4 Lantai</t>
+          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1498" t="n">
-        <v>6900000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1498" t="n">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="E1498" t="n">
-        <v>76</v>
+        <v>696</v>
       </c>
       <c r="F1498" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1498" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1498" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1499">
@@ -42392,26 +42392,26 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>For Sale Rumah Murah Harga NJOP Lokasi Strategis Dekat Kebayoran Baru dan Kemang Area Bangka Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1499" t="n">
-        <v>12000000000</v>
+        <v>21300000000</v>
       </c>
       <c r="D1499" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1499" t="n">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="F1499" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1499" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1499" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1500">
@@ -42420,17 +42420,17 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>For Sale Rumah Tropical Garden Mininalis Lokasi Nyaman dan Asri Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1500" t="n">
-        <v>21300000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1500" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1500" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="F1500" t="n">
         <v>5</v>
@@ -42448,17 +42448,17 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>For Sale House Modern Furnish Lokasi Prime Area Dekat Senayan dan Kebayoran Baru Area Permata Hijau Jakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1501" t="n">
-        <v>38000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1501" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1501" t="n">
-        <v>660</v>
+        <v>584</v>
       </c>
       <c r="F1501" t="n">
         <v>5</v>
@@ -42476,23 +42476,23 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Lokasi Strategis Dekat Kemang Raya dan Dekat Kebayoran Baru Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1502" t="n">
-        <v>19000000000</v>
+        <v>22000000000</v>
       </c>
       <c r="D1502" t="n">
-        <v>600</v>
+        <v>325</v>
       </c>
       <c r="E1502" t="n">
-        <v>584</v>
+        <v>931</v>
       </c>
       <c r="F1502" t="n">
         <v>5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1502" t="n">
         <v>4</v>
@@ -42504,26 +42504,26 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Tanah Luas bisa Bangun Rumah atau Mini Townhouse atau Tempat Tinggal Dekat Sekolah Internasional dan Dekat Kuliner dan MRT Cipete Harga Murah Area Cipete Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1503" t="n">
-        <v>22000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1503" t="n">
-        <v>325</v>
+        <v>600</v>
       </c>
       <c r="E1503" t="n">
-        <v>931</v>
+        <v>550</v>
       </c>
       <c r="F1503" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1503" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1503" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1504">
@@ -42532,26 +42532,26 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Modern Cantik Lokasi Tenang Asri Dekat Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>32000000000</v>
+        <v>42000000000</v>
       </c>
       <c r="D1504" t="n">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="E1504" t="n">
-        <v>550</v>
+        <v>1925</v>
       </c>
       <c r="F1504" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1504" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1504" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1505">
@@ -42560,7 +42560,7 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Design Tropical Resort Prime Area Cipete Cilandak Jakarta Selatan</t>
+          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
         </is>
       </c>
       <c r="C1505" t="n">
@@ -42588,26 +42588,26 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>For Salerumah Mewahdesign Tropical Resort Tanah Luas Lokasi Strategis Dekat MRT Area Cipete Cilandakjakarta Selatan</t>
+          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1506" t="n">
-        <v>42000000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1506" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="E1506" t="n">
-        <v>1925</v>
+        <v>620</v>
       </c>
       <c r="F1506" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1506" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1506" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1507">
@@ -42616,26 +42616,26 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>For Sale House Modern Minimalis Dekat Kemang Raya Area Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
         </is>
       </c>
       <c r="C1507" t="n">
-        <v>17000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1507" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="E1507" t="n">
-        <v>620</v>
+        <v>1295</v>
       </c>
       <c r="F1507" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1507" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1507" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1508">
@@ -42644,26 +42644,26 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>For Sale Rumah Konsep Compound Terdiri Dari 3 Hunian dengan Akses Masuk Masing-Masing Sangat Cocok untuk Kost atau Multifungsi atau Kantor atau Ruang Usaha atau Klik atau untuk Keluarga Besar Multi-Generasi, Private Residence, atau Kombinasi Tinggal &amp; Sew</t>
+          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
         </is>
       </c>
       <c r="C1508" t="n">
-        <v>35000000000</v>
+        <v>3600000000</v>
       </c>
       <c r="D1508" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="E1508" t="n">
-        <v>1295</v>
+        <v>201</v>
       </c>
       <c r="F1508" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G1508" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H1508" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1509">
@@ -42672,23 +42672,23 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Rumah Hook Drkat Jalan Benda Jagakarsa Harga Siap Nego Siap Huni</t>
+          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
         </is>
       </c>
       <c r="C1509" t="n">
-        <v>3600000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1509" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="E1509" t="n">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="F1509" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1509" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1509" t="n">
         <v>11</v>
@@ -42700,26 +42700,26 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai 15x18 6+2 Kt Akses Dekat Jl. Raya Fatmawati</t>
+          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
         </is>
       </c>
       <c r="C1510" t="n">
-        <v>5500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1510" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1510" t="n">
-        <v>263</v>
+        <v>1180</v>
       </c>
       <c r="F1510" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1510" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H1510" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1511">
@@ -42728,26 +42728,26 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Rumah Besar, Nyaman dengan Swimming Pool Ada 3 Paviliun di Kemang</t>
+          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1511" t="n">
-        <v>25000000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1511" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1511" t="n">
-        <v>1180</v>
+        <v>242</v>
       </c>
       <c r="F1511" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1511" t="n">
         <v>11</v>
-      </c>
-      <c r="G1511" t="n">
-        <v>10</v>
-      </c>
-      <c r="H1511" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="1512">
@@ -42756,26 +42756,26 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lokasi di Hook Lebak Bulus Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
         </is>
       </c>
       <c r="C1512" t="n">
-        <v>5500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1512" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="E1512" t="n">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="F1512" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1512" t="n">
         <v>4</v>
       </c>
       <c r="H1512" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1513">
@@ -42784,23 +42784,23 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Jaksel Super Strategis</t>
+          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
         </is>
       </c>
       <c r="C1513" t="n">
-        <v>6900000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1513" t="n">
-        <v>375</v>
+        <v>610</v>
       </c>
       <c r="E1513" t="n">
-        <v>76</v>
+        <v>822</v>
       </c>
       <c r="F1513" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1513" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1513" t="n">
         <v>22</v>
@@ -42812,23 +42812,23 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Best Price Pondok Indah Row Jalan 3 Mobil Hoek</t>
+          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>28500000000</v>
+        <v>6900000000</v>
       </c>
       <c r="D1514" t="n">
-        <v>610</v>
+        <v>375</v>
       </c>
       <c r="E1514" t="n">
-        <v>822</v>
+        <v>76</v>
       </c>
       <c r="F1514" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1514" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1514" t="n">
         <v>22</v>
@@ -42840,26 +42840,26 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah 4 Lantai Kondisi Baru di Pusat Jakarta Selatan Dekat SCBD Senopati</t>
+          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>6900000000</v>
+        <v>17000000000</v>
       </c>
       <c r="D1515" t="n">
-        <v>375</v>
+        <v>245</v>
       </c>
       <c r="E1515" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="F1515" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1515" t="n">
         <v>4</v>
       </c>
       <c r="H1515" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1516">
@@ -42868,26 +42868,26 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Jual Rumah di Ciniru Kebayoran Baru ..Tenang..Sertifikat Hak Milik ..Bebas Banjir..Dekat Sekali dengan Scbd..Cocok untuk Kalangan Yg Berkelas</t>
+          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1516" t="n">
-        <v>17000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="D1516" t="n">
-        <v>245</v>
+        <v>1220</v>
       </c>
       <c r="E1516" t="n">
-        <v>260</v>
+        <v>1430</v>
       </c>
       <c r="F1516" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1516" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1516" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1517">
@@ -42896,26 +42896,26 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Pondok Indah, Jakarta Selatan</t>
+          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1517" t="n">
-        <v>100000000000</v>
+        <v>15800000000</v>
       </c>
       <c r="D1517" t="n">
-        <v>1220</v>
+        <v>600</v>
       </c>
       <c r="E1517" t="n">
-        <v>1430</v>
+        <v>575</v>
       </c>
       <c r="F1517" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1517" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1517" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1518">
@@ -42924,23 +42924,23 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Regina Realty, Dijual Rumah Cilandak, Jakarta Selatan</t>
+          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1518" t="n">
-        <v>15800000000</v>
+        <v>12700000000</v>
       </c>
       <c r="D1518" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1518" t="n">
-        <v>575</v>
+        <v>209</v>
       </c>
       <c r="F1518" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1518" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1518" t="n">
         <v>22</v>
@@ -42952,23 +42952,23 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Baru di Renovasi di Kemang Jakarta Selatan</t>
+          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
         </is>
       </c>
       <c r="C1519" t="n">
-        <v>12700000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1519" t="n">
         <v>450</v>
       </c>
       <c r="E1519" t="n">
-        <v>209</v>
+        <v>612</v>
       </c>
       <c r="F1519" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1519" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="H1519" t="n">
         <v>22</v>
@@ -42980,26 +42980,26 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Terawat SHM Dikemang Jaksel</t>
+          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
         </is>
       </c>
       <c r="C1520" t="n">
-        <v>20000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1520" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="E1520" t="n">
-        <v>612</v>
+        <v>1925</v>
       </c>
       <c r="F1520" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1520" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H1520" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1521">
@@ -43008,26 +43008,26 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak LT 1925M² Pool Dekat MRT dan Toll</t>
+          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
         </is>
       </c>
       <c r="C1521" t="n">
-        <v>49000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1521" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="E1521" t="n">
-        <v>1925</v>
+        <v>2500</v>
       </c>
       <c r="F1521" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G1521" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H1521" t="n">
-        <v>210</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1522">
@@ -43036,26 +43036,26 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Tanah Cilandak SHM Paling Murah Dari Harga Pasaran Jaksel</t>
+          <t>Rumah Terawat dan Asri di Pondok Indah</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>35000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1522" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="E1522" t="n">
-        <v>2500</v>
+        <v>750</v>
       </c>
       <c r="F1522" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G1522" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="H1522" t="n">
-        <v>412</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1523">
@@ -43064,26 +43064,26 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Rumah Terawat dan Asri di Pondok Indah</t>
+          <t>Rumah Asri Siap Huni di Pondok Indah</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>25000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1523" t="n">
-        <v>630</v>
+        <v>300</v>
       </c>
       <c r="E1523" t="n">
-        <v>750</v>
+        <v>430</v>
       </c>
       <c r="F1523" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G1523" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H1523" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1524">
@@ -43092,26 +43092,26 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni di Pondok Indah</t>
+          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>17500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1524" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1524" t="n">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="F1524" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1524" t="n">
         <v>31</v>
       </c>
       <c r="H1524" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1525">
@@ -43120,17 +43120,17 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Turun Harga! Rumah 2 Lantai Pejaten - Luas, Asri, Siap Huni | 347M² | 6,8M Nego SHM</t>
+          <t>Rumah di Jual Cepat Lebak Bulus</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>6800000000</v>
+        <v>5800000000</v>
       </c>
       <c r="D1525" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E1525" t="n">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="F1525" t="n">
         <v>41</v>
@@ -43139,7 +43139,7 @@
         <v>31</v>
       </c>
       <c r="H1525" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1526">
@@ -43148,26 +43148,26 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Rumah di Jual Cepat Lebak Bulus</t>
+          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
         </is>
       </c>
       <c r="C1526" t="n">
-        <v>5800000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1526" t="n">
         <v>250</v>
       </c>
       <c r="E1526" t="n">
-        <v>305</v>
+        <v>179</v>
       </c>
       <c r="F1526" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1526" t="n">
         <v>41</v>
       </c>
-      <c r="G1526" t="n">
-        <v>31</v>
-      </c>
       <c r="H1526" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1527">
@@ -43176,26 +43176,26 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Ok. Siap Huni di Tebet</t>
+          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
         </is>
       </c>
       <c r="C1527" t="n">
-        <v>6500000000</v>
+        <v>13000000000</v>
       </c>
       <c r="D1527" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E1527" t="n">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="F1527" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1527" t="n">
         <v>41</v>
       </c>
       <c r="H1527" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1528">
@@ -43204,26 +43204,26 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Strategis Dekat Ecopark</t>
+          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>13000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1528" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="E1528" t="n">
-        <v>324</v>
+        <v>106</v>
       </c>
       <c r="F1528" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1528" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H1528" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1529">
@@ -43232,26 +43232,26 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Rumah Moh Kahfi 103M2 Hanya 1.2 M</t>
+          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>1200000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1529" t="n">
-        <v>65</v>
+        <v>850</v>
       </c>
       <c r="E1529" t="n">
-        <v>106</v>
+        <v>1800</v>
       </c>
       <c r="F1529" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1529" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1529" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1530">
@@ -43260,26 +43260,26 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Rumah Mewah LT 1800 Meter Dijual Murah Kebayoran Lama Jaksel</t>
+          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
         </is>
       </c>
       <c r="C1530" t="n">
-        <v>40000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1530" t="n">
-        <v>850</v>
+        <v>609</v>
       </c>
       <c r="E1530" t="n">
-        <v>1800</v>
+        <v>822</v>
       </c>
       <c r="F1530" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1530" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H1530" t="n">
-        <v>220</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1531">
@@ -43288,26 +43288,26 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Rumah Murah Pondok Indah 822 Meter Dibawah NJOP SHM</t>
+          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
         </is>
       </c>
       <c r="C1531" t="n">
-        <v>30000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1531" t="n">
-        <v>609</v>
+        <v>400</v>
       </c>
       <c r="E1531" t="n">
-        <v>822</v>
+        <v>580</v>
       </c>
       <c r="F1531" t="n">
         <v>51</v>
       </c>
       <c r="G1531" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H1531" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1532">
@@ -43316,26 +43316,26 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Rumah Mewah Gandaria Utara Kebayoran Baru LT 580 Harga Turun Jarang Ada</t>
+          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>12500000000</v>
+        <v>9600000000</v>
       </c>
       <c r="D1532" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1532" t="n">
-        <v>580</v>
+        <v>257</v>
       </c>
       <c r="F1532" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G1532" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1532" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1533">
@@ -43344,26 +43344,26 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>"Rumah Klasik Investasi Cuan ~ Harga Nyaris Njop" di Pondok Indah</t>
+          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
         </is>
       </c>
       <c r="C1533" t="n">
-        <v>9600000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1533" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1533" t="n">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="F1533" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G1533" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1533" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1534">
@@ -43372,26 +43372,26 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Buc!! Rumah Rempoa Deket Pim Tol Jor MRT</t>
+          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
         </is>
       </c>
       <c r="C1534" t="n">
-        <v>3500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1534" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E1534" t="n">
-        <v>388</v>
+        <v>237</v>
       </c>
       <c r="F1534" t="n">
         <v>4</v>
       </c>
       <c r="G1534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1534" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1535">
@@ -43400,26 +43400,26 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Termurah!! Furnished Komplek Jatibening Baru</t>
+          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
         </is>
       </c>
       <c r="C1535" t="n">
-        <v>1700000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1535" t="n">
-        <v>350</v>
+        <v>145</v>
       </c>
       <c r="E1535" t="n">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="F1535" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G1535" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1535" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1536">
@@ -43428,26 +43428,26 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Bebas Banjir Rumah Baru Lebak Bulus Dekat MRT</t>
+          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
         </is>
       </c>
       <c r="C1536" t="n">
-        <v>2550000000</v>
+        <v>2000000000</v>
       </c>
       <c r="D1536" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E1536" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F1536" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1536" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1537">
@@ -43456,26 +43456,26 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Butuh Cash!! Rumah di Komplek Dpr Bintaro</t>
+          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>2000000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1537" t="n">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="E1537" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="F1537" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1537" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1537" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1538">
@@ -43484,26 +43484,26 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Termurah! Rumah Dalam Townhouse di Kemang Jaksel Fully Furnish</t>
+          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
         </is>
       </c>
       <c r="C1538" t="n">
-        <v>4700000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1538" t="n">
-        <v>275</v>
+        <v>800</v>
       </c>
       <c r="E1538" t="n">
-        <v>130</v>
+        <v>667</v>
       </c>
       <c r="F1538" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G1538" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H1538" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1539">
@@ -43512,26 +43512,26 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Rumah di Hangtuah Arah Senayan Jalan Tenang Lokasi Elite Perumahan</t>
+          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1539" t="n">
-        <v>48000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1539" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1539" t="n">
-        <v>667</v>
+        <v>703</v>
       </c>
       <c r="F1539" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G1539" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1539" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1540">
@@ -43540,26 +43540,26 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Rumah Bagus 2 Lantai Jalan Besar Dekat Blok M di Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
         </is>
       </c>
       <c r="C1540" t="n">
-        <v>32000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1540" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E1540" t="n">
-        <v>703</v>
+        <v>196</v>
       </c>
       <c r="F1540" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G1540" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1540" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1541">
@@ -43568,26 +43568,26 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Rumah Blok A Kebayoran Baru Jakarta Selatan Harga Termurah</t>
+          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
         </is>
       </c>
       <c r="C1541" t="n">
-        <v>4500000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1541" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1541" t="n">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="F1541" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1541" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1541" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1542">
@@ -43596,26 +43596,26 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>For Sale Tebet Strategis Akses 2 Mobil</t>
+          <t>Dijual Rumah Tebet Strategis</t>
         </is>
       </c>
       <c r="C1542" t="n">
-        <v>6800000000</v>
+        <v>3500000000</v>
       </c>
       <c r="D1542" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E1542" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="F1542" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1542" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1542" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1543">
@@ -43624,26 +43624,26 @@
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tebet Strategis</t>
+          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
         </is>
       </c>
       <c r="C1543" t="n">
-        <v>3500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1543" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E1543" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="F1543" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1543" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1543" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1544">
@@ -43652,26 +43652,26 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>(Termurah di Pejaten) Rumah 2 Lantai Dalam Cluster Jaksel</t>
+          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
         </is>
       </c>
       <c r="C1544" t="n">
-        <v>2900000000</v>
+        <v>14800000000</v>
       </c>
       <c r="D1544" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E1544" t="n">
-        <v>91</v>
+        <v>700</v>
       </c>
       <c r="F1544" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1544" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H1544" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1545">
@@ -43680,26 +43680,26 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Rumah Dijual@Fully Furnished Modern dan Siap Huni</t>
+          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>14800000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1545" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E1545" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F1545" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1545" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1545" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1546">
@@ -43708,26 +43708,26 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah di Kebayoran Lama Jakarta Selatan</t>
+          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>15700000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1546" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
       <c r="E1546" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="F1546" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1546" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1546" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1547">
@@ -43736,17 +43736,17 @@
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Termurah!! Strategis Menteng Kuningan bisa KPR</t>
+          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
         </is>
       </c>
       <c r="C1547" t="n">
-        <v>1200000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1547" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E1547" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F1547" t="n">
         <v>3</v>
@@ -43764,26 +43764,26 @@
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Brand New Tanjung Barat Kalcer Skena KPR</t>
+          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
         </is>
       </c>
       <c r="C1548" t="n">
-        <v>1400000000</v>
+        <v>18500000000</v>
       </c>
       <c r="D1548" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="E1548" t="n">
-        <v>60</v>
+        <v>625</v>
       </c>
       <c r="F1548" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1548" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1548" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1549">
@@ -43792,26 +43792,26 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Tebet Barat LT 625 M² Lokasi Premium Harga Nego</t>
+          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
         </is>
       </c>
       <c r="C1549" t="n">
-        <v>18500000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1549" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E1549" t="n">
-        <v>625</v>
+        <v>528</v>
       </c>
       <c r="F1549" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1549" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H1549" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1550">
@@ -43820,26 +43820,26 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Strategis Tebet Barat Raya Shgb Harga Below Market</t>
+          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1550" t="n">
-        <v>12800000000</v>
+        <v>50000000000</v>
       </c>
       <c r="D1550" t="n">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="E1550" t="n">
-        <v>528</v>
+        <v>714</v>
       </c>
       <c r="F1550" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1550" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H1550" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1551">
@@ -43848,26 +43848,26 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Dijual Rumah Tenang 700m2 Di Tulodong Dekat Scbd Kebayoran Baru</t>
+          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
         </is>
       </c>
       <c r="C1551" t="n">
-        <v>50000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1551" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="E1551" t="n">
-        <v>714</v>
+        <v>526</v>
       </c>
       <c r="F1551" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1551" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1552">
@@ -43876,26 +43876,26 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Bagus Di Cipete – Lokasi Strategis &amp; Siap Huni ✨</t>
+          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
         </is>
       </c>
       <c r="C1552" t="n">
-        <v>18000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1552" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1552" t="n">
-        <v>526</v>
+        <v>650</v>
       </c>
       <c r="F1552" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1552" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="H1552" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1553">
@@ -43904,26 +43904,26 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Dijual rumah di Jalan Galuh Senopati dekat SCBD</t>
+          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
         </is>
       </c>
       <c r="C1553" t="n">
-        <v>97000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1553" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E1553" t="n">
-        <v>650</v>
+        <v>345</v>
       </c>
       <c r="F1553" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="G1553" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1553" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1554">
@@ -43932,26 +43932,26 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>RUMAH DIJUAL JALAN SAIDI KEBAYORAN BARU JAKARTA SELATAN</t>
+          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
         </is>
       </c>
       <c r="C1554" t="n">
-        <v>11000000000</v>
+        <v>4200000000</v>
       </c>
       <c r="D1554" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E1554" t="n">
-        <v>345</v>
+        <v>90</v>
       </c>
       <c r="F1554" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1554" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1554" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1555">
@@ -43960,26 +43960,26 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Rare Listing! Rumah 4 Lantai Tebet Barat - Lokasi Super Strategis</t>
+          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
         </is>
       </c>
       <c r="C1555" t="n">
-        <v>4200000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1555" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E1555" t="n">
-        <v>90</v>
+        <v>1722</v>
       </c>
       <c r="F1555" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1555" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1555" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1556">
@@ -43988,26 +43988,26 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah di Ciganjur Jagakarsa Dekat Toll Brigif SHM</t>
+          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
         </is>
       </c>
       <c r="C1556" t="n">
-        <v>17200000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1556" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="E1556" t="n">
-        <v>1722</v>
+        <v>68</v>
       </c>
       <c r="F1556" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1556" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1556" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1557">
@@ -44016,26 +44016,26 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Rumah 3 Lantai Di Cilandak Kko Siap Huni Full Furnished Shm Bagus</t>
+          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>2500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1557" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="E1557" t="n">
-        <v>68</v>
+        <v>260</v>
       </c>
       <c r="F1557" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1557" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H1557" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1558">
@@ -44044,26 +44044,26 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni di Kemang Ada Kolam Renang SHM Bebas Banjir</t>
+          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>6500000000</v>
+        <v>830000000</v>
       </c>
       <c r="D1558" t="n">
-        <v>400</v>
+        <v>56</v>
       </c>
       <c r="E1558" t="n">
-        <v>260</v>
+        <v>54</v>
       </c>
       <c r="F1558" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1558" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1558" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1559">
@@ -44072,17 +44072,17 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Hanya 7 Menit ke Tol &amp; Akses Mudah ke MRT</t>
+          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>830000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1559" t="n">
-        <v>56</v>
+        <v>350</v>
       </c>
       <c r="E1559" t="n">
-        <v>54</v>
+        <v>498</v>
       </c>
       <c r="F1559" t="n">
         <v>3</v>
@@ -44091,7 +44091,7 @@
         <v>2</v>
       </c>
       <c r="H1559" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1560">
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Lebak Bulus Jakarta Selatan Dekat ke Fatmawati</t>
+          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>11000000000</v>
+        <v>12500000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="E1560" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F1560" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1560" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1560" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Cipete Utara Kebayoran Baru Lokasi Strategis</t>
+          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>12500000000</v>
+        <v>9200000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>318</v>
+        <v>440</v>
       </c>
       <c r="E1561" t="n">
-        <v>497</v>
+        <v>317</v>
       </c>
       <c r="F1561" t="n">
         <v>5</v>
       </c>
       <c r="G1561" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1561" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,26 +44156,26 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>1400000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="E1562" t="n">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="F1562" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="G1562" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1562" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,26 +44184,26 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Rumah Mewah Cilandak Dekat MRT | Tenang, Private, Siap Huni</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>9200000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="E1563" t="n">
-        <v>317</v>
+        <v>800</v>
       </c>
       <c r="F1563" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1563" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1563" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1564">
@@ -44212,23 +44212,23 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>16500000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>185</v>
+        <v>775</v>
       </c>
       <c r="E1564" t="n">
-        <v>300</v>
+        <v>925</v>
       </c>
       <c r="F1564" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G1564" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1564" t="n">
         <v>22</v>
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Dijual Rumah Area Jakarta Selatan</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>25000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="E1565" t="n">
-        <v>800</v>
+        <v>664</v>
       </c>
       <c r="F1565" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1565" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1565" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>120000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>775</v>
+        <v>300</v>
       </c>
       <c r="E1566" t="n">
-        <v>925</v>
+        <v>301</v>
       </c>
       <c r="F1566" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G1566" t="n">
         <v>31</v>
       </c>
       <c r="H1566" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>9500000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="E1567" t="n">
-        <v>664</v>
+        <v>29</v>
       </c>
       <c r="F1567" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G1567" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1567" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1568" t="n">
-        <v>6000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1568" t="n">
         <v>300</v>
       </c>
       <c r="E1568" t="n">
-        <v>301</v>
+        <v>208</v>
       </c>
       <c r="F1568" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="G1568" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1568" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>890000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>56</v>
+        <v>400</v>
       </c>
       <c r="E1569" t="n">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="F1569" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1569" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1569" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>9000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>300</v>
+        <v>457</v>
       </c>
       <c r="E1570" t="n">
-        <v>208</v>
+        <v>500</v>
       </c>
       <c r="F1570" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1570" t="n">
         <v>3</v>
       </c>
       <c r="H1570" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>32000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="E1571" t="n">
-        <v>346</v>
+        <v>1165</v>
       </c>
       <c r="F1571" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1571" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1571" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>55000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>457</v>
+        <v>880</v>
       </c>
       <c r="E1572" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F1572" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1572" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1572" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>55000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="E1573" t="n">
-        <v>1165</v>
+        <v>412</v>
       </c>
       <c r="F1573" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1573" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1573" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>62000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>880</v>
+        <v>1050</v>
       </c>
       <c r="E1574" t="n">
-        <v>1000</v>
+        <v>627</v>
       </c>
       <c r="F1574" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1574" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1574" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,23 +44520,23 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>17500000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="E1575" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F1575" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1575" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1575" t="n">
         <v>4</v>
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>40000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>1050</v>
+        <v>1600</v>
       </c>
       <c r="E1576" t="n">
-        <v>627</v>
+        <v>1800</v>
       </c>
       <c r="F1576" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1576" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1576" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,23 +44576,23 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>7500000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1577" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1577" t="n">
-        <v>404</v>
+        <v>540</v>
       </c>
       <c r="F1577" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1577" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1577" t="n">
         <v>4</v>
@@ -44604,26 +44604,26 @@
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>55000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1578" t="n">
-        <v>1600</v>
+        <v>650</v>
       </c>
       <c r="E1578" t="n">
-        <v>1800</v>
+        <v>1230</v>
       </c>
       <c r="F1578" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1578" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1578" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1579">
@@ -44632,26 +44632,26 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>49000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1579" t="n">
-        <v>1100</v>
+        <v>750</v>
       </c>
       <c r="E1579" t="n">
-        <v>540</v>
+        <v>425</v>
       </c>
       <c r="F1579" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G1579" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H1579" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1580">
@@ -44660,26 +44660,26 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>32000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1580" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="E1580" t="n">
-        <v>1230</v>
+        <v>1050</v>
       </c>
       <c r="F1580" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="G1580" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1580" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1581">
@@ -44688,26 +44688,26 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>25000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1581" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E1581" t="n">
-        <v>425</v>
+        <v>1554</v>
       </c>
       <c r="F1581" t="n">
         <v>71</v>
       </c>
       <c r="G1581" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H1581" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1582">
@@ -44716,26 +44716,26 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>23000000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1582" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="E1582" t="n">
-        <v>1050</v>
+        <v>70</v>
       </c>
       <c r="F1582" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G1582" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1582" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1583">
@@ -44744,26 +44744,26 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>52500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1583" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E1583" t="n">
-        <v>1554</v>
+        <v>450</v>
       </c>
       <c r="F1583" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="G1583" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1583" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1584">
@@ -44772,26 +44772,26 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
+          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>1700000000</v>
+        <v>7950000000</v>
       </c>
       <c r="D1584" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="E1584" t="n">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="F1584" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1584" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1584" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1585">
@@ -44800,26 +44800,26 @@
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>20000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1585" t="n">
-        <v>550</v>
+        <v>1500</v>
       </c>
       <c r="E1585" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="F1585" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G1585" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1585" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1586">
@@ -44828,26 +44828,26 @@
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
+          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>7950000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1586" t="n">
-        <v>260</v>
+        <v>366</v>
       </c>
       <c r="E1586" t="n">
-        <v>240</v>
+        <v>393</v>
       </c>
       <c r="F1586" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1586" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1586" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1587">
@@ -44856,26 +44856,26 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>30000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1587" t="n">
-        <v>1500</v>
+        <v>360</v>
       </c>
       <c r="E1587" t="n">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="F1587" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G1587" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1587" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1588">
@@ -44884,17 +44884,17 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>20000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1588" t="n">
-        <v>366</v>
+        <v>69</v>
       </c>
       <c r="E1588" t="n">
-        <v>393</v>
+        <v>63</v>
       </c>
       <c r="F1588" t="n">
         <v>3</v>
@@ -44903,7 +44903,7 @@
         <v>2</v>
       </c>
       <c r="H1588" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1589">
@@ -44912,26 +44912,26 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>24000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1589" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="E1589" t="n">
-        <v>518</v>
+        <v>1050</v>
       </c>
       <c r="F1589" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1589" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1589" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1590">
@@ -44940,26 +44940,26 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>1100000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1590" t="n">
-        <v>69</v>
+        <v>467</v>
       </c>
       <c r="E1590" t="n">
-        <v>63</v>
+        <v>899</v>
       </c>
       <c r="F1590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1590" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1590" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1591">
@@ -44968,26 +44968,26 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>80000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1591" t="n">
-        <v>600</v>
+        <v>340</v>
       </c>
       <c r="E1591" t="n">
-        <v>1050</v>
+        <v>350</v>
       </c>
       <c r="F1591" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1591" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H1591" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1592">
@@ -44996,26 +44996,26 @@
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>16000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1592" t="n">
-        <v>467</v>
+        <v>135</v>
       </c>
       <c r="E1592" t="n">
-        <v>899</v>
+        <v>30</v>
       </c>
       <c r="F1592" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1592" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1592" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1593">
@@ -45024,26 +45024,26 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>15500000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1593" t="n">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="E1593" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="F1593" t="n">
         <v>3</v>
       </c>
       <c r="G1593" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H1593" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1594">
@@ -45052,26 +45052,26 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>2500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1594" t="n">
-        <v>135</v>
+        <v>2700</v>
       </c>
       <c r="E1594" t="n">
-        <v>30</v>
+        <v>2382</v>
       </c>
       <c r="F1594" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G1594" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="H1594" t="n">
-        <v>1</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1595">
@@ -45080,23 +45080,23 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
+          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>1950000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1595" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1595" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F1595" t="n">
         <v>3</v>
       </c>
       <c r="G1595" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1595" t="n">
         <v>1</v>
@@ -45108,26 +45108,26 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
+          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>90000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1596" t="n">
-        <v>2700</v>
+        <v>95</v>
       </c>
       <c r="E1596" t="n">
-        <v>2382</v>
+        <v>95</v>
       </c>
       <c r="F1596" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="G1596" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="H1596" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1597">
@@ -45136,26 +45136,26 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
+          <t>Dijual Rumah bisa Buatusaha</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>1400000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1597" t="n">
-        <v>120</v>
+        <v>610</v>
       </c>
       <c r="E1597" t="n">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="F1597" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1597" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1597" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1598">
@@ -45164,26 +45164,26 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>1200000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1598" t="n">
-        <v>95</v>
+        <v>720</v>
       </c>
       <c r="E1598" t="n">
-        <v>95</v>
+        <v>634</v>
       </c>
       <c r="F1598" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G1598" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1598" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1599">
@@ -45192,26 +45192,26 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Dijual Rumah bisa Buatusaha</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>30000000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1599" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E1599" t="n">
-        <v>310</v>
+        <v>570</v>
       </c>
       <c r="F1599" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1599" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1599" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1600">
@@ -45220,26 +45220,26 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>32000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1600" t="n">
-        <v>720</v>
+        <v>160</v>
       </c>
       <c r="E1600" t="n">
-        <v>634</v>
+        <v>120</v>
       </c>
       <c r="F1600" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1600" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1600" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1601">
@@ -45248,26 +45248,26 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1601" t="n">
-        <v>16899999999</v>
+        <v>21000000000</v>
       </c>
       <c r="D1601" t="n">
         <v>600</v>
       </c>
       <c r="E1601" t="n">
-        <v>570</v>
+        <v>1020</v>
       </c>
       <c r="F1601" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1601" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1601" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1602">
@@ -45276,23 +45276,23 @@
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
+          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
         </is>
       </c>
       <c r="C1602" t="n">
-        <v>4099999999</v>
+        <v>281000000000</v>
       </c>
       <c r="D1602" t="n">
-        <v>160</v>
+        <v>2000</v>
       </c>
       <c r="E1602" t="n">
-        <v>120</v>
+        <v>6250</v>
       </c>
       <c r="F1602" t="n">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="G1602" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="H1602" t="n">
         <v>12</v>
@@ -45304,26 +45304,26 @@
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
+          <t>Rumah Besar di Jl. Wijaya.</t>
         </is>
       </c>
       <c r="C1603" t="n">
-        <v>21000000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1603" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E1603" t="n">
-        <v>1020</v>
+        <v>579</v>
       </c>
       <c r="F1603" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1603" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1603" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1604">
@@ -45332,26 +45332,26 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
+          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1604" t="n">
-        <v>281000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1604" t="n">
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="E1604" t="n">
-        <v>6250</v>
+        <v>607</v>
       </c>
       <c r="F1604" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="G1604" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="H1604" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1605">
@@ -45360,23 +45360,23 @@
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>Rumah Besar di Jl. Wijaya.</t>
+          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1605" t="n">
-        <v>40000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1605" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1605" t="n">
-        <v>579</v>
+        <v>475</v>
       </c>
       <c r="F1605" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="G1605" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1605" t="n">
         <v>2</v>
@@ -45388,23 +45388,23 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
+          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
         </is>
       </c>
       <c r="C1606" t="n">
-        <v>28000000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1606" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="E1606" t="n">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="F1606" t="n">
         <v>52</v>
       </c>
       <c r="G1606" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H1606" t="n">
         <v>22</v>
@@ -45416,26 +45416,26 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>11500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1607" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1607" t="n">
-        <v>475</v>
+        <v>530</v>
       </c>
       <c r="F1607" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="G1607" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1607" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1608">
@@ -45444,26 +45444,26 @@
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
+          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>28500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1608" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1608" t="n">
-        <v>637</v>
+        <v>931</v>
       </c>
       <c r="F1608" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1608" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1608" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1609">
@@ -45472,26 +45472,26 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
+          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
         </is>
       </c>
       <c r="C1609" t="n">
-        <v>30000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1609" t="n">
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="E1609" t="n">
-        <v>530</v>
+        <v>676</v>
       </c>
       <c r="F1609" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1609" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1609" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1610">
@@ -45500,26 +45500,26 @@
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
         </is>
       </c>
       <c r="C1610" t="n">
-        <v>12000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1610" t="n">
-        <v>450</v>
+        <v>264</v>
       </c>
       <c r="E1610" t="n">
-        <v>931</v>
+        <v>141</v>
       </c>
       <c r="F1610" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1610" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1610" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1611">
@@ -45528,26 +45528,26 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
+          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>25000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1611" t="n">
-        <v>560</v>
+        <v>950</v>
       </c>
       <c r="E1611" t="n">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="F1611" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1611" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1611" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1612">
@@ -45556,26 +45556,26 @@
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>3900000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1612" t="n">
-        <v>264</v>
+        <v>90</v>
       </c>
       <c r="E1612" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="F1612" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1612" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1612" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1613">
@@ -45584,26 +45584,26 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>15000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1613" t="n">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="E1613" t="n">
-        <v>704</v>
+        <v>93</v>
       </c>
       <c r="F1613" t="n">
         <v>4</v>
       </c>
       <c r="G1613" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1613" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1614">
@@ -45612,26 +45612,26 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
+          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>1100000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1614" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="E1614" t="n">
-        <v>60</v>
+        <v>660</v>
       </c>
       <c r="F1614" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1614" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1614" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1615">
@@ -45640,26 +45640,26 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Rumah Siap Huni Tebet Barat</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>2100000000</v>
+        <v>2800000000</v>
       </c>
       <c r="D1615" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="E1615" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="F1615" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G1615" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1615" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1616">
@@ -45668,26 +45668,26 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>5500000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1616" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E1616" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="F1616" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G1616" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1616" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1617">
@@ -45696,26 +45696,26 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>97000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1617" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="E1617" t="n">
-        <v>650</v>
+        <v>165</v>
       </c>
       <c r="F1617" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G1617" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="H1617" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1618">
@@ -45724,26 +45724,26 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1618" t="n">
-        <v>90000000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1618" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E1618" t="n">
-        <v>660</v>
+        <v>515</v>
       </c>
       <c r="F1618" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1618" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1618" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1619">
@@ -45752,23 +45752,23 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
+          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>1500000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1619" t="n">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="E1619" t="n">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="F1619" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1619" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H1619" t="n">
         <v>2</v>
@@ -45780,26 +45780,26 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
         </is>
       </c>
       <c r="C1620" t="n">
-        <v>32000000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1620" t="n">
-        <v>1200</v>
+        <v>185</v>
       </c>
       <c r="E1620" t="n">
-        <v>2138</v>
+        <v>114</v>
       </c>
       <c r="F1620" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1620" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H1620" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1621">
@@ -45808,26 +45808,26 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Barat</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1621" t="n">
-        <v>2800000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1621" t="n">
-        <v>100</v>
+        <v>881</v>
       </c>
       <c r="E1621" t="n">
-        <v>122</v>
+        <v>1066</v>
       </c>
       <c r="F1621" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="G1621" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H1621" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1622">
@@ -45836,26 +45836,26 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>8500000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1622" t="n">
-        <v>250</v>
+        <v>1100</v>
       </c>
       <c r="E1622" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="F1622" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G1622" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1622" t="n">
         <v>41</v>
-      </c>
-      <c r="H1622" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="1623">
@@ -45864,26 +45864,26 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>7900000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1623" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E1623" t="n">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="F1623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1623" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1623" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1624">
@@ -45892,26 +45892,26 @@
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1624" t="n">
-        <v>22500000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1624" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E1624" t="n">
-        <v>366</v>
+        <v>517</v>
       </c>
       <c r="F1624" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1624" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1624" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1625">
@@ -45920,26 +45920,26 @@
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1625" t="n">
-        <v>8000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1625" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="E1625" t="n">
-        <v>165</v>
+        <v>2360</v>
       </c>
       <c r="F1625" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G1625" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H1625" t="n">
-        <v>24</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1626">
@@ -45948,26 +45948,26 @@
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1626" t="n">
-        <v>1900000000</v>
+        <v>23600000000</v>
       </c>
       <c r="D1626" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="E1626" t="n">
-        <v>74</v>
+        <v>1495</v>
       </c>
       <c r="F1626" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1626" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H1626" t="n">
-        <v>11</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1627">
@@ -45976,26 +45976,26 @@
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>6400000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1627" t="n">
-        <v>308</v>
+        <v>1</v>
       </c>
       <c r="E1627" t="n">
-        <v>160</v>
+        <v>5500</v>
       </c>
       <c r="F1627" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1627" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H1627" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1628">
@@ -46004,26 +46004,26 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
         </is>
       </c>
       <c r="C1628" t="n">
-        <v>12800000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1628" t="n">
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="E1628" t="n">
-        <v>515</v>
+        <v>469</v>
       </c>
       <c r="F1628" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1628" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1628" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1629">
@@ -46032,26 +46032,26 @@
       </c>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
         </is>
       </c>
       <c r="C1629" t="n">
-        <v>2900000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1629" t="n">
-        <v>200</v>
+        <v>443</v>
       </c>
       <c r="E1629" t="n">
-        <v>155</v>
+        <v>655</v>
       </c>
       <c r="F1629" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1629" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1629" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1630">
@@ -46060,26 +46060,26 @@
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>7900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1630" t="n">
-        <v>262</v>
+        <v>881</v>
       </c>
       <c r="E1630" t="n">
-        <v>161</v>
+        <v>1066</v>
       </c>
       <c r="F1630" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1630" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1630" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1631">
@@ -46088,23 +46088,23 @@
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>1700000000</v>
+        <v>1340000000</v>
       </c>
       <c r="D1631" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E1631" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F1631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1631" t="n">
         <v>1</v>
@@ -46116,26 +46116,26 @@
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
+          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>4500000000</v>
+        <v>72000000000</v>
       </c>
       <c r="D1632" t="n">
-        <v>185</v>
+        <v>350</v>
       </c>
       <c r="E1632" t="n">
-        <v>114</v>
+        <v>1267</v>
       </c>
       <c r="F1632" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1632" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1632" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1633">
@@ -46144,26 +46144,26 @@
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>62000000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1633" t="n">
-        <v>881</v>
+        <v>256</v>
       </c>
       <c r="E1633" t="n">
-        <v>1066</v>
+        <v>256</v>
       </c>
       <c r="F1633" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="G1633" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="H1633" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1634">
@@ -46172,26 +46172,26 @@
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>17700000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1634" t="n">
-        <v>1100</v>
+        <v>9635</v>
       </c>
       <c r="E1634" t="n">
-        <v>360</v>
+        <v>9635</v>
       </c>
       <c r="F1634" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="G1634" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="H1634" t="n">
-        <v>41</v>
+        <v>294</v>
       </c>
     </row>
     <row r="1635">
@@ -46200,26 +46200,26 @@
       </c>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
         </is>
       </c>
       <c r="C1635" t="n">
-        <v>13500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1635" t="n">
-        <v>374</v>
+        <v>60</v>
       </c>
       <c r="E1635" t="n">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="F1635" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1635" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1635" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1636">
@@ -46228,26 +46228,26 @@
       </c>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
         </is>
       </c>
       <c r="C1636" t="n">
-        <v>6500000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1636" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="E1636" t="n">
-        <v>270</v>
+        <v>1050</v>
       </c>
       <c r="F1636" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="G1636" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H1636" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1637">
@@ -46256,26 +46256,26 @@
       </c>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1637" t="n">
-        <v>38000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1637" t="n">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="E1637" t="n">
-        <v>517</v>
+        <v>610</v>
       </c>
       <c r="F1637" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G1637" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H1637" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1638">
@@ -46284,26 +46284,26 @@
       </c>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
         </is>
       </c>
       <c r="C1638" t="n">
-        <v>48000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1638" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="E1638" t="n">
-        <v>2360</v>
+        <v>570</v>
       </c>
       <c r="F1638" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="G1638" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1638" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1639">
@@ -46312,26 +46312,26 @@
       </c>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
+          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
         </is>
       </c>
       <c r="C1639" t="n">
-        <v>23600000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1639" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="E1639" t="n">
-        <v>1495</v>
+        <v>105</v>
       </c>
       <c r="F1639" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1639" t="n">
         <v>31</v>
       </c>
-      <c r="G1639" t="n">
-        <v>11</v>
-      </c>
       <c r="H1639" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1640">
@@ -46340,26 +46340,26 @@
       </c>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+          <t>Rumah di Grinting Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1640" t="n">
-        <v>55000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1640" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E1640" t="n">
-        <v>5500</v>
+        <v>198</v>
       </c>
       <c r="F1640" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G1640" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1640" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1641">
@@ -46368,17 +46368,17 @@
       </c>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
+          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
         </is>
       </c>
       <c r="C1641" t="n">
-        <v>26000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1641" t="n">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="E1641" t="n">
-        <v>469</v>
+        <v>550</v>
       </c>
       <c r="F1641" t="n">
         <v>41</v>
@@ -46387,7 +46387,7 @@
         <v>41</v>
       </c>
       <c r="H1641" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1642">
@@ -46396,26 +46396,26 @@
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
+          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
         </is>
       </c>
       <c r="C1642" t="n">
-        <v>30000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1642" t="n">
-        <v>443</v>
+        <v>300</v>
       </c>
       <c r="E1642" t="n">
-        <v>655</v>
+        <v>208</v>
       </c>
       <c r="F1642" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1642" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1642" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1643">
@@ -46424,26 +46424,26 @@
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1643" t="n">
-        <v>62000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1643" t="n">
-        <v>881</v>
+        <v>350</v>
       </c>
       <c r="E1643" t="n">
-        <v>1066</v>
+        <v>216</v>
       </c>
       <c r="F1643" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G1643" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1643" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1644">
@@ -46452,26 +46452,26 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
+          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1644" t="n">
-        <v>1340000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1644" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="E1644" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F1644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1644" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1645">
@@ -46480,26 +46480,26 @@
       </c>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1645" t="n">
-        <v>72000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1645" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="E1645" t="n">
-        <v>1267</v>
+        <v>120</v>
       </c>
       <c r="F1645" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1645" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1645" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1646">
@@ -46508,26 +46508,26 @@
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
+          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1646" t="n">
-        <v>6000000000</v>
+        <v>175000000000</v>
       </c>
       <c r="D1646" t="n">
-        <v>256</v>
+        <v>3000</v>
       </c>
       <c r="E1646" t="n">
-        <v>256</v>
+        <v>9635</v>
       </c>
       <c r="F1646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1646" t="n">
         <v>1</v>
       </c>
       <c r="H1646" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1647">
@@ -46536,17 +46536,17 @@
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
         </is>
       </c>
       <c r="C1647" t="n">
-        <v>2600000000</v>
+        <v>900000000</v>
       </c>
       <c r="D1647" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E1647" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F1647" t="n">
         <v>2</v>
@@ -46564,26 +46564,26 @@
       </c>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
+          <t>Jual Rumah 2 Lantai 3 KT Kondisi Baru Dekat MRT Lebak Bulus</t>
         </is>
       </c>
       <c r="C1648" t="n">
-        <v>160000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1648" t="n">
-        <v>9635</v>
+        <v>50</v>
       </c>
       <c r="E1648" t="n">
-        <v>9635</v>
+        <v>47</v>
       </c>
       <c r="F1648" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1648" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H1648" t="n">
-        <v>294</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1649">
@@ -46592,17 +46592,17 @@
       </c>
       <c r="B1649" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Rumah 2 Lantai di Pondok Indah Jl Alam Segar Pondok Pinang Jakarta Selatan LT 160M2 Murah.bawah.pasar Good.invest Cash Only</t>
         </is>
       </c>
       <c r="C1649" t="n">
-        <v>1900000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1649" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="E1649" t="n">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="F1649" t="n">
         <v>3</v>
@@ -46620,26 +46620,26 @@
       </c>
       <c r="B1650" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+          <t>Hunian Premium Pondok Indah 3 Lantai Dekat Taman</t>
         </is>
       </c>
       <c r="C1650" t="n">
-        <v>20000000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1650" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E1650" t="n">
-        <v>1050</v>
+        <v>260</v>
       </c>
       <c r="F1650" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="G1650" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H1650" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1651">
@@ -46648,23 +46648,23 @@
       </c>
       <c r="B1651" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>Rumah Murah Premium Petukangan, Joglo, Kreo, Larangan</t>
         </is>
       </c>
       <c r="C1651" t="n">
-        <v>2830000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1651" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="E1651" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F1651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1651" t="n">
         <v>1</v>
@@ -46676,26 +46676,26 @@
       </c>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1652" t="n">
-        <v>19000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1652" t="n">
-        <v>750</v>
+        <v>90</v>
       </c>
       <c r="E1652" t="n">
-        <v>610</v>
+        <v>71</v>
       </c>
       <c r="F1652" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1652" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H1652" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1653">
@@ -46704,26 +46704,26 @@
       </c>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1653" t="n">
-        <v>30000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1653" t="n">
-        <v>370</v>
+        <v>120</v>
       </c>
       <c r="E1653" t="n">
-        <v>570</v>
+        <v>65</v>
       </c>
       <c r="F1653" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1653" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1654">
@@ -46732,26 +46732,26 @@
       </c>
       <c r="B1654" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1654" t="n">
-        <v>2700000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1654" t="n">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="E1654" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="F1654" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1654" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H1654" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1655">
@@ -46760,26 +46760,26 @@
       </c>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>Rumah di Grinting Kebayoran Baru</t>
+          <t>Rumah Strategis 11 Menit ke Gerbang Tol Andara Siap KPR J47474</t>
         </is>
       </c>
       <c r="C1655" t="n">
-        <v>6500000000</v>
+        <v>4540000000</v>
       </c>
       <c r="D1655" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="E1655" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F1655" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G1655" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1655" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1656">
@@ -46788,26 +46788,26 @@
       </c>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
+          <t>Rumah LB 180 SHM 10 Menit ke Aeon Mall Tanjung Barat J-40352</t>
         </is>
       </c>
       <c r="C1656" t="n">
-        <v>38000000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1656" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="E1656" t="n">
-        <v>550</v>
+        <v>151</v>
       </c>
       <c r="F1656" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1656" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1656" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1657">
@@ -46816,26 +46816,26 @@
       </c>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+          <t>Rumah Idaman 13 Menit ke Terminal Ragunan 2 Lantai Siap Huni J45428</t>
         </is>
       </c>
       <c r="C1657" t="n">
-        <v>10000000000</v>
+        <v>3990000000</v>
       </c>
       <c r="D1657" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="E1657" t="n">
-        <v>208</v>
+        <v>127</v>
       </c>
       <c r="F1657" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1657" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1657" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1658">
@@ -46844,26 +46844,26 @@
       </c>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Luxe Court Permata Hijau Signature</t>
         </is>
       </c>
       <c r="C1658" t="n">
-        <v>10000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1658" t="n">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="E1658" t="n">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="F1658" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G1658" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1658" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1659">
@@ -46872,26 +46872,26 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
+          <t>Rumah Luas 2 LT 13 Menit ke Aeon Mall Tanjung Barat Hadap Timur J48669</t>
         </is>
       </c>
       <c r="C1659" t="n">
-        <v>1400000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1659" t="n">
-        <v>120</v>
+        <v>265</v>
       </c>
       <c r="E1659" t="n">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="F1659" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1659" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1659" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1660">
@@ -46900,26 +46900,26 @@
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Rumah LB 180 SHM 10 Menit ke Gerbang Tol Brigif Dibantu KPR J-37554</t>
         </is>
       </c>
       <c r="C1660" t="n">
-        <v>5200000000</v>
+        <v>1830000000</v>
       </c>
       <c r="D1660" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E1660" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F1660" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1660" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1660" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1661">
@@ -46928,26 +46928,894 @@
       </c>
       <c r="B1661" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
+          <t>Rumah Hadap Selatan LT 240 SHM 7 Menit ke Kebayoran Park Mall J-45991</t>
         </is>
       </c>
       <c r="C1661" t="n">
-        <v>175000000000</v>
+        <v>3870000000</v>
       </c>
       <c r="D1661" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="E1661" t="n">
-        <v>9635</v>
+        <v>240</v>
       </c>
       <c r="F1661" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1661" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1661" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Padmavilla Pejaten</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>2600000000</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>88</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>55</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1662" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1662" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>Rumah 3 LT Siap Huni 15 Mnt ke Gerbang Tol Cisalak Dibantu KPR J-46437</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>1940000000</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>130</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1663" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1663" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="n">
+        <v>1663</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Rumah 2 Lantai di Kemang Bagus Ada Kolam Renang SHM Tidak Banjir</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>11900000000</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>650</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>544</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1664" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1664" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="n">
+        <v>1664</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Rumah Bawah NJOP di Ciganjur Jagakarsa Dekat Tol Brigif SHM</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="D1665" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1665" t="n">
+        <v>1722</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1665" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1665" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Padmavilla Cilandak</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>2830000000</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>112</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1666" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1666" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Dijual Di Jakarta Di Pakubuwono</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>88000000000</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1667" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1667" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="n">
+        <v>1667</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Kemang Jakarta</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>33000000000</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1668" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1668" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="n">
+        <v>1668</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>530</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>850</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1669" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1669" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>235</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1670" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1670" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="n">
+        <v>1670</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>97000000000</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1671" t="n">
+        <v>61</v>
+      </c>
+      <c r="H1671" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>35000000000</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>255</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>1584</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1672" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1672" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>3300000000</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>219</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1673" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1673" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>3200000000</v>
+      </c>
+      <c r="D1674" t="n">
+        <v>150</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>159</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1674" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1674" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1675" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1675" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="n">
+        <v>1675</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Rumah Area Senopati, Lokasi Bagus</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>15700000000</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>365</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>334</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1676" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1676" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="n">
+        <v>1676</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>32000000000</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E1677" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1677" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1677" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>308</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1678" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1678" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>832</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1679" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1679" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>85000000000</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1680" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1680" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>864</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1681" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1681" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1682" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1682" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>60</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>74</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1683" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1683" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1684" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>366</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1684" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1684" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>9000000000</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>261</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1685" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1685" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>850000000</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>44</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1686" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1686" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Below Market! Investasi Tepat Rumah Murah Pondok Indah Siap Huni</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>122</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1687" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1687" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Miliki Segera Dijual Rumah Baru Ready Unit di Jagakarsa Jaksel Diskon 100Jt</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>950000000</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>79</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1688" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1688" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Miliki Segera di Jual Rumah Baru Siap Huni bisa DP 0% N Diskon 200Jt di Jagakarsa Jaksel</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>1250000000</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>75</v>
+      </c>
+      <c r="E1689" t="n">
+        <v>68</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1689" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1689" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Harga Mepet NJOP Rumah Pondok Indah</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>28000000000</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>769</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1690" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1690" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>2 Lantai Jakarta Cash KPR Nego Tanpa DP Akses Bagus</t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>1600000000</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>90</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1691" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1691" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>5500000000</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>360</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1692" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1692" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/DATA RUMAH.xlsx
+++ b/data/raw/DATA RUMAH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1757"/>
+  <dimension ref="A1:H1790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44100,26 +44100,26 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
+          <t>Dijual Rumah Area Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1560" t="n">
-        <v>16500000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1560" t="n">
-        <v>185</v>
+        <v>400</v>
       </c>
       <c r="E1560" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F1560" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="G1560" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H1560" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1561">
@@ -44128,26 +44128,26 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Dijual Rumah Area Jakarta Selatan</t>
+          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
         </is>
       </c>
       <c r="C1561" t="n">
-        <v>25000000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1561" t="n">
-        <v>400</v>
+        <v>775</v>
       </c>
       <c r="E1561" t="n">
-        <v>800</v>
+        <v>925</v>
       </c>
       <c r="F1561" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G1561" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H1561" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1562">
@@ -44156,26 +44156,26 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus di Selong Kebayoran Baru Dekat Sudirman</t>
+          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
         </is>
       </c>
       <c r="C1562" t="n">
-        <v>120000000000</v>
+        <v>9500000000</v>
       </c>
       <c r="D1562" t="n">
-        <v>775</v>
+        <v>320</v>
       </c>
       <c r="E1562" t="n">
-        <v>925</v>
+        <v>664</v>
       </c>
       <c r="F1562" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G1562" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1562" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1563">
@@ -44184,26 +44184,26 @@
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Di Jual Cepat! 2 Unit Rumah Hitung Tanah - Delman, Kebayoran Lama</t>
+          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
         </is>
       </c>
       <c r="C1563" t="n">
-        <v>9500000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1563" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E1563" t="n">
-        <v>664</v>
+        <v>301</v>
       </c>
       <c r="F1563" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G1563" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H1563" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1564">
@@ -44212,26 +44212,26 @@
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Jarang Ada! Tanah 301M² (15X20) Jl Cilandak Iii - Jalan Lebar SHM</t>
+          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1564" t="n">
-        <v>6000000000</v>
+        <v>890000000</v>
       </c>
       <c r="D1564" t="n">
-        <v>300</v>
+        <v>56</v>
       </c>
       <c r="E1564" t="n">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="F1564" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="G1564" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1564" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1565">
@@ -44240,26 +44240,26 @@
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Rumah Mewah Modern 2-3 Lantai di Setia Budi Jakarta Selatan</t>
+          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1565" t="n">
-        <v>890000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1565" t="n">
-        <v>56</v>
+        <v>300</v>
       </c>
       <c r="E1565" t="n">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="F1565" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1565" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1566">
@@ -44268,26 +44268,26 @@
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>For Sale Rumah Jual Bu Lokasi Strategis Dekat Kuliner dan Dekat Scbd Area Senopati Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1566" t="n">
-        <v>9000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1566" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E1566" t="n">
-        <v>208</v>
+        <v>346</v>
       </c>
       <c r="F1566" t="n">
         <v>5</v>
       </c>
       <c r="G1566" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1566" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1567">
@@ -44296,26 +44296,26 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>For Sale House Mewah Modern Lokasi Dekat Blok M dan Mabes dan Perkantoran Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1567" t="n">
-        <v>32000000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1567" t="n">
-        <v>400</v>
+        <v>457</v>
       </c>
       <c r="E1567" t="n">
-        <v>346</v>
+        <v>500</v>
       </c>
       <c r="F1567" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1567" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1567" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1568">
@@ -44324,26 +44324,26 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mediteranian Classic Dekat Mabes dan Dekat Blok M dan MRT Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1568" t="n">
         <v>55000000000</v>
       </c>
       <c r="D1568" t="n">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="E1568" t="n">
-        <v>500</v>
+        <v>1165</v>
       </c>
       <c r="F1568" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1568" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1568" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1569">
@@ -44352,26 +44352,26 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>For Sale Rumah atau Kantor Cocok Dibangun Hotel, atau Restoran Mewah atau Gedung atau Ruang Usaha Cafe atau Kantor atau Klinik atau Lainnya Area Prime Dekat Blok M dan Mabes dan Wijaya Area Kebayoran Baru Jakarta Selatan</t>
+          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1569" t="n">
-        <v>55000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1569" t="n">
-        <v>452</v>
+        <v>880</v>
       </c>
       <c r="E1569" t="n">
-        <v>1165</v>
+        <v>1000</v>
       </c>
       <c r="F1569" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1569" t="n">
         <v>6</v>
       </c>
-      <c r="G1569" t="n">
-        <v>5</v>
-      </c>
       <c r="H1569" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1570">
@@ -44380,26 +44380,26 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>For Salebrand New Tropical Modern Mewah Tanah Luas Parkir Luas Kemangjakarta Selatan</t>
+          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
         </is>
       </c>
       <c r="C1570" t="n">
-        <v>62000000000</v>
+        <v>17500000000</v>
       </c>
       <c r="D1570" t="n">
-        <v>880</v>
+        <v>470</v>
       </c>
       <c r="E1570" t="n">
-        <v>1000</v>
+        <v>412</v>
       </c>
       <c r="F1570" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1570" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1570" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1571">
@@ -44408,26 +44408,26 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>For Sale Rumah Minimalis Siap Huni Good Location Lokasi Strategis Dekat Kemang Rayaarea Kemangjakarta Selatan</t>
+          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1571" t="n">
-        <v>17500000000</v>
+        <v>40000000000</v>
       </c>
       <c r="D1571" t="n">
-        <v>470</v>
+        <v>1050</v>
       </c>
       <c r="E1571" t="n">
-        <v>412</v>
+        <v>627</v>
       </c>
       <c r="F1571" t="n">
         <v>5</v>
       </c>
       <c r="G1571" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1571" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1572">
@@ -44436,26 +44436,26 @@
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Baru Lokasi Tenang dan Asri Bangunan Lokasi Dekat Jis dan Bukit Golf dan Mall Pondok Indah Jakarta Selatan</t>
+          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1572" t="n">
-        <v>40000000000</v>
+        <v>7500000000</v>
       </c>
       <c r="D1572" t="n">
-        <v>1050</v>
+        <v>250</v>
       </c>
       <c r="E1572" t="n">
-        <v>627</v>
+        <v>404</v>
       </c>
       <c r="F1572" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1572" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1572" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1573">
@@ -44464,26 +44464,26 @@
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>For Cepat Rumah Murah Tanah Luas Harga Murah Mendekati NJOP Area Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1573" t="n">
-        <v>7500000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1573" t="n">
-        <v>250</v>
+        <v>1600</v>
       </c>
       <c r="E1573" t="n">
-        <v>404</v>
+        <v>1800</v>
       </c>
       <c r="F1573" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1573" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1573" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1574">
@@ -44492,26 +44492,26 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>For Sale Rumah Lama Harga Dibawah NJOP Area Komersil Lokasi Strategis bisa Multifungsi dan bisa Buat Showroom atau Bengkel atau Klinik atau Gedung atau Resto atau Cafe atau Supermarket Area Hj Nawi Cipete Kebayoran Baru Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1574" t="n">
-        <v>55000000000</v>
+        <v>49000000000</v>
       </c>
       <c r="D1574" t="n">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="E1574" t="n">
-        <v>1800</v>
+        <v>540</v>
       </c>
       <c r="F1574" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1574" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1574" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1575">
@@ -44520,26 +44520,26 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Area Prime Kedutaan dan Pejabat dan Perkantoran Area Mega Kuningan Jakarta Selatan</t>
+          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1575" t="n">
-        <v>49000000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1575" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="E1575" t="n">
-        <v>540</v>
+        <v>1230</v>
       </c>
       <c r="F1575" t="n">
         <v>5</v>
       </c>
       <c r="G1575" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1575" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1576">
@@ -44548,26 +44548,26 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>For Sale Rumah Mewah Cantik Dalam Compound Lokasi Nyaman dan Asri Area Pejaten Dekat Kemang Jakarta Selatan</t>
+          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
         </is>
       </c>
       <c r="C1576" t="n">
-        <v>32000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1576" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="E1576" t="n">
-        <v>1230</v>
+        <v>425</v>
       </c>
       <c r="F1576" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G1576" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1576" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1577">
@@ -44576,26 +44576,26 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Hot Jual Murah Rumah Mewah 2 Lantai di Pondok Indah</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>25000000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1577" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="E1577" t="n">
-        <v>425</v>
+        <v>1050</v>
       </c>
       <c r="F1577" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="G1577" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H1577" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1578">
@@ -44604,26 +44604,26 @@
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh Njop</t>
+          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
         </is>
       </c>
       <c r="C1578" t="n">
-        <v>23000000000</v>
+        <v>52500000000</v>
       </c>
       <c r="D1578" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1578" t="n">
-        <v>1050</v>
+        <v>1554</v>
       </c>
       <c r="F1578" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="G1578" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H1578" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1579">
@@ -44632,26 +44632,26 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Lahan Strategis Fatmawati No. 42 Samping Ace Hardware</t>
+          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>52500000000</v>
+        <v>1700000000</v>
       </c>
       <c r="D1579" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="E1579" t="n">
-        <v>1554</v>
+        <v>70</v>
       </c>
       <c r="F1579" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="G1579" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="H1579" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1580">
@@ -44660,26 +44660,26 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Jual Rumah di Tebet Hitung Tanah di Bawah 2M</t>
+          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
         </is>
       </c>
       <c r="C1580" t="n">
-        <v>1700000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1580" t="n">
-        <v>120</v>
+        <v>550</v>
       </c>
       <c r="E1580" t="n">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="F1580" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G1580" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1580" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1581">
@@ -44688,26 +44688,26 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni Corner Bintaro Rumah Bagus SHM di Graha Taman Bintaro, Cluster Graha Taman Bintaro Blok Hc9 No.1, Pondok Pucung, Pondok Aren, Kota Tangerang Selatan, Banten, Indonesia, 15229, Bintaro</t>
+          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>20000000000</v>
+        <v>7950000000</v>
       </c>
       <c r="D1581" t="n">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="E1581" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="F1581" t="n">
         <v>7</v>
       </c>
       <c r="G1581" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1581" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1582">
@@ -44716,26 +44716,26 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Siap Huni Renovasi Dalam Komplek</t>
+          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>7950000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1582" t="n">
-        <v>260</v>
+        <v>366</v>
       </c>
       <c r="E1582" t="n">
-        <v>240</v>
+        <v>393</v>
       </c>
       <c r="F1582" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1582" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1582" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1583">
@@ -44744,26 +44744,26 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
+          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>30000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1583" t="n">
-        <v>1500</v>
+        <v>360</v>
       </c>
       <c r="E1583" t="n">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="F1583" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G1583" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1583" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1584">
@@ -44772,17 +44772,17 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Rumah di Cipaku, Kebayoran Baru, Lokasi Strategis, Bebas Banjir</t>
+          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>20000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1584" t="n">
-        <v>366</v>
+        <v>69</v>
       </c>
       <c r="E1584" t="n">
-        <v>393</v>
+        <v>63</v>
       </c>
       <c r="F1584" t="n">
         <v>3</v>
@@ -44791,7 +44791,7 @@
         <v>2</v>
       </c>
       <c r="H1584" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1585">
@@ -44800,26 +44800,26 @@
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Rare Listing Darmawangsa Kebayoran Baru, Rumah Lama, Luas Tanah 518 M2, Akses 3 Mobil</t>
+          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>24000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="D1585" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="E1585" t="n">
-        <v>518</v>
+        <v>1050</v>
       </c>
       <c r="F1585" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1585" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1585" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1586">
@@ -44828,26 +44828,26 @@
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Dikawasan Elit Bintaro. Harga 1 M-An</t>
+          <t>Rumah Cluster 899M Turun Harga</t>
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>1100000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1586" t="n">
-        <v>69</v>
+        <v>467</v>
       </c>
       <c r="E1586" t="n">
-        <v>63</v>
+        <v>899</v>
       </c>
       <c r="F1586" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1586" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1586" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1587">
@@ -44856,26 +44856,26 @@
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Rumah Lokasi Super Langka &amp; Super Aman Selong Kebayoran Baru</t>
+          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>80000000000</v>
+        <v>15500000000</v>
       </c>
       <c r="D1587" t="n">
-        <v>600</v>
+        <v>340</v>
       </c>
       <c r="E1587" t="n">
-        <v>1050</v>
+        <v>350</v>
       </c>
       <c r="F1587" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1587" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H1587" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1588">
@@ -44884,26 +44884,26 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Rumah Cluster 899M Turun Harga</t>
+          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>16000000000</v>
+        <v>2500000000</v>
       </c>
       <c r="D1588" t="n">
-        <v>467</v>
+        <v>135</v>
       </c>
       <c r="E1588" t="n">
-        <v>899</v>
+        <v>30</v>
       </c>
       <c r="F1588" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1588" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1588" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1589">
@@ -44912,26 +44912,26 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Rumah Murah Classic Modern Tebet Mas Spesifikasi Mahal Siap Huni Jual Cepat Lihat Jamin Beli</t>
+          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
         </is>
       </c>
       <c r="C1589" t="n">
-        <v>15500000000</v>
+        <v>1950000000</v>
       </c>
       <c r="D1589" t="n">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="E1589" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="F1589" t="n">
         <v>3</v>
       </c>
       <c r="G1589" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H1589" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1590">
@@ -44940,26 +44940,26 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Rumah Lebih Murah Dari Apartment Kawasan Simatupang &amp; Cilandak Siap Huni Hanya 7 Menit Jalan Kaki Dari MRT Fatmawati Sertifikat SHM Tanpa Biaya Mahal Seperti Tinggal di Apartment</t>
+          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1590" t="n">
-        <v>2500000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1590" t="n">
-        <v>135</v>
+        <v>2700</v>
       </c>
       <c r="E1590" t="n">
-        <v>30</v>
+        <v>2382</v>
       </c>
       <c r="F1590" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G1590" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="H1590" t="n">
-        <v>1</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1591">
@@ -44968,23 +44968,23 @@
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Rumah 1.5 Lantai SHM di Tebet Utara</t>
+          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
         </is>
       </c>
       <c r="C1591" t="n">
-        <v>1950000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1591" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E1591" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F1591" t="n">
         <v>3</v>
       </c>
       <c r="G1591" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1591" t="n">
         <v>1</v>
@@ -44996,26 +44996,26 @@
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Rumah Mewah Termurah Luas 2700 SHM Jakarta Selatan</t>
+          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
         </is>
       </c>
       <c r="C1592" t="n">
-        <v>90000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="D1592" t="n">
-        <v>2700</v>
+        <v>95</v>
       </c>
       <c r="E1592" t="n">
-        <v>2382</v>
+        <v>95</v>
       </c>
       <c r="F1592" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="G1592" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="H1592" t="n">
-        <v>510</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1593">
@@ -45024,26 +45024,26 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Rumah Indent Kalcer Skena di Tanjung Barat</t>
+          <t>Dijual Rumah bisa Buatusaha</t>
         </is>
       </c>
       <c r="C1593" t="n">
-        <v>1400000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1593" t="n">
-        <v>120</v>
+        <v>610</v>
       </c>
       <c r="E1593" t="n">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="F1593" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1593" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1593" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1594">
@@ -45052,26 +45052,26 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Strategis! Rumah Baru di Matraman Dekat LRT</t>
+          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
         </is>
       </c>
       <c r="C1594" t="n">
-        <v>1200000000</v>
+        <v>16899999999</v>
       </c>
       <c r="D1594" t="n">
-        <v>95</v>
+        <v>600</v>
       </c>
       <c r="E1594" t="n">
-        <v>95</v>
+        <v>570</v>
       </c>
       <c r="F1594" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1594" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1594" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1595">
@@ -45080,26 +45080,26 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Dijual Rumah bisa Buatusaha</t>
+          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
         </is>
       </c>
       <c r="C1595" t="n">
-        <v>30000000000</v>
+        <v>4099999999</v>
       </c>
       <c r="D1595" t="n">
-        <v>610</v>
+        <v>160</v>
       </c>
       <c r="E1595" t="n">
-        <v>310</v>
+        <v>120</v>
       </c>
       <c r="F1595" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1595" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1595" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1596">
@@ -45108,26 +45108,26 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>[ Gedung Harga NJOP ] Akses Jalan Raya Gandaria Kebayoran</t>
+          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
         </is>
       </c>
       <c r="C1596" t="n">
-        <v>16899999999</v>
+        <v>281000000000</v>
       </c>
       <c r="D1596" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="E1596" t="n">
-        <v>570</v>
+        <v>6250</v>
       </c>
       <c r="F1596" t="n">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="G1596" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="H1596" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1597">
@@ -45136,26 +45136,26 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah di Pondok Indah Pinang Mas</t>
+          <t>Rumah Besar di Jl. Wijaya.</t>
         </is>
       </c>
       <c r="C1597" t="n">
-        <v>4099999999</v>
+        <v>40000000000</v>
       </c>
       <c r="D1597" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="E1597" t="n">
-        <v>120</v>
+        <v>579</v>
       </c>
       <c r="F1597" t="n">
         <v>4</v>
       </c>
       <c r="G1597" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1597" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1598">
@@ -45164,26 +45164,26 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Rumah dan Kavling Besar di Pusat Kota Jakarta</t>
+          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
         </is>
       </c>
       <c r="C1598" t="n">
-        <v>281000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1598" t="n">
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="E1598" t="n">
-        <v>6250</v>
+        <v>607</v>
       </c>
       <c r="F1598" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="G1598" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="H1598" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1599">
@@ -45192,23 +45192,23 @@
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Rumah Besar di Jl. Wijaya.</t>
+          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1599" t="n">
-        <v>40000000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1599" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E1599" t="n">
-        <v>579</v>
+        <v>475</v>
       </c>
       <c r="F1599" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="G1599" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="H1599" t="n">
         <v>2</v>
@@ -45220,23 +45220,23 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Mewah di Area Pondok Indah</t>
+          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>28000000000</v>
+        <v>28500000000</v>
       </c>
       <c r="D1600" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="E1600" t="n">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="F1600" t="n">
         <v>52</v>
       </c>
       <c r="G1600" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H1600" t="n">
         <v>22</v>
@@ -45248,26 +45248,26 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Mewah Murah Gudang Peluru Tebet Jakarta Selatan</t>
+          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1601" t="n">
-        <v>11500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1601" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E1601" t="n">
-        <v>475</v>
+        <v>530</v>
       </c>
       <c r="F1601" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="G1601" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1601" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1602">
@@ -45276,26 +45276,26 @@
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Jual Cepat Rumah Ngantong Asri Bangunan Kokoh</t>
+          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
         </is>
       </c>
       <c r="C1602" t="n">
-        <v>28500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1602" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="E1602" t="n">
-        <v>637</v>
+        <v>931</v>
       </c>
       <c r="F1602" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="G1602" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1602" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1603">
@@ -45304,26 +45304,26 @@
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Rumah Luas 530 Siap Huni Termurah di Jakarta Selatan</t>
+          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
         </is>
       </c>
       <c r="C1603" t="n">
-        <v>30000000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1603" t="n">
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="E1603" t="n">
-        <v>530</v>
+        <v>676</v>
       </c>
       <c r="F1603" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1603" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H1603" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1604">
@@ -45332,26 +45332,26 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Dijual/Disewakan Rumah Mewah Asri Full Furnish, Halaman Luas</t>
+          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
         </is>
       </c>
       <c r="C1604" t="n">
-        <v>12000000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1604" t="n">
-        <v>450</v>
+        <v>264</v>
       </c>
       <c r="E1604" t="n">
-        <v>931</v>
+        <v>141</v>
       </c>
       <c r="F1604" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1604" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1604" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1605">
@@ -45360,26 +45360,26 @@
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>Harga NJOP! Rumah Mewah di Pondok Indah Jalan Lebar Area Tenang Hadap Timur</t>
+          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
         </is>
       </c>
       <c r="C1605" t="n">
-        <v>25000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="D1605" t="n">
-        <v>560</v>
+        <v>950</v>
       </c>
       <c r="E1605" t="n">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="F1605" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1605" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1605" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1606">
@@ -45388,26 +45388,26 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Rumah Bona Indah Lebak Bulus Dekat MRT Fatmawati SHM</t>
+          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
         </is>
       </c>
       <c r="C1606" t="n">
-        <v>3900000000</v>
+        <v>1100000000</v>
       </c>
       <c r="D1606" t="n">
-        <v>264</v>
+        <v>90</v>
       </c>
       <c r="E1606" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="F1606" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1606" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H1606" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1607">
@@ -45416,26 +45416,26 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Rumah Bagus Siap Huni dengan Kolam Renang di Bangka</t>
+          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>15000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1607" t="n">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="E1607" t="n">
-        <v>704</v>
+        <v>93</v>
       </c>
       <c r="F1607" t="n">
         <v>4</v>
       </c>
       <c r="G1607" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H1607" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1608">
@@ -45444,26 +45444,26 @@
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Rumah Semi Furnished Skena Kalcer Gen Z</t>
+          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>1100000000</v>
+        <v>90000000000</v>
       </c>
       <c r="D1608" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="E1608" t="n">
-        <v>60</v>
+        <v>660</v>
       </c>
       <c r="F1608" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1608" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1608" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1609">
@@ -45472,26 +45472,26 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Rumah Kalcer Skena Dekat Pintu Tol Andara</t>
+          <t>Rumah Siap Huni Tebet Barat</t>
         </is>
       </c>
       <c r="C1609" t="n">
-        <v>2100000000</v>
+        <v>2800000000</v>
       </c>
       <c r="D1609" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="E1609" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="F1609" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G1609" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H1609" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1610">
@@ -45500,26 +45500,26 @@
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Rumah Classic Lingkungan Elit Area Sriwijaya Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
         </is>
       </c>
       <c r="C1610" t="n">
-        <v>90000000000</v>
+        <v>8500000000</v>
       </c>
       <c r="D1610" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="E1610" t="n">
-        <v>660</v>
+        <v>200</v>
       </c>
       <c r="F1610" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1610" t="n">
         <v>41</v>
       </c>
-      <c r="G1610" t="n">
-        <v>42</v>
-      </c>
       <c r="H1610" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1611">
@@ -45528,26 +45528,26 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Tebet Barat</t>
+          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>2800000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1611" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E1611" t="n">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="F1611" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G1611" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H1611" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1612">
@@ -45556,26 +45556,26 @@
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Rumah Dalam Townhouse Akses Langsung Jl. Kemang Raya Jarang Ada</t>
+          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>8500000000</v>
+        <v>12800000000</v>
       </c>
       <c r="D1612" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E1612" t="n">
-        <v>200</v>
+        <v>515</v>
       </c>
       <c r="F1612" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G1612" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1612" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1613">
@@ -45584,26 +45584,26 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Brand New Full Furnished dengan Rooftop 200 Meter ke MRT Haji Nawi.</t>
+          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>8000000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1613" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E1613" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F1613" t="n">
         <v>41</v>
       </c>
       <c r="G1613" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1613" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1614">
@@ -45612,17 +45612,17 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Brand New House Modern Minimalis Lingkungan Nyaman di Cilandak, Jakarta Selatan</t>
+          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>12800000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1614" t="n">
-        <v>400</v>
+        <v>185</v>
       </c>
       <c r="E1614" t="n">
-        <v>515</v>
+        <v>114</v>
       </c>
       <c r="F1614" t="n">
         <v>4</v>
@@ -45631,7 +45631,7 @@
         <v>4</v>
       </c>
       <c r="H1614" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1615">
@@ -45640,26 +45640,26 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Dijual Brand New Luxury House di Kemang, Jakarta Selatan</t>
+          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>7900000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1615" t="n">
-        <v>262</v>
+        <v>881</v>
       </c>
       <c r="E1615" t="n">
-        <v>161</v>
+        <v>1066</v>
       </c>
       <c r="F1615" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G1615" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="H1615" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1616">
@@ -45668,26 +45668,26 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bona Indah 3 Lantai Full Furnished Siap Huni Lokasi Strategis SHM Bagus</t>
+          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>4500000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1616" t="n">
-        <v>185</v>
+        <v>350</v>
       </c>
       <c r="E1616" t="n">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="F1616" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1616" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1616" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1617">
@@ -45696,26 +45696,26 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>Brand New Luxury House Fully Furnished &amp; Private Lift At Kemang Dalam, Jakarta Selatan</t>
+          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>62000000000</v>
+        <v>26000000000</v>
       </c>
       <c r="D1617" t="n">
-        <v>881</v>
+        <v>301</v>
       </c>
       <c r="E1617" t="n">
-        <v>1066</v>
+        <v>469</v>
       </c>
       <c r="F1617" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G1617" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H1617" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1618">
@@ -45724,26 +45724,26 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cilandak Belakang Citos Siap Huni 2.Lantai Strategis Dekat MRT</t>
+          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
         </is>
       </c>
       <c r="C1618" t="n">
-        <v>6500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1618" t="n">
-        <v>350</v>
+        <v>443</v>
       </c>
       <c r="E1618" t="n">
-        <v>270</v>
+        <v>655</v>
       </c>
       <c r="F1618" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1618" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1618" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1619">
@@ -45752,26 +45752,26 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kerinci Raya Kebayoran Baru Jalan Lebar bisa Buat Usaha</t>
+          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>26000000000</v>
+        <v>1340000000</v>
       </c>
       <c r="D1619" t="n">
-        <v>301</v>
+        <v>76</v>
       </c>
       <c r="E1619" t="n">
-        <v>469</v>
+        <v>26</v>
       </c>
       <c r="F1619" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G1619" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1619" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1620">
@@ -45780,26 +45780,26 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Dijual Rumah Kantor Permata Berlian Siap Pakai Luas 665M</t>
+          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
         </is>
       </c>
       <c r="C1620" t="n">
-        <v>30000000000</v>
+        <v>72000000000</v>
       </c>
       <c r="D1620" t="n">
-        <v>443</v>
+        <v>350</v>
       </c>
       <c r="E1620" t="n">
-        <v>655</v>
+        <v>1267</v>
       </c>
       <c r="F1620" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1620" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1620" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1621">
@@ -45808,26 +45808,26 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>Rumah Tampilan Modern Minimalis 3Lt di Jl Menteng Wadas Setiabudi</t>
+          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
         </is>
       </c>
       <c r="C1621" t="n">
-        <v>1340000000</v>
+        <v>6000000000</v>
       </c>
       <c r="D1621" t="n">
-        <v>76</v>
+        <v>256</v>
       </c>
       <c r="E1621" t="n">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="F1621" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1621" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1621" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1622">
@@ -45836,26 +45836,26 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>Pondok Indah View Lapangan Golf Harga Termurah Konsep Rumah Villa bisa untuk Healing</t>
+          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
         </is>
       </c>
       <c r="C1622" t="n">
-        <v>72000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="D1622" t="n">
-        <v>350</v>
+        <v>9635</v>
       </c>
       <c r="E1622" t="n">
-        <v>1267</v>
+        <v>9635</v>
       </c>
       <c r="F1622" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1622" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H1622" t="n">
-        <v>9</v>
+        <v>294</v>
       </c>
     </row>
     <row r="1623">
@@ -45864,26 +45864,26 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>[ Akses Lebar Bebas Banjir ] Kemang Barat Kavling Siap Bangun</t>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
         </is>
       </c>
       <c r="C1623" t="n">
-        <v>6000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1623" t="n">
-        <v>256</v>
+        <v>800</v>
       </c>
       <c r="E1623" t="n">
-        <v>256</v>
+        <v>1050</v>
       </c>
       <c r="F1623" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="G1623" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H1623" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1624">
@@ -45892,26 +45892,26 @@
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>[ Harga Under NJOP ] Kemang Timur Raya 1 Hektar</t>
+          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1624" t="n">
-        <v>160000000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1624" t="n">
-        <v>9635</v>
+        <v>750</v>
       </c>
       <c r="E1624" t="n">
-        <v>9635</v>
+        <v>610</v>
       </c>
       <c r="F1624" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G1624" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H1624" t="n">
-        <v>294</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1625">
@@ -45920,26 +45920,26 @@
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
         </is>
       </c>
       <c r="C1625" t="n">
-        <v>20000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1625" t="n">
-        <v>800</v>
+        <v>370</v>
       </c>
       <c r="E1625" t="n">
-        <v>1050</v>
+        <v>570</v>
       </c>
       <c r="F1625" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="G1625" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H1625" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1626">
@@ -45948,26 +45948,26 @@
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>Rumah Mewah Murah Siap Huni di Tebet Jakarta Selatan</t>
+          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
         </is>
       </c>
       <c r="C1626" t="n">
-        <v>19000000000</v>
+        <v>2700000000</v>
       </c>
       <c r="D1626" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="E1626" t="n">
-        <v>610</v>
+        <v>105</v>
       </c>
       <c r="F1626" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G1626" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H1626" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1627">
@@ -45976,26 +45976,26 @@
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>Rumah Lama Depan Taman Pondok Indah Cocok Bangun Ulang</t>
+          <t>Rumah di Grinting Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>30000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1627" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="E1627" t="n">
-        <v>570</v>
+        <v>198</v>
       </c>
       <c r="F1627" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1627" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1627" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1628">
@@ -46004,26 +46004,26 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Rumah Modern Tropical House Dalam Cluster di Graha Raya Bintaro</t>
+          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
         </is>
       </c>
       <c r="C1628" t="n">
-        <v>2700000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1628" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E1628" t="n">
-        <v>105</v>
+        <v>550</v>
       </c>
       <c r="F1628" t="n">
         <v>41</v>
       </c>
       <c r="G1628" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1628" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1629">
@@ -46032,26 +46032,26 @@
       </c>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>Rumah di Grinting Kebayoran Baru</t>
+          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
         </is>
       </c>
       <c r="C1629" t="n">
-        <v>6500000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1629" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E1629" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="F1629" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1629" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1629" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1630">
@@ -46060,26 +46060,26 @@
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah Siap Huni di Area Senopati</t>
+          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>38000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1630" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="E1630" t="n">
-        <v>550</v>
+        <v>65</v>
       </c>
       <c r="F1630" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1630" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H1630" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1631">
@@ -46088,26 +46088,26 @@
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>Rumah Bagus, Terawat, 2 Lantai, 5 Kamar, Cocok utk Hunian Keluarga, dekat Senopati dan SCBD</t>
+          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>10000000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1631" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E1631" t="n">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="F1631" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G1631" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H1631" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1632">
@@ -46116,26 +46116,26 @@
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>Rumah Minimalis Siap Huni di Jagakarsa Jakarta Selatan</t>
+          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>1400000000</v>
+        <v>175000000000</v>
       </c>
       <c r="D1632" t="n">
-        <v>120</v>
+        <v>3000</v>
       </c>
       <c r="E1632" t="n">
-        <v>65</v>
+        <v>9635</v>
       </c>
       <c r="F1632" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1632" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1632" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1633">
@@ -46144,26 +46144,26 @@
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>Rumah 1 Lantai SHM di Pinang Emas Pondok Indah</t>
+          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>5200000000</v>
+        <v>900000000</v>
       </c>
       <c r="D1633" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E1633" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F1633" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1633" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H1633" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1634">
@@ -46172,26 +46172,26 @@
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah Hitung Tanah Ex Sekolah Internasional Jl Kemang Timur, Pejaten Barat Jakarta Selatan</t>
+          <t>Rumah 2 Lantai di Pondok Indah Jl Alam Segar Pondok Pinang Jakarta Selatan LT 160M2 Murah.bawah.pasar Good.invest Cash Only</t>
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>175000000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1634" t="n">
-        <v>3000</v>
+        <v>186</v>
       </c>
       <c r="E1634" t="n">
-        <v>9635</v>
+        <v>160</v>
       </c>
       <c r="F1634" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1634" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1634" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1635">
@@ -46200,26 +46200,26 @@
       </c>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>Di Jual Rumah Mewah 2Lantai Hanya 10 Menit Dari Pintu Tol Jor dan 15 Menit Dari Pondok Indah Jaksel</t>
+          <t>Hunian Premium Pondok Indah 3 Lantai Dekat Taman</t>
         </is>
       </c>
       <c r="C1635" t="n">
-        <v>900000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1635" t="n">
-        <v>64</v>
+        <v>600</v>
       </c>
       <c r="E1635" t="n">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="F1635" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1635" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1635" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1636">
@@ -46228,26 +46228,26 @@
       </c>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Pondok Indah Jl Alam Segar Pondok Pinang Jakarta Selatan LT 160M2 Murah.bawah.pasar Good.invest Cash Only</t>
+          <t>Rumah Murah Premium Petukangan, Joglo, Kreo, Larangan</t>
         </is>
       </c>
       <c r="C1636" t="n">
-        <v>6100000000</v>
+        <v>685000000</v>
       </c>
       <c r="D1636" t="n">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="E1636" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="F1636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1636" t="n">
         <v>2</v>
       </c>
       <c r="H1636" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1637">
@@ -46256,26 +46256,26 @@
       </c>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>Hunian Premium Pondok Indah 3 Lantai Dekat Taman</t>
+          <t>Rumah Strategis 11 Menit ke Gerbang Tol Andara Siap KPR J47474</t>
         </is>
       </c>
       <c r="C1637" t="n">
-        <v>16500000000</v>
+        <v>4540000000</v>
       </c>
       <c r="D1637" t="n">
-        <v>600</v>
+        <v>277</v>
       </c>
       <c r="E1637" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="F1637" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1637" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1637" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1638">
@@ -46284,23 +46284,23 @@
       </c>
       <c r="B1638" t="inlineStr">
         <is>
-          <t>Rumah Murah Premium Petukangan, Joglo, Kreo, Larangan</t>
+          <t>Rumah LB 180 SHM 10 Menit ke Aeon Mall Tanjung Barat J-40352</t>
         </is>
       </c>
       <c r="C1638" t="n">
-        <v>685000000</v>
+        <v>4420000000</v>
       </c>
       <c r="D1638" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="E1638" t="n">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="F1638" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1638" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1638" t="n">
         <v>1</v>
@@ -46312,23 +46312,23 @@
       </c>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>Rumah Strategis 11 Menit ke Gerbang Tol Andara Siap KPR J47474</t>
+          <t>Rumah Idaman 13 Menit ke Terminal Ragunan 2 Lantai Siap Huni J45428</t>
         </is>
       </c>
       <c r="C1639" t="n">
-        <v>4540000000</v>
+        <v>3990000000</v>
       </c>
       <c r="D1639" t="n">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="E1639" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="F1639" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1639" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1639" t="n">
         <v>1</v>
@@ -46340,20 +46340,20 @@
       </c>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>Rumah LB 180 SHM 10 Menit ke Aeon Mall Tanjung Barat J-40352</t>
+          <t>Rumah Luas 2 LT 13 Menit ke Aeon Mall Tanjung Barat Hadap Timur J48669</t>
         </is>
       </c>
       <c r="C1640" t="n">
-        <v>4420000000</v>
+        <v>4700000000</v>
       </c>
       <c r="D1640" t="n">
-        <v>180</v>
+        <v>265</v>
       </c>
       <c r="E1640" t="n">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="F1640" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1640" t="n">
         <v>4</v>
@@ -46368,23 +46368,23 @@
       </c>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>Rumah Idaman 13 Menit ke Terminal Ragunan 2 Lantai Siap Huni J45428</t>
+          <t>Rumah LB 180 SHM 10 Menit ke Gerbang Tol Brigif Dibantu KPR J-37554</t>
         </is>
       </c>
       <c r="C1641" t="n">
-        <v>3990000000</v>
+        <v>1830000000</v>
       </c>
       <c r="D1641" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E1641" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="F1641" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1641" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1641" t="n">
         <v>1</v>
@@ -46396,23 +46396,23 @@
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>Luxe Court Permata Hijau Signature</t>
+          <t>Rumah Hadap Selatan LT 240 SHM 7 Menit ke Kebayoran Park Mall J-45991</t>
         </is>
       </c>
       <c r="C1642" t="n">
-        <v>13500000000</v>
+        <v>3870000000</v>
       </c>
       <c r="D1642" t="n">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="E1642" t="n">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="F1642" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1642" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1642" t="n">
         <v>1</v>
@@ -46424,23 +46424,23 @@
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>Rumah Luas 2 LT 13 Menit ke Aeon Mall Tanjung Barat Hadap Timur J48669</t>
+          <t>Padmavilla Pejaten</t>
         </is>
       </c>
       <c r="C1643" t="n">
-        <v>4700000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1643" t="n">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c r="E1643" t="n">
-        <v>198</v>
+        <v>55</v>
       </c>
       <c r="F1643" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1643" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1643" t="n">
         <v>1</v>
@@ -46452,20 +46452,20 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>Rumah LB 180 SHM 10 Menit ke Gerbang Tol Brigif Dibantu KPR J-37554</t>
+          <t>Rumah 3 LT Siap Huni 15 Mnt ke Gerbang Tol Cisalak Dibantu KPR J-46437</t>
         </is>
       </c>
       <c r="C1644" t="n">
-        <v>1830000000</v>
+        <v>1940000000</v>
       </c>
       <c r="D1644" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="E1644" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F1644" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1644" t="n">
         <v>2</v>
@@ -46480,26 +46480,26 @@
       </c>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>Rumah Hadap Selatan LT 240 SHM 7 Menit ke Kebayoran Park Mall J-45991</t>
+          <t>Rumah 2 Lantai di Kemang Bagus Ada Kolam Renang SHM Tidak Banjir</t>
         </is>
       </c>
       <c r="C1645" t="n">
-        <v>3870000000</v>
+        <v>11900000000</v>
       </c>
       <c r="D1645" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="E1645" t="n">
-        <v>240</v>
+        <v>544</v>
       </c>
       <c r="F1645" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1645" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1645" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1646">
@@ -46508,26 +46508,26 @@
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>Padmavilla Pejaten</t>
+          <t>Rumah Bawah NJOP di Ciganjur Jagakarsa Dekat Tol Brigif SHM</t>
         </is>
       </c>
       <c r="C1646" t="n">
-        <v>2600000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1646" t="n">
-        <v>88</v>
+        <v>300</v>
       </c>
       <c r="E1646" t="n">
-        <v>55</v>
+        <v>1722</v>
       </c>
       <c r="F1646" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1646" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1646" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1647">
@@ -46536,23 +46536,23 @@
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>Rumah 3 LT Siap Huni 15 Mnt ke Gerbang Tol Cisalak Dibantu KPR J-46437</t>
+          <t>Padmavilla Cilandak</t>
         </is>
       </c>
       <c r="C1647" t="n">
-        <v>1940000000</v>
+        <v>2830000000</v>
       </c>
       <c r="D1647" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E1647" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F1647" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G1647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1647" t="n">
         <v>1</v>
@@ -46564,26 +46564,26 @@
       </c>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai di Kemang Bagus Ada Kolam Renang SHM Tidak Banjir</t>
+          <t>Rumah Mewah Dijual Di Jakarta Di Pakubuwono</t>
         </is>
       </c>
       <c r="C1648" t="n">
-        <v>11900000000</v>
+        <v>88000000000</v>
       </c>
       <c r="D1648" t="n">
-        <v>650</v>
+        <v>1100</v>
       </c>
       <c r="E1648" t="n">
-        <v>544</v>
+        <v>1026</v>
       </c>
       <c r="F1648" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G1648" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H1648" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1649">
@@ -46592,26 +46592,26 @@
       </c>
       <c r="B1649" t="inlineStr">
         <is>
-          <t>Rumah Bawah NJOP di Ciganjur Jagakarsa Dekat Tol Brigif SHM</t>
+          <t>Rumah Mewah Kemang Jakarta</t>
         </is>
       </c>
       <c r="C1649" t="n">
-        <v>17200000000</v>
+        <v>33000000000</v>
       </c>
       <c r="D1649" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="E1649" t="n">
-        <v>1722</v>
+        <v>1420</v>
       </c>
       <c r="F1649" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1649" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1649" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1650">
@@ -46620,26 +46620,26 @@
       </c>
       <c r="B1650" t="inlineStr">
         <is>
-          <t>Padmavilla Cilandak</t>
+          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
         </is>
       </c>
       <c r="C1650" t="n">
-        <v>2830000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1650" t="n">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="E1650" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="F1650" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G1650" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1650" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1651">
@@ -46648,26 +46648,26 @@
       </c>
       <c r="B1651" t="inlineStr">
         <is>
-          <t>Rumah Mewah Dijual Di Jakarta Di Pakubuwono</t>
+          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1651" t="n">
-        <v>88000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="D1651" t="n">
-        <v>1100</v>
+        <v>255</v>
       </c>
       <c r="E1651" t="n">
-        <v>1026</v>
+        <v>1584</v>
       </c>
       <c r="F1651" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1651" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H1651" t="n">
-        <v>46</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1652">
@@ -46676,26 +46676,26 @@
       </c>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>Rumah Mewah Kemang Jakarta</t>
+          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
         </is>
       </c>
       <c r="C1652" t="n">
-        <v>33000000000</v>
+        <v>3300000000</v>
       </c>
       <c r="D1652" t="n">
-        <v>1600</v>
+        <v>219</v>
       </c>
       <c r="E1652" t="n">
-        <v>1420</v>
+        <v>200</v>
       </c>
       <c r="F1652" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1652" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1652" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1653">
@@ -46704,26 +46704,26 @@
       </c>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>For Sale! 3 Story House At Riverville Lebak Bulus South Jakarta - Good Deal!!</t>
+          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
         </is>
       </c>
       <c r="C1653" t="n">
-        <v>5500000000</v>
+        <v>3200000000</v>
       </c>
       <c r="D1653" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E1653" t="n">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="F1653" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="G1653" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H1653" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1654">
@@ -46732,26 +46732,26 @@
       </c>
       <c r="B1654" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Luas Kebagusan Jakarta Selatan</t>
+          <t>Rumah Area Senopati, Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1654" t="n">
-        <v>35000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="D1654" t="n">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="E1654" t="n">
-        <v>1584</v>
+        <v>334</v>
       </c>
       <c r="F1654" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="G1654" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H1654" t="n">
-        <v>212</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1655">
@@ -46760,26 +46760,26 @@
       </c>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>Rumah SHM Baliview Termurah Dicirendeu</t>
+          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
         </is>
       </c>
       <c r="C1655" t="n">
-        <v>3300000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1655" t="n">
-        <v>219</v>
+        <v>1200</v>
       </c>
       <c r="E1655" t="n">
-        <v>200</v>
+        <v>2138</v>
       </c>
       <c r="F1655" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1655" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H1655" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1656">
@@ -46788,26 +46788,26 @@
       </c>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>Turun Harga .Jual Cepat.rumah.tebet Dalam</t>
+          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
         </is>
       </c>
       <c r="C1656" t="n">
-        <v>3200000000</v>
+        <v>14000000000</v>
       </c>
       <c r="D1656" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="E1656" t="n">
-        <v>159</v>
+        <v>832</v>
       </c>
       <c r="F1656" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1656" t="n">
         <v>3</v>
       </c>
       <c r="H1656" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1657">
@@ -46816,26 +46816,26 @@
       </c>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>Rumah Area Senopati, Lokasi Bagus</t>
+          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
         </is>
       </c>
       <c r="C1657" t="n">
-        <v>15700000000</v>
+        <v>17200000000</v>
       </c>
       <c r="D1657" t="n">
-        <v>365</v>
+        <v>700</v>
       </c>
       <c r="E1657" t="n">
-        <v>334</v>
+        <v>864</v>
       </c>
       <c r="F1657" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G1657" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1657" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1658">
@@ -46844,26 +46844,26 @@
       </c>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>Resort House, 2 Lantai, SHM, di Ragunan,</t>
+          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
         </is>
       </c>
       <c r="C1658" t="n">
-        <v>32000000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1658" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="E1658" t="n">
-        <v>2138</v>
+        <v>74</v>
       </c>
       <c r="F1658" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1658" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H1658" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1659">
@@ -46872,26 +46872,26 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+          <t>Drop Price Rumah Mewah Cantik Senopati</t>
         </is>
       </c>
       <c r="C1659" t="n">
-        <v>6400000000</v>
+        <v>22500000000</v>
       </c>
       <c r="D1659" t="n">
-        <v>308</v>
+        <v>500</v>
       </c>
       <c r="E1659" t="n">
-        <v>160</v>
+        <v>366</v>
       </c>
       <c r="F1659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1659" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1659" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1660">
@@ -46900,26 +46900,26 @@
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah di Kemang Dalam Komplek Luas 832M Rp 15 M</t>
+          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1660" t="n">
-        <v>14000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="D1660" t="n">
-        <v>700</v>
+        <v>261</v>
       </c>
       <c r="E1660" t="n">
-        <v>832</v>
+        <v>240</v>
       </c>
       <c r="F1660" t="n">
         <v>5</v>
       </c>
       <c r="G1660" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1660" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1661">
@@ -46928,26 +46928,26 @@
       </c>
       <c r="B1661" t="inlineStr">
         <is>
-          <t>Dijual Murah Bawah NJOP Rumah Siap Pakai di Kemang Timur Raya. Luas 864M Hanya Rp.17.25 M</t>
+          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1661" t="n">
-        <v>17200000000</v>
+        <v>850000000</v>
       </c>
       <c r="D1661" t="n">
-        <v>700</v>
+        <v>44</v>
       </c>
       <c r="E1661" t="n">
-        <v>864</v>
+        <v>24</v>
       </c>
       <c r="F1661" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1661" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1661" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1662">
@@ -46956,26 +46956,26 @@
       </c>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>ZENITPARC HYTT</t>
+          <t>Below Market! Investasi Tepat Rumah Murah Pondok Indah Siap Huni</t>
         </is>
       </c>
       <c r="C1662" t="n">
-        <v>1700000000</v>
+        <v>5500000000</v>
       </c>
       <c r="D1662" t="n">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="E1662" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="F1662" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1662" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1663">
@@ -46984,17 +46984,17 @@
       </c>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Strategis Dekat MRT dan Toll di Cilandak</t>
+          <t>Miliki Segera Dijual Rumah Baru Ready Unit di Jagakarsa Jaksel Diskon 100Jt</t>
         </is>
       </c>
       <c r="C1663" t="n">
-        <v>1900000000</v>
+        <v>950000000</v>
       </c>
       <c r="D1663" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E1663" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F1663" t="n">
         <v>3</v>
@@ -47003,7 +47003,7 @@
         <v>2</v>
       </c>
       <c r="H1663" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1664">
@@ -47012,26 +47012,26 @@
       </c>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>Drop Price Rumah Mewah Cantik Senopati</t>
+          <t>Miliki Segera di Jual Rumah Baru Siap Huni bisa DP 0% N Diskon 200Jt di Jagakarsa Jaksel</t>
         </is>
       </c>
       <c r="C1664" t="n">
-        <v>22500000000</v>
+        <v>1250000000</v>
       </c>
       <c r="D1664" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="E1664" t="n">
-        <v>366</v>
+        <v>68</v>
       </c>
       <c r="F1664" t="n">
         <v>3</v>
       </c>
       <c r="G1664" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1664" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1665">
@@ -47040,26 +47040,26 @@
       </c>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>Dijual Rumah Estetik Siap Huni di Kemang, Jakarta Selatan</t>
+          <t>Harga Mepet NJOP Rumah Pondok Indah</t>
         </is>
       </c>
       <c r="C1665" t="n">
-        <v>9000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="D1665" t="n">
-        <v>261</v>
+        <v>1980</v>
       </c>
       <c r="E1665" t="n">
-        <v>240</v>
+        <v>769</v>
       </c>
       <c r="F1665" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1665" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1665" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1666">
@@ -47068,26 +47068,26 @@
       </c>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>KPR Cluster Minimalis Hadir di Kuningan Jakarta Selatan</t>
+          <t>2 Lantai Jakarta Cash KPR Nego Tanpa DP Akses Bagus</t>
         </is>
       </c>
       <c r="C1666" t="n">
-        <v>850000000</v>
+        <v>1600000000</v>
       </c>
       <c r="D1666" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="E1666" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F1666" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1666" t="n">
         <v>2</v>
       </c>
       <c r="H1666" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1667">
@@ -47096,26 +47096,26 @@
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>Below Market! Investasi Tepat Rumah Murah Pondok Indah Siap Huni</t>
+          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
         </is>
       </c>
       <c r="C1667" t="n">
         <v>5500000000</v>
       </c>
       <c r="D1667" t="n">
-        <v>200</v>
+        <v>360</v>
       </c>
       <c r="E1667" t="n">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="F1667" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1667" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1667" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1668">
@@ -47124,26 +47124,26 @@
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>Miliki Segera Dijual Rumah Baru Ready Unit di Jagakarsa Jaksel Diskon 100Jt</t>
+          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1668" t="n">
-        <v>950000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1668" t="n">
-        <v>57</v>
+        <v>600</v>
       </c>
       <c r="E1668" t="n">
-        <v>79</v>
+        <v>1020</v>
       </c>
       <c r="F1668" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1668" t="n">
         <v>2</v>
       </c>
       <c r="H1668" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1669">
@@ -47152,26 +47152,26 @@
       </c>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>Miliki Segera di Jual Rumah Baru Siap Huni bisa DP 0% N Diskon 200Jt di Jagakarsa Jaksel</t>
+          <t>Dijual Rumah Karet Kuningan Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1669" t="n">
-        <v>1250000000</v>
+        <v>78700000000</v>
       </c>
       <c r="D1669" t="n">
-        <v>75</v>
+        <v>994</v>
       </c>
       <c r="E1669" t="n">
-        <v>68</v>
+        <v>1750</v>
       </c>
       <c r="F1669" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1669" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1669" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1670">
@@ -47180,26 +47180,26 @@
       </c>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>Harga Mepet NJOP Rumah Pondok Indah</t>
+          <t>Dijual Rumah Siap Pakai di Tebet Kondisi Terawat</t>
         </is>
       </c>
       <c r="C1670" t="n">
-        <v>28000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="D1670" t="n">
-        <v>1980</v>
+        <v>250</v>
       </c>
       <c r="E1670" t="n">
-        <v>769</v>
+        <v>241</v>
       </c>
       <c r="F1670" t="n">
         <v>4</v>
       </c>
       <c r="G1670" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1670" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1671">
@@ -47208,26 +47208,26 @@
       </c>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>2 Lantai Jakarta Cash KPR Nego Tanpa DP Akses Bagus</t>
+          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1671" t="n">
-        <v>1600000000</v>
+        <v>55000000000</v>
       </c>
       <c r="D1671" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E1671" t="n">
-        <v>70</v>
+        <v>5500</v>
       </c>
       <c r="F1671" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1671" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H1671" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1672">
@@ -47236,26 +47236,26 @@
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>Rumah Tropis Minimalis Konsep Villa di Lebak Bulus</t>
+          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1672" t="n">
-        <v>5500000000</v>
+        <v>23600000000</v>
       </c>
       <c r="D1672" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="E1672" t="n">
-        <v>230</v>
+        <v>1495</v>
       </c>
       <c r="F1672" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G1672" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H1672" t="n">
-        <v>11</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1673">
@@ -47264,26 +47264,26 @@
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lama Komplek Hankam Cidodol Jakarta Selatan</t>
+          <t>Gedung Pinang - Pondok Indah - Lokasi Tenang</t>
         </is>
       </c>
       <c r="C1673" t="n">
-        <v>21000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1673" t="n">
-        <v>600</v>
+        <v>320</v>
       </c>
       <c r="E1673" t="n">
-        <v>1020</v>
+        <v>300</v>
       </c>
       <c r="F1673" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1673" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1673" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1674">
@@ -47292,26 +47292,26 @@
       </c>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>Dijual Rumah Karet Kuningan Jakarta Selatan</t>
+          <t>Harewood House</t>
         </is>
       </c>
       <c r="C1674" t="n">
-        <v>78700000000</v>
+        <v>3000000000</v>
       </c>
       <c r="D1674" t="n">
-        <v>994</v>
+        <v>154</v>
       </c>
       <c r="E1674" t="n">
-        <v>1750</v>
+        <v>121</v>
       </c>
       <c r="F1674" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1674" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1674" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1675">
@@ -47320,26 +47320,26 @@
       </c>
       <c r="B1675" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Pakai di Tebet Kondisi Terawat</t>
+          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1675" t="n">
-        <v>8000000000</v>
+        <v>51000000000</v>
       </c>
       <c r="D1675" t="n">
-        <v>250</v>
+        <v>457</v>
       </c>
       <c r="E1675" t="n">
-        <v>241</v>
+        <v>494</v>
       </c>
       <c r="F1675" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1675" t="n">
         <v>4</v>
       </c>
       <c r="H1675" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1676">
@@ -47348,26 +47348,26 @@
       </c>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah 65% di Bawah NJOP di Ampera Kemang Jakarta Selatan</t>
+          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
         </is>
       </c>
       <c r="C1676" t="n">
-        <v>55000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1676" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E1676" t="n">
-        <v>5500</v>
+        <v>71</v>
       </c>
       <c r="F1676" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1676" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H1676" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1677">
@@ -47376,26 +47376,26 @@
       </c>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>Lelang Rumah Besar Buat Usaha Kantor di Bawah NJOP di Kemang Jakarta Selatan</t>
+          <t>Sthana Jeruk Purut</t>
         </is>
       </c>
       <c r="C1677" t="n">
-        <v>23600000000</v>
+        <v>4500000000</v>
       </c>
       <c r="D1677" t="n">
-        <v>1000</v>
+        <v>232</v>
       </c>
       <c r="E1677" t="n">
-        <v>1495</v>
+        <v>114</v>
       </c>
       <c r="F1677" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G1677" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1677" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1678">
@@ -47404,26 +47404,26 @@
       </c>
       <c r="B1678" t="inlineStr">
         <is>
-          <t>Gedung Pinang - Pondok Indah - Lokasi Tenang</t>
+          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
         </is>
       </c>
       <c r="C1678" t="n">
-        <v>16000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1678" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="E1678" t="n">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="F1678" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1678" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1678" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1679">
@@ -47432,26 +47432,26 @@
       </c>
       <c r="B1679" t="inlineStr">
         <is>
-          <t>Harewood House</t>
+          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
         </is>
       </c>
       <c r="C1679" t="n">
-        <v>3000000000</v>
+        <v>11000000000</v>
       </c>
       <c r="D1679" t="n">
-        <v>154</v>
+        <v>685</v>
       </c>
       <c r="E1679" t="n">
-        <v>121</v>
+        <v>685</v>
       </c>
       <c r="F1679" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1679" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1679" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1680">
@@ -47460,26 +47460,26 @@
       </c>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>Dijual Rumah Siap Huni di Area Brawijaya Kebayoran Baru Jakarta Selatan Kebayoran Baru Jakarta Selatan</t>
+          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
         </is>
       </c>
       <c r="C1680" t="n">
-        <v>51000000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1680" t="n">
-        <v>457</v>
+        <v>300</v>
       </c>
       <c r="E1680" t="n">
-        <v>494</v>
+        <v>293</v>
       </c>
       <c r="F1680" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1680" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1680" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1681">
@@ -47488,26 +47488,26 @@
       </c>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+          <t>Urban Living Gandaria</t>
         </is>
       </c>
       <c r="C1681" t="n">
-        <v>19000000000</v>
+        <v>6100000000</v>
       </c>
       <c r="D1681" t="n">
-        <v>800</v>
+        <v>355</v>
       </c>
       <c r="E1681" t="n">
-        <v>1050</v>
+        <v>140</v>
       </c>
       <c r="F1681" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1681" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H1681" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1682">
@@ -47516,26 +47516,26 @@
       </c>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>4 KM Dari Toll Akses Pinggir Jalan Legalitas SHM Bebas Banjir</t>
+          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
         </is>
       </c>
       <c r="C1682" t="n">
-        <v>1500000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1682" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="E1682" t="n">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="F1682" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1682" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1682" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1683">
@@ -47544,26 +47544,26 @@
       </c>
       <c r="B1683" t="inlineStr">
         <is>
-          <t>Sthana Jeruk Purut</t>
+          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1683" t="n">
-        <v>4500000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1683" t="n">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="E1683" t="n">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="F1683" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1683" t="n">
         <v>4</v>
       </c>
       <c r="H1683" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1684">
@@ -47572,26 +47572,26 @@
       </c>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>Hunian Strategis Jagakarsa Listrik Underground Legalitas SHM</t>
+          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
         </is>
       </c>
       <c r="C1684" t="n">
-        <v>1400000000</v>
+        <v>11500000000</v>
       </c>
       <c r="D1684" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="E1684" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="F1684" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1684" t="n">
         <v>2</v>
       </c>
       <c r="H1684" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1685">
@@ -47600,26 +47600,26 @@
       </c>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>Rumah Hitung Tanah Paling Murah Cilandak 685 Meter</t>
+          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
         </is>
       </c>
       <c r="C1685" t="n">
-        <v>11000000000</v>
+        <v>62000000000</v>
       </c>
       <c r="D1685" t="n">
-        <v>685</v>
+        <v>881</v>
       </c>
       <c r="E1685" t="n">
-        <v>685</v>
+        <v>1066</v>
       </c>
       <c r="F1685" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1685" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1685" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1686">
@@ -47628,26 +47628,26 @@
       </c>
       <c r="B1686" t="inlineStr">
         <is>
-          <t>Rumah Murah Pejaten Barat Jalan Kaki ke Rs Siaga</t>
+          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
         </is>
       </c>
       <c r="C1686" t="n">
-        <v>4900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1686" t="n">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="E1686" t="n">
-        <v>293</v>
+        <v>634</v>
       </c>
       <c r="F1686" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1686" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H1686" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1687">
@@ -47656,26 +47656,26 @@
       </c>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>Urban Living Gandaria</t>
+          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1687" t="n">
-        <v>6100000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1687" t="n">
-        <v>355</v>
+        <v>780</v>
       </c>
       <c r="E1687" t="n">
-        <v>140</v>
+        <v>936</v>
       </c>
       <c r="F1687" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="G1687" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="H1687" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1688">
@@ -47684,26 +47684,26 @@
       </c>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>Rumah Bagus 497 Meter Dekat Urban Forest</t>
+          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
         </is>
       </c>
       <c r="C1688" t="n">
-        <v>12000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1688" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E1688" t="n">
-        <v>497</v>
+        <v>182</v>
       </c>
       <c r="F1688" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1688" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1688" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1689">
@@ -47712,26 +47712,26 @@
       </c>
       <c r="B1689" t="inlineStr">
         <is>
-          <t>Rumah Baru 2 Lantai Siap Huni Jagakarsa Jakarta Selatan</t>
+          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
         </is>
       </c>
       <c r="C1689" t="n">
-        <v>2900000000</v>
+        <v>5200000000</v>
       </c>
       <c r="D1689" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="E1689" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="F1689" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G1689" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H1689" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1690">
@@ -47740,26 +47740,26 @@
       </c>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>Rumah Tua Good Deal 35,8 Juta Hitung Tanah di Kebayoran Baru Cocok Usaha</t>
+          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
         </is>
       </c>
       <c r="C1690" t="n">
-        <v>11500000000</v>
+        <v>3900000000</v>
       </c>
       <c r="D1690" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E1690" t="n">
-        <v>320</v>
+        <v>157</v>
       </c>
       <c r="F1690" t="n">
         <v>4</v>
       </c>
       <c r="G1690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1690" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1691">
@@ -47768,26 +47768,26 @@
       </c>
       <c r="B1691" t="inlineStr">
         <is>
-          <t>For Sale Brand New Luxury House Exclusive Kemang Dalam</t>
+          <t>Aparthouse River 8 Residence</t>
         </is>
       </c>
       <c r="C1691" t="n">
-        <v>62000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="D1691" t="n">
-        <v>881</v>
+        <v>45</v>
       </c>
       <c r="E1691" t="n">
-        <v>1066</v>
+        <v>15</v>
       </c>
       <c r="F1691" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1691" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1691" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1692">
@@ -47796,26 +47796,26 @@
       </c>
       <c r="B1692" t="inlineStr">
         <is>
-          <t>Termurah Jual Rugi Cepat Rumah Mewah+ Pool 634M2 di Pondok Indah</t>
+          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1692" t="n">
-        <v>32000000000</v>
+        <v>17700000000</v>
       </c>
       <c r="D1692" t="n">
-        <v>720</v>
+        <v>1100</v>
       </c>
       <c r="E1692" t="n">
-        <v>634</v>
+        <v>360</v>
       </c>
       <c r="F1692" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G1692" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H1692" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1693">
@@ -47824,26 +47824,26 @@
       </c>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>Rumah Tropis dengan Sentuhan Tradisional di Jagakarsa, Hidden Gem Jakarta Selatan</t>
+          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
         </is>
       </c>
       <c r="C1693" t="n">
-        <v>21500000000</v>
+        <v>1900000000</v>
       </c>
       <c r="D1693" t="n">
-        <v>780</v>
+        <v>60</v>
       </c>
       <c r="E1693" t="n">
-        <v>936</v>
+        <v>74</v>
       </c>
       <c r="F1693" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G1693" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="H1693" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1694">
@@ -47852,26 +47852,26 @@
       </c>
       <c r="B1694" t="inlineStr">
         <is>
-          <t>Rumah Hancur Hitung Tanah di Kasablanka Cocok Buat Kost</t>
+          <t>Pinang Residences</t>
         </is>
       </c>
       <c r="C1694" t="n">
-        <v>2900000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1694" t="n">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="E1694" t="n">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="F1694" t="n">
         <v>3</v>
       </c>
       <c r="G1694" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1694" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1695">
@@ -47880,26 +47880,26 @@
       </c>
       <c r="B1695" t="inlineStr">
         <is>
-          <t>Jual Cepat Hitung Tanah SHM 201M2 Akses Jalan Lebar</t>
+          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1695" t="n">
-        <v>5200000000</v>
+        <v>19000000000</v>
       </c>
       <c r="D1695" t="n">
-        <v>225</v>
+        <v>550</v>
       </c>
       <c r="E1695" t="n">
-        <v>201</v>
+        <v>1094</v>
       </c>
       <c r="F1695" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1695" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H1695" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1696">
@@ -47908,26 +47908,26 @@
       </c>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>Jual Rumah Siap Huni Pinggir Jalan Lebar Hanya5menit ke Kokas</t>
+          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
         </is>
       </c>
       <c r="C1696" t="n">
-        <v>3900000000</v>
+        <v>9700000000</v>
       </c>
       <c r="D1696" t="n">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="E1696" t="n">
-        <v>157</v>
+        <v>647</v>
       </c>
       <c r="F1696" t="n">
         <v>4</v>
       </c>
       <c r="G1696" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1696" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1697">
@@ -47936,26 +47936,26 @@
       </c>
       <c r="B1697" t="inlineStr">
         <is>
-          <t>Aparthouse River 8 Residence</t>
+          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
         </is>
       </c>
       <c r="C1697" t="n">
-        <v>1000000000</v>
+        <v>4280000000</v>
       </c>
       <c r="D1697" t="n">
-        <v>45</v>
+        <v>262</v>
       </c>
       <c r="E1697" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F1697" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1697" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1697" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1698">
@@ -47964,26 +47964,26 @@
       </c>
       <c r="B1698" t="inlineStr">
         <is>
-          <t>Brand New American Style Lux With Private Lift Dipejaten Barat Kemang Jakarta Selatan</t>
+          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
         </is>
       </c>
       <c r="C1698" t="n">
-        <v>17700000000</v>
+        <v>19500000000</v>
       </c>
       <c r="D1698" t="n">
-        <v>1100</v>
+        <v>580</v>
       </c>
       <c r="E1698" t="n">
-        <v>360</v>
+        <v>673</v>
       </c>
       <c r="F1698" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G1698" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="H1698" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1699">
@@ -47992,26 +47992,26 @@
       </c>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>For Sale Rumah 2 Lantai Bagus Kondisi Baru Strategis Dekat MRT Sekolah Kampus Rs</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1699" t="n">
-        <v>1900000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1699" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="E1699" t="n">
-        <v>74</v>
+        <v>2138</v>
       </c>
       <c r="F1699" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1699" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1699" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1700">
@@ -48020,26 +48020,26 @@
       </c>
       <c r="B1700" t="inlineStr">
         <is>
-          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
+          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
         </is>
       </c>
       <c r="C1700" t="n">
-        <v>38000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1700" t="n">
-        <v>760</v>
+        <v>120</v>
       </c>
       <c r="E1700" t="n">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="F1700" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1700" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1700" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1701">
@@ -48048,26 +48048,26 @@
       </c>
       <c r="B1701" t="inlineStr">
         <is>
-          <t>Pinang Residences</t>
+          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1701" t="n">
-        <v>4900000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1701" t="n">
-        <v>273</v>
+        <v>800</v>
       </c>
       <c r="E1701" t="n">
-        <v>131</v>
+        <v>1335</v>
       </c>
       <c r="F1701" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1701" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1701" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1702">
@@ -48076,26 +48076,26 @@
       </c>
       <c r="B1702" t="inlineStr">
         <is>
-          <t>Rumah Asri Siap Huni Private Pool di Pejaten Barat Kemang Jakarta Selatan</t>
+          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
         </is>
       </c>
       <c r="C1702" t="n">
-        <v>19000000000</v>
+        <v>27000000000</v>
       </c>
       <c r="D1702" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
       <c r="E1702" t="n">
-        <v>1094</v>
+        <v>1335</v>
       </c>
       <c r="F1702" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G1702" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1702" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1703">
@@ -48104,26 +48104,26 @@
       </c>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>Buc!! Aset Murah Dibawah NJOP Komersial Pejaten</t>
+          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
         </is>
       </c>
       <c r="C1703" t="n">
-        <v>9700000000</v>
+        <v>120000000000</v>
       </c>
       <c r="D1703" t="n">
-        <v>245</v>
+        <v>2100</v>
       </c>
       <c r="E1703" t="n">
-        <v>647</v>
+        <v>1025</v>
       </c>
       <c r="F1703" t="n">
         <v>4</v>
       </c>
       <c r="G1703" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1703" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1704">
@@ -48132,26 +48132,26 @@
       </c>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>Brand New Auto Skena Kalcer di Cilandak Kko</t>
+          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
         </is>
       </c>
       <c r="C1704" t="n">
-        <v>4280000000</v>
+        <v>32000000000</v>
       </c>
       <c r="D1704" t="n">
-        <v>262</v>
+        <v>1200</v>
       </c>
       <c r="E1704" t="n">
-        <v>85</v>
+        <v>2138</v>
       </c>
       <c r="F1704" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1704" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1704" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1705">
@@ -48160,26 +48160,26 @@
       </c>
       <c r="B1705" t="inlineStr">
         <is>
-          <t>Brand New Jatipadang Kalcer Skena Bossku</t>
+          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
         </is>
       </c>
       <c r="C1705" t="n">
-        <v>19500000000</v>
+        <v>10000000000</v>
       </c>
       <c r="D1705" t="n">
-        <v>580</v>
+        <v>350</v>
       </c>
       <c r="E1705" t="n">
-        <v>673</v>
+        <v>216</v>
       </c>
       <c r="F1705" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1705" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="H1705" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1706">
@@ -48188,26 +48188,26 @@
       </c>
       <c r="B1706" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Rumah 2 LT Unit Pojok No Banjir 1,3 KM Pintu Tol Brigif KPR 0</t>
         </is>
       </c>
       <c r="C1706" t="n">
-        <v>32000000000</v>
+        <v>2750000000</v>
       </c>
       <c r="D1706" t="n">
-        <v>1200</v>
+        <v>115</v>
       </c>
       <c r="E1706" t="n">
-        <v>2138</v>
+        <v>141</v>
       </c>
       <c r="F1706" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1706" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H1706" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1707">
@@ -48216,26 +48216,26 @@
       </c>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>Rumah Tanjung Barat Dekat Aeon Mall Kalcer</t>
+          <t>Rumah Bagus di Pondok Indah</t>
         </is>
       </c>
       <c r="C1707" t="n">
-        <v>1400000000</v>
+        <v>60000000000</v>
       </c>
       <c r="D1707" t="n">
-        <v>120</v>
+        <v>743</v>
       </c>
       <c r="E1707" t="n">
-        <v>60</v>
+        <v>1180</v>
       </c>
       <c r="F1707" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1707" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1707" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1708">
@@ -48244,26 +48244,26 @@
       </c>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>Rumah Vibes Ubud Furnished di Ampera Jaksel</t>
+          <t>Rumah 3 Lt Serasa Villa View Danau Jarang Ada Unit Terbatas No Banjir !!</t>
         </is>
       </c>
       <c r="C1708" t="n">
-        <v>27000000000</v>
+        <v>2600000000</v>
       </c>
       <c r="D1708" t="n">
-        <v>800</v>
+        <v>155</v>
       </c>
       <c r="E1708" t="n">
-        <v>1335</v>
+        <v>100</v>
       </c>
       <c r="F1708" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G1708" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="H1708" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1709">
@@ -48272,26 +48272,26 @@
       </c>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>Rumah Sultan Vibes Ubud di Ampera Jaksel</t>
+          <t>Dijual Rumah Mewah Siap Huni Akses 3Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1709" t="n">
-        <v>27000000000</v>
+        <v>8750000000</v>
       </c>
       <c r="D1709" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="E1709" t="n">
-        <v>1335</v>
+        <v>255</v>
       </c>
       <c r="F1709" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1709" t="n">
         <v>6</v>
       </c>
       <c r="H1709" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1710">
@@ -48300,26 +48300,26 @@
       </c>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>For Sale Pondok Indah Jakarta Selatan Brand New A Luxury American Classic House.under Finising.detail:luas Tanah 1.025 M²Luas Bangunan 2.100 M²Private Liftprivate Swimming Pool3 Lantaikamar Tidur 4 + 3(Staff)Kamar Mandi 5 + 2 (Staff)Garasi 6 Mobilcarpot 4</t>
+          <t>Dijual Rumah Bagus Siap Huni Murah Akses 1Mobil Lokasi Tebet Barat</t>
         </is>
       </c>
       <c r="C1710" t="n">
-        <v>120000000000</v>
+        <v>2550000000</v>
       </c>
       <c r="D1710" t="n">
-        <v>2100</v>
+        <v>60</v>
       </c>
       <c r="E1710" t="n">
-        <v>1025</v>
+        <v>90</v>
       </c>
       <c r="F1710" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1710" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1710" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1711">
@@ -48328,26 +48328,26 @@
       </c>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>Rumah Vibes Resort di Jagakarsa Nearby Cilandak</t>
+          <t>Dijual Rumah Mewah Siap Huni Akses 2Mobil Lokasi Tebet Timur</t>
         </is>
       </c>
       <c r="C1711" t="n">
-        <v>32000000000</v>
+        <v>6500000000</v>
       </c>
       <c r="D1711" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="E1711" t="n">
-        <v>2138</v>
+        <v>179</v>
       </c>
       <c r="F1711" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1711" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1711" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1712">
@@ -48356,26 +48356,26 @@
       </c>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>Harga NJOP, Rumah 2 Lantai, Full Furnished, 5 Kamar di Pondok Indah, Cocok U Hunian Keluarga</t>
+          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
         </is>
       </c>
       <c r="C1712" t="n">
-        <v>10000000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1712" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E1712" t="n">
-        <v>216</v>
+        <v>960</v>
       </c>
       <c r="F1712" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1712" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H1712" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1713">
@@ -48384,26 +48384,26 @@
       </c>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>Rumah 2 LT Unit Pojok No Banjir 1,3 KM Pintu Tol Brigif KPR 0</t>
+          <t>Dijual Murah Rumah Istana Super Lux Di Pondok Indah Luas 2382m Hanya Rp 89 M ( Hanya 37 Juta/m2 )</t>
         </is>
       </c>
       <c r="C1713" t="n">
-        <v>2750000000</v>
+        <v>89000000000</v>
       </c>
       <c r="D1713" t="n">
-        <v>115</v>
+        <v>2700</v>
       </c>
       <c r="E1713" t="n">
-        <v>141</v>
+        <v>2382</v>
       </c>
       <c r="F1713" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G1713" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H1713" t="n">
-        <v>2</v>
+        <v>510</v>
       </c>
     </row>
     <row r="1714">
@@ -48412,26 +48412,26 @@
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>Rumah Bagus di Pondok Indah</t>
+          <t>Edenhaus Simatupang</t>
         </is>
       </c>
       <c r="C1714" t="n">
-        <v>60000000000</v>
+        <v>9900000000</v>
       </c>
       <c r="D1714" t="n">
-        <v>743</v>
+        <v>222</v>
       </c>
       <c r="E1714" t="n">
-        <v>1180</v>
+        <v>240</v>
       </c>
       <c r="F1714" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G1714" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1714" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1715">
@@ -48440,26 +48440,26 @@
       </c>
       <c r="B1715" t="inlineStr">
         <is>
-          <t>Rumah 3 Lt Serasa Villa View Danau Jarang Ada Unit Terbatas No Banjir !!</t>
+          <t>Dijual Rumah Seperti Ddalam Komplek(Gated) Dikebayoran Baru. Luas 340M.(Fisik 360M) Rp.21.5 M</t>
         </is>
       </c>
       <c r="C1715" t="n">
-        <v>2600000000</v>
+        <v>21500000000</v>
       </c>
       <c r="D1715" t="n">
-        <v>155</v>
+        <v>500</v>
       </c>
       <c r="E1715" t="n">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="F1715" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1715" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H1715" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1716">
@@ -48468,26 +48468,26 @@
       </c>
       <c r="B1716" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Siap Huni Akses 3Mobil Lokasi Tebet Timur</t>
+          <t>Dijual Rumah di Area Dekat Jl. Sriwijaya, Kelurahan Selong, LT 875M Hanya Rp 105 M Nego. Lokasi Terbaik, Dekat Sriwijaya</t>
         </is>
       </c>
       <c r="C1716" t="n">
-        <v>8750000000</v>
+        <v>105000000000</v>
       </c>
       <c r="D1716" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E1716" t="n">
-        <v>255</v>
+        <v>815</v>
       </c>
       <c r="F1716" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1716" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1716" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1717">
@@ -48496,26 +48496,26 @@
       </c>
       <c r="B1717" t="inlineStr">
         <is>
-          <t>Dijual Rumah Bagus Siap Huni Murah Akses 1Mobil Lokasi Tebet Barat</t>
+          <t>Rumah 2 Lantai Full Furnished Kpr 0 Di Town House Tenang Bebas Banjir</t>
         </is>
       </c>
       <c r="C1717" t="n">
-        <v>2550000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1717" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E1717" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F1717" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1717" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1718">
@@ -48524,26 +48524,26 @@
       </c>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>Dijual Rumah Mewah Siap Huni Akses 2Mobil Lokasi Tebet Timur</t>
+          <t>Rumah 2 LT minimalis fungsionalis nyaman di Jaksel DP KPR 0</t>
         </is>
       </c>
       <c r="C1718" t="n">
-        <v>6500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D1718" t="n">
-        <v>250</v>
+        <v>127</v>
       </c>
       <c r="E1718" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="F1718" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1718" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H1718" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1719">
@@ -48552,26 +48552,26 @@
       </c>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>Nivara Resort Townhouse at Wijaya</t>
+          <t>Dijual Rumah Cilandak Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1719" t="n">
-        <v>7900000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1719" t="n">
-        <v>375</v>
+        <v>530</v>
       </c>
       <c r="E1719" t="n">
-        <v>76</v>
+        <v>850</v>
       </c>
       <c r="F1719" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G1719" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1719" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1720">
@@ -48580,26 +48580,26 @@
       </c>
       <c r="B1720" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Dalam Komplek Di Lebak Bulus. Luas 960m2</t>
+          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
         </is>
       </c>
       <c r="C1720" t="n">
-        <v>21000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="D1720" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="E1720" t="n">
-        <v>960</v>
+        <v>93</v>
       </c>
       <c r="F1720" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1720" t="n">
         <v>4</v>
       </c>
       <c r="H1720" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1721">
@@ -48608,23 +48608,23 @@
       </c>
       <c r="B1721" t="inlineStr">
         <is>
-          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
         </is>
       </c>
       <c r="C1721" t="n">
-        <v>85000000000</v>
+        <v>97000000000</v>
       </c>
       <c r="D1721" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="E1721" t="n">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="F1721" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="G1721" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="H1721" t="n">
         <v>44</v>
@@ -48636,26 +48636,26 @@
       </c>
       <c r="B1722" t="inlineStr">
         <is>
-          <t>Dijual Murah Rumah Istana Super Lux Di Pondok Indah Luas 2382m Hanya Rp 89 M ( Hanya 37 Juta/m2 )</t>
+          <t>Kemang Siap Huni Best Price</t>
         </is>
       </c>
       <c r="C1722" t="n">
-        <v>89000000000</v>
+        <v>13500000000</v>
       </c>
       <c r="D1722" t="n">
-        <v>2700</v>
+        <v>450</v>
       </c>
       <c r="E1722" t="n">
-        <v>2382</v>
+        <v>425</v>
       </c>
       <c r="F1722" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="G1722" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H1722" t="n">
-        <v>510</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1723">
@@ -48664,26 +48664,26 @@
       </c>
       <c r="B1723" t="inlineStr">
         <is>
-          <t>Edenhaus Simatupang</t>
+          <t>Brand New American Classic Style Dijagakarsa</t>
         </is>
       </c>
       <c r="C1723" t="n">
-        <v>9900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="D1723" t="n">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="E1723" t="n">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="F1723" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1723" t="n">
         <v>4</v>
       </c>
       <c r="H1723" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1724">
@@ -48692,26 +48692,26 @@
       </c>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>Dijual Rumah Seperti Ddalam Komplek(Gated) Dikebayoran Baru. Luas 340M.(Fisik 360M) Rp.21.5 M</t>
+          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1724" t="n">
-        <v>21500000000</v>
+        <v>39000000000</v>
       </c>
       <c r="D1724" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="E1724" t="n">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="F1724" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1724" t="n">
         <v>4</v>
       </c>
       <c r="H1724" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1725">
@@ -48720,26 +48720,26 @@
       </c>
       <c r="B1725" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Area Dekat Jl. Sriwijaya, Kelurahan Selong, LT 875M Hanya Rp 105 M Nego. Lokasi Terbaik, Dekat Sriwijaya</t>
+          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1725" t="n">
-        <v>105000000000</v>
+        <v>53000000000</v>
       </c>
       <c r="D1725" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E1725" t="n">
-        <v>815</v>
+        <v>1018</v>
       </c>
       <c r="F1725" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G1725" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1725" t="n">
-        <v>24</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1726">
@@ -48748,26 +48748,26 @@
       </c>
       <c r="B1726" t="inlineStr">
         <is>
-          <t>Jual Rumah 2 Lantai 3 KT Kondisi Baru Dekat MRT Lebak Bulus</t>
+          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
         </is>
       </c>
       <c r="C1726" t="n">
-        <v>1400000000</v>
+        <v>25000000000</v>
       </c>
       <c r="D1726" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E1726" t="n">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="F1726" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G1726" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H1726" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1727">
@@ -48776,26 +48776,26 @@
       </c>
       <c r="B1727" t="inlineStr">
         <is>
-          <t>Rumah 2 Lantai Full Furnished Kpr 0 Di Town House Tenang Bebas Banjir</t>
+          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
         </is>
       </c>
       <c r="C1727" t="n">
-        <v>1400000000</v>
+        <v>21000000000</v>
       </c>
       <c r="D1727" t="n">
-        <v>140</v>
+        <v>765</v>
       </c>
       <c r="E1727" t="n">
-        <v>75</v>
+        <v>765</v>
       </c>
       <c r="F1727" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G1727" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1727" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1728">
@@ -48804,17 +48804,17 @@
       </c>
       <c r="B1728" t="inlineStr">
         <is>
-          <t>Rumah 2 LT minimalis fungsionalis nyaman di Jaksel DP KPR 0</t>
+          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
         </is>
       </c>
       <c r="C1728" t="n">
-        <v>1500000000</v>
+        <v>23000000000</v>
       </c>
       <c r="D1728" t="n">
-        <v>127</v>
+        <v>417</v>
       </c>
       <c r="E1728" t="n">
-        <v>88</v>
+        <v>417</v>
       </c>
       <c r="F1728" t="n">
         <v>41</v>
@@ -48823,7 +48823,7 @@
         <v>41</v>
       </c>
       <c r="H1728" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1729">
@@ -48832,26 +48832,26 @@
       </c>
       <c r="B1729" t="inlineStr">
         <is>
-          <t>Rumah Mewah 1 Lantai Dalam Komplek Keamanan 24 Jam</t>
+          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1729" t="n">
-        <v>29900000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1729" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E1729" t="n">
-        <v>580</v>
+        <v>695</v>
       </c>
       <c r="F1729" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G1729" t="n">
         <v>42</v>
       </c>
       <c r="H1729" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1730">
@@ -48860,26 +48860,26 @@
       </c>
       <c r="B1730" t="inlineStr">
         <is>
-          <t>Dijual Rumah Cilandak Jakarta Selatan</t>
+          <t>Ruma Rempoa</t>
         </is>
       </c>
       <c r="C1730" t="n">
-        <v>13500000000</v>
+        <v>2290000000</v>
       </c>
       <c r="D1730" t="n">
-        <v>530</v>
+        <v>92</v>
       </c>
       <c r="E1730" t="n">
-        <v>850</v>
+        <v>89</v>
       </c>
       <c r="F1730" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1730" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1730" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1731">
@@ -48888,23 +48888,23 @@
       </c>
       <c r="B1731" t="inlineStr">
         <is>
-          <t>Rumah Dekat Pintu Tol Andara Kalcer Skena</t>
+          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
         </is>
       </c>
       <c r="C1731" t="n">
-        <v>2100000000</v>
+        <v>6800000000</v>
       </c>
       <c r="D1731" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="E1731" t="n">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="F1731" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1731" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H1731" t="n">
         <v>2</v>
@@ -48916,26 +48916,26 @@
       </c>
       <c r="B1732" t="inlineStr">
         <is>
-          <t>Dijual Rumah di Selong Senopati Dekat Scbd</t>
+          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1732" t="n">
-        <v>97000000000</v>
+        <v>48000000000</v>
       </c>
       <c r="D1732" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E1732" t="n">
-        <v>650</v>
+        <v>2360</v>
       </c>
       <c r="F1732" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G1732" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="H1732" t="n">
-        <v>44</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1733">
@@ -48944,26 +48944,26 @@
       </c>
       <c r="B1733" t="inlineStr">
         <is>
-          <t>Kemang Siap Huni Best Price</t>
+          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1733" t="n">
-        <v>13500000000</v>
+        <v>9980000000</v>
       </c>
       <c r="D1733" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E1733" t="n">
-        <v>425</v>
+        <v>785</v>
       </c>
       <c r="F1733" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G1733" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H1733" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1734">
@@ -48972,26 +48972,26 @@
       </c>
       <c r="B1734" t="inlineStr">
         <is>
-          <t>Brand New American Classic Style Dijagakarsa</t>
+          <t>M Living at Puri Pesanggrahan</t>
         </is>
       </c>
       <c r="C1734" t="n">
-        <v>2400000000</v>
+        <v>2900000000</v>
       </c>
       <c r="D1734" t="n">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="E1734" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="F1734" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1734" t="n">
         <v>4</v>
       </c>
       <c r="H1734" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1735">
@@ -49000,26 +49000,26 @@
       </c>
       <c r="B1735" t="inlineStr">
         <is>
-          <t>Rumah Baru Mewah Clasic Modern Private Lift di Kebayoran Baru Jakarta Selatan</t>
+          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1735" t="n">
-        <v>39000000000</v>
+        <v>12000000000</v>
       </c>
       <c r="D1735" t="n">
         <v>850</v>
       </c>
       <c r="E1735" t="n">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="F1735" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G1735" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H1735" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1736">
@@ -49028,26 +49028,26 @@
       </c>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>Rumah Kantor Komersil Buat Gedung Usaha Harga NJOP di Kebayoran Baru Jakarta Selatan</t>
+          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
         </is>
       </c>
       <c r="C1736" t="n">
-        <v>53000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1736" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="E1736" t="n">
-        <v>1018</v>
+        <v>412</v>
       </c>
       <c r="F1736" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G1736" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1736" t="n">
-        <v>213</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1737">
@@ -49056,26 +49056,26 @@
       </c>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>For Sale Dijual Rumah di Area Simprug Golf</t>
+          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
         </is>
       </c>
       <c r="C1737" t="n">
-        <v>25000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1737" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="E1737" t="n">
-        <v>275</v>
+        <v>674</v>
       </c>
       <c r="F1737" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G1737" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="H1737" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1738">
@@ -49084,26 +49084,26 @@
       </c>
       <c r="B1738" t="inlineStr">
         <is>
-          <t>Paling Murah Rumah Hitung Tanah Saja 765 Meter Area Pakubuwono Kyai Maja</t>
+          <t>1 Park Homes</t>
         </is>
       </c>
       <c r="C1738" t="n">
-        <v>21000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="D1738" t="n">
-        <v>765</v>
+        <v>380</v>
       </c>
       <c r="E1738" t="n">
-        <v>765</v>
+        <v>200</v>
       </c>
       <c r="F1738" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1738" t="n">
         <v>4</v>
       </c>
       <c r="H1738" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1739">
@@ -49112,26 +49112,26 @@
       </c>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>Lamandau Area 417 Meter Kawasan Tenang Jarang Ada</t>
+          <t>Dijual Cepat Rumah Kebayoran Baru. Lokasi Sangat Strategis Pusat Kota</t>
         </is>
       </c>
       <c r="C1739" t="n">
-        <v>23000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="D1739" t="n">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="E1739" t="n">
-        <v>417</v>
+        <v>500</v>
       </c>
       <c r="F1739" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G1739" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H1739" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1740">
@@ -49140,26 +49140,26 @@
       </c>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>For Sale Rumah Siap Huni di Jatipadang, Jakarta Selatan</t>
+          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
         </is>
       </c>
       <c r="C1740" t="n">
-        <v>16000000000</v>
+        <v>8800000000</v>
       </c>
       <c r="D1740" t="n">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="E1740" t="n">
-        <v>695</v>
+        <v>290</v>
       </c>
       <c r="F1740" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G1740" t="n">
         <v>42</v>
       </c>
       <c r="H1740" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1741">
@@ -49168,26 +49168,26 @@
       </c>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>Ruma Rempoa</t>
+          <t>Rumah Cibitung Kebayoran Baru Strategis Jalan 2 Mobil</t>
         </is>
       </c>
       <c r="C1741" t="n">
-        <v>2290000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1741" t="n">
-        <v>92</v>
+        <v>250</v>
       </c>
       <c r="E1741" t="n">
-        <v>89</v>
+        <v>270</v>
       </c>
       <c r="F1741" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="G1741" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H1741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1742">
@@ -49196,26 +49196,26 @@
       </c>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>Rumah Siap Huni Full Furnished di Pondok Indah, Jaksel</t>
+          <t>12 Merle Bintaro</t>
         </is>
       </c>
       <c r="C1742" t="n">
-        <v>6800000000</v>
+        <v>3950000000</v>
       </c>
       <c r="D1742" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="E1742" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F1742" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G1742" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H1742" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1743">
@@ -49224,26 +49224,26 @@
       </c>
       <c r="B1743" t="inlineStr">
         <is>
-          <t>Rumah Bagus Halaman Luas Buat Pengusaha Harga NJOP di Kemang Jakarta Selatan</t>
+          <t>Dijual Cepat Rumah Modern Pondok Indah Rapi Siap Huni</t>
         </is>
       </c>
       <c r="C1743" t="n">
-        <v>48000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="D1743" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="E1743" t="n">
-        <v>2360</v>
+        <v>320</v>
       </c>
       <c r="F1743" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G1743" t="n">
         <v>42</v>
       </c>
       <c r="H1743" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1744">
@@ -49252,26 +49252,26 @@
       </c>
       <c r="B1744" t="inlineStr">
         <is>
-          <t>Rumah Lelang Super Murah di Bawah NJOP di Area Kemang Dalam Jakarta Selatan</t>
+          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
         </is>
       </c>
       <c r="C1744" t="n">
-        <v>9980000000</v>
+        <v>6400000000</v>
       </c>
       <c r="D1744" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E1744" t="n">
-        <v>785</v>
+        <v>172</v>
       </c>
       <c r="F1744" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1744" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H1744" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1745">
@@ -49280,26 +49280,26 @@
       </c>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>M Living at Puri Pesanggrahan</t>
+          <t>Rumah Mewah Lokasi Strategis 5 Menit ke KRL Manggarai Jaksel</t>
         </is>
       </c>
       <c r="C1745" t="n">
-        <v>2900000000</v>
+        <v>898000000</v>
       </c>
       <c r="D1745" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="E1745" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="F1745" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1745" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1745" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1746">
@@ -49308,26 +49308,26 @@
       </c>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>Brand New House American Style In Town House Cipete Jakarta Selatan</t>
+          <t>Dijual Murah Rumah di Keluarahan Selong (Kebayorab Baru Area Senopati) Luas 1050M2 Dalam Portal Hanya Rp 79 M Nego</t>
         </is>
       </c>
       <c r="C1746" t="n">
-        <v>12000000000</v>
+        <v>79000000000</v>
       </c>
       <c r="D1746" t="n">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="E1746" t="n">
-        <v>353</v>
+        <v>1050</v>
       </c>
       <c r="F1746" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G1746" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1746" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1747">
@@ -49336,26 +49336,26 @@
       </c>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>Dijual Rumah Modern Good Condition Area Premier Kemang</t>
+          <t>Jual Rumah 2 Lantai 3 KT Kondisi Baru Dekat MRT Lebak Bulus</t>
         </is>
       </c>
       <c r="C1747" t="n">
-        <v>18000000000</v>
+        <v>1400000000</v>
       </c>
       <c r="D1747" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="E1747" t="n">
-        <v>412</v>
+        <v>47</v>
       </c>
       <c r="F1747" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G1747" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H1747" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1748">
@@ -49364,26 +49364,26 @@
       </c>
       <c r="B1748" t="inlineStr">
         <is>
-          <t>Dijual Rumah 5Br Lokasi Strategis Kemang Dekat Jalan Utama</t>
+          <t>Rumah Besar dan Mewah Siap Huni Dalam Kompleks Hook Private di Jakarta Selatan Rumah Bagus SHM di Lebak Bulus</t>
         </is>
       </c>
       <c r="C1748" t="n">
-        <v>20000000000</v>
+        <v>18000000000</v>
       </c>
       <c r="D1748" t="n">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="E1748" t="n">
-        <v>674</v>
+        <v>999</v>
       </c>
       <c r="F1748" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="G1748" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="H1748" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1749">
@@ -49392,26 +49392,26 @@
       </c>
       <c r="B1749" t="inlineStr">
         <is>
-          <t>1 Park Homes</t>
+          <t>Luxurious Brand New House Full Furnished Desain American Classic di Kemang, Jakarta Selatan</t>
         </is>
       </c>
       <c r="C1749" t="n">
-        <v>20000000000</v>
+        <v>38000000000</v>
       </c>
       <c r="D1749" t="n">
-        <v>380</v>
+        <v>760</v>
       </c>
       <c r="E1749" t="n">
-        <v>200</v>
+        <v>517</v>
       </c>
       <c r="F1749" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1749" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1749" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1750">
@@ -49420,26 +49420,26 @@
       </c>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Kebayoran Baru. Lokasi Sangat Strategis Pusat Kota</t>
+          <t>Rumah Pondok Indah Nego Tipis Lokasi Bagus</t>
         </is>
       </c>
       <c r="C1750" t="n">
-        <v>36000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="D1750" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E1750" t="n">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="F1750" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G1750" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="H1750" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1751">
@@ -49448,23 +49448,23 @@
       </c>
       <c r="B1751" t="inlineStr">
         <is>
-          <t>Dijual Cepat Townhouse 3Br Lokasi Strategis Kemang Ampera</t>
+          <t>Rumah Tropical Minimalis di Pondok Indah</t>
         </is>
       </c>
       <c r="C1751" t="n">
-        <v>8800000000</v>
+        <v>19800000000</v>
       </c>
       <c r="D1751" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E1751" t="n">
-        <v>290</v>
+        <v>410</v>
       </c>
       <c r="F1751" t="n">
         <v>31</v>
       </c>
       <c r="G1751" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H1751" t="n">
         <v>22</v>
@@ -49476,23 +49476,23 @@
       </c>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>Rumah Cibitung Kebayoran Baru Strategis Jalan 2 Mobil</t>
+          <t>2 Lantai,</t>
         </is>
       </c>
       <c r="C1752" t="n">
-        <v>16500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D1752" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="E1752" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="F1752" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G1752" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H1752" t="n">
         <v>2</v>
@@ -49504,23 +49504,23 @@
       </c>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>12 Merle Bintaro</t>
+          <t>Nivara Resort Townhouse at Wijaya</t>
         </is>
       </c>
       <c r="C1753" t="n">
-        <v>3950000000</v>
+        <v>7900000000</v>
       </c>
       <c r="D1753" t="n">
-        <v>140</v>
+        <v>375</v>
       </c>
       <c r="E1753" t="n">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="F1753" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1753" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1753" t="n">
         <v>1</v>
@@ -49532,26 +49532,26 @@
       </c>
       <c r="B1754" t="inlineStr">
         <is>
-          <t>Dijual Cepat Rumah Modern Pondok Indah Rapi Siap Huni</t>
+          <t>Di Cilandak,</t>
         </is>
       </c>
       <c r="C1754" t="n">
-        <v>16000000000</v>
+        <v>1300000000</v>
       </c>
       <c r="D1754" t="n">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="E1754" t="n">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="F1754" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G1754" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H1754" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1755">
@@ -49560,26 +49560,26 @@
       </c>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>Di Jual Harga Aprraisal Rumah dan Kosan Baru Bangka Kemang</t>
+          <t>Dkt Cilandak Mall...... Strategis &amp; Tenang...Nego Lsg Deal</t>
         </is>
       </c>
       <c r="C1755" t="n">
-        <v>6400000000</v>
+        <v>4900000000</v>
       </c>
       <c r="D1755" t="n">
-        <v>395</v>
+        <v>260</v>
       </c>
       <c r="E1755" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="F1755" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1755" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1755" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1756">
@@ -49588,26 +49588,26 @@
       </c>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>Rumah Permata Hijau 2 LT 1562 M2, LB 995 M2 Dekat Grand Pakubuwono Terrace</t>
+          <t>Dijual Cepat Gedung Komersial di Ahmad Dahlan Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1756" t="n">
-        <v>25000000000</v>
+        <v>30000000000</v>
       </c>
       <c r="D1756" t="n">
-        <v>620</v>
+        <v>1500</v>
       </c>
       <c r="E1756" t="n">
-        <v>1562</v>
+        <v>475</v>
       </c>
       <c r="F1756" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="G1756" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1756" t="n">
         <v>42</v>
-      </c>
-      <c r="H1756" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="1757">
@@ -49616,26 +49616,950 @@
       </c>
       <c r="B1757" t="inlineStr">
         <is>
-          <t>Rumah Mewah Lokasi Strategis 5 Menit ke KRL Manggarai Jaksel</t>
+          <t>"Rumah Mewah 3 Lantai di Tulodong - Lokasi Premium Kebayoran Baru</t>
         </is>
       </c>
       <c r="C1757" t="n">
-        <v>898000000</v>
+        <v>16500000000</v>
       </c>
       <c r="D1757" t="n">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="E1757" t="n">
+        <v>300</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1757" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="n">
+        <v>1757</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Rumah Dijual Jalan Tebet Barat Dalam Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1758" t="n">
+        <v>4200000000</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1758" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="n">
+        <v>1758</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Rumah dijual bangunan lama dekat Pakubuwono dan Senayan City</t>
+        </is>
+      </c>
+      <c r="C1759" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>328</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>101</v>
+      </c>
+      <c r="G1759" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1759" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="n">
+        <v>1759</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Elite Cipaku Kebayoran Baru, Dekat Scbd &amp; Senopati</t>
+        </is>
+      </c>
+      <c r="C1760" t="n">
+        <v>33000000000</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>410</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1760" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Hook di Cipaku, Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1761" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>229</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>359</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1761" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="n">
+        <v>1761</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Komersial di Jalan Wijaya, Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1762" t="n">
+        <v>88000000000</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>750</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1762" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1762" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="n">
+        <v>1762</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Luxe Court Permata Hijau Signature</t>
+        </is>
+      </c>
+      <c r="C1763" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>374</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>181</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1763" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1763" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="n">
+        <v>1763</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Dijual - Rumah Komersial di Jl. Cikajang, Kebayoran Baru, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1764" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>257</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>283</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1764" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="n">
+        <v>1764</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Baru Kebayoran Baru Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1765" t="n">
+        <v>39000000000</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>850</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>380</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1765" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1765" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="n">
+        <v>1765</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Lux Modern Minimalis Di Kebayoran Baru. By Alex Bayu. Luas 634m Rp 85 M Nego. Daerah Elit</t>
+        </is>
+      </c>
+      <c r="C1766" t="n">
+        <v>85000000000</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>634</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1766" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1766" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="n">
+        <v>1766</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Strategis, Pggr Jln Raya, Murah Bwh NJOP</t>
+        </is>
+      </c>
+      <c r="C1767" t="n">
+        <v>19000000000</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>800</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1767" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1767" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="n">
+        <v>1767</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni di Tebet, Selangkah ke Taman</t>
+        </is>
+      </c>
+      <c r="C1768" t="n">
+        <v>3300000000</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>143</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1768" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1768" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="n">
+        <v>1768</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Rumah Lama Dalam Komplek Area Tebet Dekat Kokas</t>
+        </is>
+      </c>
+      <c r="C1769" t="n">
+        <v>9800000000</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>480</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1769" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1769" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Tebet Timur Parkir 3 Mobil ! Akses Mudah</t>
+        </is>
+      </c>
+      <c r="C1770" t="n">
+        <v>4500000000</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>200</v>
+      </c>
+      <c r="E1770" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1770" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1770" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="n">
+        <v>1770</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Dijual Cepat Rumah dan Tanah di Kemang Jakarta Selatan - Harga Nego</t>
+        </is>
+      </c>
+      <c r="C1771" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>1598</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1771" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Rumah Mewah Tebet Timur, Akses 3 Mobil Dekat Eco Park</t>
+        </is>
+      </c>
+      <c r="C1772" t="n">
+        <v>8750000000</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>350</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>255</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1772" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="n">
+        <v>1772</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Rumah Siap Huni di Tebet Barat, Akses Jalan 3 Mobil</t>
+        </is>
+      </c>
+      <c r="C1773" t="n">
+        <v>6700000000</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>280</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>51</v>
+      </c>
+      <c r="H1773" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="n">
+        <v>1773</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Pondok Indah Town House 2 - Cluster Aurelle</t>
+        </is>
+      </c>
+      <c r="C1774" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1774" t="n">
+        <v>308</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1774" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1774" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="n">
+        <v>1774</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Tebet Timur, Rumah Siap Huni Ada Kolam Renang, Akses Jalan 2 Mobil</t>
+        </is>
+      </c>
+      <c r="C1775" t="n">
+        <v>6400000000</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>179</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1775" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="n">
+        <v>1775</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Rumah Bagus Terawat 1 Lantai Halaman Luas Lebak Bulus Cilandak Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C1776" t="n">
+        <v>22500000000</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>500</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1776" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="n">
+        <v>1776</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Rumah Minimalis Modern Satu Lantai Strategis Dekat Tol Simatupang</t>
+        </is>
+      </c>
+      <c r="C1777" t="n">
+        <v>12800000000</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>400</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>515</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1777" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="n">
+        <v>1777</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>ZENITPARC HYTT</t>
+        </is>
+      </c>
+      <c r="C1778" t="n">
+        <v>1700000000</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>92</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1778" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="n">
+        <v>1778</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Rumah Kemang Utara Bungur Lt.787 Lb 600 Mewah</t>
+        </is>
+      </c>
+      <c r="C1779" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="D1779" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>787</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1779" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1779" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="n">
+        <v>1779</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Rumah Permata Hijau 2 LT 1562 M2, LB 995 M2 Dekat Grand Pakubuwono Terrace</t>
+        </is>
+      </c>
+      <c r="C1780" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>620</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1780" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Dijual Rumah Depan Taman di Pondok Indah Luas Tanah 1094M. Njop.40.3 M. Dijual 